--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>127箇所</t>
+          <t>128箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議106・要確認20・要内訳1。本文15箇所・表21種112箇所（01シート）</t>
+          <t>要協議106・要確認21・要内訳1。本文16箇所・表21種112箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（806段落130表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（843段落137表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -718,7 +718,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>127箇所のうち55箇所（43％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>128箇所のうち55箇所（43％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（806段落130表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計127箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（843段落137表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計128箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -929,13 +929,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -1007,13 +1007,13 @@
       </c>
       <c r="C11" s="9" t="inlineStr"/>
       <c r="D11" s="10" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E11" s="10" t="n">
         <v>106</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>1</v>
@@ -1428,7 +1428,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（15件）</t>
+          <t>3　本文の未確定箇所（16件）</t>
         </is>
       </c>
     </row>
@@ -1545,17 +1545,17 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 高齢者の生活実態</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr"/>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr"/>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr"/>
@@ -1618,22 +1618,22 @@
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr"/>
@@ -1644,12 +1644,12 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr"/>
@@ -1670,22 +1670,22 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr"/>
@@ -1696,22 +1696,22 @@
       <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
@@ -1763,8 +1763,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>注1）R8のサービス別利用者数は自然体推計確認シートの月平均基準値、R9以降は自然体推計値です。居宅介護支援は介護予防支援との合算値です。いずれも地域包括ケア「見える化」システムの将来推計によります。R8は令和8年度の介護保険事業状況報告月報（令和8年4月から7月まで）の値から計算した実績見込み値であり、年度の実績ではありません。
-注1-2）本節に掲げるのは</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -1780,7 +1779,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -1790,8 +1789,8 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>注1）R8のサービス別利用者数は自然体推計確認シートの月平均基準値、R9以降は自然体推計値です。居宅介護支援は介護予防支援との合算値です。いずれも地域包括ケア「見える化」システムの将来推計によります。R8は令和8年度の介護保険事業状況報告月報（令和8年4月から7月まで）の値から計算した実績見込み値であり、年度の実績ではありません。
+注1-2）本節に掲げるのは</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
@@ -1834,103 +1833,100 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
       <c r="G44" s="6" t="inlineStr"/>
       <c r="H44" s="6" t="inlineStr"/>
     </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="45" ht="44" customHeight="1">
+      <c r="A45" s="6" t="inlineStr"/>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+        </is>
+      </c>
+      <c r="F45" s="6" t="inlineStr"/>
+      <c r="G45" s="6" t="inlineStr"/>
+      <c r="H45" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>注1）表の中の未確定箇所は21種の表に112箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="4" t="inlineStr"/>
-      <c r="B49" s="4" t="inlineStr">
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="4" t="inlineStr"/>
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="44" customHeight="1">
-      <c r="A50" s="6" t="inlineStr"/>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -1943,24 +1939,24 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第2節　計画の位置付け</t>
+          <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="6" t="inlineStr">
         <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
+          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -1973,7 +1969,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
@@ -1983,14 +1979,14 @@
         <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2003,7 +1999,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第4節　計画期間</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
@@ -2020,7 +2016,7 @@
       </c>
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
+          <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2028,29 +2024,29 @@
       <c r="A54" s="6" t="inlineStr"/>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
-        </is>
-      </c>
-      <c r="D54" s="8" t="n">
-        <v>4</v>
+          <t>第5節　計画の策定体制</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="E54" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査（4,729票）の結果が本文に入っていない。集計は調査クロス集計・分析（24シート）にあるが、本節は導入文と資料注のみである。アンケート分析の未了No.4に当たる</t>
+          <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2148,21 +2144,21 @@
       <c r="A59" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
-注4）記述が薄い節は8節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと3節です。
-注5）第2章第4節は4段落・表1と最も薄く、調査の集計結果が本文に入っていない状態です。受託者の作業だけで進むため、着手します（06シート）。</t>
+注4）記述が薄い節は7節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと2節です。
+注5）第2章第4節（高齢者の生活実態）は令和8年9月15日に健康とくらしの調査の結果を反映し、30段落・表8になりました。記述が薄い節には当たらなくなっています。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A48:H48"/>
     <mergeCell ref="A59:H59"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A47:H47"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A46:H46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3887,12 +3883,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の地区別集計・年齢調整による地域比較・社会参加や移動制約との関連分析</t>
+          <t>健康とくらしの調査の地区別集計・年齢調整による地域比較・社会参加や暮らし向きとの関連分析。令和8年9月15日に第2章第4節へ反映した（8表・30段落）。地区の定義は［要確認］のまま残している</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>第2章第4節（高齢者の状況）・第5章 基本目標1</t>
+          <t>第2章第4節（反映済み）・第5章 基本目標1（未）</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -3902,7 +3898,7 @@
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>一部完了</t>
         </is>
       </c>
     </row>
@@ -4115,7 +4111,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>健康とくらしの調査の地区別集計・年齢調整による地域比較を本文に反映する。地区の定義（小学校区とするか）のみ確認を要するため、定義に依存しない部分から進める</t>
+          <t>令和8年9月15日に反映した。調査の対象者の範囲・主要指標の町別・年齢調整と町間の差の検定・同規模保険者40との比較・社会参加との関連・暮らし向きとの関連・生活実態の主な値・地区別の8項目で、8表を掲げた。集計値は `data_survey_jages.py` に収め、個票なしで再現できる。地区の定義は［要確認］のまま残している</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4125,7 +4121,7 @@
       </c>
       <c r="E5" s="15" t="inlineStr">
         <is>
-          <t>着手できる</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="F5" s="6" t="inlineStr">
@@ -4265,7 +4261,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議106・要確認20・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議106・要確認21・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4377,7 +4373,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>806段落130表36図／127箇所</t>
+          <t>843段落137表36図／128箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -4403,7 +4399,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>127＝127</t>
+          <t>128＝128</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -4429,7 +4425,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>127＝127</t>
+          <t>128＝128</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -4611,7 +4607,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>55／127箇所（43％）</t>
+          <t>55／128箇所（43％）</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -4637,7 +4633,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>8節（うち短いことが妥当なものを除くと3節）</t>
+          <t>7節（うち短いことが妥当なものを除くと2節）</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -4653,7 +4649,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>第2章第4節に調査結果が入っていないことを示していること</t>
+          <t>第2章第4節に健康とくらしの調査の結果が入っていること（令和8年9月15日に反映）</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -4663,7 +4659,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>4段落・表1。健康とくらしの調査の集計は調査クロス集計・分析（24シート）にある</t>
+          <t>30段落・表8。記述が薄い節には当たらない</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -4850,7 +4846,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は127箇所ある（要協議106・要確認20・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は128箇所ある（要協議106・要確認21・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>140件</t>
+          <t>142件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>130件</t>
+          <t>132件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>18件</t>
+          <t>19件</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を止めているものが18件ある</t>
+          <t>第1次概算を止めているものが19件ある</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>9月26日まで残り期間が短く、うち期限が令和8年9月のものが17件あります</t>
+          <t>9月26日まで残り期間が短く、うち期限が令和8年9月のものが18件あります</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（140件）</t>
+          <t>確認事項の棚卸し（142件）</t>
         </is>
       </c>
     </row>
@@ -2232,14 +2232,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は130件</t>
+          <t>完了・了承済を除く未回答は132件</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>29</v>
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>38</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -2737,7 +2737,7 @@
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（52件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（53件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（22件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -2762,7 +2762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2776,7 +2776,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第1次概算までに決着を要するもの（18件）</t>
+          <t>第1次概算までに決着を要するもの（19件）</t>
         </is>
       </c>
     </row>
@@ -3331,34 +3331,64 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
+          <t>No.145</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
           <t>No.82</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>R8.9.24</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t>町別按分は当方の案（第1次概算）のまま示す</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>注1）18件のうち期限が令和8年9月のものは17件です。
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>注1）19件のうち期限が令和8年9月のものは18件です。
 注2）既定値はいずれも当方が作業上置いているものであり、ご了承をいただいたものではありません。第1次概算をお出しする際は、どの既定値によったかを明示します。
 注3）安全側と記したものは、決着しないまま概算すると保険料が高めに出る向きのものです。施策の達成や適正化の効果を前提に下げると、保険料が不足する側に誤ります。
 注4）No.137（単価の年度）は月額で＋185〜＋374円に当たり、本表のうち最も効きが大きいものです。</t>
@@ -3367,9 +3397,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4451,7 +4481,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>140件（未回答130件）</t>
+          <t>142件（未回答132件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -4477,7 +4507,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>140件／一意140件</t>
+          <t>142件／一意142件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -4550,7 +4580,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>18件</t>
+          <t>19件</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -4576,7 +4606,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>18件</t>
+          <t>19件</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -4814,7 +4844,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が18件あり、うち期限が令和8年9月のものが17件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度。月額＋185〜＋374円）であり、これだけは9月26日までに決定をいただきたい。</t>
+          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が19件あり、うち期限が令和8年9月のものが18件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度。月額＋185〜＋374円）であり、これだけは9月26日までに決定をいただきたい。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4869,7 +4899,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている130件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている132件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>142件</t>
+          <t>143件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>132件</t>
+          <t>133件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが69件（02シート）</t>
+          <t>このうち計画素案を止めているものが70件（02シート）</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>19件</t>
+          <t>20件</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を止めているものが19件ある</t>
+          <t>第1次概算を止めているものが20件ある</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>9月26日まで残り期間が短く、うち期限が令和8年9月のものが18件あります</t>
+          <t>9月26日まで残り期間が短く、うち期限が令和8年9月のものが19件あります</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（142件）</t>
+          <t>確認事項の棚卸し（143件）</t>
         </is>
       </c>
     </row>
@@ -2232,14 +2232,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は132件</t>
+          <t>完了・了承済を除く未回答は133件</t>
         </is>
       </c>
     </row>
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -2762,7 +2762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2776,7 +2776,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第1次概算までに決着を要するもの（19件）</t>
+          <t>第1次概算までに決着を要するもの（20件）</t>
         </is>
       </c>
     </row>
@@ -3361,34 +3361,64 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
+          <t>No.146</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する。差は月額＋8円である</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
           <t>No.82</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>R8.9.24</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>町別按分は当方の案（第1次概算）のまま示す</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="56" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>注1）19件のうち期限が令和8年9月のものは18件です。
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>注1）20件のうち期限が令和8年9月のものは19件です。
 注2）既定値はいずれも当方が作業上置いているものであり、ご了承をいただいたものではありません。第1次概算をお出しする際は、どの既定値によったかを明示します。
 注3）安全側と記したものは、決着しないまま概算すると保険料が高めに出る向きのものです。施策の達成や適正化の効果を前提に下げると、保険料が不足する側に誤ります。
 注4）No.137（単価の年度）は月額で＋185〜＋374円に当たり、本表のうち最も効きが大きいものです。</t>
@@ -3397,9 +3427,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4481,7 +4511,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>142件（未回答132件）</t>
+          <t>143件（未回答133件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -4507,7 +4537,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>142件／一意142件</t>
+          <t>143件／一意143件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -4580,7 +4610,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>19件</t>
+          <t>20件</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -4606,7 +4636,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>19件</t>
+          <t>20件</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -4844,7 +4874,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が19件あり、うち期限が令和8年9月のものが18件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度。月額＋185〜＋374円）であり、これだけは9月26日までに決定をいただきたい。</t>
+          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が20件あり、うち期限が令和8年9月のものが19件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度。月額＋185〜＋374円）であり、これだけは9月26日までに決定をいただきたい。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4899,7 +4929,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている132件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている133件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>143件</t>
+          <t>145件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>133件</t>
+          <t>135件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>20件</t>
+          <t>21件</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を止めているものが20件ある</t>
+          <t>第1次概算を止めているものが21件ある</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>9月26日まで残り期間が短く、うち期限が令和8年9月のものが19件あります</t>
+          <t>9月26日まで残り期間が短く、うち期限が令和8年9月のものが20件あります</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（143件）</t>
+          <t>確認事項の棚卸し（145件）</t>
         </is>
       </c>
     </row>
@@ -2232,14 +2232,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は133件</t>
+          <t>完了・了承済を除く未回答は135件</t>
         </is>
       </c>
     </row>
@@ -2469,13 +2469,13 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D20" s="5" t="n">
         <v>39</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -2762,7 +2762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2776,7 +2776,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第1次概算までに決着を要するもの（20件）</t>
+          <t>第1次概算までに決着を要するもの（21件）</t>
         </is>
       </c>
     </row>
@@ -3391,34 +3391,64 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
+          <t>No.147</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
           <t>No.82</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>R8.9.24</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>町別按分は当方の案（第1次概算）のまま示す</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="56" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>注1）20件のうち期限が令和8年9月のものは19件です。
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>注1）21件のうち期限が令和8年9月のものは20件です。
 注2）既定値はいずれも当方が作業上置いているものであり、ご了承をいただいたものではありません。第1次概算をお出しする際は、どの既定値によったかを明示します。
 注3）安全側と記したものは、決着しないまま概算すると保険料が高めに出る向きのものです。施策の達成や適正化の効果を前提に下げると、保険料が不足する側に誤ります。
 注4）No.137（単価の年度）は月額で＋185〜＋374円に当たり、本表のうち最も効きが大きいものです。</t>
@@ -3427,9 +3457,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4511,7 +4541,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>143件（未回答133件）</t>
+          <t>145件（未回答135件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -4537,7 +4567,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>143件／一意143件</t>
+          <t>145件／一意145件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -4610,7 +4640,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>20件</t>
+          <t>22件</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -4636,7 +4666,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>20件</t>
+          <t>21件</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -4874,7 +4904,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が20件あり、うち期限が令和8年9月のものが19件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度。月額＋185〜＋374円）であり、これだけは9月26日までに決定をいただきたい。</t>
+          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が21件あり、うち期限が令和8年9月のものが20件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度。月額＋185〜＋374円）であり、これだけは9月26日までに決定をいただきたい。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -4929,7 +4959,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている133件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている135件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>128箇所</t>
+          <t>130箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議106・要確認21・要内訳1。本文16箇所・表21種112箇所（01シート）</t>
+          <t>要協議107・要確認22・要内訳1。本文23箇所・表20種107箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（843段落137表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（886段落142表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -718,7 +718,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>128箇所のうち55箇所（43％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>130箇所のうち55箇所（42％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（843段落137表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計128箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（886段落142表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計130箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -877,13 +877,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -1007,13 +1007,13 @@
       </c>
       <c r="C11" s="9" t="inlineStr"/>
       <c r="D11" s="10" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>1</v>
@@ -1189,29 +1189,29 @@
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
+          <t>No.114（中長期推計の範囲）</t>
         </is>
       </c>
     </row>
@@ -1219,29 +1219,29 @@
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>No.114（中長期推計の範囲）</t>
+          <t>No.75（代表KPIの再整理案）</t>
         </is>
       </c>
     </row>
@@ -1249,29 +1249,29 @@
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>No.75（代表KPIの再整理案）</t>
+          <t>確認事項B No.19（医療側の連携の実施状況）</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>確認事項B No.19（医療側の連携の実施状況）</t>
+          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
         </is>
       </c>
     </row>
@@ -1309,29 +1309,29 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+          <t>No.112（地域支援事業の量）</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1369,29 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E25" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F25" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No.8（3調査の点検事項）</t>
+          <t>No.86（交付金の控除）ほか</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -1421,94 +1421,102 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
+          <t>No.8（3調査の点検事項）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="6" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>第2章　高齢者及び介護保険の状況</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
           <t>No.8（同）</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>3　本文の未確定箇所（16件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="inlineStr"/>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>3　本文の未確定箇所（23件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>本文（抜粋）</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr"/>
-    </row>
-    <row r="30" ht="44" customHeight="1">
-      <c r="A30" s="6" t="inlineStr"/>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることを受託者の案とします［要協議］。</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr"/>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31" ht="44" customHeight="1">
-      <c r="A31" s="6" t="inlineStr"/>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr"/>
     </row>
     <row r="32" ht="44" customHeight="1">
       <c r="A32" s="6" t="inlineStr"/>
@@ -1519,17 +1527,17 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることを受託者の案とします［要協議］。</t>
         </is>
       </c>
       <c r="F32" s="6" t="inlineStr"/>
@@ -1545,17 +1553,17 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr"/>
@@ -1571,17 +1579,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 サービス提供体制の状況</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr"/>
@@ -1597,7 +1605,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1607,7 +1615,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr"/>
@@ -1623,17 +1631,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr"/>
@@ -1644,22 +1652,22 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr"/>
@@ -1670,22 +1678,22 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr"/>
@@ -1696,22 +1704,22 @@
       <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
@@ -1722,12 +1730,12 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
@@ -1737,7 +1745,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
@@ -1748,22 +1756,22 @@
       <c r="A41" s="6" t="inlineStr"/>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -1779,7 +1787,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -1789,8 +1797,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>注1）R8のサービス別利用者数は自然体推計確認シートの月平均基準値、R9以降は自然体推計値です。居宅介護支援は介護予防支援との合算値です。いずれも地域包括ケア「見える化」システムの将来推計によります。R8は令和8年度の介護保険事業状況報告月報（令和8年4月から7月まで）の値から計算した実績見込み値であり、年度の実績ではありません。
-注1-2）本節に掲げるのは</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
@@ -1806,7 +1813,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -1816,8 +1823,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1833,7 +1839,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
@@ -1843,8 +1849,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1860,288 +1865,526 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
       <c r="G45" s="6" t="inlineStr"/>
       <c r="H45" s="6" t="inlineStr"/>
     </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は21種の表に112箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
-注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="4" t="inlineStr"/>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>章</t>
-        </is>
-      </c>
-      <c r="C50" s="4" t="inlineStr">
-        <is>
-          <t>節</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>段落</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>うち注・出典</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>表</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>未確定</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
+    <row r="46" ht="44" customHeight="1">
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-2）必要利用定員総数は第4節4により、</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr"/>
+      <c r="G46" s="6" t="inlineStr"/>
+      <c r="H46" s="6" t="inlineStr"/>
+    </row>
+    <row r="47" ht="44" customHeight="1">
+      <c r="A47" s="6" t="inlineStr"/>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
+        <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の総合事業の実績を受領した時点で置き直します。</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr"/>
+      <c r="G47" s="6" t="inlineStr"/>
+      <c r="H47" s="6" t="inlineStr"/>
+    </row>
+    <row r="48" ht="44" customHeight="1">
+      <c r="A48" s="6" t="inlineStr"/>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr"/>
+      <c r="G48" s="6" t="inlineStr"/>
+      <c r="H48" s="6" t="inlineStr"/>
+    </row>
+    <row r="49" ht="44" customHeight="1">
+      <c r="A49" s="6" t="inlineStr"/>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="inlineStr"/>
+      <c r="G49" s="6" t="inlineStr"/>
+      <c r="H49" s="6" t="inlineStr"/>
+    </row>
+    <row r="50" ht="44" customHeight="1">
+      <c r="A50" s="6" t="inlineStr"/>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr"/>
+      <c r="G50" s="6" t="inlineStr"/>
+      <c r="H50" s="6" t="inlineStr"/>
     </row>
     <row r="51" ht="44" customHeight="1">
       <c r="A51" s="6" t="inlineStr"/>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr"/>
     </row>
     <row r="52" ht="44" customHeight="1">
       <c r="A52" s="6" t="inlineStr"/>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
-        </is>
-      </c>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr"/>
     </row>
     <row r="53" ht="44" customHeight="1">
       <c r="A53" s="6" t="inlineStr"/>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="6" t="inlineStr">
-        <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
-        </is>
-      </c>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr"/>
     </row>
     <row r="54" ht="44" customHeight="1">
       <c r="A54" s="6" t="inlineStr"/>
       <c r="B54" s="6" t="inlineStr">
         <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。改定率は令和9年度の告示を待って反映します。</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr"/>
+      <c r="G54" s="6" t="inlineStr"/>
+      <c r="H54" s="6" t="inlineStr"/>
+    </row>
+    <row r="56" ht="28" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は20種の表に107箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="30" customHeight="1">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>章</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>節</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>段落</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>うち注・出典</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>本来入るべき内容と所在</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="44" customHeight="1">
+      <c r="A60" s="6" t="inlineStr"/>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>第1節　計画策定の趣旨</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="6" t="inlineStr">
+        <is>
+          <t>趣旨の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="44" customHeight="1">
+      <c r="A61" s="6" t="inlineStr"/>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="6" t="inlineStr">
+        <is>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="44" customHeight="1">
+      <c r="A62" s="6" t="inlineStr"/>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>第4節　計画期間</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="6" t="inlineStr">
+        <is>
+          <t>計画期間の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="44" customHeight="1">
+      <c r="A63" s="6" t="inlineStr"/>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D54" s="5" t="n">
+      <c r="D63" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="6" t="inlineStr">
+      <c r="E63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="44" customHeight="1">
-      <c r="A55" s="6" t="inlineStr"/>
-      <c r="B55" s="6" t="inlineStr">
+    <row r="64" ht="44" customHeight="1">
+      <c r="A64" s="6" t="inlineStr"/>
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D55" s="5" t="n">
+      <c r="D64" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="5" t="n">
+      <c r="E64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G55" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="6" t="inlineStr">
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="44" customHeight="1">
-      <c r="A56" s="6" t="inlineStr"/>
-      <c r="B56" s="6" t="inlineStr">
+    <row r="65" ht="44" customHeight="1">
+      <c r="A65" s="6" t="inlineStr"/>
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
-      <c r="D56" s="8" t="n">
+      <c r="D65" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="E56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="5" t="n">
+      <c r="E65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G56" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
+      <c r="G65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="6" t="inlineStr">
         <is>
           <t>整備の方針。第4節4の必要利用定員総数（確認事項No.88）の決定を待っている</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="44" customHeight="1">
-      <c r="A57" s="6" t="inlineStr"/>
-      <c r="B57" s="6" t="inlineStr">
+    <row r="66" ht="44" customHeight="1">
+      <c r="A66" s="6" t="inlineStr"/>
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>第7節 低所得者支援</t>
         </is>
       </c>
-      <c r="D57" s="8" t="n">
+      <c r="D66" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="5" t="n">
+      <c r="E66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G57" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="6" t="inlineStr">
+      <c r="G66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="6" t="inlineStr">
         <is>
           <t>所得段階と公費軽減。第10期の政令改正（確認事項No.33）を待っている</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="42" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は7節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと2節です。
@@ -2151,14 +2394,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A68:H68"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4351,7 +4594,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議106・要確認21・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議107・要確認22・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4463,7 +4706,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>843段落137表36図／128箇所</t>
+          <t>886段落142表36図／130箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -4489,7 +4732,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>128＝128</t>
+          <t>130＝130</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -4515,7 +4758,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>128＝128</t>
+          <t>130＝130</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -4697,7 +4940,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>55／128箇所（43％）</t>
+          <t>55／130箇所（42％）</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -4936,7 +5179,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は128箇所ある（要協議106・要確認21・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は130箇所ある（要協議107・要確認22・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>130箇所</t>
+          <t>133箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議107・要確認22・要内訳1。本文23箇所・表20種107箇所（01シート）</t>
+          <t>要協議108・要確認24・要内訳1。本文24箇所・表21種109箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（886段落142表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（893段落143表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -718,7 +718,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>130箇所のうち55箇所（42％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>133箇所のうち58箇所（44％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（886段落142表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計130箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（893段落143表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計133箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -877,13 +877,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -1007,13 +1007,13 @@
       </c>
       <c r="C11" s="9" t="inlineStr"/>
       <c r="D11" s="10" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G11" s="10" t="n">
         <v>1</v>
@@ -1078,13 +1078,13 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0</v>
@@ -1488,7 +1488,7 @@
     <row r="30" ht="20" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（23件）</t>
+          <t>3　本文の未確定箇所（24件）</t>
         </is>
       </c>
     </row>
@@ -2026,15 +2026,16 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>注1）R7実績及びR11見込は第2節と同じ基準です。年報は施設の所在地を問わず当広域連合の被保険者を数えるため、区域内の施設の定員は当広域連合の被保険者にとっての上限ではありません。区域外の施設の利用により、率が100％を超えることがあります。
+注2）介護医療院は区域内に施設がないため率を算定していません。
+注3）介護老人保健施設及び特定施設入居者生活介護は</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2077,17 +2078,18 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2106,100 +2108,96 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。改定率は令和9年度の告示を待って反映します。</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
       <c r="G54" s="6" t="inlineStr"/>
       <c r="H54" s="6" t="inlineStr"/>
     </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は20種の表に107箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+    <row r="55" ht="44" customHeight="1">
+      <c r="A55" s="6" t="inlineStr"/>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。改定率は令和9年度の告示を待って反映します。</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr"/>
+      <c r="G55" s="6" t="inlineStr"/>
+      <c r="H55" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は21種の表に109箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="4" t="inlineStr"/>
-      <c r="B59" s="4" t="inlineStr">
+    <row r="60" ht="30" customHeight="1">
+      <c r="A60" s="4" t="inlineStr"/>
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C60" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D59" s="4" t="inlineStr">
+      <c r="D60" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
+      <c r="E60" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F59" s="4" t="inlineStr">
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G59" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="44" customHeight="1">
-      <c r="A60" s="6" t="inlineStr"/>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2212,24 +2210,24 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第2節　計画の位置付け</t>
+          <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
+          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2240,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
@@ -2252,14 +2250,14 @@
         <v>0</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2270,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第4節　計画期間</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
@@ -2289,7 +2287,7 @@
       </c>
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
+          <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2297,12 +2295,12 @@
       <c r="A64" s="6" t="inlineStr"/>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第1節 計画の基本理念</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
@@ -2312,14 +2310,14 @@
         <v>0</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>基本理念であり、短いことは妥当</t>
+          <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2327,15 +2325,15 @@
       <c r="A65" s="6" t="inlineStr"/>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D65" s="8" t="n">
+          <t>第1節 計画の基本理念</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E65" s="5" t="n">
@@ -2349,7 +2347,7 @@
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>整備の方針。第4節4の必要利用定員総数（確認事項No.88）の決定を待っている</t>
+          <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2362,11 +2360,11 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D66" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>0</v>
@@ -2379,12 +2377,42 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
+          <t>整備の方針。第4節4の必要利用定員総数（確認事項No.88）の決定を待っている</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="44" customHeight="1">
+      <c r="A67" s="6" t="inlineStr"/>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D67" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
           <t>所得段階と公費軽減。第10期の政令改正（確認事項No.33）を待っている</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="42" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
+    <row r="69" ht="42" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は7節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと2節です。
@@ -2394,14 +2422,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A68:H68"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A58:H58"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4594,7 +4622,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議107・要確認22・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議108・要確認24・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4706,7 +4734,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>886段落142表36図／130箇所</t>
+          <t>893段落143表36図／133箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -4732,7 +4760,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>130＝130</t>
+          <t>133＝133</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -4758,7 +4786,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>130＝130</t>
+          <t>133＝133</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -4940,7 +4968,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>55／130箇所（42％）</t>
+          <t>58／133箇所（44％）</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -5179,7 +5207,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は130箇所ある（要協議107・要確認22・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は133箇所ある（要協議108・要確認24・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>145件</t>
+          <t>148件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>135件</t>
+          <t>138件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが70件（02シート）</t>
+          <t>このうち計画素案を止めているものが73件（02シート）</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>21件</t>
+          <t>22件</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を止めているものが21件ある</t>
+          <t>第1次概算を止めているものが22件ある</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>9月26日まで残り期間が短く、うち期限が令和8年9月のものが20件あります</t>
+          <t>9月26日まで残り期間が短く、うち期限が令和8年9月のものが21件あります</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（145件）</t>
+          <t>確認事項の棚卸し（148件）</t>
         </is>
       </c>
     </row>
@@ -2503,14 +2503,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は135件</t>
+          <t>完了・了承済を除く未回答は138件</t>
         </is>
       </c>
     </row>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>1</v>
@@ -2740,13 +2740,13 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr"/>
@@ -2863,7 +2863,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -3008,7 +3008,7 @@
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（53件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（54件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（22件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -3033,7 +3033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3047,7 +3047,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第1次概算までに決着を要するもの（21件）</t>
+          <t>第1次概算までに決着を要するもの（22件）</t>
         </is>
       </c>
     </row>
@@ -3692,34 +3692,64 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
+          <t>No.151</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+        </is>
+      </c>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="44" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
           <t>No.82</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>R8.9.24</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>町別按分は当方の案（第1次概算）のまま示す</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="56" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>注1）21件のうち期限が令和8年9月のものは20件です。
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>注1）22件のうち期限が令和8年9月のものは21件です。
 注2）既定値はいずれも当方が作業上置いているものであり、ご了承をいただいたものではありません。第1次概算をお出しする際は、どの既定値によったかを明示します。
 注3）安全側と記したものは、決着しないまま概算すると保険料が高めに出る向きのものです。施策の達成や適正化の効果を前提に下げると、保険料が不足する側に誤ります。
 注4）No.137（単価の年度）は月額で＋185〜＋374円に当たり、本表のうち最も効きが大きいものです。</t>
@@ -3730,7 +3760,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:F28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4812,7 +4842,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>145件（未回答135件）</t>
+          <t>148件（未回答138件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -4838,7 +4868,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>145件／一意145件</t>
+          <t>148件／一意148件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -4911,7 +4941,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>22件</t>
+          <t>23件</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -4937,7 +4967,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>21件</t>
+          <t>22件</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -5175,7 +5205,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が21件あり、うち期限が令和8年9月のものが20件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度。月額＋185〜＋374円）であり、これだけは9月26日までに決定をいただきたい。</t>
+          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が22件あり、うち期限が令和8年9月のものが21件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度。月額＋185〜＋374円）であり、これだけは9月26日までに決定をいただきたい。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -5230,7 +5260,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている135件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている138件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>133箇所</t>
+          <t>135箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議108・要確認24・要内訳1。本文24箇所・表21種109箇所（01シート）</t>
+          <t>要協議109・要確認25・要内訳1。本文26箇所・表21種109箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（893段落143表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（896段落143表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -718,7 +718,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>133箇所のうち58箇所（44％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>135箇所のうち58箇所（43％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（893段落143表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計133箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（896段落143表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計135箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -998,100 +998,92 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="9" t="inlineStr"/>
-      <c r="B11" s="9" t="inlineStr">
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="6" t="inlineStr"/>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="9" t="inlineStr"/>
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr"/>
-      <c r="D11" s="10" t="n">
-        <v>133</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>108</v>
-      </c>
-      <c r="F11" s="10" t="n">
-        <v>24</v>
-      </c>
-      <c r="G11" s="10" t="n">
+      <c r="C12" s="9" t="inlineStr"/>
+      <c r="D12" s="10" t="n">
+        <v>135</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>109</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="G12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H11" s="9" t="inlineStr"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2　節別（3箇所以上）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>要内訳</t>
         </is>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>主に止めている確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="6" t="inlineStr"/>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="n">
-        <v>58</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>54</v>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>No.88（必要利用定員総数）・No.113（混合型特定施設）・No.141（区域を越えた施設利用）</t>
         </is>
       </c>
     </row>
@@ -1099,19 +1091,19 @@
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>13</v>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="n">
+        <v>58</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>9</v>
+        <v>54</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>4</v>
@@ -1121,7 +1113,7 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>No.91〜No.94（給付適正化）・確認事項A No.14（住宅改修等の点検）</t>
+          <t>No.88（必要利用定員総数）・No.113（混合型特定施設）・No.141（区域を越えた施設利用）</t>
         </is>
       </c>
     </row>
@@ -1129,29 +1121,29 @@
       <c r="A17" s="6" t="inlineStr"/>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>No.4（代表KPIの代理指標）</t>
+          <t>No.91〜No.94（給付適正化）・確認事項A No.14（住宅改修等の点検）</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1151,12 @@
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
@@ -1181,7 +1173,7 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>No.118〜No.121（地域ケア会議のKPI）・No.130（認知症基本法）</t>
+          <t>No.4（代表KPIの代理指標）</t>
         </is>
       </c>
     </row>
@@ -1189,29 +1181,29 @@
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>No.114（中長期推計の範囲）</t>
+          <t>No.118〜No.121（地域ケア会議のKPI）・No.130（認知症基本法）</t>
         </is>
       </c>
     </row>
@@ -1219,29 +1211,29 @@
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="F20" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>No.75（代表KPIの再整理案）</t>
+          <t>No.114（中長期推計の範囲）</t>
         </is>
       </c>
     </row>
@@ -1249,29 +1241,29 @@
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>確認事項B No.19（医療側の連携の実施状況）</t>
+          <t>No.75（代表KPIの再整理案）</t>
         </is>
       </c>
     </row>
@@ -1284,7 +1276,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
@@ -1301,7 +1293,7 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+          <t>確認事項B No.19（医療側の連携の実施状況）</t>
         </is>
       </c>
     </row>
@@ -1309,29 +1301,29 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>No.112（地域支援事業の量）</t>
+          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
         </is>
       </c>
     </row>
@@ -1339,29 +1331,29 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
+          <t>No.112（地域支援事業の量）</t>
         </is>
       </c>
     </row>
@@ -1369,29 +1361,29 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No.86（交付金の控除）ほか</t>
+          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
         </is>
       </c>
     </row>
@@ -1399,29 +1391,29 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F26" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>No.8（3調査の点検事項）</t>
+          <t>No.86（交付金の控除）ほか</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1426,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -1451,7 +1443,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>No.8（同）</t>
+          <t>No.8（3調査の点検事項）</t>
         </is>
       </c>
     </row>
@@ -1459,101 +1451,105 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
+          <t>No.8（同）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
           <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>3　本文の未確定箇所（24件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="inlineStr"/>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>3　本文の未確定箇所（26件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>本文（抜粋）</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr"/>
-      <c r="H31" s="4" t="inlineStr"/>
-    </row>
-    <row r="32" ht="44" customHeight="1">
-      <c r="A32" s="6" t="inlineStr"/>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
-        <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることを受託者の案とします［要協議］。</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr"/>
     </row>
     <row r="33" ht="44" customHeight="1">
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
@@ -1563,7 +1559,7 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr"/>
@@ -1574,12 +1570,12 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1589,7 +1585,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。都道府県認知症施策推進計画の策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr"/>
@@ -1605,17 +1601,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることを受託者の案とします［要協議］。</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr"/>
@@ -1631,7 +1627,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
@@ -1641,7 +1637,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr"/>
@@ -1657,7 +1653,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1667,7 +1663,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr"/>
@@ -1683,7 +1679,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1693,7 +1689,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr"/>
@@ -1704,12 +1700,12 @@
       <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
@@ -1719,7 +1715,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
@@ -1730,22 +1726,22 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
@@ -1756,12 +1752,12 @@
       <c r="A41" s="6" t="inlineStr"/>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1771,7 +1767,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -1782,12 +1778,12 @@
       <c r="A42" s="6" t="inlineStr"/>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
@@ -1797,7 +1793,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
@@ -1808,12 +1804,12 @@
       <c r="A43" s="6" t="inlineStr"/>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -1823,7 +1819,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1834,22 +1830,22 @@
       <c r="A44" s="6" t="inlineStr"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1865,7 +1861,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
@@ -1875,7 +1871,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1891,7 +1887,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -1901,8 +1897,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-2）必要利用定員総数は第4節4により、</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1918,7 +1913,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -1928,8 +1923,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の総合事業の実績を受領した時点で置き直します。</t>
+          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1945,17 +1939,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr"/>
@@ -1971,7 +1965,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -1981,7 +1975,8 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-2）必要利用定員総数は第4節4により、</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -2007,7 +2002,8 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の総合事業の実績を受領した時点で置き直します。</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2023,101 +2019,99 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr"/>
+      <c r="G51" s="6" t="inlineStr"/>
+      <c r="H51" s="6" t="inlineStr"/>
+    </row>
+    <row r="52" ht="44" customHeight="1">
+      <c r="A52" s="6" t="inlineStr"/>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr"/>
+      <c r="G52" s="6" t="inlineStr"/>
+      <c r="H52" s="6" t="inlineStr"/>
+    </row>
+    <row r="53" ht="44" customHeight="1">
+      <c r="A53" s="6" t="inlineStr"/>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr"/>
+      <c r="G53" s="6" t="inlineStr"/>
+      <c r="H53" s="6" t="inlineStr"/>
+    </row>
+    <row r="54" ht="44" customHeight="1">
+      <c r="A54" s="6" t="inlineStr"/>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>注1）R7実績及びR11見込は第2節と同じ基準です。年報は施設の所在地を問わず当広域連合の被保険者を数えるため、区域内の施設の定員は当広域連合の被保険者にとっての上限ではありません。区域外の施設の利用により、率が100％を超えることがあります。
 注2）介護医療院は区域内に施設がないため率を算定していません。
 注3）介護老人保健施設及び特定施設入居者生活介護は</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr"/>
-      <c r="G51" s="6" t="inlineStr"/>
-      <c r="H51" s="6" t="inlineStr"/>
-    </row>
-    <row r="52" ht="44" customHeight="1">
-      <c r="A52" s="6" t="inlineStr"/>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr"/>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="6" t="inlineStr"/>
-    </row>
-    <row r="53" ht="44" customHeight="1">
-      <c r="A53" s="6" t="inlineStr"/>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr"/>
-      <c r="G53" s="6" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr"/>
-    </row>
-    <row r="54" ht="44" customHeight="1">
-      <c r="A54" s="6" t="inlineStr"/>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
-        <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
-        </is>
-      </c>
       <c r="F54" s="6" t="inlineStr"/>
       <c r="G54" s="6" t="inlineStr"/>
       <c r="H54" s="6" t="inlineStr"/>
@@ -2131,7 +2125,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
@@ -2141,153 +2135,143 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。改定率は令和9年度の告示を待って反映します。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
       <c r="G55" s="6" t="inlineStr"/>
       <c r="H55" s="6" t="inlineStr"/>
     </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="7" t="inlineStr">
+    <row r="56" ht="44" customHeight="1">
+      <c r="A56" s="6" t="inlineStr"/>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+        </is>
+      </c>
+      <c r="F56" s="6" t="inlineStr"/>
+      <c r="G56" s="6" t="inlineStr"/>
+      <c r="H56" s="6" t="inlineStr"/>
+    </row>
+    <row r="57" ht="44" customHeight="1">
+      <c r="A57" s="6" t="inlineStr"/>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+        </is>
+      </c>
+      <c r="F57" s="6" t="inlineStr"/>
+      <c r="G57" s="6" t="inlineStr"/>
+      <c r="H57" s="6" t="inlineStr"/>
+    </row>
+    <row r="58" ht="44" customHeight="1">
+      <c r="A58" s="6" t="inlineStr"/>
+      <c r="B58" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。改定率は令和9年度の告示を待って反映します。</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr"/>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr"/>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="7" t="inlineStr">
         <is>
           <t>注1）表の中の未確定箇所は21種の表に109箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="4" t="inlineStr"/>
-      <c r="B60" s="4" t="inlineStr">
+    <row r="63" ht="30" customHeight="1">
+      <c r="A63" s="4" t="inlineStr"/>
+      <c r="B63" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C63" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D63" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
+      <c r="E63" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F60" s="4" t="inlineStr">
+      <c r="F63" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G60" s="4" t="inlineStr">
+      <c r="G63" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="H63" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="44" customHeight="1">
-      <c r="A61" s="6" t="inlineStr"/>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D61" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="44" customHeight="1">
-      <c r="A62" s="6" t="inlineStr"/>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="6" t="inlineStr">
-        <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="44" customHeight="1">
-      <c r="A63" s="6" t="inlineStr"/>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>第4節　計画期間</t>
-        </is>
-      </c>
-      <c r="D63" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="6" t="inlineStr">
-        <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2300,11 +2284,11 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>0</v>
@@ -2317,7 +2301,7 @@
       </c>
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
+          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2325,16 +2309,16 @@
       <c r="A65" s="6" t="inlineStr"/>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第1節 計画の基本理念</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E65" s="5" t="n">
         <v>0</v>
@@ -2343,11 +2327,11 @@
         <v>1</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>基本理念であり、短いことは妥当</t>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2355,29 +2339,29 @@
       <c r="A66" s="6" t="inlineStr"/>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="n">
+          <t>第4節　計画期間</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>整備の方針。第4節4の必要利用定員総数（確認事項No.88）の決定を待っている</t>
+          <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2385,34 +2369,124 @@
       <c r="A67" s="6" t="inlineStr"/>
       <c r="B67" s="6" t="inlineStr">
         <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>第5節　計画の策定体制</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="6" t="inlineStr">
+        <is>
+          <t>策定体制の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="44" customHeight="1">
+      <c r="A68" s="6" t="inlineStr"/>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>第4章　計画の基本理念及び基本目標</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>第1節 計画の基本理念</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="6" t="inlineStr">
+        <is>
+          <t>基本理念であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="44" customHeight="1">
+      <c r="A69" s="6" t="inlineStr"/>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D69" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="6" t="inlineStr">
+        <is>
+          <t>整備の方針。第4節4の必要利用定員総数（確認事項No.88）の決定を待っている</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="44" customHeight="1">
+      <c r="A70" s="6" t="inlineStr"/>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>第7節 低所得者支援</t>
         </is>
       </c>
-      <c r="D67" s="8" t="n">
+      <c r="D70" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="E67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="5" t="n">
+      <c r="E70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="G70" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="6" t="inlineStr">
         <is>
           <t>所得段階と公費軽減。第10期の政令改正（確認事項No.33）を待っている</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="42" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
+    <row r="72" ht="42" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は7節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと2節です。
@@ -2423,13 +2497,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A69:H69"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A62:H62"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A72:H72"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A31:H31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4652,7 +4726,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議108・要確認24・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議109・要確認25・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4764,7 +4838,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>893段落143表36図／133箇所</t>
+          <t>896段落143表36図／135箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -4790,7 +4864,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>133＝133</t>
+          <t>135＝135</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -4811,12 +4885,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>5章</t>
+          <t>6章</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>133＝133</t>
+          <t>135＝135</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -4998,7 +5072,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>58／133箇所（44％）</t>
+          <t>58／135箇所（43％）</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -5237,7 +5311,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は133箇所ある（要協議108・要確認24・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は135箇所ある（要協議109・要確認25・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>148件</t>
+          <t>150件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>138件</t>
+          <t>140件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが73件（02シート）</t>
+          <t>このうち計画素案を止めているものが75件（02シート）</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（148件）</t>
+          <t>確認事項の棚卸し（150件）</t>
         </is>
       </c>
     </row>
@@ -2577,14 +2577,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は138件</t>
+          <t>完了・了承済を除く未回答は140件</t>
         </is>
       </c>
     </row>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>1</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（54件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（56件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（22件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>148件（未回答138件）</t>
+          <t>150件（未回答140件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>148件／一意148件</t>
+          <t>150件／一意150件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -5334,7 +5334,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている138件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている140件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>150件</t>
+          <t>151件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>140件</t>
+          <t>141件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが75件（02シート）</t>
+          <t>このうち計画素案を止めているものが76件（02シート）</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（150件）</t>
+          <t>確認事項の棚卸し（151件）</t>
         </is>
       </c>
     </row>
@@ -2577,14 +2577,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は140件</t>
+          <t>完了・了承済を除く未回答は141件</t>
         </is>
       </c>
     </row>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>1</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（56件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（57件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（22件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -4916,7 +4916,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>150件（未回答140件）</t>
+          <t>151件（未回答141件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>150件／一意150件</t>
+          <t>151件／一意151件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -5334,7 +5334,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている140件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている141件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>151件</t>
+          <t>154件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>141件</t>
+          <t>144件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが76件（02シート）</t>
+          <t>このうち計画素案を止めているものが77件（02シート）</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>22件</t>
+          <t>24件</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を止めているものが22件ある</t>
+          <t>第1次概算を止めているものが24件ある</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -2530,7 +2530,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（151件）</t>
+          <t>確認事項の棚卸し（154件）</t>
         </is>
       </c>
     </row>
@@ -2577,14 +2577,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は141件</t>
+          <t>完了・了承済を除く未回答は144件</t>
         </is>
       </c>
     </row>
@@ -2722,13 +2722,13 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr">
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（57件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（60件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（22件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -3107,7 +3107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3121,7 +3121,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第1次概算までに決着を要するもの（22件）</t>
+          <t>第1次概算までに決着を要するもの（24件）</t>
         </is>
       </c>
     </row>
@@ -3196,27 +3196,27 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>No.88</t>
+          <t>No.128</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
+          <t>令和8年度の実績見込み値を編集するか</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
+          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
         </is>
       </c>
     </row>
@@ -3226,17 +3226,17 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>No.98</t>
+          <t>No.129</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
+          <t>見える化システムの利用率等の伸びの選択</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
+          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
         </is>
       </c>
     </row>
@@ -3256,12 +3256,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>No.100</t>
+          <t>No.88</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
+          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）で概算する</t>
+          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
         </is>
       </c>
     </row>
@@ -3286,12 +3286,12 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>No.101</t>
+          <t>No.98</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
+          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節の表は見える化の自然体推計値のまま置き、P3による値を別掲する</t>
+          <t>省令上の類型を計画に掲げないまま概算する</t>
         </is>
       </c>
     </row>
@@ -3316,12 +3316,12 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>No.103</t>
+          <t>No.100</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
+          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）で概算する</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>No.105</t>
+          <t>No.101</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
+          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
+          <t>素案 第6章第2節の表は見える化の自然体推計値のまま置き、P3による値を別掲する</t>
         </is>
       </c>
     </row>
@@ -3376,12 +3376,12 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>No.106</t>
+          <t>No.103</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
+          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -3396,7 +3396,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>一律の伸びのまま概算し、補正の効き（月額▲58円又は＋48円）を併記する</t>
+          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
         </is>
       </c>
     </row>
@@ -3406,12 +3406,12 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>No.107</t>
+          <t>No.105</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
+          <t>施策反映を行うか。行う場合の対象と歯止め</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
@@ -3421,12 +3421,12 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
+          <t>施策反映を行わないまま概算する（安全側）</t>
         </is>
       </c>
     </row>
@@ -3436,12 +3436,12 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>No.113</t>
+          <t>No.106</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか</t>
+          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
+          <t>一律の伸びのまま概算し、補正の効き（月額▲58円又は＋48円）を併記する</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>No.123</t>
+          <t>No.107</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
+          <t>施設・居住系の実績の減少を将来へ延長するか</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
+          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
         </is>
       </c>
     </row>
@@ -3496,12 +3496,12 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>No.126</t>
+          <t>No.113</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
+          <t>混合型特定施設の必要利用定員総数を定めるか</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>基本推計に近いP3で概算する</t>
+          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
         </is>
       </c>
     </row>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>No.131</t>
+          <t>No.123</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
+          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節は利用者数のみを掲げたまま概算する</t>
+          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
         </is>
       </c>
     </row>
@@ -3556,12 +3556,12 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>No.132</t>
+          <t>No.126</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
+          <t>見える化システムの推計方式は基本推計でよいか</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
+          <t>基本推計に近いP3で概算する</t>
         </is>
       </c>
     </row>
@@ -3586,12 +3586,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>No.137</t>
+          <t>No.131</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
+          <t>第6章第2節の見込量の表に何を掲げるか</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -3606,7 +3606,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（月額で＋185〜＋374円に当たる）</t>
+          <t>第6章第2節は利用者数のみを掲げたまま概算する</t>
         </is>
       </c>
     </row>
@@ -3616,12 +3616,12 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>No.141</t>
+          <t>No.132</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>区域を越えた施設利用の扱い</t>
+          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
+          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
         </is>
       </c>
     </row>
@@ -3646,12 +3646,12 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>No.142</t>
+          <t>No.137</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
+          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
@@ -3666,7 +3666,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（月額で＋185〜＋374円に当たる）</t>
         </is>
       </c>
     </row>
@@ -3676,12 +3676,12 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>No.145</t>
+          <t>No.141</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
+          <t>区域を越えた施設利用の扱い</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
+          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
         </is>
       </c>
     </row>
@@ -3706,12 +3706,12 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>No.146</t>
+          <t>No.142</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
+          <t>第1次概算を既定値のまま出してよいか</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する。差は月額＋8円である</t>
+          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
         </is>
       </c>
     </row>
@@ -3736,12 +3736,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>No.147</t>
+          <t>No.145</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
+          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -3756,7 +3756,7 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
         </is>
       </c>
     </row>
@@ -3766,12 +3766,12 @@
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>No.151</t>
+          <t>No.146</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+          <t>見込量の伸びを要介護度別に改めてよいか</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する。差は月額＋8円である</t>
         </is>
       </c>
     </row>
@@ -3796,34 +3796,94 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
+          <t>No.147</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>見える化システムの伸びの選択肢をどれとするか</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="44" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>No.151</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>発注者</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="44" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
           <t>No.82</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>構成町の一般会計繰入金の町別按分の方法</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>R8.9.24</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>発注者</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>町別按分は当方の案（第1次概算）のまま示す</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="56" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>注1）22件のうち期限が令和8年9月のものは21件です。
+    <row r="30" ht="56" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>注1）24件のうち期限が令和8年9月のものは21件です。
 注2）既定値はいずれも当方が作業上置いているものであり、ご了承をいただいたものではありません。第1次概算をお出しする際は、どの既定値によったかを明示します。
 注3）安全側と記したものは、決着しないまま概算すると保険料が高めに出る向きのものです。施策の達成や適正化の効果を前提に下げると、保険料が不足する側に誤ります。
 注4）No.137（単価の年度）は月額で＋185〜＋374円に当たり、本表のうち最も効きが大きいものです。</t>
@@ -3834,7 +3894,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4916,7 +4976,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>151件（未回答141件）</t>
+          <t>154件（未回答144件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -4942,7 +5002,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>151件／一意151件</t>
+          <t>154件／一意154件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -5015,7 +5075,7 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>23件</t>
+          <t>25件</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -5041,7 +5101,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>22件</t>
+          <t>24件</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -5279,7 +5339,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が22件あり、うち期限が令和8年9月のものが21件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度。月額＋185〜＋374円）であり、これだけは9月26日までに決定をいただきたい。</t>
+          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が24件あり、うち期限が令和8年9月のものが21件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度。月額＋185〜＋374円）であり、これだけは9月26日までに決定をいただきたい。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -5334,7 +5394,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている141件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている144件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>154件</t>
+          <t>157件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>144件</t>
+          <t>147件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが77件（02シート）</t>
+          <t>このうち計画素案を止めているものが78件（02シート）</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（154件）</t>
+          <t>確認事項の棚卸し（157件）</t>
         </is>
       </c>
     </row>
@@ -2577,14 +2577,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は144件</t>
+          <t>完了・了承済を除く未回答は147件</t>
         </is>
       </c>
     </row>
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>3</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（60件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（63件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（22件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>154件（未回答144件）</t>
+          <t>157件（未回答147件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>154件／一意154件</t>
+          <t>157件／一意157件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -5394,7 +5394,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている144件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている147件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>業務工程管理表 03_確認事項一覧。うち完了・了承済10件</t>
+          <t>業務工程管理表 03_確認事項一覧。うち完了・了承済11件</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>147件</t>
+          <t>146件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -2577,14 +2577,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は147件</t>
+          <t>完了・了承済を除く未回答は146件</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       <c r="A7" s="6" t="inlineStr"/>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>了承済</t>
         </is>
       </c>
       <c r="C7" s="12" t="n">
@@ -2607,11 +2607,11 @@
       <c r="A8" s="6" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>了承済</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="6" t="inlineStr"/>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D16" s="5" t="n">
         <v>35</v>
@@ -2937,7 +2937,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -3082,7 +3082,7 @@
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（63件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（62件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（22件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>157件（未回答147件）</t>
+          <t>157件（未回答146件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -5394,7 +5394,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている147件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている146件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>135箇所</t>
+          <t>137箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議109・要確認25・要内訳1。本文26箇所・表21種109箇所（01シート）</t>
+          <t>要協議109・要確認27・要内訳1。本文28箇所・表21種109箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（896段落143表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（923段落145表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -718,7 +718,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>135箇所のうち58箇所（43％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>137箇所のうち58箇所（42％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（896段落143表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計135箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（923段落145表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計137箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -877,13 +877,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>65</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -1007,13 +1007,13 @@
       </c>
       <c r="C11" s="6" t="inlineStr"/>
       <c r="D11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
@@ -1029,13 +1029,13 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>109</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>1</v>
@@ -1510,7 +1510,7 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（26件）</t>
+          <t>3　本文の未確定箇所（28件）</t>
         </is>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。都道府県認知症施策推進計画の策定の状況は［要確認］です。</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr"/>
@@ -1596,22 +1596,22 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第8節　関係計画等との関係</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることを受託者の案とします［要協議］。</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。都道府県認知症施策推進計画の策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr"/>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることを受託者の案とします［要協議］。</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr"/>
@@ -1653,17 +1653,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr"/>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr"/>
@@ -1705,17 +1705,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 高齢者の生活実態</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
@@ -1731,17 +1731,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -1778,22 +1778,22 @@
       <c r="A42" s="6" t="inlineStr"/>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
@@ -1804,12 +1804,12 @@
       <c r="A43" s="6" t="inlineStr"/>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1830,22 +1830,22 @@
       <c r="A44" s="6" t="inlineStr"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1856,22 +1856,22 @@
       <c r="A45" s="6" t="inlineStr"/>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1975,8 +1975,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-2）必要利用定員総数は第4節4により、</t>
+          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -1992,7 +1991,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -2002,8 +2001,8 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の総合事業の実績を受領した時点で置き直します。</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-2）必要利用定員総数は第4節4により、</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2022,14 +2021,15 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の総合事業の実績を受領した時点で置き直します。</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2048,9 +2048,9 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2097,19 +2097,17 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績及びR11見込は第2節と同じ基準です。年報は施設の所在地を問わず当広域連合の被保険者を数えるため、区域内の施設の定員は当広域連合の被保険者にとっての上限ではありません。区域外の施設の利用により、率が100％を超えることがあります。
-注2）介護医療院は区域内に施設がないため率を算定していません。
-注3）介護老人保健施設及び特定施設入居者生活介護は</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2128,15 +2126,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2179,17 +2176,18 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2205,133 +2203,125 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。改定率は令和9年度の告示を待って反映します。</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
       <c r="G58" s="6" t="inlineStr"/>
       <c r="H58" s="6" t="inlineStr"/>
     </row>
-    <row r="60" ht="28" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="6" t="inlineStr"/>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr"/>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60" ht="44" customHeight="1">
+      <c r="A60" s="6" t="inlineStr"/>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。改定率は令和9年度の告示を待って反映します。</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr"/>
+    </row>
+    <row r="62" ht="28" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
         <is>
           <t>注1）表の中の未確定箇所は21種の表に109箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="4" t="inlineStr"/>
-      <c r="B63" s="4" t="inlineStr">
+    <row r="65" ht="30" customHeight="1">
+      <c r="A65" s="4" t="inlineStr"/>
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
+      <c r="E65" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F63" s="4" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G63" s="4" t="inlineStr">
+      <c r="G65" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="H65" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="44" customHeight="1">
-      <c r="A64" s="6" t="inlineStr"/>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="44" customHeight="1">
-      <c r="A65" s="6" t="inlineStr"/>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H65" s="6" t="inlineStr">
-        <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2344,11 +2334,11 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
+          <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>0</v>
@@ -2361,7 +2351,7 @@
       </c>
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
+          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2374,24 +2364,24 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2389,12 @@
       <c r="A68" s="6" t="inlineStr"/>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第1節 計画の基本理念</t>
+          <t>第4節　計画期間</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
@@ -2414,14 +2404,14 @@
         <v>0</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>基本理念であり、短いことは妥当</t>
+          <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2429,29 +2419,29 @@
       <c r="A69" s="6" t="inlineStr"/>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D69" s="8" t="n">
+          <t>第5節　計画の策定体制</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>整備の方針。第4節4の必要利用定員総数（確認事項No.88）の決定を待っている</t>
+          <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2459,16 +2449,16 @@
       <c r="A70" s="6" t="inlineStr"/>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="n">
-        <v>3</v>
+          <t>第1節 計画の基本理念</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>0</v>
@@ -2481,15 +2471,45 @@
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
+          <t>基本理念であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="44" customHeight="1">
+      <c r="A71" s="6" t="inlineStr"/>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D71" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="6" t="inlineStr">
+        <is>
           <t>所得段階と公費軽減。第10期の政令改正（確認事項No.33）を待っている</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="42" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
+    <row r="73" ht="42" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
-注4）記述が薄い節は7節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと2節です。
+注4）記述が薄い節は6節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと1節です。
 注5）第2章第4節（高齢者の生活実態）は令和8年9月15日に健康とくらしの調査の結果を反映し、30段落・表8になりました。記述が薄い節には当たらなくなっています。</t>
         </is>
       </c>
@@ -2498,9 +2518,9 @@
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A62:H62"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A72:H72"/>
-    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A64:H64"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A31:H31"/>
@@ -2577,7 +2597,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
@@ -2622,11 +2642,11 @@
       <c r="A9" s="6" t="inlineStr"/>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>一部回答済</t>
+          <t>対応中</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="6" t="inlineStr"/>
@@ -2637,7 +2657,7 @@
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>了承済（保管せず廃棄）</t>
+          <t>一部回答済</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
@@ -2652,7 +2672,7 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
@@ -4786,7 +4806,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議109・要確認25・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議109・要確認27・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4898,7 +4918,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>896段落143表36図／135箇所</t>
+          <t>923段落145表36図／137箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -4924,7 +4944,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>135＝135</t>
+          <t>137＝137</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -4950,7 +4970,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>135＝135</t>
+          <t>137＝137</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -5132,7 +5152,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>58／135箇所（43％）</t>
+          <t>58／137箇所（42％）</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -5158,7 +5178,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>7節（うち短いことが妥当なものを除くと2節）</t>
+          <t>6節（うち短いことが妥当なものを除くと1節）</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -5371,7 +5391,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は135箇所ある（要協議109・要確認25・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は137箇所ある（要協議109・要確認27・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（923段落145表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（925段落145表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（923段落145表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計137箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（925段落145表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計137箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は6節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと1節です。
-注5）第2章第4節（高齢者の生活実態）は令和8年9月15日に健康とくらしの調査の結果を反映し、30段落・表8になりました。記述が薄い節には当たらなくなっています。</t>
+注5）第2章第4節（高齢者の生活実態）は令和8年9月15日に健康とくらしの調査の結果を反映し、32段落・表8になりました。記述が薄い節には当たらなくなっています。</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>923段落145表36図／137箇所</t>
+          <t>925段落145表36図／137箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>30段落・表8。記述が薄い節には当たらない</t>
+          <t>32段落・表8。記述が薄い節には当たらない</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>137箇所</t>
+          <t>138箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議109・要確認27・要内訳1。本文28箇所・表21種109箇所（01シート）</t>
+          <t>要協議110・要確認27・要内訳1。本文28箇所・表21種110箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>157件</t>
+          <t>158件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>146件</t>
+          <t>147件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが78件（02シート）</t>
+          <t>このうち計画素案を止めているものが79件（02シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（925段落145表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（926段落145表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -718,7 +718,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>137箇所のうち58箇所（42％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>138箇所のうち58箇所（42％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（925段落145表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計137箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（926段落145表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計138箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -903,10 +903,10 @@
       </c>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>6</v>
@@ -1029,10 +1029,10 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>27</v>
@@ -1306,24 +1306,24 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
         </is>
       </c>
     </row>
@@ -1331,29 +1331,29 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>No.112（地域支援事業の量）</t>
+          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
         </is>
       </c>
     </row>
@@ -1361,29 +1361,29 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
+          <t>No.112（地域支援事業の量）</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -2275,7 +2275,7 @@
     <row r="62" ht="28" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>注1）表の中の未確定箇所は21種の表に109箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+          <t>注1）表の中の未確定箇所は21種の表に110箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
@@ -2550,7 +2550,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（157件）</t>
+          <t>確認事項の棚卸し（158件）</t>
         </is>
       </c>
     </row>
@@ -2597,14 +2597,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は146件</t>
+          <t>完了・了承済を除く未回答は147件</t>
         </is>
       </c>
     </row>
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>3</v>
@@ -2834,10 +2834,10 @@
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>20</v>
@@ -2957,7 +2957,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -3102,7 +3102,7 @@
     <row r="39" ht="42" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（62件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（64件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（22件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議109・要確認27・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議110・要確認27・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>925段落145表36図／137箇所</t>
+          <t>926段落145表36図／138箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>137＝137</t>
+          <t>138＝138</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>137＝137</t>
+          <t>138＝138</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>157件（未回答146件）</t>
+          <t>158件（未回答147件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>157件／一意157件</t>
+          <t>158件／一意158件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>58／137箇所（42％）</t>
+          <t>58／138箇所（42％）</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は137箇所ある（要協議109・要確認27・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は138箇所ある（要協議110・要確認27・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -5414,7 +5414,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている146件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている147件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -2029,7 +2029,7 @@
       <c r="E51" s="6" t="inlineStr">
         <is>
           <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の総合事業の実績を受領した時点で置き直します。</t>
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
@@ -2672,7 +2672,7 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>了承済（保管せず廃棄）</t>
+          <t>解決</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
@@ -2687,7 +2687,7 @@
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
@@ -2698,85 +2698,69 @@
       <c r="F12" s="6" t="inlineStr"/>
       <c r="G12" s="6" t="inlineStr"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="6" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>実施中</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
+      <c r="G13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="6" t="inlineStr"/>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>一部確認済み</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>2　期限別（未回答のみ）</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="4" t="inlineStr"/>
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>うち計画素案を止めている</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>うち第1次概算を止めている</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr"/>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="6" t="inlineStr"/>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>56</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>37</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>期限が過ぎているもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="6" t="inlineStr"/>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr">
-        <is>
-          <t>期限が過ぎているもの</t>
         </is>
       </c>
     </row>
@@ -2784,17 +2768,17 @@
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" s="6" t="inlineStr"/>
       <c r="G18" s="6" t="inlineStr">
@@ -2807,11 +2791,11 @@
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D19" s="5" t="n">
         <v>0</v>
@@ -2830,55 +2814,63 @@
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>79</v>
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>1</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>期限が過ぎているもの</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>R8.9.2</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>1</v>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>期限が過ぎているもの</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F22" s="6" t="inlineStr"/>
       <c r="G22" s="6" t="inlineStr"/>
@@ -2887,7 +2879,7 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.9.2</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
@@ -2906,7 +2898,7 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
@@ -2916,78 +2908,86 @@
         <v>0</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="6" t="inlineStr"/>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>R9.4</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr"/>
+      <c r="G25" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="6" t="inlineStr"/>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr"/>
+      <c r="G26" s="6" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>3　確認先別（未回答のみ）</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="4" t="inlineStr"/>
-      <c r="B27" s="4" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="4" t="inlineStr"/>
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="6" t="inlineStr"/>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="n">
-        <v>111</v>
-      </c>
-      <c r="D28" s="6" t="inlineStr"/>
-      <c r="E28" s="6" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr"/>
-      <c r="G28" s="6" t="inlineStr"/>
-    </row>
-    <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="6" t="inlineStr"/>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="6" t="inlineStr"/>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>6</v>
+        <v>111</v>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="6" t="inlineStr"/>
@@ -2998,11 +2998,11 @@
       <c r="A31" s="6" t="inlineStr"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="6" t="inlineStr"/>
@@ -3013,11 +3013,11 @@
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
@@ -3028,11 +3028,11 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
@@ -3043,7 +3043,7 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
@@ -3058,7 +3058,7 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
@@ -3073,7 +3073,7 @@
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -3088,7 +3088,7 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>北海道上川総合振興局</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -3099,8 +3099,38 @@
       <c r="F37" s="6" t="inlineStr"/>
       <c r="G37" s="6" t="inlineStr"/>
     </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町・北海道</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="6" t="inlineStr"/>
+      <c r="G38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="6" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>国の情報</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>注1）期限が令和8年8月以前のもの（64件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（22件）は、3町への照会の様式と時期の決定を先に要します。
@@ -3110,12 +3140,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A39:G39"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（926段落145表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（928段落145表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（926段落145表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計138箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（928段落145表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計138箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>926段落145表36図／138箇所</t>
+          <t>928段落145表36図／138箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>158件</t>
+          <t>167件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>147件</t>
+          <t>156件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが79件（02シート）</t>
+          <t>このうち計画素案を止めているものが88件（02シート）</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。都道府県認知症施策推進計画の策定の状況は［要確認］です。</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr"/>
@@ -2535,7 +2535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2550,7 +2550,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（158件）</t>
+          <t>確認事項の棚卸し（167件）</t>
         </is>
       </c>
     </row>
@@ -2597,14 +2597,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は147件</t>
+          <t>完了・了承済を除く未回答は156件</t>
         </is>
       </c>
     </row>
@@ -2772,10 +2772,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>3</v>
@@ -3028,11 +3028,11 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
@@ -3043,11 +3043,11 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="6" t="inlineStr"/>
@@ -3058,11 +3058,11 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="6" t="inlineStr"/>
@@ -3073,11 +3073,11 @@
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・東神楽町</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="6" t="inlineStr"/>
@@ -3088,7 +3088,7 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -3103,7 +3103,7 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>北海道上川総合振興局</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -3118,7 +3118,7 @@
       <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -3129,10 +3129,25 @@
       <c r="F39" s="6" t="inlineStr"/>
       <c r="G39" s="6" t="inlineStr"/>
     </row>
-    <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>注1）期限が令和8年8月以前のもの（64件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="6" t="inlineStr"/>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>国の情報</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr"/>
+      <c r="E40" s="6" t="inlineStr"/>
+      <c r="F40" s="6" t="inlineStr"/>
+      <c r="G40" s="6" t="inlineStr"/>
+    </row>
+    <row r="42" ht="42" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>注1）期限が令和8年8月以前のもの（73件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（22件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -3144,7 +3159,7 @@
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
     <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5026,7 +5041,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>158件（未回答147件）</t>
+          <t>167件（未回答156件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -5052,7 +5067,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>158件／一意158件</t>
+          <t>167件／一意167件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -5444,7 +5459,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている147件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている156件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>167件</t>
+          <t>169件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,7 +639,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>156件</t>
+          <t>158件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -2550,7 +2550,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（167件）</t>
+          <t>確認事項の棚卸し（169件）</t>
         </is>
       </c>
     </row>
@@ -2597,14 +2597,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は156件</t>
+          <t>完了・了承済を除く未回答は158件</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>46</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="6" t="inlineStr"/>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
@@ -3147,8 +3147,8 @@
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（73件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
-注2）確認先が「発注者・3町」のもの（22件）は、3町への照会の様式と時期の決定を先に要します。
+          <t>注1）期限が令和8年8月以前のもの（75件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+注2）確認先が「発注者・3町」のもの（23件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
       </c>
@@ -5041,7 +5041,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>167件（未回答156件）</t>
+          <t>169件（未回答158件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>167件／一意167件</t>
+          <t>169件／一意169件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -5459,7 +5459,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている156件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている158件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
@@ -2657,11 +2657,11 @@
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>一部回答済</t>
+          <t>一部確認済み</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="6" t="inlineStr"/>
@@ -2672,7 +2672,7 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>解決</t>
+          <t>一部回答済</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
@@ -2687,7 +2687,7 @@
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>了承済（保管せず廃棄）</t>
+          <t>解決</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
@@ -2702,7 +2702,7 @@
       <c r="A13" s="6" t="inlineStr"/>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
@@ -2717,7 +2717,7 @@
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>一部確認済み</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="6" t="inlineStr"/>
@@ -3017,7 +3017,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -2657,7 +2657,7 @@
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>一部確認済み</t>
+          <t>解決</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
@@ -2687,7 +2687,7 @@
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>解決</t>
+          <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
@@ -2702,7 +2702,7 @@
       <c r="A13" s="6" t="inlineStr"/>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>了承済（保管せず廃棄）</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
@@ -2717,7 +2717,7 @@
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>一部確認済み</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>138箇所</t>
+          <t>146箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議110・要確認27・要内訳1。本文28箇所・表21種110箇所（01シート）</t>
+          <t>要協議112・要確認33・要内訳1。本文30箇所・表22種116箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（928段落145表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（943段落147表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -718,7 +718,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>138箇所のうち58箇所（42％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>146箇所のうち58箇所（40％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（928段落145表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計138箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（943段落147表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計146箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -877,13 +877,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>65</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -950,41 +950,37 @@
       <c r="A9" s="6" t="inlineStr"/>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>代表KPIの定義変更と目標の方向。確認事項No.4ほか</t>
-        </is>
-      </c>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr"/>
       <c r="D10" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0</v>
@@ -994,7 +990,7 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>第9期評価の表現と役割分担</t>
+          <t>代表KPIの定義変更と目標の方向。確認事項No.4ほか</t>
         </is>
       </c>
     </row>
@@ -1002,23 +998,27 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr"/>
       <c r="D11" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>第9期評価の表現と役割分担</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="9" t="inlineStr"/>
@@ -1029,13 +1029,13 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>1</v>
@@ -1151,42 +1151,38 @@
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>No.4（代表KPIの代理指標）</t>
-        </is>
-      </c>
+      <c r="H18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -1203,7 +1199,7 @@
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>No.118〜No.121（地域ケア会議のKPI）・No.130（認知症基本法）</t>
+          <t>No.4（代表KPIの代理指標）</t>
         </is>
       </c>
     </row>
@@ -1211,29 +1207,29 @@
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E20" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>5</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>No.114（中長期推計の範囲）</t>
+          <t>No.118〜No.121（地域ケア会議のKPI）・No.130（認知症基本法）</t>
         </is>
       </c>
     </row>
@@ -1241,29 +1237,29 @@
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>No.75（代表KPIの再整理案）</t>
+          <t>No.114（中長期推計の範囲）</t>
         </is>
       </c>
     </row>
@@ -1271,29 +1267,29 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>確認事項B No.19（医療側の連携の実施状況）</t>
+          <t>No.75（代表KPIの再整理案）</t>
         </is>
       </c>
     </row>
@@ -1306,24 +1302,24 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
+          <t>確認事項B No.19（医療側の連携の実施状況）</t>
         </is>
       </c>
     </row>
@@ -1336,24 +1332,24 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
         </is>
       </c>
     </row>
@@ -1361,29 +1357,29 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No.112（地域支援事業の量）</t>
+          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
         </is>
       </c>
     </row>
@@ -1396,11 +1392,11 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>3</v>
@@ -1409,11 +1405,11 @@
         <v>1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>No.86（交付金の控除）ほか</t>
+          <t>No.112（地域支援事業の量）</t>
         </is>
       </c>
     </row>
@@ -1421,29 +1417,29 @@
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E27" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F27" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>No.8（3調査の点検事項）</t>
+          <t>No.86（交付金の控除）ほか</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1452,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
@@ -1473,7 +1469,7 @@
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>No.8（同）</t>
+          <t>No.8（3調査の点検事項）</t>
         </is>
       </c>
     </row>
@@ -1481,90 +1477,94 @@
       <c r="A29" s="6" t="inlineStr"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
+          <t>No.8（同）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
           <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>3　本文の未確定箇所（28件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="4" t="inlineStr"/>
-      <c r="B32" s="4" t="inlineStr">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>3　本文の未確定箇所（30件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>本文（抜粋）</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr"/>
-    </row>
-    <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="6" t="inlineStr"/>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
-        <is>
-          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
     </row>
     <row r="34" ht="44" customHeight="1">
       <c r="A34" s="6" t="inlineStr"/>
@@ -1575,17 +1575,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
-        </is>
-      </c>
-      <c r="D34" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr"/>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr"/>
@@ -1622,22 +1622,22 @@
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第8節　関係計画等との関係</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることを受託者の案とします［要協議］。</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr"/>
@@ -1648,22 +1648,22 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr"/>
@@ -1679,17 +1679,17 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることを受託者の案とします［要協議］。</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr"/>
@@ -1705,17 +1705,17 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
@@ -1731,17 +1731,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 サービス提供体制の状況</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -1783,17 +1783,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
@@ -1804,22 +1804,22 @@
       <c r="A43" s="6" t="inlineStr"/>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1830,22 +1830,22 @@
       <c r="A44" s="6" t="inlineStr"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1856,22 +1856,22 @@
       <c r="A45" s="6" t="inlineStr"/>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1882,12 +1882,12 @@
       <c r="A46" s="6" t="inlineStr"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1908,22 +1908,22 @@
       <c r="A47" s="6" t="inlineStr"/>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr"/>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -2001,8 +2001,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-2）必要利用定員総数は第4節4により、</t>
+          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2018,7 +2017,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -2028,8 +2027,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2045,17 +2043,18 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-2）必要利用定員総数は第4節4により、</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2081,7 +2080,8 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2100,14 +2100,14 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2123,17 +2123,17 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
@@ -2159,8 +2159,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2179,15 +2178,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2203,17 +2201,18 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2229,17 +2228,18 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2255,163 +2255,151 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。改定率は令和9年度の告示を待って反映します。</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
       <c r="G60" s="6" t="inlineStr"/>
       <c r="H60" s="6" t="inlineStr"/>
     </row>
-    <row r="62" ht="28" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は21種の表に110箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+    <row r="61" ht="44" customHeight="1">
+      <c r="A61" s="6" t="inlineStr"/>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62" ht="44" customHeight="1">
+      <c r="A62" s="6" t="inlineStr"/>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63" ht="44" customHeight="1">
+      <c r="A63" s="6" t="inlineStr"/>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr"/>
+    </row>
+    <row r="65" ht="28" customHeight="1">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は22種の表に116箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="3" t="inlineStr">
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="4" t="inlineStr"/>
-      <c r="B65" s="4" t="inlineStr">
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="4" t="inlineStr"/>
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F68" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="H68" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="44" customHeight="1">
-      <c r="A66" s="6" t="inlineStr"/>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D66" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G66" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="44" customHeight="1">
-      <c r="A67" s="6" t="inlineStr"/>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D67" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67" s="6" t="inlineStr">
-        <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="44" customHeight="1">
-      <c r="A68" s="6" t="inlineStr"/>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>第4節　計画期間</t>
-        </is>
-      </c>
-      <c r="D68" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="6" t="inlineStr">
-        <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2424,11 +2412,11 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E69" s="5" t="n">
         <v>0</v>
@@ -2441,7 +2429,7 @@
       </c>
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
+          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2449,16 +2437,16 @@
       <c r="A70" s="6" t="inlineStr"/>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第1節 計画の基本理念</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>0</v>
@@ -2467,11 +2455,11 @@
         <v>1</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>基本理念であり、短いことは妥当</t>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2479,37 +2467,97 @@
       <c r="A71" s="6" t="inlineStr"/>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="n">
-        <v>3</v>
+          <t>第4節　計画期間</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>2</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>所得段階と公費軽減。第10期の政令改正（確認事項No.33）を待っている</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="42" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
+          <t>計画期間の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="44" customHeight="1">
+      <c r="A72" s="6" t="inlineStr"/>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>第5節　計画の策定体制</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="6" t="inlineStr">
+        <is>
+          <t>策定体制の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="44" customHeight="1">
+      <c r="A73" s="6" t="inlineStr"/>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>第4章　計画の基本理念及び基本目標</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>第1節 計画の基本理念</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="6" t="inlineStr">
+        <is>
+          <t>基本理念であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="42" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
-注4）記述が薄い節は6節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと1節です。
+注4）記述が薄い節は5節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
 注5）第2章第4節（高齢者の生活実態）は令和8年9月15日に健康とくらしの調査の結果を反映し、32段落・表8になりました。記述が薄い節には当たらなくなっています。</t>
         </is>
       </c>
@@ -2517,13 +2565,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A65:H65"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A64:H64"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A32:H32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4851,7 +4899,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議110・要確認27・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議112・要確認33・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4963,7 +5011,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>928段落145表36図／138箇所</t>
+          <t>943段落147表36図／146箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -4989,7 +5037,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>138＝138</t>
+          <t>146＝146</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -5015,7 +5063,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>138＝138</t>
+          <t>146＝146</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -5197,7 +5245,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>58／138箇所（42％）</t>
+          <t>58／146箇所（40％）</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -5223,7 +5271,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>6節（うち短いことが妥当なものを除くと1節）</t>
+          <t>5節（うち短いことが妥当なものを除くと0節）</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -5436,7 +5484,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は138箇所ある（要協議110・要確認27・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は146箇所ある（要協議112・要確認33・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>169件</t>
+          <t>171件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>158件</t>
+          <t>160件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが88件（02シート）</t>
+          <t>このうち計画素案を止めているものが90件（02シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（943段落147表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（916段落141表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（943段落147表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計146箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（916段落141表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計146箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2598,7 +2598,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（169件）</t>
+          <t>確認事項の棚卸し（171件）</t>
         </is>
       </c>
     </row>
@@ -2645,14 +2645,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は158件</t>
+          <t>完了・了承済を除く未回答は160件</t>
         </is>
       </c>
     </row>
@@ -2776,62 +2776,54 @@
       <c r="F14" s="6" t="inlineStr"/>
       <c r="G14" s="6" t="inlineStr"/>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="6" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>一部解消</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>2　期限別（未回答のみ）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="4" t="inlineStr"/>
-      <c r="B17" s="4" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="4" t="inlineStr"/>
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>うち計画素案を止めている</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>うち第1次概算を止めている</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr"/>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>67</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="6" t="inlineStr">
-        <is>
-          <t>期限が過ぎているもの</t>
         </is>
       </c>
     </row>
@@ -2839,17 +2831,17 @@
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>2</v>
+        <v>68</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
       <c r="G19" s="6" t="inlineStr">
@@ -2862,14 +2854,14 @@
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>0</v>
@@ -2885,11 +2877,11 @@
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
         <v>0</v>
@@ -2908,36 +2900,40 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>79</v>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="6" t="inlineStr"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>期限が過ぎているもの</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>R8.9.2</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="6" t="inlineStr"/>
@@ -2946,17 +2942,17 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.9.2</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
@@ -2965,17 +2961,17 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="F25" s="6" t="inlineStr"/>
       <c r="G25" s="6" t="inlineStr"/>
@@ -2984,14 +2980,14 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R9.4</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0</v>
@@ -2999,58 +2995,62 @@
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
     </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="6" t="inlineStr"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr"/>
+      <c r="G27" s="6" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>3　確認先別（未回答のみ）</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="4" t="inlineStr"/>
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="6" t="inlineStr"/>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="n">
-        <v>112</v>
-      </c>
-      <c r="D30" s="6" t="inlineStr"/>
-      <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr"/>
-      <c r="G30" s="6" t="inlineStr"/>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="6" t="inlineStr"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="6" t="inlineStr"/>
@@ -3061,11 +3061,11 @@
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
@@ -3076,11 +3076,11 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
@@ -3091,11 +3091,11 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="6" t="inlineStr"/>
@@ -3106,11 +3106,11 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="6" t="inlineStr"/>
@@ -3121,7 +3121,7 @@
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>発注者・東神楽町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -3136,11 +3136,11 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者・東神楽町</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
       <c r="E37" s="6" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -3166,7 +3166,7 @@
       <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>北海道上川総合振興局</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -3181,7 +3181,7 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -3192,10 +3192,25 @@
       <c r="F40" s="6" t="inlineStr"/>
       <c r="G40" s="6" t="inlineStr"/>
     </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>注1）期限が令和8年8月以前のもの（75件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="6" t="inlineStr"/>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>国の情報</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="6" t="inlineStr"/>
+      <c r="G41" s="6" t="inlineStr"/>
+    </row>
+    <row r="43" ht="42" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>注1）期限が令和8年8月以前のもの（77件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（23件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -3204,11 +3219,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A43:G43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5011,7 +5026,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>943段落147表36図／146箇所</t>
+          <t>916段落141表36図／146箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -5089,7 +5104,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>169件（未回答158件）</t>
+          <t>171件（未回答160件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -5115,7 +5130,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>169件／一意169件</t>
+          <t>171件／一意171件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -5507,7 +5522,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている158件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている160件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>146箇所</t>
+          <t>149箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議112・要確認33・要内訳1。本文30箇所・表22種116箇所（01シート）</t>
+          <t>要協議114・要確認34・要内訳1。本文31箇所・表23種118箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（916段落141表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（927段落143表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -718,7 +718,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>146箇所のうち58箇所（40％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>149箇所のうち58箇所（39％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（916段落141表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計146箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（927段落143表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計149箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -955,13 +955,13 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
@@ -1029,13 +1029,13 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>1</v>
@@ -1447,31 +1447,27 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="6" t="inlineStr">
-        <is>
-          <t>No.8（3調査の点検事項）</t>
-        </is>
-      </c>
+      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="6" t="inlineStr"/>
@@ -1482,7 +1478,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
@@ -1499,7 +1495,7 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>No.8（同）</t>
+          <t>No.8（3調査の点検事項）</t>
         </is>
       </c>
     </row>
@@ -1507,90 +1503,94 @@
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
+          <t>No.8（同）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="32" customHeight="1">
+      <c r="A31" s="6" t="inlineStr"/>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
           <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>3　本文の未確定箇所（30件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="4" t="inlineStr">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>3　本文の未確定箇所（31件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="inlineStr"/>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
+      <c r="E34" s="4" t="inlineStr">
         <is>
           <t>本文（抜粋）</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
-      <c r="G33" s="4" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr"/>
-    </row>
-    <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
-        <is>
-          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr"/>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="6" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr"/>
     </row>
     <row r="35" ht="44" customHeight="1">
       <c r="A35" s="6" t="inlineStr"/>
@@ -1601,17 +1601,17 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr"/>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
+          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr"/>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr"/>
@@ -1674,22 +1674,22 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第8節　関係計画等との関係</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることを受託者の案とします［要協議］。</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr"/>
@@ -1700,22 +1700,22 @@
       <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
@@ -1731,17 +1731,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることを受託者の案とします［要協議］。</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -1783,17 +1783,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 サービス提供体制の状況</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1835,17 +1835,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1856,22 +1856,22 @@
       <c r="A45" s="6" t="inlineStr"/>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1882,22 +1882,22 @@
       <c r="A46" s="6" t="inlineStr"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1908,22 +1908,22 @@
       <c r="A47" s="6" t="inlineStr"/>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1934,12 +1934,12 @@
       <c r="A48" s="6" t="inlineStr"/>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr"/>
@@ -1960,22 +1960,22 @@
       <c r="A49" s="6" t="inlineStr"/>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D49" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2053,8 +2053,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-2）必要利用定員総数は第4節4により、</t>
+          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2070,7 +2069,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
@@ -2080,8 +2079,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2097,17 +2095,18 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-2）必要利用定員総数は第4節4により、</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2133,7 +2132,8 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2152,14 +2152,14 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2175,17 +2175,17 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
@@ -2211,8 +2211,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2231,15 +2230,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2255,17 +2253,18 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2281,17 +2280,18 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2307,17 +2307,17 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2343,123 +2343,115 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
       <c r="G63" s="6" t="inlineStr"/>
       <c r="H63" s="6" t="inlineStr"/>
     </row>
-    <row r="65" ht="28" customHeight="1">
-      <c r="A65" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は22種の表に116箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+    <row r="64" ht="44" customHeight="1">
+      <c r="A64" s="6" t="inlineStr"/>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr"/>
+      <c r="G64" s="6" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65" ht="44" customHeight="1">
+      <c r="A65" s="6" t="inlineStr"/>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr"/>
+    </row>
+    <row r="67" ht="28" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は23種の表に118箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="4" t="inlineStr"/>
-      <c r="B68" s="4" t="inlineStr">
+    <row r="70" ht="30" customHeight="1">
+      <c r="A70" s="4" t="inlineStr"/>
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D68" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
+      <c r="E70" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F68" s="4" t="inlineStr">
+      <c r="F70" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="H70" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="44" customHeight="1">
-      <c r="A69" s="6" t="inlineStr"/>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D69" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="44" customHeight="1">
-      <c r="A70" s="6" t="inlineStr"/>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E70" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H70" s="6" t="inlineStr">
-        <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2472,11 +2464,11 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
+          <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>0</v>
@@ -2489,7 +2481,7 @@
       </c>
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
+          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2502,24 +2494,24 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2527,12 +2519,12 @@
       <c r="A73" s="6" t="inlineStr"/>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第1節 計画の基本理念</t>
+          <t>第4節　計画期間</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
@@ -2542,19 +2534,79 @@
         <v>0</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
+          <t>計画期間の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="44" customHeight="1">
+      <c r="A74" s="6" t="inlineStr"/>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>第5節　計画の策定体制</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H74" s="6" t="inlineStr">
+        <is>
+          <t>策定体制の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="44" customHeight="1">
+      <c r="A75" s="6" t="inlineStr"/>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>第4章　計画の基本理念及び基本目標</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>第1節 計画の基本理念</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="6" t="inlineStr">
+        <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="42" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
+    <row r="77" ht="42" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は5節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -2566,12 +2618,12 @@
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A65:H65"/>
+    <mergeCell ref="A77:H77"/>
+    <mergeCell ref="A69:H69"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A32:H32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4914,7 +4966,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議112・要確認33・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議114・要確認34・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -5026,7 +5078,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>916段落141表36図／146箇所</t>
+          <t>927段落143表36図／149箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -5052,7 +5104,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>146＝146</t>
+          <t>149＝149</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -5078,7 +5130,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>146＝146</t>
+          <t>149＝149</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -5260,7 +5312,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>58／146箇所（40％）</t>
+          <t>58／149箇所（39％）</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -5499,7 +5551,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は146箇所ある（要協議112・要確認33・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は149箇所ある（要協議114・要確認34・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（927段落143表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（928段落143表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（927段落143表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計149箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（928段落143表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計149箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることを受託者の案とします［要協議］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>927段落143表36図／149箇所</t>
+          <t>928段落143表36図／149箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -619,7 +619,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>171件</t>
+          <t>173件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -639,12 +639,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>160件</t>
+          <t>162件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが90件（02シート）</t>
+          <t>このうち計画素案を止めているものが92件（02シート）</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2650,7 +2650,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（171件）</t>
+          <t>確認事項の棚卸し（173件）</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は160件</t>
+          <t>完了・了承済を除く未回答は162件</t>
         </is>
       </c>
     </row>
@@ -2772,11 +2772,11 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>一部回答済</t>
+          <t>未回答</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="6" t="inlineStr"/>
@@ -2787,7 +2787,7 @@
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>了承済（保管せず廃棄）</t>
+          <t>一部回答済</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
@@ -2802,7 +2802,7 @@
       <c r="A13" s="6" t="inlineStr"/>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>実施中</t>
+          <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
       <c r="C13" s="12" t="n">
@@ -2817,7 +2817,7 @@
       <c r="A14" s="6" t="inlineStr"/>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>一部確認済み</t>
+          <t>実施中</t>
         </is>
       </c>
       <c r="C14" s="12" t="n">
@@ -2832,7 +2832,7 @@
       <c r="A15" s="6" t="inlineStr"/>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>一部解消</t>
+          <t>一部確認済み</t>
         </is>
       </c>
       <c r="C15" s="12" t="n">
@@ -2843,62 +2843,54 @@
       <c r="F15" s="6" t="inlineStr"/>
       <c r="G15" s="6" t="inlineStr"/>
     </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="6" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>一部解消</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>2　期限別（未回答のみ）</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="4" t="inlineStr"/>
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>うち計画素案を止めている</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>うち第1次概算を止めている</t>
         </is>
       </c>
-      <c r="F18" s="4" t="inlineStr"/>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr"/>
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="6" t="inlineStr"/>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>68</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>47</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>期限が過ぎているもの</t>
         </is>
       </c>
     </row>
@@ -2906,17 +2898,17 @@
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
+        <v>69</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr">
@@ -2929,14 +2921,14 @@
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
@@ -2952,11 +2944,11 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D22" s="5" t="n">
         <v>0</v>
@@ -2975,36 +2967,40 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="n">
-        <v>79</v>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>期限が過ぎているもの</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="18" customHeight="1">
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>R8.9.2</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
@@ -3013,17 +3009,17 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.9.2</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="n">
         <v>0</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="F25" s="6" t="inlineStr"/>
       <c r="G25" s="6" t="inlineStr"/>
@@ -3032,17 +3028,17 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="5" t="n">
         <v>1</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
@@ -3051,14 +3047,14 @@
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R9.4</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>0</v>
@@ -3066,58 +3062,62 @@
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr"/>
+      <c r="G28" s="6" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>3　確認先別（未回答のみ）</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="4" t="inlineStr"/>
-      <c r="B30" s="4" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr"/>
-      <c r="G30" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-    </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="6" t="inlineStr"/>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="n">
-        <v>114</v>
-      </c>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>23</v>
+        <v>116</v>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
@@ -3128,11 +3128,11 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
@@ -3143,11 +3143,11 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="6" t="inlineStr"/>
@@ -3158,11 +3158,11 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="6" t="inlineStr"/>
@@ -3173,11 +3173,11 @@
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="6" t="inlineStr"/>
@@ -3188,7 +3188,7 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>発注者・東神楽町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -3203,11 +3203,11 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者・東神楽町</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
       <c r="E38" s="6" t="inlineStr"/>
@@ -3218,7 +3218,7 @@
       <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
@@ -3233,7 +3233,7 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>北海道上川総合振興局</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -3248,7 +3248,7 @@
       <c r="A41" s="6" t="inlineStr"/>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -3259,10 +3259,25 @@
       <c r="F41" s="6" t="inlineStr"/>
       <c r="G41" s="6" t="inlineStr"/>
     </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>注1）期限が令和8年8月以前のもの（77件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="6" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>国の情報</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr"/>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
+    </row>
+    <row r="44" ht="42" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>注1）期限が令和8年8月以前のもの（79件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（23件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -3270,12 +3285,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A18:G18"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A43:G43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5156,7 +5171,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>171件（未回答160件）</t>
+          <t>173件（未回答162件）</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -5182,7 +5197,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>171件／一意171件</t>
+          <t>173件／一意173件</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -5574,7 +5589,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている160件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている162件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>149箇所</t>
+          <t>151箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議114・要確認34・要内訳1。本文31箇所・表23種118箇所（01シート）</t>
+          <t>要協議115・要確認35・要内訳1。本文33箇所・表23種118箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（928段落143表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（942段落145表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -718,7 +718,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>149箇所のうち58箇所（39％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>151箇所のうち59箇所（39％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H77"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（928段落143表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計149箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（942段落145表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計151箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -877,13 +877,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -1029,13 +1029,13 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>1</v>
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>54</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>0</v>
@@ -1426,10 +1426,10 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>1</v>
@@ -1562,7 +1562,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（31件）</t>
+          <t>3　本文の未確定箇所（33件）</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2317,7 +2317,8 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2333,7 +2334,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2343,7 +2344,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2369,7 +2370,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2385,7 +2386,7 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2395,123 +2396,115 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
       <c r="G65" s="6" t="inlineStr"/>
       <c r="H65" s="6" t="inlineStr"/>
     </row>
-    <row r="67" ht="28" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
+    <row r="66" ht="44" customHeight="1">
+      <c r="A66" s="6" t="inlineStr"/>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr"/>
+      <c r="G66" s="6" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67" ht="44" customHeight="1">
+      <c r="A67" s="6" t="inlineStr"/>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr"/>
+    </row>
+    <row r="69" ht="28" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>注1）表の中の未確定箇所は23種の表に118箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="4" t="inlineStr"/>
-      <c r="B70" s="4" t="inlineStr">
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="4" t="inlineStr"/>
+      <c r="B72" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C72" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D70" s="4" t="inlineStr">
+      <c r="D72" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
+      <c r="E72" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F70" s="4" t="inlineStr">
+      <c r="F72" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="H72" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="44" customHeight="1">
-      <c r="A71" s="6" t="inlineStr"/>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D71" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="44" customHeight="1">
-      <c r="A72" s="6" t="inlineStr"/>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E72" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H72" s="6" t="inlineStr">
-        <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2524,11 +2517,11 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
+          <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>0</v>
@@ -2541,7 +2534,7 @@
       </c>
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
+          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2554,24 +2547,24 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E74" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F74" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2579,12 +2572,12 @@
       <c r="A75" s="6" t="inlineStr"/>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第1節 計画の基本理念</t>
+          <t>第4節　計画期間</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
@@ -2594,19 +2587,79 @@
         <v>0</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G75" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
+          <t>計画期間の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="44" customHeight="1">
+      <c r="A76" s="6" t="inlineStr"/>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>第5節　計画の策定体制</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H76" s="6" t="inlineStr">
+        <is>
+          <t>策定体制の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="44" customHeight="1">
+      <c r="A77" s="6" t="inlineStr"/>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>第4章　計画の基本理念及び基本目標</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>第1節 計画の基本理念</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="6" t="inlineStr">
+        <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="42" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は5節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -2617,13 +2670,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A77:H77"/>
     <mergeCell ref="A69:H69"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A71:H71"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A79:H79"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3651,7 +3704,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>一律の伸びのまま概算し、補正の効き（月額▲58円又は＋48円）を併記する</t>
+          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3854,7 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>第6章第2節は利用者数のみを掲げたまま概算する</t>
+          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
         </is>
       </c>
     </row>
@@ -3981,7 +4034,7 @@
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する。差は月額＋8円である</t>
+          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
     </row>
@@ -4981,7 +5034,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議114・要確認34・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議115・要確認35・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -5093,7 +5146,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>928段落143表36図／149箇所</t>
+          <t>942段落145表36図／151箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -5119,7 +5172,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>149＝149</t>
+          <t>151＝151</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -5145,7 +5198,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>149＝149</t>
+          <t>151＝151</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -5327,7 +5380,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>58／149箇所（39％）</t>
+          <t>59／151箇所（39％）</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -5566,7 +5619,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は149箇所ある（要協議114・要確認34・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は151箇所ある（要協議115・要確認35・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>151箇所</t>
+          <t>153箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議115・要確認35・要内訳1。本文33箇所・表23種118箇所（01シート）</t>
+          <t>要協議117・要確認35・要内訳1。本文35箇所・表23種118箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（942段落145表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（949段落146表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -718,7 +718,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>151箇所のうち59箇所（39％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>153箇所のうち59箇所（39％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（942段落145表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計151箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（949段落146表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計153箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -877,10 +877,10 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>9</v>
@@ -1029,10 +1029,10 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F12" s="10" t="n">
         <v>35</v>
@@ -1237,29 +1237,29 @@
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>No.114（中長期推計の範囲）</t>
+          <t>No.112（地域支援事業の量）</t>
         </is>
       </c>
     </row>
@@ -1267,29 +1267,29 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>No.75（代表KPIの再整理案）</t>
+          <t>No.86（交付金の控除）ほか</t>
         </is>
       </c>
     </row>
@@ -1297,29 +1297,29 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>確認事項B No.19（医療側の連携の実施状況）</t>
+          <t>No.114（中長期推計の範囲）</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
+          <t>No.75（代表KPIの再整理案）</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+          <t>確認事項B No.19（医療側の連携の実施状況）</t>
         </is>
       </c>
     </row>
@@ -1387,29 +1387,29 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>No.112（地域支援事業の量）</t>
+          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>No.86（交付金の控除）ほか</t>
+          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（33件）</t>
+          <t>3　本文の未確定箇所（35件）</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2106,7 @@
       <c r="E54" s="6" t="inlineStr">
         <is>
           <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-2）必要利用定員総数は第4節4により、</t>
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2211,7 +2211,9 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
+          <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
+注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
+注3）事業ごとの</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2227,17 +2229,17 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2256,15 +2258,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2310,15 +2311,15 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2334,7 +2335,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2344,7 +2345,8 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2360,17 +2362,17 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2389,14 +2391,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2415,14 +2417,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2438,133 +2440,125 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
       <c r="G67" s="6" t="inlineStr"/>
       <c r="H67" s="6" t="inlineStr"/>
     </row>
-    <row r="69" ht="28" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
+    <row r="68" ht="44" customHeight="1">
+      <c r="A68" s="6" t="inlineStr"/>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr"/>
+      <c r="G68" s="6" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69" ht="44" customHeight="1">
+      <c r="A69" s="6" t="inlineStr"/>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr"/>
+      <c r="G69" s="6" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr"/>
+    </row>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="7" t="inlineStr">
         <is>
           <t>注1）表の中の未確定箇所は23種の表に118箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="4" t="inlineStr"/>
-      <c r="B72" s="4" t="inlineStr">
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="4" t="inlineStr"/>
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D72" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F72" s="4" t="inlineStr">
+      <c r="F74" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
+      <c r="H74" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="44" customHeight="1">
-      <c r="A73" s="6" t="inlineStr"/>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D73" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="44" customHeight="1">
-      <c r="A74" s="6" t="inlineStr"/>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E74" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H74" s="6" t="inlineStr">
-        <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2577,11 +2571,11 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
+          <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>0</v>
@@ -2594,7 +2588,7 @@
       </c>
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
+          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -2607,24 +2601,24 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D76" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F76" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2626,12 @@
       <c r="A77" s="6" t="inlineStr"/>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第1節 計画の基本理念</t>
+          <t>第4節　計画期間</t>
         </is>
       </c>
       <c r="D77" s="5" t="n">
@@ -2647,19 +2641,79 @@
         <v>0</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G77" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H77" s="6" t="inlineStr">
         <is>
+          <t>計画期間の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="44" customHeight="1">
+      <c r="A78" s="6" t="inlineStr"/>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>第5節　計画の策定体制</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H78" s="6" t="inlineStr">
+        <is>
+          <t>策定体制の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="44" customHeight="1">
+      <c r="A79" s="6" t="inlineStr"/>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>第4章　計画の基本理念及び基本目標</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>第1節 計画の基本理念</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="6" t="inlineStr">
+        <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="42" customHeight="1">
-      <c r="A79" s="7" t="inlineStr">
+    <row r="81" ht="42" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は5節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -2670,13 +2724,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A69:H69"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A73:H73"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A71:H71"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A79:H79"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3584,7 +3638,7 @@
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）で概算する</t>
+          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3668,7 @@
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>素案 第6章第2節の表は見える化の自然体推計値のまま置き、P3による値を別掲する</t>
+          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
         </is>
       </c>
     </row>
@@ -3914,7 +3968,7 @@
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（月額で＋185〜＋374円に当たる）</t>
+          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
         </is>
       </c>
     </row>
@@ -4134,7 +4188,7 @@
           <t>注1）24件のうち期限が令和8年9月のものは21件です。
 注2）既定値はいずれも当方が作業上置いているものであり、ご了承をいただいたものではありません。第1次概算をお出しする際は、どの既定値によったかを明示します。
 注3）安全側と記したものは、決着しないまま概算すると保険料が高めに出る向きのものです。施策の達成や適正化の効果を前提に下げると、保険料が不足する側に誤ります。
-注4）No.137（単価の年度）は月額で＋185〜＋374円に当たり、本表のうち最も効きが大きいものです。</t>
+注4）No.137（単価の年度）は本表のうち最も効きが大きいものです。額は計画素案 第6章第6節2によります。</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4397,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>見える化システムに令和7年度とするか令和8年度とするかを選ぶ項目があり、施設・居住系と在宅で別に選べる。令和7年度で固定することは月額で＋185〜＋374円に当たる</t>
+          <t>見える化システムに令和7年度とするか令和8年度とするかを選ぶ項目があり、施設・居住系と在宅で別に選べる。令和7年度で固定することは単価の趨勢を落としており、効きは計画素案 第6章第6節2に掲げる</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -5034,7 +5088,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議115・要確認35・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議117・要確認35・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -5146,7 +5200,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>942段落145表36図／151箇所</t>
+          <t>949段落146表36図／153箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -5172,7 +5226,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>151＝151</t>
+          <t>153＝153</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -5198,7 +5252,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>151＝151</t>
+          <t>153＝153</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -5380,7 +5434,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>59／151箇所（39％）</t>
+          <t>59／153箇所（39％）</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -5587,7 +5641,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が24件あり、うち期限が令和8年9月のものが21件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度。月額＋185〜＋374円）であり、これだけは9月26日までに決定をいただきたい。</t>
+          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が24件あり、うち期限が令和8年9月のものが21件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度）であり、これだけは9月26日までに決定をいただきたい。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -5619,7 +5673,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は151箇所ある（要協議115・要確認35・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は153箇所ある（要協議117・要確認35・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -599,12 +599,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>153箇所</t>
+          <t>158箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議117・要確認35・要内訳1。本文35箇所・表23種118箇所（01シート）</t>
+          <t>要協議118・要確認39・要内訳1。本文40箇所・表23種118箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（949段落146表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（951段落146表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -718,7 +718,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>153箇所のうち59箇所（39％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>158箇所のうち60箇所（38％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H81"/>
+  <dimension ref="A1:H86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -823,7 +823,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（949段落146表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計153箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（951段落146表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計158箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -877,13 +877,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -903,13 +903,13 @@
       </c>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>29</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -1029,13 +1029,13 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>1</v>
@@ -1100,13 +1100,13 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>54</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>0</v>
@@ -1130,13 +1130,13 @@
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>9</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0</v>
@@ -1151,68 +1151,68 @@
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>No.86（交付金の控除）ほか</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>No.4（代表KPIの代理指標）</t>
-        </is>
-      </c>
+      <c r="H19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>No.118〜No.121（地域ケア会議のKPI）・No.130（認知症基本法）</t>
+          <t>No.4（代表KPIの代理指標）</t>
         </is>
       </c>
     </row>
@@ -1237,29 +1237,29 @@
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>No.112（地域支援事業の量）</t>
+          <t>No.118〜No.121（地域ケア会議のKPI）・No.130（認知症基本法）</t>
         </is>
       </c>
     </row>
@@ -1272,24 +1272,24 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>No.86（交付金の控除）ほか</t>
+          <t>No.112（地域支援事業の量）</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（35件）</t>
+          <t>3　本文の未確定箇所（40件）</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1975,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>介護給付適正化の計画策定に関する指針は、介護給付費財政調整交付金の算定に当たって主要3事業の取組状況を勘案することとしています。ケアプランの点検が実施されていないことは、交付金の評価にとどまらず調整交付金の交付割合を通じて保険料に及ぶ可能性があります。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この勘</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -1986,22 +1986,22 @@
       <c r="A50" s="6" t="inlineStr"/>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2043,7 +2043,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2105,8 +2105,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2122,7 +2121,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
@@ -2132,8 +2131,8 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2152,14 +2151,15 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2178,9 +2178,9 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -2211,37 +2211,37 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F58" s="6" t="inlineStr"/>
+      <c r="G58" s="6" t="inlineStr"/>
+      <c r="H58" s="6" t="inlineStr"/>
+    </row>
+    <row r="59" ht="44" customHeight="1">
+      <c r="A59" s="6" t="inlineStr"/>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
+        <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr"/>
-      <c r="G58" s="6" t="inlineStr"/>
-      <c r="H58" s="6" t="inlineStr"/>
-    </row>
-    <row r="59" ht="44" customHeight="1">
-      <c r="A59" s="6" t="inlineStr"/>
-      <c r="B59" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
       <c r="F59" s="6" t="inlineStr"/>
       <c r="G59" s="6" t="inlineStr"/>
       <c r="H59" s="6" t="inlineStr"/>
@@ -2255,17 +2255,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2284,15 +2284,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2338,15 +2337,15 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2362,7 +2361,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2372,7 +2371,8 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2388,17 +2388,18 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2414,7 +2415,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2424,7 +2425,7 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。また調整交付金の算定基礎に加える総合事業費は、介護保険事業計画作成支援ツールの「介護予防・日常生活支援総合事業費」（3町計107,129,318円）によります。第3節2の表に掲</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2450,7 +2451,7 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2476,7 +2477,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2492,7 +2493,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2502,218 +2503,348 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
       <c r="G69" s="6" t="inlineStr"/>
       <c r="H69" s="6" t="inlineStr"/>
     </row>
-    <row r="71" ht="28" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+    <row r="70" ht="44" customHeight="1">
+      <c r="A70" s="6" t="inlineStr"/>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr"/>
+      <c r="H70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71" ht="44" customHeight="1">
+      <c r="A71" s="6" t="inlineStr"/>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr"/>
+      <c r="G71" s="6" t="inlineStr"/>
+      <c r="H71" s="6" t="inlineStr"/>
+    </row>
+    <row r="72" ht="44" customHeight="1">
+      <c r="A72" s="6" t="inlineStr"/>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr"/>
+      <c r="G72" s="6" t="inlineStr"/>
+      <c r="H72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73" ht="44" customHeight="1">
+      <c r="A73" s="6" t="inlineStr"/>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費です。Eの調整交付金見込額は第9期計画と同水準の交付割合によって</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr"/>
+      <c r="G73" s="6" t="inlineStr"/>
+      <c r="H73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74" ht="44" customHeight="1">
+      <c r="A74" s="6" t="inlineStr"/>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr"/>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr"/>
+    </row>
+    <row r="76" ht="28" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>注1）表の中の未確定箇所は23種の表に118箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="4" t="inlineStr"/>
-      <c r="B74" s="4" t="inlineStr">
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="4" t="inlineStr"/>
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
+      <c r="F79" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H74" s="4" t="inlineStr">
+      <c r="H79" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="44" customHeight="1">
-      <c r="A75" s="6" t="inlineStr"/>
-      <c r="B75" s="6" t="inlineStr">
+    <row r="80" ht="44" customHeight="1">
+      <c r="A80" s="6" t="inlineStr"/>
+      <c r="B80" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
-      <c r="D75" s="5" t="n">
+      <c r="D80" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E75" s="5" t="n">
+      <c r="E80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="F80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G75" s="5" t="n">
+      <c r="G80" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H75" s="6" t="inlineStr">
+      <c r="H80" s="6" t="inlineStr">
         <is>
           <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="44" customHeight="1">
-      <c r="A76" s="6" t="inlineStr"/>
-      <c r="B76" s="6" t="inlineStr">
+    <row r="81" ht="44" customHeight="1">
+      <c r="A81" s="6" t="inlineStr"/>
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>第2節　計画の位置付け</t>
         </is>
       </c>
-      <c r="D76" s="5" t="n">
+      <c r="D81" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E76" s="5" t="n">
+      <c r="E81" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F76" s="5" t="n">
+      <c r="F81" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G76" s="5" t="n">
+      <c r="G81" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H76" s="6" t="inlineStr">
+      <c r="H81" s="6" t="inlineStr">
         <is>
           <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="44" customHeight="1">
-      <c r="A77" s="6" t="inlineStr"/>
-      <c r="B77" s="6" t="inlineStr">
+    <row r="82" ht="44" customHeight="1">
+      <c r="A82" s="6" t="inlineStr"/>
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>第4節　計画期間</t>
         </is>
       </c>
-      <c r="D77" s="5" t="n">
+      <c r="D82" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E77" s="5" t="n">
+      <c r="E82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="F82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G77" s="5" t="n">
+      <c r="G82" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H77" s="6" t="inlineStr">
+      <c r="H82" s="6" t="inlineStr">
         <is>
           <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="44" customHeight="1">
-      <c r="A78" s="6" t="inlineStr"/>
-      <c r="B78" s="6" t="inlineStr">
+    <row r="83" ht="44" customHeight="1">
+      <c r="A83" s="6" t="inlineStr"/>
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D78" s="5" t="n">
+      <c r="D83" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E78" s="5" t="n">
+      <c r="E83" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F83" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G78" s="5" t="n">
+      <c r="G83" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H78" s="6" t="inlineStr">
+      <c r="H83" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="44" customHeight="1">
-      <c r="A79" s="6" t="inlineStr"/>
-      <c r="B79" s="6" t="inlineStr">
+    <row r="84" ht="44" customHeight="1">
+      <c r="A84" s="6" t="inlineStr"/>
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D79" s="5" t="n">
+      <c r="D84" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E79" s="5" t="n">
+      <c r="E84" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F84" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G79" s="5" t="n">
+      <c r="G84" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H79" s="6" t="inlineStr">
+      <c r="H84" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="42" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
+    <row r="86" ht="42" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は5節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -2724,10 +2855,10 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A81:H81"/>
-    <mergeCell ref="A73:H73"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A86:H86"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A76:H76"/>
     <mergeCell ref="A33:H33"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
@@ -4178,7 +4309,7 @@
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>町別按分は当方の案（第1次概算）のまま示す</t>
+          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5219,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議117・要確認35・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議118・要確認39・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -5200,7 +5331,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>949段落146表36図／153箇所</t>
+          <t>951段落146表36図／158箇所</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -5226,7 +5357,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>153＝153</t>
+          <t>158＝158</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -5252,7 +5383,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>153＝153</t>
+          <t>158＝158</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -5434,7 +5565,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>59／153箇所（39％）</t>
+          <t>60／158箇所（38％）</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -5673,7 +5804,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は153箇所ある（要協議117・要確認35・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は158箇所ある（要協議118・要確認39・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -129,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -162,9 +162,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -659,12 +656,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>24件</t>
+          <t>0件</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項（03シート）</t>
+          <t>令和8年9月26日（サービス見込量の算定）を止めている確認事項（03シート）</t>
         </is>
       </c>
     </row>
@@ -728,7 +725,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>第1次概算を止めているものが24件ある</t>
+          <t>第1次概算を止めているものが0件ある</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -738,7 +735,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>9月26日まで残り期間が短く、うち期限が令和8年9月のものが21件あります</t>
+          <t>9月26日まで残り期間が短く、うち期限が令和8年9月のものが0件あります</t>
         </is>
       </c>
     </row>
@@ -3146,7 +3143,7 @@
         <v>48</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F20" s="6" t="inlineStr"/>
       <c r="G20" s="6" t="inlineStr">
@@ -3238,7 +3235,7 @@
         <v>40</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F24" s="6" t="inlineStr"/>
       <c r="G24" s="6" t="inlineStr"/>
@@ -3276,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" s="6" t="inlineStr"/>
       <c r="G26" s="6" t="inlineStr"/>
@@ -3540,7 +3537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3554,14 +3551,14 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>第1次概算までに決着を要するもの（24件）</t>
+          <t>第1次概算までに決着を要するもの（0件）</t>
         </is>
       </c>
     </row>
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項。決着しない場合の当方の扱い（既定値）を併せて示す。決着しなくても概算は出せるが、その前提を明示することになる。</t>
+          <t>令和8年9月26日（サービス見込量の算定）を止めている確認事項。決着しない場合の当方の扱い（既定値）を併せて示す。決着しなくても概算は出せるが、その前提を明示することになる。</t>
         </is>
       </c>
     </row>
@@ -3593,730 +3590,10 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>No.110</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化の効果を見込量に織り込まないことでよいか</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>給付適正化の効果を織り込まないまま概算する（安全側）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>No.128</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度の実績見込み値を編集するか</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの令和8年度の実績見込み値は編集しないまま概算する。当方の算定は年報（令和7年度）によるため見込量は動かず、システムの出力との差として残る</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>No.129</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの利用率等の伸びの選択</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度（4か月）を含まない④（令和6年度→令和7年度）の伸びを選んだものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>No.88</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>日常生活圏域ごとの必要利用定員総数（法定記載事項）</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>3町（3圏域）を基盤整備単位とする案のまま概算する。必要利用定員総数は［要協議］のまま残す</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>No.98</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>基盤整備の選択肢として省令上の類型を計画に掲げるか</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>省令上の類型を計画に掲げないまま概算する</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>No.100</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>サービス見込量及び給付費の算定に用いる基準年度と出所</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>採用パターンP3（令和7年度基準・総括表・認定者数シナリオ②）により、要介護度別の伸びで概算する</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>No.101</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第6章第2節2の見込量の表の数値の差し替え</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第6章第2節の表は当方の算定（令和7年度の実績に要介護度別の認定者数の伸びを乗じたもの）による値とし、見える化システムの自然体推計による値は第6節2に対比として掲げる</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>No.103</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度を基準年度に用いず、季節を理由とする補正も行わないこと</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度を基準年度に用いず、季節補正も行わないまま概算する</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>No.105</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>施策反映を行うか。行う場合の対象と歯止め</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>施策反映を行わないまま概算する（安全側）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>No.106</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>見込量の伸びを一律からサービス別の趨勢を半分反映する置き方に改めるか</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>サービス別の趨勢を反映する補正は行わない（見込量は要介護度別の伸びによる）。補正を行った場合の月額への効きは計画素案 第6章第6節2に併記する</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>No.107</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>施設・居住系の実績の減少を将来へ延長するか</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>施設・居住系の実績の減少を将来へ延長しないまま概算する</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>No.113</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>混合型特定施設の必要利用定員総数を定めるか</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>発注者・北海道</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>混合型特定施設の必要利用定員総数を定めないまま概算する</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>No.123</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの施設・居住系の画面から先へ進めない件</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの推計値は現行の自然体推計のまま用いる</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>No.126</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの推計方式は基本推計でよいか</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>基本推計に近いP3で概算する</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>No.131</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>第6章第2節の見込量の表に何を掲げるか</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>計画素案 第6章第2節に利用回（日）数を、第3節2に介護予防・日常生活支援総合事業及び一般介護予防事業の量の見込みを掲げた現行のまま確定する。必要利用定員総数の第2節への再掲は行わない（第4節4による）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>No.132</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>在宅サービスの実績見込み値の編集画面の現在値のご提供</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>在宅の実績見込み値は当方の入力案のまま置く</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>No.137</t>
-        </is>
-      </c>
-      <c r="C21" s="6" t="inlineStr">
-        <is>
-          <t>1人1月あたり給付費の実績値をどの年度にするか</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>1人1月あたり給付費は令和7年度で固定して概算する（単価の趨勢を織り込まないことによる効きは計画素案 第6章第6節2に掲げる）</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>No.141</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>区域を越えた施設利用の扱い</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>必要利用定員総数は区域内の施設の定員とは別に整理したまま概算する</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>No.142</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>第1次概算を既定値のまま出してよいか</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>本表そのものに係る確認事項である。決着しない場合は、本シートの既定値によったことを第1次概算の資料に明示して提出する</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>No.145</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>計画作成支援ツールと年報のどちらを町別の値に用いるか</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>サービス見込量・給付費・保険料は年報（保険者単位）の値で概算し、町別データシートは計画作成支援ツールの値のまま示す。3町を足しても年報の値にならないことを注記する</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="5" t="n">
-        <v>21</v>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>No.146</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>見込量の伸びを要介護度別に改めてよいか</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>要介護度別の伸びによる算定（第1次概算）で概算し、一律の伸びによる従前の値を併記する（差は計画素案 第6章第6節2に掲げる）</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="44" customHeight="1">
-      <c r="A26" s="5" t="n">
-        <v>22</v>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>No.147</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>見える化システムの伸びの選択肢をどれとするか</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>令和8年度を含まない④（令和6年度→令和7年度）を採ったものとして概算する。当方の算定（令和7年度基準）と置き方がそろう</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="44" customHeight="1">
-      <c r="A27" s="5" t="n">
-        <v>23</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>No.151</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護を対計画比の補正の対象から外してよいか</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>認知症対応型共同生活介護及び介護老人福祉施設を対計画比の補正の対象から外したものとして概算する。定員の縮小を趨勢として二重に織り込まないため（安全側）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="44" customHeight="1">
-      <c r="A28" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>No.82</t>
-        </is>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>構成町の一般会計繰入金の町別按分の方法</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>R8.9.24</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>町別への按分は広域連合の規約によるものであり算定できないため、構成町の一般会計繰入金は3町計の概算のみを示す（按分の方法のご教示を受けた時点で町別までお示しする）</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="56" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>注1）24件のうち期限が令和8年9月のものは21件です。
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>注1）0件のうち期限が令和8年9月のものは0件です。
 注2）既定値はいずれも当方が作業上置いているものであり、ご了承をいただいたものではありません。第1次概算をお出しする際は、どの既定値によったかを明示します。
 注3）安全側と記したものは、決着しないまま概算すると保険料が高めに出る向きのものです。施策の達成や適正化の効果を前提に下げると、保険料が不足する側に誤ります。
 注4）No.137（単価の年度）は本表のうち最も効きが大きいものです。額は計画素案 第6章第6節2によります。</t>
@@ -4326,8 +3603,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A6:F6"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4794,7 +4071,7 @@
           <t>No.8</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -4824,7 +4101,7 @@
           <t>No.8</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -4854,7 +4131,7 @@
           <t>No.9（地区の定義の部分）</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>一部完了</t>
         </is>
@@ -5077,7 +4354,7 @@
           <t>第2章第4節</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>完了</t>
         </is>
@@ -5107,7 +4384,7 @@
           <t>第6章第1節・第8節</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>着手できる</t>
         </is>
@@ -5137,7 +4414,7 @@
           <t>第6章第3節2</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>様式のみ着手できる</t>
         </is>
@@ -5197,7 +4474,7 @@
           <t>第1章第2節・第5章 基本目標2</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>協議資料は着手できる</t>
         </is>
@@ -5227,7 +4504,7 @@
           <t>素案全体</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>着手できる</t>
         </is>
@@ -5334,7 +4611,7 @@
           <t>951段落146表36図／158箇所</t>
         </is>
       </c>
-      <c r="E5" s="15" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5360,7 +4637,7 @@
           <t>158＝158</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5386,7 +4663,7 @@
           <t>158＝158</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5412,7 +4689,7 @@
           <t>173件（未回答162件）</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5438,7 +4715,7 @@
           <t>173件／一意173件</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5464,7 +4741,7 @@
           <t>全件実在</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5490,7 +4767,7 @@
           <t>全件実在</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5516,7 +4793,7 @@
           <t>全件実在</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5534,7 +4811,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>24件</t>
+          <t>0件</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -5542,7 +4819,7 @@
           <t>全件に置いている</t>
         </is>
       </c>
-      <c r="E13" s="15" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5568,7 +4845,7 @@
           <t>60／158箇所（38％）</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5594,7 +4871,7 @@
           <t>5節（うち短いことが妥当なものを除くと0節）</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5620,7 +4897,7 @@
           <t>32段落・表8。記述が薄い節には当たらない</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5646,7 +4923,7 @@
           <t>本スクリプトは素案を読むだけで書き換えていない</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5670,7 +4947,7 @@
           <t>適合13件・不適合0件</t>
         </is>
       </c>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="15" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
@@ -5772,12 +5049,12 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>令和8年9月26日（サービス見込量 第1次概算）を止めている確認事項が24件あり、うち期限が令和8年9月のものが21件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度）であり、これだけは9月26日までに決定をいただきたい。</t>
+          <t>令和8年9月26日（サービス見込量の算定）を止めている確認事項が0件あり、うち期限が令和8年9月のものが0件ある。9月26日までに全件の決着は難しいと見込まれる。①決着していないものは当方の既定値（03シート）により概算し、どの既定値によったかを明示する扱いでよいか。②既定値のうち保険料を高めに出す向きのもの（施策反映を行わない・給付適正化の効果を織り込まない・施設の減少を延長しない）は安全側の置き方である。この向きでよいか。③効きが最も大きいのはNo.137（1人1月あたり給付費の年度）であり、これだけは9月26日までに決定をいただきたい。</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量 第1次概算</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>158箇所</t>
+          <t>163箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議118・要確認39・要内訳1。本文40箇所・表23種118箇所（01シート）</t>
+          <t>要協議119・要確認43・要内訳1。本文44箇所・表24種119箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（951段落146表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（973段落148表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>158箇所のうち60箇所（38％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>163箇所のうち61箇所（37％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H86"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（951段落146表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計158箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（973段落148表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計163箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -926,13 +926,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -974,13 +974,13 @@
       </c>
       <c r="C10" s="6" t="inlineStr"/>
       <c r="D10" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0</v>
@@ -1026,13 +1026,13 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>1</v>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>6</v>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
@@ -1178,57 +1178,57 @@
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E19" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F19" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>No.4（代表KPIの代理指標）</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>No.4（代表KPIの代理指標）</t>
-        </is>
-      </c>
+      <c r="H20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="6" t="inlineStr"/>
@@ -1444,57 +1444,57 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H28" s="6" t="inlineStr"/>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>No.8（3調査の点検事項）</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="32" customHeight="1">
       <c r="A29" s="6" t="inlineStr"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>No.8（3調査の点検事項）</t>
-        </is>
-      </c>
+      <c r="H29" s="6" t="inlineStr"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="6" t="inlineStr"/>
@@ -1505,24 +1505,24 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>No.8（同）</t>
+          <t>No.3（町別人口）</t>
         </is>
       </c>
     </row>
@@ -1530,90 +1530,94 @@
       <c r="A31" s="6" t="inlineStr"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
+          <t>No.8（同）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="6" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
           <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>3　本文の未確定箇所（40件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="4" t="inlineStr"/>
-      <c r="B34" s="4" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>3　本文の未確定箇所（44件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D34" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="E35" s="4" t="inlineStr">
         <is>
           <t>本文（抜粋）</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr"/>
-      <c r="G34" s="4" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr"/>
-    </row>
-    <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="6" t="inlineStr"/>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D35" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
-          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr"/>
-      <c r="G35" s="6" t="inlineStr"/>
-      <c r="H35" s="6" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr"/>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="6" t="inlineStr"/>
@@ -1624,17 +1628,17 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
-        </is>
-      </c>
-      <c r="D36" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr"/>
@@ -1650,7 +1654,7 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1660,7 +1664,7 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。</t>
+          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr"/>
@@ -1676,7 +1680,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1686,7 +1690,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr"/>
@@ -1702,7 +1706,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1712,7 +1716,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
@@ -1723,22 +1727,22 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
@@ -1764,7 +1768,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -1780,17 +1784,17 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
@@ -1806,7 +1810,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1816,7 +1820,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1832,17 +1836,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 サービス提供体制の状況</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1858,7 +1862,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1868,7 +1872,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1884,7 +1888,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1894,7 +1898,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1905,12 +1909,12 @@
       <c r="A47" s="6" t="inlineStr"/>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
@@ -1920,7 +1924,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1931,22 +1935,22 @@
       <c r="A48" s="6" t="inlineStr"/>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr"/>
@@ -1957,12 +1961,12 @@
       <c r="A49" s="6" t="inlineStr"/>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1972,7 +1976,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>介護給付適正化の計画策定に関する指針は、介護給付費財政調整交付金の算定に当たって主要3事業の取組状況を勘案することとしています。ケアプランの点検が実施されていないことは、交付金の評価にとどまらず調整交付金の交付割合を通じて保険料に及ぶ可能性があります。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この勘</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -1983,22 +1987,22 @@
       <c r="A50" s="6" t="inlineStr"/>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2009,12 +2013,12 @@
       <c r="A51" s="6" t="inlineStr"/>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -2024,7 +2028,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2035,22 +2039,22 @@
       <c r="A52" s="6" t="inlineStr"/>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標を下回る見込みであることによります。町別の総人口の置き方は住民基本台帳の実績趨勢によることとし、確定を要する事項として整理しています［要協議］。</t>
+          <t>介護給付適正化の計画策定に関する指針は、介護給付費財政調整交付金の算定に当たって主要3事業の取組状況を勘案することとしています。ケアプランの点検が実施されていないことは、交付金の評価にとどまらず調整交付金の交付割合を通じて保険料に及ぶ可能性があります。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この勘</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2061,22 +2065,22 @@
       <c r="A53" s="6" t="inlineStr"/>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2092,7 +2096,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
@@ -2102,7 +2106,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>注）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2118,7 +2122,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
@@ -2128,8 +2132,7 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2145,7 +2148,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
@@ -2155,8 +2158,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2172,17 +2174,17 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2198,7 +2200,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
@@ -2208,7 +2210,8 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2234,90 +2237,90 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F59" s="6" t="inlineStr"/>
+      <c r="G59" s="6" t="inlineStr"/>
+      <c r="H59" s="6" t="inlineStr"/>
+    </row>
+    <row r="60" ht="44" customHeight="1">
+      <c r="A60" s="6" t="inlineStr"/>
+      <c r="B60" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F60" s="6" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr"/>
+      <c r="H60" s="6" t="inlineStr"/>
+    </row>
+    <row r="61" ht="44" customHeight="1">
+      <c r="A61" s="6" t="inlineStr"/>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr"/>
+      <c r="H61" s="6" t="inlineStr"/>
+    </row>
+    <row r="62" ht="44" customHeight="1">
+      <c r="A62" s="6" t="inlineStr"/>
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr"/>
-      <c r="G59" s="6" t="inlineStr"/>
-      <c r="H59" s="6" t="inlineStr"/>
-    </row>
-    <row r="60" ht="44" customHeight="1">
-      <c r="A60" s="6" t="inlineStr"/>
-      <c r="B60" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C60" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F60" s="6" t="inlineStr"/>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="6" t="inlineStr"/>
-    </row>
-    <row r="61" ht="44" customHeight="1">
-      <c r="A61" s="6" t="inlineStr"/>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
-        </is>
-      </c>
-      <c r="F61" s="6" t="inlineStr"/>
-      <c r="G61" s="6" t="inlineStr"/>
-      <c r="H61" s="6" t="inlineStr"/>
-    </row>
-    <row r="62" ht="44" customHeight="1">
-      <c r="A62" s="6" t="inlineStr"/>
-      <c r="B62" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
       <c r="F62" s="6" t="inlineStr"/>
       <c r="G62" s="6" t="inlineStr"/>
       <c r="H62" s="6" t="inlineStr"/>
@@ -2331,7 +2334,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
@@ -2341,8 +2344,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2361,15 +2363,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2395,8 +2396,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2412,17 +2412,18 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2438,7 +2439,7 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
@@ -2448,7 +2449,8 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2464,17 +2466,18 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2490,7 +2493,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2500,7 +2503,8 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2516,7 +2520,7 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2526,7 +2530,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2545,14 +2549,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2578,7 +2582,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2597,14 +2601,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費です。Eの調整交付金見込額は第9期計画と同水準の交付割合によって</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2620,7 +2624,7 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2630,218 +2634,348 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
       <c r="G74" s="6" t="inlineStr"/>
       <c r="H74" s="6" t="inlineStr"/>
     </row>
-    <row r="76" ht="28" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は23種の表に118箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+    <row r="75" ht="44" customHeight="1">
+      <c r="A75" s="6" t="inlineStr"/>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr"/>
+      <c r="G75" s="6" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr"/>
+    </row>
+    <row r="76" ht="44" customHeight="1">
+      <c r="A76" s="6" t="inlineStr"/>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr"/>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr"/>
+    </row>
+    <row r="77" ht="44" customHeight="1">
+      <c r="A77" s="6" t="inlineStr"/>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr"/>
+      <c r="G77" s="6" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr"/>
+    </row>
+    <row r="78" ht="44" customHeight="1">
+      <c r="A78" s="6" t="inlineStr"/>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費です。Eの調整交付金見込額は第9期計画と同水準の交付割合によって</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79" ht="44" customHeight="1">
+      <c r="A79" s="6" t="inlineStr"/>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr"/>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr"/>
+    </row>
+    <row r="81" ht="28" customHeight="1">
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は24種の表に119箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="20" customHeight="1">
-      <c r="A78" s="3" t="inlineStr">
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="4" t="inlineStr"/>
-      <c r="B79" s="4" t="inlineStr">
+    <row r="84" ht="30" customHeight="1">
+      <c r="A84" s="4" t="inlineStr"/>
+      <c r="B84" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C79" s="4" t="inlineStr">
+      <c r="C84" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D79" s="4" t="inlineStr">
+      <c r="D84" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
+      <c r="E84" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F79" s="4" t="inlineStr">
+      <c r="F84" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G79" s="4" t="inlineStr">
+      <c r="G84" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H79" s="4" t="inlineStr">
+      <c r="H84" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="44" customHeight="1">
-      <c r="A80" s="6" t="inlineStr"/>
-      <c r="B80" s="6" t="inlineStr">
+    <row r="85" ht="44" customHeight="1">
+      <c r="A85" s="6" t="inlineStr"/>
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
-      <c r="D80" s="5" t="n">
+      <c r="D85" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E80" s="5" t="n">
+      <c r="E85" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F85" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G80" s="5" t="n">
+      <c r="G85" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H80" s="6" t="inlineStr">
+      <c r="H85" s="6" t="inlineStr">
         <is>
           <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="44" customHeight="1">
-      <c r="A81" s="6" t="inlineStr"/>
-      <c r="B81" s="6" t="inlineStr">
+    <row r="86" ht="44" customHeight="1">
+      <c r="A86" s="6" t="inlineStr"/>
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>第2節　計画の位置付け</t>
         </is>
       </c>
-      <c r="D81" s="5" t="n">
+      <c r="D86" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E81" s="5" t="n">
+      <c r="E86" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F86" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G81" s="5" t="n">
+      <c r="G86" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H81" s="6" t="inlineStr">
+      <c r="H86" s="6" t="inlineStr">
         <is>
           <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="44" customHeight="1">
-      <c r="A82" s="6" t="inlineStr"/>
-      <c r="B82" s="6" t="inlineStr">
+    <row r="87" ht="44" customHeight="1">
+      <c r="A87" s="6" t="inlineStr"/>
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>第4節　計画期間</t>
         </is>
       </c>
-      <c r="D82" s="5" t="n">
+      <c r="D87" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E82" s="5" t="n">
+      <c r="E87" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F82" s="5" t="n">
+      <c r="F87" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G82" s="5" t="n">
+      <c r="G87" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H82" s="6" t="inlineStr">
+      <c r="H87" s="6" t="inlineStr">
         <is>
           <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="44" customHeight="1">
-      <c r="A83" s="6" t="inlineStr"/>
-      <c r="B83" s="6" t="inlineStr">
+    <row r="88" ht="44" customHeight="1">
+      <c r="A88" s="6" t="inlineStr"/>
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D83" s="5" t="n">
+      <c r="D88" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E83" s="5" t="n">
+      <c r="E88" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F83" s="5" t="n">
+      <c r="F88" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G83" s="5" t="n">
+      <c r="G88" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H83" s="6" t="inlineStr">
+      <c r="H88" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="44" customHeight="1">
-      <c r="A84" s="6" t="inlineStr"/>
-      <c r="B84" s="6" t="inlineStr">
+    <row r="89" ht="44" customHeight="1">
+      <c r="A89" s="6" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D84" s="5" t="n">
+      <c r="D89" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E84" s="5" t="n">
+      <c r="E89" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F84" s="5" t="n">
+      <c r="F89" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G84" s="5" t="n">
+      <c r="G89" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H84" s="6" t="inlineStr">
+      <c r="H89" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="86" ht="42" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
+    <row r="91" ht="42" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は5節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -2852,13 +2986,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A86:H86"/>
+    <mergeCell ref="A91:H91"/>
+    <mergeCell ref="A83:H83"/>
+    <mergeCell ref="A81:H81"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A76:H76"/>
-    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4033,7 +4167,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第5節・第6節（未確定7箇所）</t>
+          <t>第2章第3節・第5節・第6節（未確定8箇所）</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -4153,7 +4287,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>第4章第3節・資料1（未確定7箇所）</t>
+          <t>第4章第3節・資料1（未確定8箇所）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4496,7 +4630,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議118・要確認39・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議119・要確認43・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4608,7 +4742,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>951段落146表36図／158箇所</t>
+          <t>973段落148表36図／163箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -4634,7 +4768,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>158＝158</t>
+          <t>163＝163</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -4660,7 +4794,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>158＝158</t>
+          <t>163＝163</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -4842,7 +4976,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>60／158箇所（38％）</t>
+          <t>61／163箇所（37％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -5081,7 +5215,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は158箇所ある（要協議118・要確認39・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は163箇所ある（要協議119・要確認43・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>173件</t>
+          <t>174件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>162件</t>
+          <t>163件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが92件（02シート）</t>
+          <t>このうち計画素案を止めているものが93件（02シート）</t>
         </is>
       </c>
     </row>
@@ -3019,7 +3019,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（173件）</t>
+          <t>確認事項の棚卸し（174件）</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3073,7 @@
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は162件</t>
+          <t>完了・了承済を除く未回答は163件</t>
         </is>
       </c>
     </row>
@@ -3126,11 +3126,11 @@
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>解決</t>
+          <t>未回答</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="6" t="inlineStr"/>
@@ -3141,7 +3141,7 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>解決</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
@@ -3271,10 +3271,10 @@
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>0</v>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
@@ -3646,7 +3646,7 @@
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（79件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（80件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（23件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>173件（未回答162件）</t>
+          <t>174件（未回答163件）</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>173件／一意173件</t>
+          <t>174件／一意174件</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -5238,7 +5238,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている162件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている163件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>163箇所</t>
+          <t>179箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議119・要確認43・要内訳1。本文44箇所・表24種119箇所（01シート）</t>
+          <t>要協議121・要確認57・要内訳1。本文53箇所・表25種126箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>174件</t>
+          <t>177件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>163件</t>
+          <t>166件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが93件（02シート）</t>
+          <t>このうち計画素案を止めているものが96件（02シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（973段落148表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1000段落151表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>163箇所のうち61箇所（37％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>179箇所のうち61箇所（34％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（973段落148表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計163箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1000段落151表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計179箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>70</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -900,13 +900,13 @@
       </c>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="8" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -921,15 +921,15 @@
       <c r="A8" s="6" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="5" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>14</v>
@@ -937,33 +937,33 @@
       <c r="G8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>調査の点検事項と出所の食い違い。確認事項No.8ほか</t>
-        </is>
-      </c>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="6" t="inlineStr"/>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>調査の点検事項と出所の食い違い。確認事項No.8ほか</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="6" t="inlineStr"/>
@@ -1026,13 +1026,13 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="n">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>1</v>
@@ -1148,59 +1148,55 @@
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>No.86（交付金の控除）ほか</t>
-        </is>
-      </c>
+      <c r="H18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E19" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" s="5" t="n">
         <v>7</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>No.4（代表KPIの代理指標）</t>
+          <t>No.86（交付金の控除）ほか</t>
         </is>
       </c>
     </row>
@@ -1208,55 +1204,59 @@
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="32" customHeight="1">
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>No.118〜No.121（地域ケア会議のKPI）・No.130（認知症基本法）</t>
+          <t>No.4（代表KPIの代理指標）</t>
         </is>
       </c>
     </row>
@@ -1264,29 +1264,29 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>No.112（地域支援事業の量）</t>
+          <t>No.118〜No.121（地域ケア会議のKPI）・No.130（認知症基本法）</t>
         </is>
       </c>
     </row>
@@ -1294,29 +1294,29 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E23" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F23" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>No.114（中長期推計の範囲）</t>
+          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
         </is>
       </c>
     </row>
@@ -1324,29 +1324,29 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>No.75（代表KPIの再整理案）</t>
+          <t>No.112（地域支援事業の量）</t>
         </is>
       </c>
     </row>
@@ -1354,29 +1354,29 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>確認事項B No.19（医療側の連携の実施状況）</t>
+          <t>No.114（中長期推計の範囲）</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
+          <t>No.75（代表KPIの再整理案）</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+          <t>確認事項B No.19（医療側の連携の実施状況）</t>
         </is>
       </c>
     </row>
@@ -1474,19 +1474,19 @@
       <c r="A29" s="6" t="inlineStr"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E29" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>1</v>
@@ -1494,18 +1494,22 @@
       <c r="G29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
@@ -1520,11 +1524,7 @@
       <c r="G30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>No.3（町別人口）</t>
-        </is>
-      </c>
+      <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="6" t="inlineStr"/>
@@ -1535,24 +1535,24 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>No.8（同）</t>
+          <t>No.3（町別人口）</t>
         </is>
       </c>
     </row>
@@ -1560,36 +1560,36 @@
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="F32" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
+          <t>No.8（同）</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（44件）</t>
+          <t>3　本文の未確定箇所（53件）</t>
         </is>
       </c>
     </row>
@@ -1753,22 +1753,23 @@
       <c r="A41" s="6" t="inlineStr"/>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D41" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。
+出典：厚生労</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -1794,7 +1795,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
@@ -1813,14 +1814,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1836,7 +1837,7 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -1846,7 +1847,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1872,7 +1873,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1888,7 +1889,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1898,7 +1899,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1914,17 +1915,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 高齢者の生活実態</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1940,17 +1941,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr"/>
@@ -1976,7 +1977,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -1987,22 +1988,22 @@
       <c r="A50" s="6" t="inlineStr"/>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2013,12 +2014,12 @@
       <c r="A51" s="6" t="inlineStr"/>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
@@ -2028,7 +2029,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2039,22 +2040,22 @@
       <c r="A52" s="6" t="inlineStr"/>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>介護給付適正化の計画策定に関する指針は、介護給付費財政調整交付金の算定に当たって主要3事業の取組状況を勘案することとしています。ケアプランの点検が実施されていないことは、交付金の評価にとどまらず調整交付金の交付割合を通じて保険料に及ぶ可能性があります。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この勘</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2070,7 +2071,7 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
@@ -2080,7 +2081,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2091,22 +2092,22 @@
       <c r="A54" s="6" t="inlineStr"/>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2117,22 +2118,22 @@
       <c r="A55" s="6" t="inlineStr"/>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2143,22 +2144,22 @@
       <c r="A56" s="6" t="inlineStr"/>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2169,22 +2170,22 @@
       <c r="A57" s="6" t="inlineStr"/>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2200,7 +2201,7 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
@@ -2210,8 +2211,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
@@ -2237,8 +2237,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2254,17 +2253,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2280,7 +2279,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
@@ -2290,7 +2289,7 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2306,153 +2305,154 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr"/>
+      <c r="G62" s="6" t="inlineStr"/>
+      <c r="H62" s="6" t="inlineStr"/>
+    </row>
+    <row r="63" ht="44" customHeight="1">
+      <c r="A63" s="6" t="inlineStr"/>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr"/>
+      <c r="G63" s="6" t="inlineStr"/>
+      <c r="H63" s="6" t="inlineStr"/>
+    </row>
+    <row r="64" ht="44" customHeight="1">
+      <c r="A64" s="6" t="inlineStr"/>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D64" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr"/>
+      <c r="G64" s="6" t="inlineStr"/>
+      <c r="H64" s="6" t="inlineStr"/>
+    </row>
+    <row r="65" ht="44" customHeight="1">
+      <c r="A65" s="6" t="inlineStr"/>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr"/>
+      <c r="G65" s="6" t="inlineStr"/>
+      <c r="H65" s="6" t="inlineStr"/>
+    </row>
+    <row r="66" ht="44" customHeight="1">
+      <c r="A66" s="6" t="inlineStr"/>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F66" s="6" t="inlineStr"/>
+      <c r="G66" s="6" t="inlineStr"/>
+      <c r="H66" s="6" t="inlineStr"/>
+    </row>
+    <row r="67" ht="44" customHeight="1">
+      <c r="A67" s="6" t="inlineStr"/>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr"/>
-      <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="6" t="inlineStr"/>
-    </row>
-    <row r="63" ht="44" customHeight="1">
-      <c r="A63" s="6" t="inlineStr"/>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr"/>
-      <c r="G63" s="6" t="inlineStr"/>
-      <c r="H63" s="6" t="inlineStr"/>
-    </row>
-    <row r="64" ht="44" customHeight="1">
-      <c r="A64" s="6" t="inlineStr"/>
-      <c r="B64" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
-        <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr"/>
-      <c r="G64" s="6" t="inlineStr"/>
-      <c r="H64" s="6" t="inlineStr"/>
-    </row>
-    <row r="65" ht="44" customHeight="1">
-      <c r="A65" s="6" t="inlineStr"/>
-      <c r="B65" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
-        <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr"/>
-      <c r="G65" s="6" t="inlineStr"/>
-      <c r="H65" s="6" t="inlineStr"/>
-    </row>
-    <row r="66" ht="44" customHeight="1">
-      <c r="A66" s="6" t="inlineStr"/>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F66" s="6" t="inlineStr"/>
-      <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="6" t="inlineStr"/>
-    </row>
-    <row r="67" ht="44" customHeight="1">
-      <c r="A67" s="6" t="inlineStr"/>
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
       <c r="F67" s="6" t="inlineStr"/>
       <c r="G67" s="6" t="inlineStr"/>
       <c r="H67" s="6" t="inlineStr"/>
@@ -2466,18 +2466,17 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2496,15 +2495,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2520,7 +2518,7 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2530,7 +2528,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2546,17 +2544,18 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2572,7 +2571,7 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
@@ -2582,7 +2581,8 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2598,17 +2598,18 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2624,7 +2625,7 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2634,7 +2635,8 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -2650,7 +2652,7 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2660,7 +2662,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2679,14 +2681,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr"/>
@@ -2712,7 +2714,7 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2731,14 +2733,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費です。Eの調整交付金見込額は第9期計画と同水準の交付割合によって</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2754,7 +2756,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2764,218 +2766,455 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化及び一定以上所得基準の見直しは、第10期の計画期間中に施行されるものです。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。施行の時期及び対象者数は［要確認］として残し、内容が示された時点で補います。</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
       <c r="G79" s="6" t="inlineStr"/>
       <c r="H79" s="6" t="inlineStr"/>
     </row>
-    <row r="81" ht="28" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は24種の表に119箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
-注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="3" t="inlineStr">
-        <is>
-          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="4" t="inlineStr"/>
-      <c r="B84" s="4" t="inlineStr">
-        <is>
-          <t>章</t>
-        </is>
-      </c>
-      <c r="C84" s="4" t="inlineStr">
-        <is>
-          <t>節</t>
-        </is>
-      </c>
-      <c r="D84" s="4" t="inlineStr">
-        <is>
-          <t>段落</t>
-        </is>
-      </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>うち注・出典</t>
-        </is>
-      </c>
-      <c r="F84" s="4" t="inlineStr">
-        <is>
-          <t>表</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>未確定</t>
-        </is>
-      </c>
-      <c r="H84" s="4" t="inlineStr">
-        <is>
-          <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
+    <row r="80" ht="44" customHeight="1">
+      <c r="A80" s="6" t="inlineStr"/>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr"/>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr"/>
+    </row>
+    <row r="81" ht="44" customHeight="1">
+      <c r="A81" s="6" t="inlineStr"/>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr"/>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr"/>
+    </row>
+    <row r="82" ht="44" customHeight="1">
+      <c r="A82" s="6" t="inlineStr"/>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr"/>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr"/>
+    </row>
+    <row r="83" ht="44" customHeight="1">
+      <c r="A83" s="6" t="inlineStr"/>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
+注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
+注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr"/>
+      <c r="G83" s="6" t="inlineStr"/>
+      <c r="H83" s="6" t="inlineStr"/>
+    </row>
+    <row r="84" ht="44" customHeight="1">
+      <c r="A84" s="6" t="inlineStr"/>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr"/>
+      <c r="G84" s="6" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr"/>
     </row>
     <row r="85" ht="44" customHeight="1">
       <c r="A85" s="6" t="inlineStr"/>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D85" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費です。Eの調整交付金見込額は第9期計画と同水準の交付割合によって</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr"/>
+      <c r="G85" s="6" t="inlineStr"/>
+      <c r="H85" s="6" t="inlineStr"/>
     </row>
     <row r="86" ht="44" customHeight="1">
       <c r="A86" s="6" t="inlineStr"/>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D86" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E86" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H86" s="6" t="inlineStr">
-        <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
-        </is>
-      </c>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr"/>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr"/>
     </row>
     <row r="87" ht="44" customHeight="1">
       <c r="A87" s="6" t="inlineStr"/>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H87" s="6" t="inlineStr">
-        <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
-        </is>
-      </c>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr"/>
+      <c r="G87" s="6" t="inlineStr"/>
+      <c r="H87" s="6" t="inlineStr"/>
     </row>
     <row r="88" ht="44" customHeight="1">
       <c r="A88" s="6" t="inlineStr"/>
       <c r="B88" s="6" t="inlineStr">
         <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr"/>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr"/>
+    </row>
+    <row r="90" ht="28" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は25種の表に126箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
+        <is>
+          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="4" t="inlineStr"/>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>章</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>節</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>段落</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>うち注・出典</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>本来入るべき内容と所在</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="44" customHeight="1">
+      <c r="A94" s="6" t="inlineStr"/>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>第1節　計画策定の趣旨</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>趣旨の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="44" customHeight="1">
+      <c r="A95" s="6" t="inlineStr"/>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H95" s="6" t="inlineStr">
+        <is>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="44" customHeight="1">
+      <c r="A96" s="6" t="inlineStr"/>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>第4節　計画期間</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="6" t="inlineStr">
+        <is>
+          <t>計画期間の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="44" customHeight="1">
+      <c r="A97" s="6" t="inlineStr"/>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D88" s="5" t="n">
+      <c r="D97" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E88" s="5" t="n">
+      <c r="E97" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F88" s="5" t="n">
+      <c r="F97" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G88" s="5" t="n">
+      <c r="G97" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H88" s="6" t="inlineStr">
+      <c r="H97" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="44" customHeight="1">
-      <c r="A89" s="6" t="inlineStr"/>
-      <c r="B89" s="6" t="inlineStr">
+    <row r="98" ht="44" customHeight="1">
+      <c r="A98" s="6" t="inlineStr"/>
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D89" s="5" t="n">
+      <c r="D98" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E89" s="5" t="n">
+      <c r="E98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F89" s="5" t="n">
+      <c r="F98" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G89" s="5" t="n">
+      <c r="G98" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="H98" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="91" ht="42" customHeight="1">
-      <c r="A91" s="7" t="inlineStr">
+    <row r="100" ht="42" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は5節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -2986,10 +3225,10 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A91:H91"/>
-    <mergeCell ref="A83:H83"/>
-    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A100:H100"/>
+    <mergeCell ref="A92:H92"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A90:H90"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A34:H34"/>
@@ -3019,7 +3258,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（174件）</t>
+          <t>確認事項の棚卸し（177件）</t>
         </is>
       </c>
     </row>
@@ -3073,7 +3312,7 @@
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は163件</t>
+          <t>完了・了承済を除く未回答は166件</t>
         </is>
       </c>
     </row>
@@ -3081,11 +3320,11 @@
       <c r="A7" s="6" t="inlineStr"/>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>了承済</t>
+          <t>未回答</t>
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
@@ -3096,7 +3335,7 @@
       <c r="A8" s="6" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>了承済</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
@@ -3111,11 +3350,11 @@
       <c r="A9" s="6" t="inlineStr"/>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" s="6" t="inlineStr"/>
       <c r="E9" s="6" t="inlineStr"/>
@@ -3126,7 +3365,7 @@
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>対応中</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
@@ -3294,10 +3533,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
@@ -3317,10 +3556,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>0</v>
@@ -3486,7 +3725,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
@@ -3501,7 +3740,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
@@ -3516,7 +3755,7 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="6" t="inlineStr"/>
@@ -3646,8 +3885,8 @@
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（80件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
-注2）確認先が「発注者・3町」のもの（23件）は、3町への照会の様式と時期の決定を先に要します。
+          <t>注1）期限が令和8年8月以前のもの（83件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+注2）確認先が「発注者・3町」のもの（24件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
       </c>
@@ -4630,7 +4869,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議119・要確認43・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議121・要確認57・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4742,7 +4981,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>973段落148表36図／163箇所</t>
+          <t>1000段落151表36図／179箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -4768,7 +5007,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>163＝163</t>
+          <t>179＝179</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -4794,7 +5033,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>163＝163</t>
+          <t>179＝179</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -4820,7 +5059,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>174件（未回答163件）</t>
+          <t>177件（未回答166件）</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -4846,7 +5085,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>174件／一意174件</t>
+          <t>177件／一意177件</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -4976,7 +5215,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>61／163箇所（37％）</t>
+          <t>61／179箇所（34％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -5215,7 +5454,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は163箇所ある（要協議119・要確認43・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は179箇所ある（要協議121・要確認57・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -5238,7 +5477,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている163件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている166件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>179箇所</t>
+          <t>182箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議121・要確認57・要内訳1。本文53箇所・表25種126箇所（01シート）</t>
+          <t>要協議121・要確認60・要内訳1。本文55箇所・表26種127箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1000段落151表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1001段落151表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>179箇所のうち61箇所（34％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>182箇所のうち61箇所（34％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H100"/>
+  <dimension ref="A1:H102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1000段落151表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計179箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1001段落151表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計182箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -948,13 +948,13 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
@@ -974,13 +974,13 @@
       </c>
       <c r="C10" s="6" t="inlineStr"/>
       <c r="D10" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0</v>
@@ -1026,13 +1026,13 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E12" s="10" t="n">
         <v>121</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>1</v>
@@ -1204,19 +1204,19 @@
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>3</v>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+          <t>No.4（代表KPIの代理指標）</t>
         </is>
       </c>
     </row>
@@ -1234,29 +1234,29 @@
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>No.4（代表KPIの代理指標）</t>
+          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
         </is>
       </c>
     </row>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No.114（中長期推計の範囲）</t>
+          <t>No.8（3調査の点検事項）</t>
         </is>
       </c>
     </row>
@@ -1384,29 +1384,29 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="F26" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>No.75（代表KPIの再整理案）</t>
+          <t>No.114（中長期推計の範囲）</t>
         </is>
       </c>
     </row>
@@ -1414,29 +1414,29 @@
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>確認事項B No.19（医療側の連携の実施状況）</t>
+          <t>No.75（代表KPIの再整理案）</t>
         </is>
       </c>
     </row>
@@ -1444,29 +1444,29 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F28" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>No.8（3調査の点検事項）</t>
+          <t>確認事項B No.19（医療側の連携の実施状況）</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（53件）</t>
+          <t>3　本文の未確定箇所（55件）</t>
         </is>
       </c>
     </row>
@@ -2048,14 +2048,14 @@
           <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2066,22 +2066,22 @@
       <c r="A53" s="6" t="inlineStr"/>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2092,12 +2092,12 @@
       <c r="A54" s="6" t="inlineStr"/>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2107,7 +2107,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2196,22 +2196,22 @@
       <c r="A58" s="6" t="inlineStr"/>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2222,22 +2222,22 @@
       <c r="A59" s="6" t="inlineStr"/>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2315,8 +2315,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2335,15 +2334,14 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2359,7 +2357,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
@@ -2369,8 +2367,8 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2386,7 +2384,7 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2396,7 +2394,8 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2422,7 +2421,8 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2441,70 +2441,70 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F67" s="6" t="inlineStr"/>
+      <c r="G67" s="6" t="inlineStr"/>
+      <c r="H67" s="6" t="inlineStr"/>
+    </row>
+    <row r="68" ht="44" customHeight="1">
+      <c r="A68" s="6" t="inlineStr"/>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr"/>
+      <c r="G68" s="6" t="inlineStr"/>
+      <c r="H68" s="6" t="inlineStr"/>
+    </row>
+    <row r="69" ht="44" customHeight="1">
+      <c r="A69" s="6" t="inlineStr"/>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F67" s="6" t="inlineStr"/>
-      <c r="G67" s="6" t="inlineStr"/>
-      <c r="H67" s="6" t="inlineStr"/>
-    </row>
-    <row r="68" ht="44" customHeight="1">
-      <c r="A68" s="6" t="inlineStr"/>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr"/>
-      <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="6" t="inlineStr"/>
-    </row>
-    <row r="69" ht="44" customHeight="1">
-      <c r="A69" s="6" t="inlineStr"/>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
-        <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
-        </is>
-      </c>
       <c r="F69" s="6" t="inlineStr"/>
       <c r="G69" s="6" t="inlineStr"/>
       <c r="H69" s="6" t="inlineStr"/>
@@ -2518,17 +2518,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2554,8 +2554,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2574,15 +2573,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2601,9 +2599,9 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -2628,15 +2626,15 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -2652,7 +2650,7 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2662,7 +2660,8 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2678,7 +2677,7 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2688,7 +2687,8 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr"/>
@@ -2704,17 +2704,17 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2733,14 +2733,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2759,14 +2759,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2785,14 +2785,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr"/>
@@ -2811,14 +2811,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr"/>
@@ -2837,14 +2837,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
@@ -2863,70 +2863,70 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr"/>
+      <c r="G83" s="6" t="inlineStr"/>
+      <c r="H83" s="6" t="inlineStr"/>
+    </row>
+    <row r="84" ht="44" customHeight="1">
+      <c r="A84" s="6" t="inlineStr"/>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr"/>
+      <c r="G84" s="6" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr"/>
+    </row>
+    <row r="85" ht="44" customHeight="1">
+      <c r="A85" s="6" t="inlineStr"/>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E85" s="6" t="inlineStr">
         <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr"/>
-      <c r="G83" s="6" t="inlineStr"/>
-      <c r="H83" s="6" t="inlineStr"/>
-    </row>
-    <row r="84" ht="44" customHeight="1">
-      <c r="A84" s="6" t="inlineStr"/>
-      <c r="B84" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C84" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="inlineStr"/>
-      <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="6" t="inlineStr"/>
-    </row>
-    <row r="85" ht="44" customHeight="1">
-      <c r="A85" s="6" t="inlineStr"/>
-      <c r="B85" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費です。Eの調整交付金見込額は第9期計画と同水準の交付割合によって</t>
-        </is>
-      </c>
       <c r="F85" s="6" t="inlineStr"/>
       <c r="G85" s="6" t="inlineStr"/>
       <c r="H85" s="6" t="inlineStr"/>
@@ -2950,8 +2950,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
-注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr"/>
@@ -2967,7 +2966,7 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2977,7 +2976,7 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費です。Eの調整交付金見込額は第9期計画と同水準の交付割合によって</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr"/>
@@ -2993,7 +2992,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -3003,123 +3002,116 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr"/>
       <c r="G88" s="6" t="inlineStr"/>
       <c r="H88" s="6" t="inlineStr"/>
     </row>
-    <row r="90" ht="28" customHeight="1">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は25種の表に126箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+    <row r="89" ht="44" customHeight="1">
+      <c r="A89" s="6" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr"/>
+      <c r="G89" s="6" t="inlineStr"/>
+      <c r="H89" s="6" t="inlineStr"/>
+    </row>
+    <row r="90" ht="44" customHeight="1">
+      <c r="A90" s="6" t="inlineStr"/>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr"/>
+    </row>
+    <row r="92" ht="28" customHeight="1">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は26種の表に127箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="4" t="inlineStr"/>
-      <c r="B93" s="4" t="inlineStr">
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="4" t="inlineStr"/>
+      <c r="B95" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C95" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D93" s="4" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E93" s="4" t="inlineStr">
+      <c r="E95" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F93" s="4" t="inlineStr">
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G93" s="4" t="inlineStr">
+      <c r="G95" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H93" s="4" t="inlineStr">
+      <c r="H95" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="44" customHeight="1">
-      <c r="A94" s="6" t="inlineStr"/>
-      <c r="B94" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C94" s="6" t="inlineStr">
-        <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E94" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="44" customHeight="1">
-      <c r="A95" s="6" t="inlineStr"/>
-      <c r="B95" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C95" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H95" s="6" t="inlineStr">
-        <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -3132,11 +3124,11 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
+          <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
       <c r="D96" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E96" s="5" t="n">
         <v>0</v>
@@ -3149,7 +3141,7 @@
       </c>
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
+          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -3162,24 +3154,24 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D97" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E97" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F97" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
@@ -3187,12 +3179,12 @@
       <c r="A98" s="6" t="inlineStr"/>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第1節 計画の基本理念</t>
+          <t>第4節　計画期間</t>
         </is>
       </c>
       <c r="D98" s="5" t="n">
@@ -3202,19 +3194,79 @@
         <v>0</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H98" s="6" t="inlineStr">
         <is>
+          <t>計画期間の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="44" customHeight="1">
+      <c r="A99" s="6" t="inlineStr"/>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>第5節　計画の策定体制</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E99" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H99" s="6" t="inlineStr">
+        <is>
+          <t>策定体制の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="44" customHeight="1">
+      <c r="A100" s="6" t="inlineStr"/>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>第4章　計画の基本理念及び基本目標</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>第1節 計画の基本理念</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="6" t="inlineStr">
+        <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="42" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
+    <row r="102" ht="42" customHeight="1">
+      <c r="A102" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は5節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -3224,12 +3276,12 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A94:H94"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A100:H100"/>
     <mergeCell ref="A92:H92"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A90:H90"/>
     <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A102:H102"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A34:H34"/>
   </mergeCells>
@@ -4406,7 +4458,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第5節・第6節（未確定8箇所）</t>
+          <t>第2章第3節・第5節・第6節（未確定9箇所）</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -4526,7 +4578,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>第4章第3節・資料1（未確定8箇所）</t>
+          <t>第4章第3節・資料1（未確定10箇所）</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4869,7 +4921,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議121・要確認57・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議121・要確認60・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -4981,7 +5033,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1000段落151表36図／179箇所</t>
+          <t>1001段落151表36図／182箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -5007,7 +5059,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>179＝179</t>
+          <t>182＝182</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -5033,7 +5085,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>179＝179</t>
+          <t>182＝182</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -5215,7 +5267,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>61／179箇所（34％）</t>
+          <t>61／182箇所（34％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -5454,7 +5506,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は179箇所ある（要協議121・要確認57・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は182箇所ある（要協議121・要確認60・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>182箇所</t>
+          <t>190箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議121・要確認60・要内訳1。本文55箇所・表26種127箇所（01シート）</t>
+          <t>要協議122・要確認67・要内訳1。本文63箇所・表26種127箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1001段落151表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1006段落151表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>182箇所のうち61箇所（34％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>190箇所のうち61箇所（32％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H102"/>
+  <dimension ref="A1:H111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1001段落151表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計182箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1006段落151表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計190箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>70</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -926,13 +926,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -948,13 +948,13 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
@@ -1000,13 +1000,13 @@
       </c>
       <c r="C11" s="6" t="inlineStr"/>
       <c r="D11" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E11" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
@@ -1026,13 +1026,13 @@
       </c>
       <c r="C12" s="9" t="inlineStr"/>
       <c r="D12" s="10" t="n">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G12" s="10" t="n">
         <v>1</v>
@@ -1118,29 +1118,29 @@
       <c r="A17" s="6" t="inlineStr"/>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" s="5" t="n">
         <v>9</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>5</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>No.91〜No.94（給付適正化）・確認事項A No.14（住宅改修等の点検）</t>
+          <t>No.86（交付金の控除）ほか</t>
         </is>
       </c>
     </row>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
@@ -1174,29 +1174,29 @@
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>No.86（交付金の控除）ほか</t>
+          <t>No.91〜No.94（給付適正化）・確認事項A No.14（住宅改修等の点検）</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
+          <t>No.75（代表KPIの再整理案）</t>
         </is>
       </c>
     </row>
@@ -1324,29 +1324,29 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>No.112（地域支援事業の量）</t>
+          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
         </is>
       </c>
     </row>
@@ -1354,29 +1354,29 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No.8（3調査の点検事項）</t>
+          <t>No.112（地域支援事業の量）</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>No.114（中長期推計の範囲）</t>
+          <t>No.8（3調査の点検事項）</t>
         </is>
       </c>
     </row>
@@ -1414,29 +1414,29 @@
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>No.75（代表KPIの再整理案）</t>
+          <t>No.114（中長期推計の範囲）</t>
         </is>
       </c>
     </row>
@@ -1586,64 +1586,68 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>3　本文の未確定箇所（55件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="inlineStr"/>
-      <c r="B35" s="4" t="inlineStr">
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="6" t="inlineStr"/>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t>No.1（認定率のシナリオ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>3　本文の未確定箇所（63件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
+      <c r="E36" s="4" t="inlineStr">
         <is>
           <t>本文（抜粋）</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr"/>
-      <c r="G35" s="4" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr"/>
-    </row>
-    <row r="36" ht="44" customHeight="1">
-      <c r="A36" s="6" t="inlineStr"/>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr"/>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr"/>
     </row>
     <row r="37" ht="44" customHeight="1">
       <c r="A37" s="6" t="inlineStr"/>
@@ -1654,17 +1658,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr"/>
@@ -1680,7 +1684,7 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -1690,7 +1694,7 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。</t>
+          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr"/>
@@ -1706,7 +1710,7 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -1716,7 +1720,7 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。</t>
         </is>
       </c>
       <c r="F39" s="6" t="inlineStr"/>
@@ -1732,7 +1736,7 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -1742,7 +1746,7 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
@@ -1768,8 +1772,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。
-出典：厚生労</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -1780,22 +1783,22 @@
       <c r="A42" s="6" t="inlineStr"/>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
@@ -1806,22 +1809,22 @@
       <c r="A43" s="6" t="inlineStr"/>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1840,14 +1843,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1863,17 +1866,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1889,7 +1892,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1899,7 +1902,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1915,17 +1918,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1941,17 +1944,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D48" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 サービス提供体制の状況</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr"/>
@@ -1967,7 +1970,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1977,7 +1980,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -1993,7 +1996,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -2003,7 +2006,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2014,22 +2017,23 @@
       <c r="A51" s="6" t="inlineStr"/>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
+注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2040,22 +2044,22 @@
       <c r="A52" s="6" t="inlineStr"/>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2066,22 +2070,22 @@
       <c r="A53" s="6" t="inlineStr"/>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2092,12 +2096,12 @@
       <c r="A54" s="6" t="inlineStr"/>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2107,7 +2111,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2118,12 +2122,12 @@
       <c r="A55" s="6" t="inlineStr"/>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2133,7 +2137,7 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2144,22 +2148,22 @@
       <c r="A56" s="6" t="inlineStr"/>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2170,12 +2174,12 @@
       <c r="A57" s="6" t="inlineStr"/>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2185,7 +2189,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2196,12 +2200,12 @@
       <c r="A58" s="6" t="inlineStr"/>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2211,7 +2215,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2222,22 +2226,22 @@
       <c r="A59" s="6" t="inlineStr"/>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2248,22 +2252,22 @@
       <c r="A60" s="6" t="inlineStr"/>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2274,22 +2278,22 @@
       <c r="A61" s="6" t="inlineStr"/>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2300,22 +2304,22 @@
       <c r="A62" s="6" t="inlineStr"/>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2326,22 +2330,22 @@
       <c r="A63" s="6" t="inlineStr"/>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2352,23 +2356,22 @@
       <c r="A64" s="6" t="inlineStr"/>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2379,12 +2382,12 @@
       <c r="A65" s="6" t="inlineStr"/>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2394,8 +2397,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2411,18 +2413,17 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2438,17 +2439,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2464,7 +2465,7 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
@@ -2474,7 +2475,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2490,207 +2491,206 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
+        <is>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr"/>
+      <c r="G69" s="6" t="inlineStr"/>
+      <c r="H69" s="6" t="inlineStr"/>
+    </row>
+    <row r="70" ht="44" customHeight="1">
+      <c r="A70" s="6" t="inlineStr"/>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr"/>
+      <c r="G70" s="6" t="inlineStr"/>
+      <c r="H70" s="6" t="inlineStr"/>
+    </row>
+    <row r="71" ht="44" customHeight="1">
+      <c r="A71" s="6" t="inlineStr"/>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr"/>
+      <c r="G71" s="6" t="inlineStr"/>
+      <c r="H71" s="6" t="inlineStr"/>
+    </row>
+    <row r="72" ht="44" customHeight="1">
+      <c r="A72" s="6" t="inlineStr"/>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr"/>
+      <c r="G72" s="6" t="inlineStr"/>
+      <c r="H72" s="6" t="inlineStr"/>
+    </row>
+    <row r="73" ht="44" customHeight="1">
+      <c r="A73" s="6" t="inlineStr"/>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D69" s="11" t="inlineStr">
+      <c r="D73" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr"/>
+      <c r="G73" s="6" t="inlineStr"/>
+      <c r="H73" s="6" t="inlineStr"/>
+    </row>
+    <row r="74" ht="44" customHeight="1">
+      <c r="A74" s="6" t="inlineStr"/>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr"/>
+      <c r="G74" s="6" t="inlineStr"/>
+      <c r="H74" s="6" t="inlineStr"/>
+    </row>
+    <row r="75" ht="44" customHeight="1">
+      <c r="A75" s="6" t="inlineStr"/>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr"/>
+      <c r="G75" s="6" t="inlineStr"/>
+      <c r="H75" s="6" t="inlineStr"/>
+    </row>
+    <row r="76" ht="44" customHeight="1">
+      <c r="A76" s="6" t="inlineStr"/>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr"/>
-      <c r="G69" s="6" t="inlineStr"/>
-      <c r="H69" s="6" t="inlineStr"/>
-    </row>
-    <row r="70" ht="44" customHeight="1">
-      <c r="A70" s="6" t="inlineStr"/>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr"/>
-      <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="6" t="inlineStr"/>
-    </row>
-    <row r="71" ht="44" customHeight="1">
-      <c r="A71" s="6" t="inlineStr"/>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
-        <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr"/>
-      <c r="G71" s="6" t="inlineStr"/>
-      <c r="H71" s="6" t="inlineStr"/>
-    </row>
-    <row r="72" ht="44" customHeight="1">
-      <c r="A72" s="6" t="inlineStr"/>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
-        <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr"/>
-      <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="6" t="inlineStr"/>
-    </row>
-    <row r="73" ht="44" customHeight="1">
-      <c r="A73" s="6" t="inlineStr"/>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr"/>
-      <c r="G73" s="6" t="inlineStr"/>
-      <c r="H73" s="6" t="inlineStr"/>
-    </row>
-    <row r="74" ht="44" customHeight="1">
-      <c r="A74" s="6" t="inlineStr"/>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr"/>
-      <c r="G74" s="6" t="inlineStr"/>
-      <c r="H74" s="6" t="inlineStr"/>
-    </row>
-    <row r="75" ht="44" customHeight="1">
-      <c r="A75" s="6" t="inlineStr"/>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr"/>
-      <c r="G75" s="6" t="inlineStr"/>
-      <c r="H75" s="6" t="inlineStr"/>
-    </row>
-    <row r="76" ht="44" customHeight="1">
-      <c r="A76" s="6" t="inlineStr"/>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
-        <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
-        </is>
-      </c>
       <c r="F76" s="6" t="inlineStr"/>
       <c r="G76" s="6" t="inlineStr"/>
       <c r="H76" s="6" t="inlineStr"/>
@@ -2704,17 +2704,17 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2730,17 +2730,17 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -2792,7 +2792,8 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr"/>
@@ -2808,17 +2809,18 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr"/>
@@ -2834,7 +2836,7 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2844,7 +2846,8 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
@@ -2860,17 +2863,18 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr"/>
@@ -2886,17 +2890,17 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr"/>
@@ -2922,351 +2926,586 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr"/>
+      <c r="G85" s="6" t="inlineStr"/>
+      <c r="H85" s="6" t="inlineStr"/>
+    </row>
+    <row r="86" ht="44" customHeight="1">
+      <c r="A86" s="6" t="inlineStr"/>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
+注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr"/>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87" ht="44" customHeight="1">
+      <c r="A87" s="6" t="inlineStr"/>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr"/>
+      <c r="G87" s="6" t="inlineStr"/>
+      <c r="H87" s="6" t="inlineStr"/>
+    </row>
+    <row r="88" ht="44" customHeight="1">
+      <c r="A88" s="6" t="inlineStr"/>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr"/>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr"/>
+    </row>
+    <row r="89" ht="44" customHeight="1">
+      <c r="A89" s="6" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr"/>
+      <c r="G89" s="6" t="inlineStr"/>
+      <c r="H89" s="6" t="inlineStr"/>
+    </row>
+    <row r="90" ht="44" customHeight="1">
+      <c r="A90" s="6" t="inlineStr"/>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr"/>
+    </row>
+    <row r="91" ht="44" customHeight="1">
+      <c r="A91" s="6" t="inlineStr"/>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr"/>
+      <c r="G91" s="6" t="inlineStr"/>
+      <c r="H91" s="6" t="inlineStr"/>
+    </row>
+    <row r="92" ht="44" customHeight="1">
+      <c r="A92" s="6" t="inlineStr"/>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr"/>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="inlineStr"/>
+    </row>
+    <row r="93" ht="44" customHeight="1">
+      <c r="A93" s="6" t="inlineStr"/>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr"/>
+      <c r="G93" s="6" t="inlineStr"/>
+      <c r="H93" s="6" t="inlineStr"/>
+    </row>
+    <row r="94" ht="44" customHeight="1">
+      <c r="A94" s="6" t="inlineStr"/>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr"/>
-      <c r="G85" s="6" t="inlineStr"/>
-      <c r="H85" s="6" t="inlineStr"/>
-    </row>
-    <row r="86" ht="44" customHeight="1">
-      <c r="A86" s="6" t="inlineStr"/>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="6" t="inlineStr"/>
+    </row>
+    <row r="95" ht="44" customHeight="1">
+      <c r="A95" s="6" t="inlineStr"/>
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr"/>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="6" t="inlineStr"/>
-    </row>
-    <row r="87" ht="44" customHeight="1">
-      <c r="A87" s="6" t="inlineStr"/>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費です。Eの調整交付金見込額は第9期計画と同水準の交付割合によって</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr"/>
-      <c r="G87" s="6" t="inlineStr"/>
-      <c r="H87" s="6" t="inlineStr"/>
-    </row>
-    <row r="88" ht="44" customHeight="1">
-      <c r="A88" s="6" t="inlineStr"/>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
-        <is>
-          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
-注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr"/>
-      <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr"/>
-    </row>
-    <row r="89" ht="44" customHeight="1">
-      <c r="A89" s="6" t="inlineStr"/>
-      <c r="B89" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C89" s="6" t="inlineStr">
-        <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
-        <is>
-          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="inlineStr"/>
-      <c r="G89" s="6" t="inlineStr"/>
-      <c r="H89" s="6" t="inlineStr"/>
-    </row>
-    <row r="90" ht="44" customHeight="1">
-      <c r="A90" s="6" t="inlineStr"/>
-      <c r="B90" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
-        <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr"/>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="6" t="inlineStr"/>
-    </row>
-    <row r="92" ht="28" customHeight="1">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は26種の表に127箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
-注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="4" t="inlineStr"/>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>章</t>
-        </is>
-      </c>
-      <c r="C95" s="4" t="inlineStr">
-        <is>
-          <t>節</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>段落</t>
-        </is>
-      </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>うち注・出典</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>表</t>
-        </is>
-      </c>
-      <c r="G95" s="4" t="inlineStr">
-        <is>
-          <t>未確定</t>
-        </is>
-      </c>
-      <c r="H95" s="4" t="inlineStr">
-        <is>
-          <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
+      <c r="F95" s="6" t="inlineStr"/>
+      <c r="G95" s="6" t="inlineStr"/>
+      <c r="H95" s="6" t="inlineStr"/>
     </row>
     <row r="96" ht="44" customHeight="1">
       <c r="A96" s="6" t="inlineStr"/>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D96" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H96" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費です。Eの調整交付金見込額は第9期計画と同水準の交付割合によって</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr"/>
+      <c r="G96" s="6" t="inlineStr"/>
+      <c r="H96" s="6" t="inlineStr"/>
     </row>
     <row r="97" ht="44" customHeight="1">
       <c r="A97" s="6" t="inlineStr"/>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D97" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E97" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H97" s="6" t="inlineStr">
-        <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
-        </is>
-      </c>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr"/>
+      <c r="G97" s="6" t="inlineStr"/>
+      <c r="H97" s="6" t="inlineStr"/>
     </row>
     <row r="98" ht="44" customHeight="1">
       <c r="A98" s="6" t="inlineStr"/>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
-        </is>
-      </c>
-      <c r="D98" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E98" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="6" t="inlineStr">
-        <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
-        </is>
-      </c>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr"/>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="6" t="inlineStr"/>
     </row>
     <row r="99" ht="44" customHeight="1">
       <c r="A99" s="6" t="inlineStr"/>
       <c r="B99" s="6" t="inlineStr">
         <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr"/>
+      <c r="G99" s="6" t="inlineStr"/>
+      <c r="H99" s="6" t="inlineStr"/>
+    </row>
+    <row r="101" ht="28" customHeight="1">
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は26種の表に127箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="4" t="inlineStr"/>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>章</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>節</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>段落</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>うち注・出典</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>本来入るべき内容と所在</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="44" customHeight="1">
+      <c r="A105" s="6" t="inlineStr"/>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>第1節　計画策定の趣旨</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="6" t="inlineStr">
+        <is>
+          <t>趣旨の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="44" customHeight="1">
+      <c r="A106" s="6" t="inlineStr"/>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H106" s="6" t="inlineStr">
+        <is>
+          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="44" customHeight="1">
+      <c r="A107" s="6" t="inlineStr"/>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>第4節　計画期間</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="6" t="inlineStr">
+        <is>
+          <t>計画期間の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="44" customHeight="1">
+      <c r="A108" s="6" t="inlineStr"/>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D99" s="5" t="n">
+      <c r="D108" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E99" s="5" t="n">
+      <c r="E108" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F99" s="5" t="n">
+      <c r="F108" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G99" s="5" t="n">
+      <c r="G108" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H99" s="6" t="inlineStr">
+      <c r="H108" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="44" customHeight="1">
-      <c r="A100" s="6" t="inlineStr"/>
-      <c r="B100" s="6" t="inlineStr">
+    <row r="109" ht="44" customHeight="1">
+      <c r="A109" s="6" t="inlineStr"/>
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D100" s="5" t="n">
+      <c r="D109" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E100" s="5" t="n">
+      <c r="E109" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F100" s="5" t="n">
+      <c r="F109" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G100" s="5" t="n">
+      <c r="G109" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H100" s="6" t="inlineStr">
+      <c r="H109" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="42" customHeight="1">
-      <c r="A102" s="7" t="inlineStr">
+    <row r="111" ht="42" customHeight="1">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は5節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -3276,14 +3515,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A94:H94"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A92:H92"/>
+    <mergeCell ref="A101:H101"/>
+    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A103:H103"/>
     <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A102:H102"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A111:H111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4458,7 +4697,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第5節・第6節（未確定9箇所）</t>
+          <t>第2章第3節・第5節・第6節（未確定10箇所）</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -4921,7 +5160,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議121・要確認60・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議122・要確認67・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -5033,7 +5272,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1001段落151表36図／182箇所</t>
+          <t>1006段落151表36図／190箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -5059,7 +5298,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>182＝182</t>
+          <t>190＝190</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -5085,7 +5324,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>182＝182</t>
+          <t>190＝190</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -5267,7 +5506,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>61／182箇所（34％）</t>
+          <t>61／190箇所（32％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -5506,7 +5745,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は182箇所ある（要協議121・要確認60・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は190箇所ある（要協議122・要確認67・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>190箇所</t>
+          <t>221箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議122・要確認67・要内訳1。本文63箇所・表26種127箇所（01シート）</t>
+          <t>要協議134・要確認85・要内訳2。本文88箇所・表28種133箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1006段落151表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1019段落152表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>190箇所のうち61箇所（32％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>221箇所のうち61箇所（28％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H111"/>
+  <dimension ref="A1:H139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1006段落151表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計190箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1019段落152表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計221箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -900,13 +900,13 @@
       </c>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="8" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -926,13 +926,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -948,13 +948,13 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
@@ -969,25 +969,25 @@
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr"/>
       <c r="D10" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>代表KPIの定義変更と目標の方向。確認事項No.4ほか</t>
+          <t>第9期評価の表現と役割分担</t>
         </is>
       </c>
     </row>
@@ -995,122 +995,114 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr"/>
       <c r="D11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E11" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="F11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>第9期評価の表現と役割分担</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="9" t="inlineStr"/>
-      <c r="B12" s="9" t="inlineStr">
+          <t>代表KPIの定義変更と目標の方向。確認事項No.4ほか</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>資料7 図表番号一覧</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr"/>
+      <c r="D12" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr"/>
-      <c r="D12" s="10" t="n">
-        <v>190</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>122</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>67</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="9" t="inlineStr"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr"/>
+      <c r="D13" s="10" t="n">
+        <v>221</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>134</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="9" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>2　節別（3箇所以上）</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="4" t="inlineStr"/>
-      <c r="B15" s="4" t="inlineStr">
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="4" t="inlineStr"/>
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>計</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>要内訳</t>
         </is>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>主に止めている確認事項</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="6" t="inlineStr"/>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n">
-        <v>61</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>55</v>
-      </c>
-      <c r="F16" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>No.88（必要利用定員総数）・No.113（混合型特定施設）・No.141（区域を越えた施設利用）</t>
         </is>
       </c>
     </row>
@@ -1123,24 +1115,24 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>15</v>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>61</v>
       </c>
       <c r="E17" s="5" t="n">
+        <v>55</v>
+      </c>
+      <c r="F17" s="5" t="n">
         <v>6</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>9</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>No.86（交付金の控除）ほか</t>
+          <t>No.88（必要利用定員総数）・No.113（混合型特定施設）・No.141（区域を越えた施設利用）</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1140,19 @@
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="F18" s="5" t="n">
         <v>12</v>
@@ -1168,65 +1160,65 @@
       <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>No.86（交付金の控除）ほか</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>No.91〜No.94（給付適正化）・確認事項A No.14（住宅改修等の点検）</t>
-        </is>
-      </c>
+      <c r="H19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>No.4（代表KPIの代理指標）</t>
+          <t>No.91〜No.94（給付適正化）・確認事項A No.14（住宅改修等の点検）</t>
         </is>
       </c>
     </row>
@@ -1239,24 +1231,24 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+          <t>No.118〜No.121（地域ケア会議のKPI）・No.130（認知症基本法）</t>
         </is>
       </c>
     </row>
@@ -1264,29 +1256,29 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>No.118〜No.121（地域ケア会議のKPI）・No.130（認知症基本法）</t>
+          <t>No.4（代表KPIの代理指標）</t>
         </is>
       </c>
     </row>
@@ -1294,29 +1286,29 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E23" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="E23" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="F23" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>No.75（代表KPIの再整理案）</t>
+          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
         </is>
       </c>
     </row>
@@ -1329,14 +1321,14 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>1</v>
@@ -1346,7 +1338,7 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
+          <t>確認事項B No.19（医療側の連携の実施状況）</t>
         </is>
       </c>
     </row>
@@ -1354,29 +1346,29 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No.112（地域支援事業の量）</t>
+          <t>No.75（代表KPIの再整理案）</t>
         </is>
       </c>
     </row>
@@ -1393,13 +1385,13 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0</v>
@@ -1414,29 +1406,29 @@
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F27" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>No.114（中長期推計の範囲）</t>
+          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
         </is>
       </c>
     </row>
@@ -1444,29 +1436,29 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>確認事項B No.19（医療側の連携の実施状況）</t>
+          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
         </is>
       </c>
     </row>
@@ -1479,24 +1471,24 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E29" s="5" t="n">
         <v>4</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>3</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
+          <t>No.112（地域支援事業の量）</t>
         </is>
       </c>
     </row>
@@ -1504,27 +1496,31 @@
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>No.114（中長期推計の範囲）</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="6" t="inlineStr"/>
@@ -1539,13 +1535,13 @@
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
@@ -1560,31 +1556,27 @@
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="6" t="inlineStr">
-        <is>
-          <t>No.8（同）</t>
-        </is>
-      </c>
+      <c r="H32" s="6" t="inlineStr"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="6" t="inlineStr"/>
@@ -1599,13 +1591,13 @@
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0</v>
@@ -1616,116 +1608,120 @@
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>3　本文の未確定箇所（63件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="4" t="inlineStr">
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="6" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>第5節　計画の策定体制</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="6" t="inlineStr"/>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>第2章　高齢者及び介護保険の状況</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>No.8（同）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="6" t="inlineStr"/>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>資料7 図表番号一覧</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>（節の前）</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>3　本文の未確定箇所（88件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D39" s="4" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
+      <c r="E39" s="4" t="inlineStr">
         <is>
           <t>本文（抜粋）</t>
         </is>
       </c>
-      <c r="F36" s="4" t="inlineStr"/>
-      <c r="G36" s="4" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr"/>
-    </row>
-    <row r="37" ht="44" customHeight="1">
-      <c r="A37" s="6" t="inlineStr"/>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr"/>
-      <c r="G37" s="6" t="inlineStr"/>
-      <c r="H37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38" ht="44" customHeight="1">
-      <c r="A38" s="6" t="inlineStr"/>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>第5節　計画の策定体制</t>
-        </is>
-      </c>
-      <c r="D38" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
-        <is>
-          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
-        </is>
-      </c>
-      <c r="F38" s="6" t="inlineStr"/>
-      <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39" ht="44" customHeight="1">
-      <c r="A39" s="6" t="inlineStr"/>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>第7節　日常生活圏域の設定</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
-        <is>
-          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr"/>
-      <c r="G39" s="6" t="inlineStr"/>
-      <c r="H39" s="6" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
     </row>
     <row r="40" ht="44" customHeight="1">
       <c r="A40" s="6" t="inlineStr"/>
@@ -1736,17 +1732,17 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr"/>
@@ -1762,7 +1758,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1772,7 +1768,7 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
+          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr"/>
@@ -1788,7 +1784,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第6節　計画の進行管理・推進体制</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1798,7 +1794,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
+          <t>注）北海道の高齢者保健福祉計画が定める評価指標のうち「取り組んでいる市町村数」を単位とするものは、1保険者である当広域連合にそのまま適用することができません。読替えの方法は第8節に掲げます。北海道から広域連合に対する読替えの考え方は示されていないため、本計画は当広域連合の整理によっており、考え方が示された場合はこれに合わせて改めます［要確認］。</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
@@ -1814,7 +1810,7 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -1824,7 +1820,8 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
+注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1835,22 +1832,23 @@
       <c r="A44" s="6" t="inlineStr"/>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第7節　日常生活圏域の設定</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
+注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1861,22 +1859,22 @@
       <c r="A45" s="6" t="inlineStr"/>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D45" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第8節　関係計画等との関係</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1887,12 +1885,12 @@
       <c r="A46" s="6" t="inlineStr"/>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1902,7 +1900,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1913,22 +1911,22 @@
       <c r="A47" s="6" t="inlineStr"/>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
-        </is>
-      </c>
-      <c r="D47" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
+          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1939,12 +1937,12 @@
       <c r="A48" s="6" t="inlineStr"/>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1954,7 +1952,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr"/>
@@ -1965,12 +1963,12 @@
       <c r="A49" s="6" t="inlineStr"/>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1980,7 +1978,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -1991,22 +1989,22 @@
       <c r="A50" s="6" t="inlineStr"/>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2022,18 +2020,17 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
-注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2049,17 +2046,17 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2075,17 +2072,17 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2101,7 +2098,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2111,7 +2108,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2122,22 +2119,22 @@
       <c r="A55" s="6" t="inlineStr"/>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
+          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2148,22 +2145,22 @@
       <c r="A56" s="6" t="inlineStr"/>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 サービス提供体制の状況</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2174,12 +2171,12 @@
       <c r="A57" s="6" t="inlineStr"/>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2189,7 +2186,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2200,12 +2197,12 @@
       <c r="A58" s="6" t="inlineStr"/>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
@@ -2215,7 +2212,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
+          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2226,22 +2223,22 @@
       <c r="A59" s="6" t="inlineStr"/>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 高齢者の生活実態</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2252,12 +2249,12 @@
       <c r="A60" s="6" t="inlineStr"/>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D60" s="6" t="inlineStr">
@@ -2267,7 +2264,8 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
+          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
+注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2278,12 +2276,12 @@
       <c r="A61" s="6" t="inlineStr"/>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2293,7 +2291,8 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
+注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2304,22 +2303,22 @@
       <c r="A62" s="6" t="inlineStr"/>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2330,12 +2329,12 @@
       <c r="A63" s="6" t="inlineStr"/>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2345,7 +2344,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2356,12 +2355,12 @@
       <c r="A64" s="6" t="inlineStr"/>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2371,7 +2370,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2382,12 +2381,12 @@
       <c r="A65" s="6" t="inlineStr"/>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2397,7 +2396,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2408,12 +2407,12 @@
       <c r="A66" s="6" t="inlineStr"/>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2423,7 +2422,8 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
+          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
+注）分母は地域包括ケア「見え</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2434,22 +2434,22 @@
       <c r="A67" s="6" t="inlineStr"/>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 地域支援事業の実績</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2460,22 +2460,22 @@
       <c r="A68" s="6" t="inlineStr"/>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 地域支援事業の実績</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2486,12 +2486,12 @@
       <c r="A69" s="6" t="inlineStr"/>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2512,22 +2512,22 @@
       <c r="A70" s="6" t="inlineStr"/>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2538,23 +2538,22 @@
       <c r="A71" s="6" t="inlineStr"/>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2565,12 +2564,12 @@
       <c r="A72" s="6" t="inlineStr"/>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2580,8 +2579,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2592,12 +2590,12 @@
       <c r="A73" s="6" t="inlineStr"/>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
@@ -2607,8 +2605,7 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2619,12 +2616,12 @@
       <c r="A74" s="6" t="inlineStr"/>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2634,7 +2631,7 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -2645,12 +2642,12 @@
       <c r="A75" s="6" t="inlineStr"/>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
@@ -2660,7 +2657,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2671,841 +2668,1576 @@
       <c r="A76" s="6" t="inlineStr"/>
       <c r="B76" s="6" t="inlineStr">
         <is>
+          <t>第5章　施策の展開</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr"/>
+      <c r="G76" s="6" t="inlineStr"/>
+      <c r="H76" s="6" t="inlineStr"/>
+    </row>
+    <row r="77" ht="44" customHeight="1">
+      <c r="A77" s="6" t="inlineStr"/>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>第5章　施策の展開</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr"/>
+      <c r="G77" s="6" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr"/>
+    </row>
+    <row r="78" ht="44" customHeight="1">
+      <c r="A78" s="6" t="inlineStr"/>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>第5章　施策の展開</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr"/>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr"/>
+    </row>
+    <row r="79" ht="44" customHeight="1">
+      <c r="A79" s="6" t="inlineStr"/>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>第5章　施策の展開</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr"/>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr"/>
+    </row>
+    <row r="80" ht="44" customHeight="1">
+      <c r="A80" s="6" t="inlineStr"/>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>第5章　施策の展開</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr"/>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr"/>
+    </row>
+    <row r="81" ht="44" customHeight="1">
+      <c r="A81" s="6" t="inlineStr"/>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>第5章　施策の展開</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr"/>
+      <c r="G81" s="6" t="inlineStr"/>
+      <c r="H81" s="6" t="inlineStr"/>
+    </row>
+    <row r="82" ht="44" customHeight="1">
+      <c r="A82" s="6" t="inlineStr"/>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>第5章　施策の展開</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr"/>
+      <c r="G82" s="6" t="inlineStr"/>
+      <c r="H82" s="6" t="inlineStr"/>
+    </row>
+    <row r="83" ht="44" customHeight="1">
+      <c r="A83" s="6" t="inlineStr"/>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>第5章　施策の展開</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr"/>
+      <c r="G83" s="6" t="inlineStr"/>
+      <c r="H83" s="6" t="inlineStr"/>
+    </row>
+    <row r="84" ht="44" customHeight="1">
+      <c r="A84" s="6" t="inlineStr"/>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>第5章　施策の展開</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
+        <is>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr"/>
+      <c r="G84" s="6" t="inlineStr"/>
+      <c r="H84" s="6" t="inlineStr"/>
+    </row>
+    <row r="85" ht="44" customHeight="1">
+      <c r="A85" s="6" t="inlineStr"/>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>第5章　施策の展開</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr"/>
+      <c r="G85" s="6" t="inlineStr"/>
+      <c r="H85" s="6" t="inlineStr"/>
+    </row>
+    <row r="86" ht="44" customHeight="1">
+      <c r="A86" s="6" t="inlineStr"/>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>第5章　施策の展開</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr"/>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr"/>
+    </row>
+    <row r="87" ht="44" customHeight="1">
+      <c r="A87" s="6" t="inlineStr"/>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr"/>
+      <c r="G87" s="6" t="inlineStr"/>
+      <c r="H87" s="6" t="inlineStr"/>
+    </row>
+    <row r="88" ht="44" customHeight="1">
+      <c r="A88" s="6" t="inlineStr"/>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr"/>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr"/>
+    </row>
+    <row r="89" ht="44" customHeight="1">
+      <c r="A89" s="6" t="inlineStr"/>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr"/>
+      <c r="G89" s="6" t="inlineStr"/>
+      <c r="H89" s="6" t="inlineStr"/>
+    </row>
+    <row r="90" ht="44" customHeight="1">
+      <c r="A90" s="6" t="inlineStr"/>
+      <c r="B90" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr"/>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr"/>
+    </row>
+    <row r="91" ht="44" customHeight="1">
+      <c r="A91" s="6" t="inlineStr"/>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+        </is>
+      </c>
+      <c r="F91" s="6" t="inlineStr"/>
+      <c r="G91" s="6" t="inlineStr"/>
+      <c r="H91" s="6" t="inlineStr"/>
+    </row>
+    <row r="92" ht="44" customHeight="1">
+      <c r="A92" s="6" t="inlineStr"/>
+      <c r="B92" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="inlineStr"/>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="inlineStr"/>
+    </row>
+    <row r="93" ht="44" customHeight="1">
+      <c r="A93" s="6" t="inlineStr"/>
+      <c r="B93" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F93" s="6" t="inlineStr"/>
+      <c r="G93" s="6" t="inlineStr"/>
+      <c r="H93" s="6" t="inlineStr"/>
+    </row>
+    <row r="94" ht="44" customHeight="1">
+      <c r="A94" s="6" t="inlineStr"/>
+      <c r="B94" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F94" s="6" t="inlineStr"/>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="6" t="inlineStr"/>
+    </row>
+    <row r="95" ht="44" customHeight="1">
+      <c r="A95" s="6" t="inlineStr"/>
+      <c r="B95" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr"/>
+      <c r="G95" s="6" t="inlineStr"/>
+      <c r="H95" s="6" t="inlineStr"/>
+    </row>
+    <row r="96" ht="44" customHeight="1">
+      <c r="A96" s="6" t="inlineStr"/>
+      <c r="B96" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr"/>
+      <c r="G96" s="6" t="inlineStr"/>
+      <c r="H96" s="6" t="inlineStr"/>
+    </row>
+    <row r="97" ht="44" customHeight="1">
+      <c r="A97" s="6" t="inlineStr"/>
+      <c r="B97" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D76" s="11" t="inlineStr">
+      <c r="D97" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E97" s="6" t="inlineStr">
+        <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr"/>
+      <c r="G97" s="6" t="inlineStr"/>
+      <c r="H97" s="6" t="inlineStr"/>
+    </row>
+    <row r="98" ht="44" customHeight="1">
+      <c r="A98" s="6" t="inlineStr"/>
+      <c r="B98" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D98" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr"/>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="6" t="inlineStr"/>
+    </row>
+    <row r="99" ht="44" customHeight="1">
+      <c r="A99" s="6" t="inlineStr"/>
+      <c r="B99" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr"/>
+      <c r="G99" s="6" t="inlineStr"/>
+      <c r="H99" s="6" t="inlineStr"/>
+    </row>
+    <row r="100" ht="44" customHeight="1">
+      <c r="A100" s="6" t="inlineStr"/>
+      <c r="B100" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr"/>
-      <c r="G76" s="6" t="inlineStr"/>
-      <c r="H76" s="6" t="inlineStr"/>
-    </row>
-    <row r="77" ht="44" customHeight="1">
-      <c r="A77" s="6" t="inlineStr"/>
-      <c r="B77" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr"/>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="6" t="inlineStr"/>
+    </row>
+    <row r="101" ht="44" customHeight="1">
+      <c r="A101" s="6" t="inlineStr"/>
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D77" s="11" t="inlineStr">
+      <c r="D101" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr"/>
-      <c r="G77" s="6" t="inlineStr"/>
-      <c r="H77" s="6" t="inlineStr"/>
-    </row>
-    <row r="78" ht="44" customHeight="1">
-      <c r="A78" s="6" t="inlineStr"/>
-      <c r="B78" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr"/>
+      <c r="G101" s="6" t="inlineStr"/>
+      <c r="H101" s="6" t="inlineStr"/>
+    </row>
+    <row r="102" ht="44" customHeight="1">
+      <c r="A102" s="6" t="inlineStr"/>
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D78" s="11" t="inlineStr">
+      <c r="D102" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E102" s="6" t="inlineStr">
         <is>
           <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr"/>
-      <c r="G78" s="6" t="inlineStr"/>
-      <c r="H78" s="6" t="inlineStr"/>
-    </row>
-    <row r="79" ht="44" customHeight="1">
-      <c r="A79" s="6" t="inlineStr"/>
-      <c r="B79" s="6" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr"/>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="6" t="inlineStr"/>
+    </row>
+    <row r="103" ht="44" customHeight="1">
+      <c r="A103" s="6" t="inlineStr"/>
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
+      <c r="D103" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr"/>
-      <c r="G79" s="6" t="inlineStr"/>
-      <c r="H79" s="6" t="inlineStr"/>
-    </row>
-    <row r="80" ht="44" customHeight="1">
-      <c r="A80" s="6" t="inlineStr"/>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr"/>
+      <c r="G103" s="6" t="inlineStr"/>
+      <c r="H103" s="6" t="inlineStr"/>
+    </row>
+    <row r="104" ht="44" customHeight="1">
+      <c r="A104" s="6" t="inlineStr"/>
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D80" s="11" t="inlineStr">
+      <c r="D104" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="E104" s="6" t="inlineStr">
         <is>
           <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
 注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr"/>
-      <c r="G80" s="6" t="inlineStr"/>
-      <c r="H80" s="6" t="inlineStr"/>
-    </row>
-    <row r="81" ht="44" customHeight="1">
-      <c r="A81" s="6" t="inlineStr"/>
-      <c r="B81" s="6" t="inlineStr">
+      <c r="F104" s="6" t="inlineStr"/>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="6" t="inlineStr"/>
+    </row>
+    <row r="105" ht="44" customHeight="1">
+      <c r="A105" s="6" t="inlineStr"/>
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D81" s="11" t="inlineStr">
+      <c r="D105" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
 注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr"/>
-      <c r="G81" s="6" t="inlineStr"/>
-      <c r="H81" s="6" t="inlineStr"/>
-    </row>
-    <row r="82" ht="44" customHeight="1">
-      <c r="A82" s="6" t="inlineStr"/>
-      <c r="B82" s="6" t="inlineStr">
+      <c r="F105" s="6" t="inlineStr"/>
+      <c r="G105" s="6" t="inlineStr"/>
+      <c r="H105" s="6" t="inlineStr"/>
+    </row>
+    <row r="106" ht="44" customHeight="1">
+      <c r="A106" s="6" t="inlineStr"/>
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C106" s="6" t="inlineStr">
         <is>
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D82" s="6" t="inlineStr">
+      <c r="D106" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="E106" s="6" t="inlineStr">
         <is>
           <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
 注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr"/>
-      <c r="G82" s="6" t="inlineStr"/>
-      <c r="H82" s="6" t="inlineStr"/>
-    </row>
-    <row r="83" ht="44" customHeight="1">
-      <c r="A83" s="6" t="inlineStr"/>
-      <c r="B83" s="6" t="inlineStr">
+      <c r="F106" s="6" t="inlineStr"/>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="6" t="inlineStr"/>
+    </row>
+    <row r="107" ht="44" customHeight="1">
+      <c r="A107" s="6" t="inlineStr"/>
+      <c r="B107" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C107" s="6" t="inlineStr">
         <is>
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D83" s="6" t="inlineStr">
+      <c r="D107" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="E107" s="6" t="inlineStr">
         <is>
           <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
 注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr"/>
-      <c r="G83" s="6" t="inlineStr"/>
-      <c r="H83" s="6" t="inlineStr"/>
-    </row>
-    <row r="84" ht="44" customHeight="1">
-      <c r="A84" s="6" t="inlineStr"/>
-      <c r="B84" s="6" t="inlineStr">
+      <c r="F107" s="6" t="inlineStr"/>
+      <c r="G107" s="6" t="inlineStr"/>
+      <c r="H107" s="6" t="inlineStr"/>
+    </row>
+    <row r="108" ht="44" customHeight="1">
+      <c r="A108" s="6" t="inlineStr"/>
+      <c r="B108" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C108" s="6" t="inlineStr">
         <is>
           <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D108" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E108" s="6" t="inlineStr">
         <is>
           <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr"/>
-      <c r="G84" s="6" t="inlineStr"/>
-      <c r="H84" s="6" t="inlineStr"/>
-    </row>
-    <row r="85" ht="44" customHeight="1">
-      <c r="A85" s="6" t="inlineStr"/>
-      <c r="B85" s="6" t="inlineStr">
+      <c r="F108" s="6" t="inlineStr"/>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr"/>
+    </row>
+    <row r="109" ht="44" customHeight="1">
+      <c r="A109" s="6" t="inlineStr"/>
+      <c r="B109" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C109" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D85" s="6" t="inlineStr">
+      <c r="D109" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="E109" s="6" t="inlineStr">
         <is>
           <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr"/>
-      <c r="G85" s="6" t="inlineStr"/>
-      <c r="H85" s="6" t="inlineStr"/>
-    </row>
-    <row r="86" ht="44" customHeight="1">
-      <c r="A86" s="6" t="inlineStr"/>
-      <c r="B86" s="6" t="inlineStr">
+      <c r="F109" s="6" t="inlineStr"/>
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr"/>
+    </row>
+    <row r="110" ht="44" customHeight="1">
+      <c r="A110" s="6" t="inlineStr"/>
+      <c r="B110" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C110" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
+      <c r="D110" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E110" s="6" t="inlineStr">
         <is>
           <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
 注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr"/>
-      <c r="G86" s="6" t="inlineStr"/>
-      <c r="H86" s="6" t="inlineStr"/>
-    </row>
-    <row r="87" ht="44" customHeight="1">
-      <c r="A87" s="6" t="inlineStr"/>
-      <c r="B87" s="6" t="inlineStr">
+      <c r="F110" s="6" t="inlineStr"/>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="6" t="inlineStr"/>
+    </row>
+    <row r="111" ht="44" customHeight="1">
+      <c r="A111" s="6" t="inlineStr"/>
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
+      <c r="D111" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr"/>
-      <c r="G87" s="6" t="inlineStr"/>
-      <c r="H87" s="6" t="inlineStr"/>
-    </row>
-    <row r="88" ht="44" customHeight="1">
-      <c r="A88" s="6" t="inlineStr"/>
-      <c r="B88" s="6" t="inlineStr">
+      <c r="F111" s="6" t="inlineStr"/>
+      <c r="G111" s="6" t="inlineStr"/>
+      <c r="H111" s="6" t="inlineStr"/>
+    </row>
+    <row r="112" ht="44" customHeight="1">
+      <c r="A112" s="6" t="inlineStr"/>
+      <c r="B112" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C112" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D88" s="11" t="inlineStr">
+      <c r="D112" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="E112" s="6" t="inlineStr">
         <is>
           <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr"/>
-      <c r="G88" s="6" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr"/>
-    </row>
-    <row r="89" ht="44" customHeight="1">
-      <c r="A89" s="6" t="inlineStr"/>
-      <c r="B89" s="6" t="inlineStr">
+      <c r="F112" s="6" t="inlineStr"/>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="6" t="inlineStr"/>
+    </row>
+    <row r="113" ht="44" customHeight="1">
+      <c r="A113" s="6" t="inlineStr"/>
+      <c r="B113" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C113" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D89" s="11" t="inlineStr">
+      <c r="D113" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E113" s="6" t="inlineStr">
         <is>
           <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr"/>
-      <c r="G89" s="6" t="inlineStr"/>
-      <c r="H89" s="6" t="inlineStr"/>
-    </row>
-    <row r="90" ht="44" customHeight="1">
-      <c r="A90" s="6" t="inlineStr"/>
-      <c r="B90" s="6" t="inlineStr">
+      <c r="F113" s="6" t="inlineStr"/>
+      <c r="G113" s="6" t="inlineStr"/>
+      <c r="H113" s="6" t="inlineStr"/>
+    </row>
+    <row r="114" ht="44" customHeight="1">
+      <c r="A114" s="6" t="inlineStr"/>
+      <c r="B114" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C114" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
+      <c r="D114" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr"/>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="6" t="inlineStr"/>
+    </row>
+    <row r="115" ht="44" customHeight="1">
+      <c r="A115" s="6" t="inlineStr"/>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr"/>
+      <c r="G115" s="6" t="inlineStr"/>
+      <c r="H115" s="6" t="inlineStr"/>
+    </row>
+    <row r="116" ht="44" customHeight="1">
+      <c r="A116" s="6" t="inlineStr"/>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
         <is>
           <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr"/>
-      <c r="G90" s="6" t="inlineStr"/>
-      <c r="H90" s="6" t="inlineStr"/>
-    </row>
-    <row r="91" ht="44" customHeight="1">
-      <c r="A91" s="6" t="inlineStr"/>
-      <c r="B91" s="6" t="inlineStr">
+      <c r="F116" s="6" t="inlineStr"/>
+      <c r="G116" s="6" t="inlineStr"/>
+      <c r="H116" s="6" t="inlineStr"/>
+    </row>
+    <row r="117" ht="44" customHeight="1">
+      <c r="A117" s="6" t="inlineStr"/>
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="E117" s="6" t="inlineStr">
         <is>
           <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr"/>
-      <c r="G91" s="6" t="inlineStr"/>
-      <c r="H91" s="6" t="inlineStr"/>
-    </row>
-    <row r="92" ht="44" customHeight="1">
-      <c r="A92" s="6" t="inlineStr"/>
-      <c r="B92" s="6" t="inlineStr">
+      <c r="F117" s="6" t="inlineStr"/>
+      <c r="G117" s="6" t="inlineStr"/>
+      <c r="H117" s="6" t="inlineStr"/>
+    </row>
+    <row r="118" ht="44" customHeight="1">
+      <c r="A118" s="6" t="inlineStr"/>
+      <c r="B118" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C118" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D92" s="11" t="inlineStr">
+      <c r="D118" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E92" s="6" t="inlineStr">
-        <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。介護報酬改定率は1％当たり月額61円です。介護報酬は、令和9年度改定を待たず令和8年度にも改定が行われることとされており（第1章第9節4）、基準年度である令和7年度の単価</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr"/>
-      <c r="G92" s="6" t="inlineStr"/>
-      <c r="H92" s="6" t="inlineStr"/>
-    </row>
-    <row r="93" ht="44" customHeight="1">
-      <c r="A93" s="6" t="inlineStr"/>
-      <c r="B93" s="6" t="inlineStr">
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr"/>
+      <c r="G118" s="6" t="inlineStr"/>
+      <c r="H118" s="6" t="inlineStr"/>
+    </row>
+    <row r="119" ht="44" customHeight="1">
+      <c r="A119" s="6" t="inlineStr"/>
+      <c r="B119" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C119" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D93" s="11" t="inlineStr">
+      <c r="D119" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="E119" s="6" t="inlineStr">
         <is>
           <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr"/>
-      <c r="G93" s="6" t="inlineStr"/>
-      <c r="H93" s="6" t="inlineStr"/>
-    </row>
-    <row r="94" ht="44" customHeight="1">
-      <c r="A94" s="6" t="inlineStr"/>
-      <c r="B94" s="6" t="inlineStr">
+      <c r="F119" s="6" t="inlineStr"/>
+      <c r="G119" s="6" t="inlineStr"/>
+      <c r="H119" s="6" t="inlineStr"/>
+    </row>
+    <row r="120" ht="44" customHeight="1">
+      <c r="A120" s="6" t="inlineStr"/>
+      <c r="B120" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C120" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D120" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="E120" s="6" t="inlineStr">
         <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr"/>
-      <c r="G94" s="6" t="inlineStr"/>
-      <c r="H94" s="6" t="inlineStr"/>
-    </row>
-    <row r="95" ht="44" customHeight="1">
-      <c r="A95" s="6" t="inlineStr"/>
-      <c r="B95" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr"/>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="6" t="inlineStr"/>
+    </row>
+    <row r="121" ht="44" customHeight="1">
+      <c r="A121" s="6" t="inlineStr"/>
+      <c r="B121" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C121" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr"/>
+      <c r="G121" s="6" t="inlineStr"/>
+      <c r="H121" s="6" t="inlineStr"/>
+    </row>
+    <row r="122" ht="44" customHeight="1">
+      <c r="A122" s="6" t="inlineStr"/>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E122" s="6" t="inlineStr">
         <is>
           <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr"/>
-      <c r="G95" s="6" t="inlineStr"/>
-      <c r="H95" s="6" t="inlineStr"/>
-    </row>
-    <row r="96" ht="44" customHeight="1">
-      <c r="A96" s="6" t="inlineStr"/>
-      <c r="B96" s="6" t="inlineStr">
+      <c r="F122" s="6" t="inlineStr"/>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="6" t="inlineStr"/>
+    </row>
+    <row r="123" ht="44" customHeight="1">
+      <c r="A123" s="6" t="inlineStr"/>
+      <c r="B123" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C123" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D123" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費です。Eの調整交付金見込額は第9期計画と同水準の交付割合によって</t>
-        </is>
-      </c>
-      <c r="F96" s="6" t="inlineStr"/>
-      <c r="G96" s="6" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr"/>
-    </row>
-    <row r="97" ht="44" customHeight="1">
-      <c r="A97" s="6" t="inlineStr"/>
-      <c r="B97" s="6" t="inlineStr">
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr"/>
+      <c r="G123" s="6" t="inlineStr"/>
+      <c r="H123" s="6" t="inlineStr"/>
+    </row>
+    <row r="124" ht="44" customHeight="1">
+      <c r="A124" s="6" t="inlineStr"/>
+      <c r="B124" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="C124" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D97" s="6" t="inlineStr">
+      <c r="D124" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr"/>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="6" t="inlineStr"/>
+    </row>
+    <row r="125" ht="44" customHeight="1">
+      <c r="A125" s="6" t="inlineStr"/>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
         <is>
           <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
 注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr"/>
-      <c r="G97" s="6" t="inlineStr"/>
-      <c r="H97" s="6" t="inlineStr"/>
-    </row>
-    <row r="98" ht="44" customHeight="1">
-      <c r="A98" s="6" t="inlineStr"/>
-      <c r="B98" s="6" t="inlineStr">
+      <c r="F125" s="6" t="inlineStr"/>
+      <c r="G125" s="6" t="inlineStr"/>
+      <c r="H125" s="6" t="inlineStr"/>
+    </row>
+    <row r="126" ht="44" customHeight="1">
+      <c r="A126" s="6" t="inlineStr"/>
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C126" s="6" t="inlineStr">
         <is>
           <t>第7節 低所得者支援</t>
         </is>
       </c>
-      <c r="D98" s="6" t="inlineStr">
+      <c r="D126" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="E126" s="6" t="inlineStr">
         <is>
           <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr"/>
-      <c r="G98" s="6" t="inlineStr"/>
-      <c r="H98" s="6" t="inlineStr"/>
-    </row>
-    <row r="99" ht="44" customHeight="1">
-      <c r="A99" s="6" t="inlineStr"/>
-      <c r="B99" s="6" t="inlineStr">
+      <c r="F126" s="6" t="inlineStr"/>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="6" t="inlineStr"/>
+    </row>
+    <row r="127" ht="44" customHeight="1">
+      <c r="A127" s="6" t="inlineStr"/>
+      <c r="B127" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C127" s="6" t="inlineStr">
         <is>
           <t>第7節 低所得者支援</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
+      <c r="D127" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="E127" s="6" t="inlineStr">
         <is>
           <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr"/>
-      <c r="G99" s="6" t="inlineStr"/>
-      <c r="H99" s="6" t="inlineStr"/>
-    </row>
-    <row r="101" ht="28" customHeight="1">
-      <c r="A101" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は26種の表に127箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+      <c r="F127" s="6" t="inlineStr"/>
+      <c r="G127" s="6" t="inlineStr"/>
+      <c r="H127" s="6" t="inlineStr"/>
+    </row>
+    <row r="129" ht="28" customHeight="1">
+      <c r="A129" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は28種の表に133箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="3" t="inlineStr">
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="4" t="inlineStr"/>
-      <c r="B104" s="4" t="inlineStr">
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="4" t="inlineStr"/>
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C104" s="4" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D104" s="4" t="inlineStr">
+      <c r="D132" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
+      <c r="E132" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F104" s="4" t="inlineStr">
+      <c r="F132" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G104" s="4" t="inlineStr">
+      <c r="G132" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H104" s="4" t="inlineStr">
+      <c r="H132" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
         </is>
       </c>
     </row>
-    <row r="105" ht="44" customHeight="1">
-      <c r="A105" s="6" t="inlineStr"/>
-      <c r="B105" s="6" t="inlineStr">
+    <row r="133" ht="44" customHeight="1">
+      <c r="A133" s="6" t="inlineStr"/>
+      <c r="B133" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="C133" s="6" t="inlineStr">
         <is>
           <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
-      <c r="D105" s="5" t="n">
+      <c r="D133" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E105" s="5" t="n">
+      <c r="E133" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F105" s="5" t="n">
+      <c r="F133" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G105" s="5" t="n">
+      <c r="G133" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H105" s="6" t="inlineStr">
+      <c r="H133" s="6" t="inlineStr">
         <is>
           <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="44" customHeight="1">
-      <c r="A106" s="6" t="inlineStr"/>
-      <c r="B106" s="6" t="inlineStr">
+    <row r="134" ht="44" customHeight="1">
+      <c r="A134" s="6" t="inlineStr"/>
+      <c r="B134" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C134" s="6" t="inlineStr">
         <is>
           <t>第2節　計画の位置付け</t>
         </is>
       </c>
-      <c r="D106" s="5" t="n">
+      <c r="D134" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="E106" s="5" t="n">
+      <c r="E134" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F106" s="5" t="n">
+      <c r="F134" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G106" s="5" t="n">
+      <c r="G134" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H106" s="6" t="inlineStr">
+      <c r="H134" s="6" t="inlineStr">
         <is>
           <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="44" customHeight="1">
-      <c r="A107" s="6" t="inlineStr"/>
-      <c r="B107" s="6" t="inlineStr">
+    <row r="135" ht="44" customHeight="1">
+      <c r="A135" s="6" t="inlineStr"/>
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
+      <c r="C135" s="6" t="inlineStr">
         <is>
           <t>第4節　計画期間</t>
         </is>
       </c>
-      <c r="D107" s="5" t="n">
+      <c r="D135" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E107" s="5" t="n">
+      <c r="E135" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F107" s="5" t="n">
+      <c r="F135" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G107" s="5" t="n">
+      <c r="G135" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H107" s="6" t="inlineStr">
+      <c r="H135" s="6" t="inlineStr">
         <is>
           <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="44" customHeight="1">
-      <c r="A108" s="6" t="inlineStr"/>
-      <c r="B108" s="6" t="inlineStr">
+    <row r="136" ht="44" customHeight="1">
+      <c r="A136" s="6" t="inlineStr"/>
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D108" s="5" t="n">
+      <c r="D136" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E108" s="5" t="n">
+      <c r="E136" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F108" s="5" t="n">
+      <c r="F136" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G108" s="5" t="n">
+      <c r="G136" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H108" s="6" t="inlineStr">
+      <c r="H136" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="44" customHeight="1">
-      <c r="A109" s="6" t="inlineStr"/>
-      <c r="B109" s="6" t="inlineStr">
+    <row r="137" ht="44" customHeight="1">
+      <c r="A137" s="6" t="inlineStr"/>
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D109" s="5" t="n">
+      <c r="D137" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E109" s="5" t="n">
+      <c r="E137" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F109" s="5" t="n">
+      <c r="F137" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G109" s="5" t="n">
+      <c r="G137" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H109" s="6" t="inlineStr">
+      <c r="H137" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="42" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
+    <row r="139" ht="42" customHeight="1">
+      <c r="A139" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は5節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -3515,14 +4247,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="A131:H131"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A101:H101"/>
-    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A139:H139"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A103:H103"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A129:H129"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A111:H111"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4697,7 +5429,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第5節・第6節（未確定10箇所）</t>
+          <t>第2章第3節・第5節・第6節（未確定11箇所）</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -5160,7 +5892,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議122・要確認67・要内訳1で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議134・要確認85・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -5272,7 +6004,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1006段落151表36図／190箇所</t>
+          <t>1019段落152表36図／221箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -5298,7 +6030,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>190＝190</t>
+          <t>221＝221</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -5319,12 +6051,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>6章</t>
+          <t>7章</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>190＝190</t>
+          <t>221＝221</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -5496,17 +6228,17 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>未確定箇所が第6章第4節に集中していること</t>
+          <t>未確定箇所が最も多い節が第6章第4節であること</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>同節／全体</t>
+          <t>最多の節／同節／全体</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>61／190箇所（32％）</t>
+          <t>第4節 介護保険サービス等における施設の見込み／61／221箇所（28％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -5745,7 +6477,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は190箇所ある（要協議122・要確認67・要内訳1）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は221箇所ある（要協議134・要確認85・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>221箇所</t>
+          <t>228箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議134・要確認85・要内訳2。本文88箇所・表28種133箇所（01シート）</t>
+          <t>要協議136・要確認90・要内訳2。本文94箇所・表29種134箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>177件</t>
+          <t>181件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>166件</t>
+          <t>170件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが96件（02シート）</t>
+          <t>このうち計画素案を止めているものが100件（02シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1019段落152表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1024段落152表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>221箇所のうち61箇所（28％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>228箇所のうち61箇所（27％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1019段落152表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計221箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1024段落152表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計228箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -900,13 +900,13 @@
       </c>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="8" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>38</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -926,13 +926,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -1048,13 +1048,13 @@
       </c>
       <c r="C13" s="9" t="inlineStr"/>
       <c r="D13" s="10" t="n">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>2</v>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>9</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -1638,142 +1638,142 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>No.8（同）</t>
-        </is>
-      </c>
+      <c r="H35" s="6" t="inlineStr"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>資料7 図表番号一覧</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>（節の前）</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>No.8（同）</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="6" t="inlineStr"/>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>資料7 図表番号一覧</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>（節の前）</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="F38" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>3　本文の未確定箇所（88件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="G38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>3　本文の未確定箇所（94件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>本文（抜粋）</t>
         </is>
       </c>
-      <c r="F39" s="4" t="inlineStr"/>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-    </row>
-    <row r="40" ht="44" customHeight="1">
-      <c r="A40" s="6" t="inlineStr"/>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D40" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr"/>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr"/>
-    </row>
-    <row r="41" ht="44" customHeight="1">
-      <c r="A41" s="6" t="inlineStr"/>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>第5節　計画の策定体制</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr"/>
-      <c r="G41" s="6" t="inlineStr"/>
-      <c r="H41" s="6" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
     </row>
     <row r="42" ht="44" customHeight="1">
       <c r="A42" s="6" t="inlineStr"/>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>第6節　計画の進行管理・推進体制</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>注）北海道の高齢者保健福祉計画が定める評価指標のうち「取り組んでいる市町村数」を単位とするものは、1保険者である当広域連合にそのまま適用することができません。読替えの方法は第8節に掲げます。北海道から広域連合に対する読替えの考え方は示されていないため、本計画は当広域連合の整理によっており、考え方が示された場合はこれに合わせて改めます［要確認］。</t>
+          <t>注）各法律の条文の受領前であるため、条番号のみを記載し項番号は記載していません［要確認］。構成3町の高齢者福祉計画が老人福祉法第20条の8による市町村老人福祉計画に当たることの確認、成年後見制度の利用の促進に関する施策についての基本的な計画の構成3町における策定の状況、及び一体のものとして作成する方法は構成3町と協議して定めます［要協議］。</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr"/>
@@ -1810,18 +1810,17 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
-注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
+          <t>注）各法律の条文の受領前であるため、条番号のみを記載し項番号は記載していません［要確認］。構成3町の高齢者福祉計画が老人福祉法第20条の8による市町村老人福祉計画に当たることの確認、成年後見制度の利用の促進に関する施策についての基本的な計画の構成3町における策定の状況、及び一体のものとして作成する方法は構成3町と協議して定めます［要協議］。</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1837,18 +1836,17 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
-注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1864,7 +1862,7 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
@@ -1874,7 +1872,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
+          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1890,7 +1888,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第6節　計画の進行管理・推進体制</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1900,7 +1898,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
+          <t>注）北海道の高齢者保健福祉計画が定める評価指標のうち「取り組んでいる市町村数」を単位とするものは、1保険者である当広域連合にそのまま適用することができません。読替えの方法は第8節に掲げます。北海道から広域連合に対する読替えの考え方は示されていないため、本計画は当広域連合の整理によっており、考え方が示された場合はこれに合わせて改めます［要確認］。</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1916,7 +1914,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1926,7 +1924,8 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
+注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1942,7 +1941,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1952,7 +1951,8 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
+注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr"/>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
+          <t>介護保険法第117条は、市町村介護保険事業計画は医療計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合は、在宅医療・介護連携（第5章 基本目標1）、協力医療機関の確保（第1章第9節1）並びに施設・居住系サービスの整備（第6章第5節）において図ります。北海道の第10期高齢者保健福祉計画・介護保険事業支援計画</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -1994,17 +1994,17 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第8節　関係計画等との関係</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2015,22 +2015,22 @@
       <c r="A51" s="6" t="inlineStr"/>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D51" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2041,12 +2041,12 @@
       <c r="A52" s="6" t="inlineStr"/>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
+          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2067,22 +2067,22 @@
       <c r="A53" s="6" t="inlineStr"/>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2093,12 +2093,12 @@
       <c r="A54" s="6" t="inlineStr"/>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2119,12 +2119,12 @@
       <c r="A55" s="6" t="inlineStr"/>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2150,17 +2150,17 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2202,17 +2202,17 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2254,18 +2254,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
-注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
+          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2281,7 +2280,7 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2291,8 +2290,7 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
-注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2308,17 +2306,17 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 サービス提供体制の状況</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2334,7 +2332,7 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D63" s="6" t="inlineStr">
@@ -2344,7 +2342,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
+          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2360,7 +2358,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2370,7 +2368,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2381,12 +2379,12 @@
       <c r="A65" s="6" t="inlineStr"/>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2396,7 +2394,8 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
+          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
+注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2407,12 +2406,12 @@
       <c r="A66" s="6" t="inlineStr"/>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2422,8 +2421,8 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
-注）分母は地域包括ケア「見え</t>
+          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
+注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2434,22 +2433,22 @@
       <c r="A67" s="6" t="inlineStr"/>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2460,12 +2459,12 @@
       <c r="A68" s="6" t="inlineStr"/>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2475,7 +2474,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2486,22 +2485,22 @@
       <c r="A69" s="6" t="inlineStr"/>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2517,7 +2516,7 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2527,7 +2526,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2543,7 +2542,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2553,7 +2552,8 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
+注）分母は地域包括ケア「見え</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2564,12 +2564,12 @@
       <c r="A72" s="6" t="inlineStr"/>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
+          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2590,22 +2590,22 @@
       <c r="A73" s="6" t="inlineStr"/>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 地域支援事業の実績</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2616,22 +2616,22 @@
       <c r="A74" s="6" t="inlineStr"/>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -2642,22 +2642,22 @@
       <c r="A75" s="6" t="inlineStr"/>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2668,22 +2668,22 @@
       <c r="A76" s="6" t="inlineStr"/>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
-        </is>
-      </c>
-      <c r="D76" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D76" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr"/>
@@ -2694,22 +2694,22 @@
       <c r="A77" s="6" t="inlineStr"/>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2720,12 +2720,12 @@
       <c r="A78" s="6" t="inlineStr"/>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2746,22 +2746,22 @@
       <c r="A79" s="6" t="inlineStr"/>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr"/>
@@ -2803,17 +2803,17 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr"/>
@@ -2829,17 +2829,17 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
@@ -2855,17 +2855,17 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr"/>
@@ -2881,17 +2881,17 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr"/>
@@ -2907,17 +2907,17 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr"/>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr"/>
@@ -2954,12 +2954,12 @@
       <c r="A87" s="6" t="inlineStr"/>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr"/>
@@ -2980,12 +2980,12 @@
       <c r="A88" s="6" t="inlineStr"/>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr"/>
@@ -3006,22 +3006,22 @@
       <c r="A89" s="6" t="inlineStr"/>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr"/>
@@ -3032,22 +3032,22 @@
       <c r="A90" s="6" t="inlineStr"/>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D90" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr"/>
@@ -3058,22 +3058,22 @@
       <c r="A91" s="6" t="inlineStr"/>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr"/>
@@ -3084,22 +3084,22 @@
       <c r="A92" s="6" t="inlineStr"/>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D92" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr"/>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -3125,8 +3125,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr"/>
@@ -3142,7 +3141,7 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -3152,8 +3151,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr"/>
@@ -3169,7 +3167,7 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
@@ -3179,8 +3177,7 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr"/>
@@ -3196,18 +3193,17 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr"/>
@@ -3223,7 +3219,7 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
@@ -3233,8 +3229,7 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr"/>
@@ -3250,17 +3245,17 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D98" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr"/>
@@ -3276,17 +3271,18 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D99" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr"/>
@@ -3302,180 +3298,181 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr"/>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="6" t="inlineStr"/>
+    </row>
+    <row r="101" ht="44" customHeight="1">
+      <c r="A101" s="6" t="inlineStr"/>
+      <c r="B101" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr"/>
+      <c r="G101" s="6" t="inlineStr"/>
+      <c r="H101" s="6" t="inlineStr"/>
+    </row>
+    <row r="102" ht="44" customHeight="1">
+      <c r="A102" s="6" t="inlineStr"/>
+      <c r="B102" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="inlineStr"/>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="6" t="inlineStr"/>
+    </row>
+    <row r="103" ht="44" customHeight="1">
+      <c r="A103" s="6" t="inlineStr"/>
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D100" s="11" t="inlineStr">
+      <c r="D103" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr"/>
+      <c r="G103" s="6" t="inlineStr"/>
+      <c r="H103" s="6" t="inlineStr"/>
+    </row>
+    <row r="104" ht="44" customHeight="1">
+      <c r="A104" s="6" t="inlineStr"/>
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr"/>
+      <c r="G104" s="6" t="inlineStr"/>
+      <c r="H104" s="6" t="inlineStr"/>
+    </row>
+    <row r="105" ht="44" customHeight="1">
+      <c r="A105" s="6" t="inlineStr"/>
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr"/>
+      <c r="G105" s="6" t="inlineStr"/>
+      <c r="H105" s="6" t="inlineStr"/>
+    </row>
+    <row r="106" ht="44" customHeight="1">
+      <c r="A106" s="6" t="inlineStr"/>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
         <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr"/>
-      <c r="G100" s="6" t="inlineStr"/>
-      <c r="H100" s="6" t="inlineStr"/>
-    </row>
-    <row r="101" ht="44" customHeight="1">
-      <c r="A101" s="6" t="inlineStr"/>
-      <c r="B101" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C101" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F101" s="6" t="inlineStr"/>
-      <c r="G101" s="6" t="inlineStr"/>
-      <c r="H101" s="6" t="inlineStr"/>
-    </row>
-    <row r="102" ht="44" customHeight="1">
-      <c r="A102" s="6" t="inlineStr"/>
-      <c r="B102" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C102" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
-        <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
-        </is>
-      </c>
-      <c r="F102" s="6" t="inlineStr"/>
-      <c r="G102" s="6" t="inlineStr"/>
-      <c r="H102" s="6" t="inlineStr"/>
-    </row>
-    <row r="103" ht="44" customHeight="1">
-      <c r="A103" s="6" t="inlineStr"/>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
-        </is>
-      </c>
-      <c r="F103" s="6" t="inlineStr"/>
-      <c r="G103" s="6" t="inlineStr"/>
-      <c r="H103" s="6" t="inlineStr"/>
-    </row>
-    <row r="104" ht="44" customHeight="1">
-      <c r="A104" s="6" t="inlineStr"/>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D104" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F104" s="6" t="inlineStr"/>
-      <c r="G104" s="6" t="inlineStr"/>
-      <c r="H104" s="6" t="inlineStr"/>
-    </row>
-    <row r="105" ht="44" customHeight="1">
-      <c r="A105" s="6" t="inlineStr"/>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D105" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F105" s="6" t="inlineStr"/>
-      <c r="G105" s="6" t="inlineStr"/>
-      <c r="H105" s="6" t="inlineStr"/>
-    </row>
-    <row r="106" ht="44" customHeight="1">
-      <c r="A106" s="6" t="inlineStr"/>
-      <c r="B106" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C106" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
       <c r="F106" s="6" t="inlineStr"/>
       <c r="G106" s="6" t="inlineStr"/>
       <c r="H106" s="6" t="inlineStr"/>
@@ -3489,18 +3486,17 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr"/>
@@ -3516,17 +3512,17 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr"/>
@@ -3542,7 +3538,7 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -3552,7 +3548,7 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr"/>
@@ -3568,18 +3564,18 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
-注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr"/>
@@ -3595,17 +3591,18 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr"/>
@@ -3621,17 +3618,18 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D112" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr"/>
@@ -3647,17 +3645,18 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D113" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr"/>
@@ -3673,18 +3672,17 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr"/>
@@ -3700,7 +3698,7 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -3710,8 +3708,7 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr"/>
@@ -3727,7 +3724,7 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -3737,7 +3734,7 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr"/>
@@ -3763,7 +3760,7 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr"/>
@@ -3782,14 +3779,15 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D118" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
+注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr"/>
@@ -3808,14 +3806,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D119" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr"/>
@@ -3834,427 +3832,607 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr"/>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="6" t="inlineStr"/>
+    </row>
+    <row r="121" ht="44" customHeight="1">
+      <c r="A121" s="6" t="inlineStr"/>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr"/>
+      <c r="G121" s="6" t="inlineStr"/>
+      <c r="H121" s="6" t="inlineStr"/>
+    </row>
+    <row r="122" ht="44" customHeight="1">
+      <c r="A122" s="6" t="inlineStr"/>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr"/>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="6" t="inlineStr"/>
+    </row>
+    <row r="123" ht="44" customHeight="1">
+      <c r="A123" s="6" t="inlineStr"/>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr"/>
+      <c r="G123" s="6" t="inlineStr"/>
+      <c r="H123" s="6" t="inlineStr"/>
+    </row>
+    <row r="124" ht="44" customHeight="1">
+      <c r="A124" s="6" t="inlineStr"/>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr"/>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="6" t="inlineStr"/>
+    </row>
+    <row r="125" ht="44" customHeight="1">
+      <c r="A125" s="6" t="inlineStr"/>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr"/>
+      <c r="G125" s="6" t="inlineStr"/>
+      <c r="H125" s="6" t="inlineStr"/>
+    </row>
+    <row r="126" ht="44" customHeight="1">
+      <c r="A126" s="6" t="inlineStr"/>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr"/>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="6" t="inlineStr"/>
+    </row>
+    <row r="127" ht="44" customHeight="1">
+      <c r="A127" s="6" t="inlineStr"/>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr"/>
+      <c r="G127" s="6" t="inlineStr"/>
+      <c r="H127" s="6" t="inlineStr"/>
+    </row>
+    <row r="128" ht="44" customHeight="1">
+      <c r="A128" s="6" t="inlineStr"/>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
         <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F120" s="6" t="inlineStr"/>
-      <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="6" t="inlineStr"/>
-    </row>
-    <row r="121" ht="44" customHeight="1">
-      <c r="A121" s="6" t="inlineStr"/>
-      <c r="B121" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr"/>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr"/>
+    </row>
+    <row r="129" ht="44" customHeight="1">
+      <c r="A129" s="6" t="inlineStr"/>
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C121" s="6" t="inlineStr">
+      <c r="C129" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D121" s="11" t="inlineStr">
+      <c r="D129" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E129" s="6" t="inlineStr">
         <is>
           <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
         </is>
       </c>
-      <c r="F121" s="6" t="inlineStr"/>
-      <c r="G121" s="6" t="inlineStr"/>
-      <c r="H121" s="6" t="inlineStr"/>
-    </row>
-    <row r="122" ht="44" customHeight="1">
-      <c r="A122" s="6" t="inlineStr"/>
-      <c r="B122" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr"/>
+      <c r="G129" s="6" t="inlineStr"/>
+      <c r="H129" s="6" t="inlineStr"/>
+    </row>
+    <row r="130" ht="44" customHeight="1">
+      <c r="A130" s="6" t="inlineStr"/>
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
+      <c r="D130" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E130" s="6" t="inlineStr">
         <is>
           <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr"/>
-      <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="6" t="inlineStr"/>
-    </row>
-    <row r="123" ht="44" customHeight="1">
-      <c r="A123" s="6" t="inlineStr"/>
-      <c r="B123" s="6" t="inlineStr">
+      <c r="F130" s="6" t="inlineStr"/>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="6" t="inlineStr"/>
+    </row>
+    <row r="131" ht="44" customHeight="1">
+      <c r="A131" s="6" t="inlineStr"/>
+      <c r="B131" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="C131" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
+      <c r="D131" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E131" s="6" t="inlineStr">
         <is>
           <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr"/>
-      <c r="G123" s="6" t="inlineStr"/>
-      <c r="H123" s="6" t="inlineStr"/>
-    </row>
-    <row r="124" ht="44" customHeight="1">
-      <c r="A124" s="6" t="inlineStr"/>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr"/>
+      <c r="G131" s="6" t="inlineStr"/>
+      <c r="H131" s="6" t="inlineStr"/>
+    </row>
+    <row r="132" ht="44" customHeight="1">
+      <c r="A132" s="6" t="inlineStr"/>
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C132" s="6" t="inlineStr">
         <is>
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D132" s="6" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E132" s="6" t="inlineStr">
         <is>
           <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
         </is>
       </c>
-      <c r="F124" s="6" t="inlineStr"/>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="6" t="inlineStr"/>
-    </row>
-    <row r="125" ht="44" customHeight="1">
-      <c r="A125" s="6" t="inlineStr"/>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
-注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
-        </is>
-      </c>
-      <c r="F125" s="6" t="inlineStr"/>
-      <c r="G125" s="6" t="inlineStr"/>
-      <c r="H125" s="6" t="inlineStr"/>
-    </row>
-    <row r="126" ht="44" customHeight="1">
-      <c r="A126" s="6" t="inlineStr"/>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
-        </is>
-      </c>
-      <c r="F126" s="6" t="inlineStr"/>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="6" t="inlineStr"/>
-    </row>
-    <row r="127" ht="44" customHeight="1">
-      <c r="A127" s="6" t="inlineStr"/>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
-        </is>
-      </c>
-      <c r="F127" s="6" t="inlineStr"/>
-      <c r="G127" s="6" t="inlineStr"/>
-      <c r="H127" s="6" t="inlineStr"/>
-    </row>
-    <row r="129" ht="28" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は28種の表に133箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
-注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="3" t="inlineStr">
-        <is>
-          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="30" customHeight="1">
-      <c r="A132" s="4" t="inlineStr"/>
-      <c r="B132" s="4" t="inlineStr">
-        <is>
-          <t>章</t>
-        </is>
-      </c>
-      <c r="C132" s="4" t="inlineStr">
-        <is>
-          <t>節</t>
-        </is>
-      </c>
-      <c r="D132" s="4" t="inlineStr">
-        <is>
-          <t>段落</t>
-        </is>
-      </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>うち注・出典</t>
-        </is>
-      </c>
-      <c r="F132" s="4" t="inlineStr">
-        <is>
-          <t>表</t>
-        </is>
-      </c>
-      <c r="G132" s="4" t="inlineStr">
-        <is>
-          <t>未確定</t>
-        </is>
-      </c>
-      <c r="H132" s="4" t="inlineStr">
-        <is>
-          <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
+      <c r="F132" s="6" t="inlineStr"/>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr"/>
     </row>
     <row r="133" ht="44" customHeight="1">
       <c r="A133" s="6" t="inlineStr"/>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D133" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E133" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G133" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr"/>
+      <c r="G133" s="6" t="inlineStr"/>
+      <c r="H133" s="6" t="inlineStr"/>
     </row>
     <row r="134" ht="44" customHeight="1">
       <c r="A134" s="6" t="inlineStr"/>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D134" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E134" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H134" s="6" t="inlineStr">
-        <is>
-          <t>他計画との関係の記述であり短いことは妥当だが、認知症基本法第13条の市町村認知症施策推進計画をどう扱うかが決まれば本節に加筆する（確認事項No.130）。給付適正化計画（第7期）の位置づけは反映済み</t>
-        </is>
-      </c>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr"/>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr"/>
     </row>
     <row r="135" ht="44" customHeight="1">
       <c r="A135" s="6" t="inlineStr"/>
       <c r="B135" s="6" t="inlineStr">
         <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr"/>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr"/>
+    </row>
+    <row r="137" ht="28" customHeight="1">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は29種の表に134箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="20" customHeight="1">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="30" customHeight="1">
+      <c r="A140" s="4" t="inlineStr"/>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>章</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>節</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>段落</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>うち注・出典</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>本来入るべき内容と所在</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="44" customHeight="1">
+      <c r="A141" s="6" t="inlineStr"/>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>第1節　計画策定の趣旨</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" s="6" t="inlineStr">
+        <is>
+          <t>趣旨の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="44" customHeight="1">
+      <c r="A142" s="6" t="inlineStr"/>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
         <is>
           <t>第4節　計画期間</t>
         </is>
       </c>
-      <c r="D135" s="5" t="n">
+      <c r="D142" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E135" s="5" t="n">
+      <c r="E142" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F135" s="5" t="n">
+      <c r="F142" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G135" s="5" t="n">
+      <c r="G142" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="H142" s="6" t="inlineStr">
         <is>
           <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="44" customHeight="1">
-      <c r="A136" s="6" t="inlineStr"/>
-      <c r="B136" s="6" t="inlineStr">
+    <row r="143" ht="44" customHeight="1">
+      <c r="A143" s="6" t="inlineStr"/>
+      <c r="B143" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
+      <c r="C143" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D136" s="5" t="n">
+      <c r="D143" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E136" s="5" t="n">
+      <c r="E143" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F136" s="5" t="n">
+      <c r="F143" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G136" s="5" t="n">
+      <c r="G143" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="H143" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="44" customHeight="1">
-      <c r="A137" s="6" t="inlineStr"/>
-      <c r="B137" s="6" t="inlineStr">
+    <row r="144" ht="44" customHeight="1">
+      <c r="A144" s="6" t="inlineStr"/>
+      <c r="B144" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="C144" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D137" s="5" t="n">
+      <c r="D144" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E137" s="5" t="n">
+      <c r="E144" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F137" s="5" t="n">
+      <c r="F144" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G137" s="5" t="n">
+      <c r="G144" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H137" s="6" t="inlineStr">
+      <c r="H144" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="42" customHeight="1">
-      <c r="A139" s="7" t="inlineStr">
+    <row r="146" ht="42" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
-注4）記述が薄い節は5節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
+注4）記述が薄い節は4節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
 注5）第2章第4節（高齢者の生活実態）は令和8年9月15日に健康とくらしの調査の結果を反映し、32段落・表8になりました。記述が薄い節には当たらなくなっています。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A131:H131"/>
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A146:H146"/>
     <mergeCell ref="A139:H139"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A129:H129"/>
+    <mergeCell ref="A137:H137"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4281,7 +4459,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（177件）</t>
+          <t>確認事項の棚卸し（181件）</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4513,7 @@
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は166件</t>
+          <t>完了・了承済を除く未回答は170件</t>
         </is>
       </c>
     </row>
@@ -4347,7 +4525,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
@@ -4556,10 +4734,10 @@
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
@@ -4748,7 +4926,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
@@ -4763,7 +4941,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
@@ -4908,8 +5086,8 @@
     <row r="44" ht="42" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（83件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
-注2）確認先が「発注者・3町」のもの（24件）は、3町への照会の様式と時期の決定を先に要します。
+          <t>注1）期限が令和8年8月以前のもの（87件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+注2）確認先が「発注者・3町」のもの（27件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
       </c>
@@ -5892,7 +6070,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議134・要確認85・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議136・要確認90・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -6004,7 +6182,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1019段落152表36図／221箇所</t>
+          <t>1024段落152表36図／228箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -6030,7 +6208,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>221＝221</t>
+          <t>228＝228</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -6056,7 +6234,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>221＝221</t>
+          <t>228＝228</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -6082,7 +6260,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>177件（未回答166件）</t>
+          <t>181件（未回答170件）</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -6108,7 +6286,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>177件／一意177件</t>
+          <t>181件／一意181件</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -6238,7 +6416,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み／61／221箇所（28％）</t>
+          <t>第4節 介護保険サービス等における施設の見込み／61／228箇所（27％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -6264,7 +6442,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>5節（うち短いことが妥当なものを除くと0節）</t>
+          <t>4節（うち短いことが妥当なものを除くと0節）</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -6477,7 +6655,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は221箇所ある（要協議134・要確認85・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は228箇所ある（要協議136・要確認90・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -6500,7 +6678,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている166件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている170件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>228箇所</t>
+          <t>233箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議136・要確認90・要内訳2。本文94箇所・表29種134箇所（01シート）</t>
+          <t>要協議136・要確認95・要内訳2。本文98箇所・表30種135箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>181件</t>
+          <t>184件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>170件</t>
+          <t>173件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが100件（02シート）</t>
+          <t>このうち計画素案を止めているものが103件（02シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1024段落152表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1027段落153表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>228箇所のうち61箇所（27％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>233箇所のうち61箇所（26％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H146"/>
+  <dimension ref="A1:H150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1024段落152表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計228箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1027段落153表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計233箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>72</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -926,13 +926,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -1048,13 +1048,13 @@
       </c>
       <c r="C13" s="9" t="inlineStr"/>
       <c r="D13" s="10" t="n">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>136</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>2</v>
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
@@ -1346,29 +1346,29 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="F25" s="5" t="n">
-        <v>2</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No.75（代表KPIの再整理案）</t>
+          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
         </is>
       </c>
     </row>
@@ -1376,29 +1376,29 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>No.8（3調査の点検事項）</t>
+          <t>No.75（代表KPIの再整理案）</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1406,29 @@
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
+          <t>No.8（3調査の点検事項）</t>
         </is>
       </c>
     </row>
@@ -1436,29 +1436,29 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
+          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（94件）</t>
+          <t>3　本文の未確定箇所（98件）</t>
         </is>
       </c>
     </row>
@@ -2145,22 +2145,22 @@
       <c r="A56" s="6" t="inlineStr"/>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>注）本項に掲げた事項はいずれも検討されている段階のものであり、単位数、算定の要件及び施行の時期は示されていません。また、介護給付費分科会の資料の原本を確認できていないため、内容及び時期は［要確認］です。本計画は、これらを前提として見込量又は給付費を増減させることは行っていません。介護給付費分科会は介護報酬（単位数・算定の要件・運営の基準）を、社会保障審議会介</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2179,14 +2179,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2205,14 +2205,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2231,14 +2231,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2254,17 +2254,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2280,17 +2280,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2342,7 +2342,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2394,8 +2394,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
-注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2411,7 +2410,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2421,8 +2420,8 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
-注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
+          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
+注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2441,14 +2440,15 @@
           <t>第5節 在宅介護の実態</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
+注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2464,17 +2464,17 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2511,12 +2511,12 @@
       <c r="A70" s="6" t="inlineStr"/>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2552,8 +2552,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
-注）分母は地域包括ケア「見え</t>
+          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2569,7 +2568,7 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2579,7 +2578,8 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
+          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
+注）分母は地域包括ケア「見え</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
+          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 地域支援事業の実績</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -2650,14 +2650,14 @@
           <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2694,12 +2694,12 @@
       <c r="A77" s="6" t="inlineStr"/>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2728,14 +2728,14 @@
           <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2754,14 +2754,14 @@
           <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2772,22 +2772,22 @@
       <c r="A80" s="6" t="inlineStr"/>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr"/>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
@@ -2936,9 +2936,9 @@
           <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr"/>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr"/>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr"/>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr"/>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr"/>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr"/>
@@ -3110,12 +3110,12 @@
       <c r="A93" s="6" t="inlineStr"/>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
+          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
+          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr"/>
@@ -3170,14 +3170,14 @@
           <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
-      <c r="D95" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D95" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr"/>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr"/>
@@ -3274,15 +3274,14 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr"/>
@@ -3328,9 +3327,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3379,18 +3378,18 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D103" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr"/>
@@ -3406,17 +3405,18 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr"/>
@@ -3432,17 +3432,18 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D105" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr"/>
@@ -3468,89 +3469,90 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr"/>
+      <c r="G106" s="6" t="inlineStr"/>
+      <c r="H106" s="6" t="inlineStr"/>
+    </row>
+    <row r="107" ht="44" customHeight="1">
+      <c r="A107" s="6" t="inlineStr"/>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr"/>
+      <c r="G107" s="6" t="inlineStr"/>
+      <c r="H107" s="6" t="inlineStr"/>
+    </row>
+    <row r="108" ht="44" customHeight="1">
+      <c r="A108" s="6" t="inlineStr"/>
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr"/>
+      <c r="G108" s="6" t="inlineStr"/>
+      <c r="H108" s="6" t="inlineStr"/>
+    </row>
+    <row r="109" ht="44" customHeight="1">
+      <c r="A109" s="6" t="inlineStr"/>
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F106" s="6" t="inlineStr"/>
-      <c r="G106" s="6" t="inlineStr"/>
-      <c r="H106" s="6" t="inlineStr"/>
-    </row>
-    <row r="107" ht="44" customHeight="1">
-      <c r="A107" s="6" t="inlineStr"/>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D107" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F107" s="6" t="inlineStr"/>
-      <c r="G107" s="6" t="inlineStr"/>
-      <c r="H107" s="6" t="inlineStr"/>
-    </row>
-    <row r="108" ht="44" customHeight="1">
-      <c r="A108" s="6" t="inlineStr"/>
-      <c r="B108" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C108" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D108" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
-        </is>
-      </c>
-      <c r="F108" s="6" t="inlineStr"/>
-      <c r="G108" s="6" t="inlineStr"/>
-      <c r="H108" s="6" t="inlineStr"/>
-    </row>
-    <row r="109" ht="44" customHeight="1">
-      <c r="A109" s="6" t="inlineStr"/>
-      <c r="B109" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C109" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
-        <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
-        </is>
-      </c>
       <c r="F109" s="6" t="inlineStr"/>
       <c r="G109" s="6" t="inlineStr"/>
       <c r="H109" s="6" t="inlineStr"/>
@@ -3564,7 +3566,7 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
@@ -3574,8 +3576,7 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr"/>
@@ -3601,8 +3602,7 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr"/>
@@ -3628,8 +3628,7 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr"/>
@@ -3648,15 +3647,15 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr"/>
@@ -3672,7 +3671,7 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
@@ -3682,7 +3681,8 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr"/>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -3708,7 +3708,8 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr"/>
@@ -3724,7 +3725,7 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -3734,7 +3735,8 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr"/>
@@ -3750,17 +3752,17 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr"/>
@@ -3776,7 +3778,7 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D118" s="6" t="inlineStr">
@@ -3786,8 +3788,7 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
-注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr"/>
@@ -3803,7 +3804,7 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -3813,7 +3814,7 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr"/>
@@ -3832,14 +3833,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D120" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr"/>
@@ -3858,14 +3859,15 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
+注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr"/>
@@ -3891,8 +3893,7 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr"/>
@@ -3911,15 +3912,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr"/>
@@ -3938,14 +3938,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr"/>
@@ -3971,7 +3971,8 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr"/>
@@ -3990,14 +3991,15 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D126" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr"/>
@@ -4016,14 +4018,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D127" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr"/>
@@ -4049,115 +4051,115 @@
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr"/>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr"/>
+    </row>
+    <row r="129" ht="44" customHeight="1">
+      <c r="A129" s="6" t="inlineStr"/>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr"/>
+      <c r="G129" s="6" t="inlineStr"/>
+      <c r="H129" s="6" t="inlineStr"/>
+    </row>
+    <row r="130" ht="44" customHeight="1">
+      <c r="A130" s="6" t="inlineStr"/>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr"/>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="6" t="inlineStr"/>
+    </row>
+    <row r="131" ht="44" customHeight="1">
+      <c r="A131" s="6" t="inlineStr"/>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr"/>
+      <c r="G131" s="6" t="inlineStr"/>
+      <c r="H131" s="6" t="inlineStr"/>
+    </row>
+    <row r="132" ht="44" customHeight="1">
+      <c r="A132" s="6" t="inlineStr"/>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D132" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr"/>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="6" t="inlineStr"/>
-    </row>
-    <row r="129" ht="44" customHeight="1">
-      <c r="A129" s="6" t="inlineStr"/>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D129" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
-        </is>
-      </c>
-      <c r="F129" s="6" t="inlineStr"/>
-      <c r="G129" s="6" t="inlineStr"/>
-      <c r="H129" s="6" t="inlineStr"/>
-    </row>
-    <row r="130" ht="44" customHeight="1">
-      <c r="A130" s="6" t="inlineStr"/>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
-        </is>
-      </c>
-      <c r="F130" s="6" t="inlineStr"/>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="6" t="inlineStr"/>
-    </row>
-    <row r="131" ht="44" customHeight="1">
-      <c r="A131" s="6" t="inlineStr"/>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
-      <c r="F131" s="6" t="inlineStr"/>
-      <c r="G131" s="6" t="inlineStr"/>
-      <c r="H131" s="6" t="inlineStr"/>
-    </row>
-    <row r="132" ht="44" customHeight="1">
-      <c r="A132" s="6" t="inlineStr"/>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
       <c r="F132" s="6" t="inlineStr"/>
       <c r="G132" s="6" t="inlineStr"/>
       <c r="H132" s="6" t="inlineStr"/>
@@ -4174,15 +4176,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
-注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr"/>
@@ -4198,7 +4199,7 @@
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
@@ -4208,7 +4209,7 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr"/>
@@ -4224,7 +4225,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -4234,188 +4235,293 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr"/>
       <c r="G135" s="6" t="inlineStr"/>
       <c r="H135" s="6" t="inlineStr"/>
     </row>
-    <row r="137" ht="28" customHeight="1">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は29種の表に134箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+    <row r="136" ht="44" customHeight="1">
+      <c r="A136" s="6" t="inlineStr"/>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr"/>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr"/>
+    </row>
+    <row r="137" ht="44" customHeight="1">
+      <c r="A137" s="6" t="inlineStr"/>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr"/>
+      <c r="G137" s="6" t="inlineStr"/>
+      <c r="H137" s="6" t="inlineStr"/>
+    </row>
+    <row r="138" ht="44" customHeight="1">
+      <c r="A138" s="6" t="inlineStr"/>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr"/>
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="6" t="inlineStr"/>
+    </row>
+    <row r="139" ht="44" customHeight="1">
+      <c r="A139" s="6" t="inlineStr"/>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr"/>
+      <c r="G139" s="6" t="inlineStr"/>
+      <c r="H139" s="6" t="inlineStr"/>
+    </row>
+    <row r="141" ht="28" customHeight="1">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は30種の表に135箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="3" t="inlineStr">
+    <row r="143" ht="20" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="30" customHeight="1">
-      <c r="A140" s="4" t="inlineStr"/>
-      <c r="B140" s="4" t="inlineStr">
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="4" t="inlineStr"/>
+      <c r="B144" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C144" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D144" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
+      <c r="E144" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F140" s="4" t="inlineStr">
+      <c r="F144" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G140" s="4" t="inlineStr">
+      <c r="G144" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H140" s="4" t="inlineStr">
+      <c r="H144" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
         </is>
       </c>
     </row>
-    <row r="141" ht="44" customHeight="1">
-      <c r="A141" s="6" t="inlineStr"/>
-      <c r="B141" s="6" t="inlineStr">
+    <row r="145" ht="44" customHeight="1">
+      <c r="A145" s="6" t="inlineStr"/>
+      <c r="B145" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C141" s="6" t="inlineStr">
+      <c r="C145" s="6" t="inlineStr">
         <is>
           <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
-      <c r="D141" s="5" t="n">
+      <c r="D145" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E141" s="5" t="n">
+      <c r="E145" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F141" s="5" t="n">
+      <c r="F145" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G141" s="5" t="n">
+      <c r="G145" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H141" s="6" t="inlineStr">
+      <c r="H145" s="6" t="inlineStr">
         <is>
           <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="142" ht="44" customHeight="1">
-      <c r="A142" s="6" t="inlineStr"/>
-      <c r="B142" s="6" t="inlineStr">
+    <row r="146" ht="44" customHeight="1">
+      <c r="A146" s="6" t="inlineStr"/>
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C142" s="6" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
         <is>
           <t>第4節　計画期間</t>
         </is>
       </c>
-      <c r="D142" s="5" t="n">
+      <c r="D146" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E142" s="5" t="n">
+      <c r="E146" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F142" s="5" t="n">
+      <c r="F146" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G142" s="5" t="n">
+      <c r="G146" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H142" s="6" t="inlineStr">
+      <c r="H146" s="6" t="inlineStr">
         <is>
           <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="44" customHeight="1">
-      <c r="A143" s="6" t="inlineStr"/>
-      <c r="B143" s="6" t="inlineStr">
+    <row r="147" ht="44" customHeight="1">
+      <c r="A147" s="6" t="inlineStr"/>
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C143" s="6" t="inlineStr">
+      <c r="C147" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D143" s="5" t="n">
+      <c r="D147" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E143" s="5" t="n">
+      <c r="E147" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F143" s="5" t="n">
+      <c r="F147" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G143" s="5" t="n">
+      <c r="G147" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H143" s="6" t="inlineStr">
+      <c r="H147" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="44" customHeight="1">
-      <c r="A144" s="6" t="inlineStr"/>
-      <c r="B144" s="6" t="inlineStr">
+    <row r="148" ht="44" customHeight="1">
+      <c r="A148" s="6" t="inlineStr"/>
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C144" s="6" t="inlineStr">
+      <c r="C148" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D144" s="5" t="n">
+      <c r="D148" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E144" s="5" t="n">
+      <c r="E148" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F144" s="5" t="n">
+      <c r="F148" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G144" s="5" t="n">
+      <c r="G148" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H144" s="6" t="inlineStr">
+      <c r="H148" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="42" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
+    <row r="150" ht="42" customHeight="1">
+      <c r="A150" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は4節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -4426,12 +4532,12 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A146:H146"/>
-    <mergeCell ref="A139:H139"/>
+    <mergeCell ref="A143:H143"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A137:H137"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A150:H150"/>
+    <mergeCell ref="A141:H141"/>
     <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4444,7 +4550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4459,7 +4565,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（181件）</t>
+          <t>確認事項の棚卸し（184件）</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4619,7 @@
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は170件</t>
+          <t>完了・了承済を除く未回答は173件</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4631,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
@@ -4757,10 +4863,10 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>0</v>
@@ -4926,7 +5032,7 @@
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
@@ -5083,10 +5189,25 @@
       <c r="F42" s="6" t="inlineStr"/>
       <c r="G42" s="6" t="inlineStr"/>
     </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>注1）期限が令和8年8月以前のもの（87件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+    <row r="43" ht="18" customHeight="1">
+      <c r="A43" s="6" t="inlineStr"/>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町・事業者</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="6" t="inlineStr"/>
+      <c r="G43" s="6" t="inlineStr"/>
+    </row>
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>注1）期限が令和8年8月以前のもの（90件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（27件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -5094,12 +5215,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A44:G44"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A45:G45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6070,7 +6191,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議136・要確認90・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議136・要確認95・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -6182,7 +6303,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1024段落152表36図／228箇所</t>
+          <t>1027段落153表36図／233箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -6208,7 +6329,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>228＝228</t>
+          <t>233＝233</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -6234,7 +6355,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>228＝228</t>
+          <t>233＝233</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -6260,7 +6381,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>181件（未回答170件）</t>
+          <t>184件（未回答173件）</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -6286,7 +6407,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>181件／一意181件</t>
+          <t>184件／一意184件</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -6416,7 +6537,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み／61／228箇所（27％）</t>
+          <t>第4節 介護保険サービス等における施設の見込み／61／233箇所（26％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -6655,7 +6776,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は228箇所ある（要協議136・要確認90・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は233箇所ある（要協議136・要確認95・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -6678,7 +6799,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている170件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている173件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>233箇所</t>
+          <t>244箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議136・要確認95・要内訳2。本文98箇所・表30種135箇所（01シート）</t>
+          <t>要協議138・要確認104・要内訳2。本文103箇所・表31種141箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1027段落153表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1031段落153表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>233箇所のうち61箇所（26％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>244箇所のうち62箇所（25％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H150"/>
+  <dimension ref="A1:H155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1027段落153表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計233箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1031段落153表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計244箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -925,14 +925,14 @@
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="5" t="n">
-        <v>29</v>
+      <c r="D8" s="8" t="n">
+        <v>36</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -948,13 +948,13 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
@@ -1048,13 +1048,13 @@
       </c>
       <c r="C13" s="9" t="inlineStr"/>
       <c r="D13" s="10" t="n">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>2</v>
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>6</v>
@@ -1140,57 +1140,57 @@
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>No.86（交付金の控除）ほか</t>
-        </is>
-      </c>
+      <c r="H18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="6" t="inlineStr"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>No.86（交付金の控除）ほか</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="32" customHeight="1">
       <c r="A20" s="6" t="inlineStr"/>
@@ -1316,29 +1316,29 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>確認事項B No.19（医療側の連携の実施状況）</t>
+          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
         </is>
       </c>
     </row>
@@ -1346,29 +1346,29 @@
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
+          <t>確認事項B No.19（医療側の連携の実施状況）</t>
         </is>
       </c>
     </row>
@@ -1501,24 +1501,24 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>No.114（中長期推計の範囲）</t>
+          <t>No.3（町別人口）</t>
         </is>
       </c>
     </row>
@@ -1531,24 +1531,24 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>No.3（町別人口）</t>
+          <t>No.114（中長期推計の範囲）</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（98件）</t>
+          <t>3　本文の未確定箇所（103件）</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>注）本項に掲げた事項はいずれも検討されている段階のものであり、単位数、算定の要件及び施行の時期は示されていません。また、介護給付費分科会の資料の原本を確認できていないため、内容及び時期は［要確認］です。本計画は、これらを前提として見込量又は給付費を増減させることは行っていません。介護給付費分科会は介護報酬（単位数・算定の要件・運営の基準）を、社会保障審議会介</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2171,22 +2171,22 @@
       <c r="A57" s="6" t="inlineStr"/>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2205,14 +2205,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2231,14 +2231,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2257,14 +2257,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2280,17 +2280,17 @@
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
-        </is>
-      </c>
-      <c r="D61" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
+          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2306,7 +2306,7 @@
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D62" s="6" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2332,17 +2332,17 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2420,8 +2420,7 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
-注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
+          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2437,7 +2436,7 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2447,8 +2446,7 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
-注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2464,17 +2462,18 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 高齢者の生活実態</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
+注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2490,7 +2489,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2500,7 +2499,8 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
+          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
+注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2516,17 +2516,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2537,12 +2537,12 @@
       <c r="A71" s="6" t="inlineStr"/>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2563,12 +2563,12 @@
       <c r="A72" s="6" t="inlineStr"/>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2578,8 +2578,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
-注）分母は地域包括ケア「見え</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2595,7 +2594,7 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
@@ -2605,7 +2604,7 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
+          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2621,7 +2620,7 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2631,7 +2630,8 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
+          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
+注）分母は地域包括ケア「見え</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -2647,17 +2647,17 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 地域支援事業の実績</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr"/>
@@ -2702,14 +2702,14 @@
           <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2720,12 +2720,12 @@
       <c r="A78" s="6" t="inlineStr"/>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2746,22 +2746,22 @@
       <c r="A79" s="6" t="inlineStr"/>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr"/>
@@ -2798,12 +2798,12 @@
       <c r="A81" s="6" t="inlineStr"/>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr"/>
@@ -2824,22 +2824,22 @@
       <c r="A82" s="6" t="inlineStr"/>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr"/>
@@ -2962,9 +2962,9 @@
           <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
@@ -2985,17 +2985,17 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
-        </is>
-      </c>
-      <c r="D88" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr"/>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr"/>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr"/>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D91" s="6" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr"/>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr"/>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr"/>
@@ -3136,12 +3136,12 @@
       <c r="A94" s="6" t="inlineStr"/>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr"/>
@@ -3162,12 +3162,12 @@
       <c r="A95" s="6" t="inlineStr"/>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
+          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr"/>
@@ -3196,14 +3196,14 @@
           <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
-      <c r="D96" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr"/>
@@ -3222,14 +3222,14 @@
           <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
-      <c r="D97" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D97" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr"/>
@@ -3300,15 +3300,14 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr"/>
@@ -3327,15 +3326,14 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr"/>
@@ -3361,8 +3359,7 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr"/>
@@ -3408,9 +3405,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D104" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
@@ -3459,18 +3456,18 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D106" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr"/>
@@ -3486,17 +3483,18 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr"/>
@@ -3512,17 +3510,18 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D108" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr"/>
@@ -3548,89 +3547,90 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr"/>
+      <c r="G109" s="6" t="inlineStr"/>
+      <c r="H109" s="6" t="inlineStr"/>
+    </row>
+    <row r="110" ht="44" customHeight="1">
+      <c r="A110" s="6" t="inlineStr"/>
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr"/>
+      <c r="G110" s="6" t="inlineStr"/>
+      <c r="H110" s="6" t="inlineStr"/>
+    </row>
+    <row r="111" ht="44" customHeight="1">
+      <c r="A111" s="6" t="inlineStr"/>
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr"/>
+      <c r="G111" s="6" t="inlineStr"/>
+      <c r="H111" s="6" t="inlineStr"/>
+    </row>
+    <row r="112" ht="44" customHeight="1">
+      <c r="A112" s="6" t="inlineStr"/>
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr"/>
-      <c r="G109" s="6" t="inlineStr"/>
-      <c r="H109" s="6" t="inlineStr"/>
-    </row>
-    <row r="110" ht="44" customHeight="1">
-      <c r="A110" s="6" t="inlineStr"/>
-      <c r="B110" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D110" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F110" s="6" t="inlineStr"/>
-      <c r="G110" s="6" t="inlineStr"/>
-      <c r="H110" s="6" t="inlineStr"/>
-    </row>
-    <row r="111" ht="44" customHeight="1">
-      <c r="A111" s="6" t="inlineStr"/>
-      <c r="B111" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C111" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D111" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
-        <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
-        </is>
-      </c>
-      <c r="F111" s="6" t="inlineStr"/>
-      <c r="G111" s="6" t="inlineStr"/>
-      <c r="H111" s="6" t="inlineStr"/>
-    </row>
-    <row r="112" ht="44" customHeight="1">
-      <c r="A112" s="6" t="inlineStr"/>
-      <c r="B112" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C112" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D112" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
-        <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
-        </is>
-      </c>
       <c r="F112" s="6" t="inlineStr"/>
       <c r="G112" s="6" t="inlineStr"/>
       <c r="H112" s="6" t="inlineStr"/>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
@@ -3654,8 +3654,7 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr"/>
@@ -3681,8 +3680,7 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr"/>
@@ -3701,15 +3699,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr"/>
@@ -3735,8 +3732,7 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr"/>
@@ -3752,7 +3748,7 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
@@ -3762,7 +3758,8 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr"/>
@@ -3778,17 +3775,18 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr"/>
@@ -3804,7 +3802,7 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D119" s="6" t="inlineStr">
@@ -3814,7 +3812,8 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr"/>
@@ -3830,7 +3829,7 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D120" s="6" t="inlineStr">
@@ -3840,7 +3839,8 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr"/>
@@ -3856,18 +3856,17 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
-注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr"/>
@@ -3883,7 +3882,7 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -3893,7 +3892,7 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr"/>
@@ -3909,17 +3908,17 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr"/>
@@ -3938,14 +3937,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D124" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr"/>
@@ -3971,8 +3970,8 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
+注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr"/>
@@ -3998,8 +3997,7 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr"/>
@@ -4018,14 +4016,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D127" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr"/>
@@ -4044,14 +4042,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr"/>
@@ -4070,14 +4068,15 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr"/>
@@ -4103,7 +4102,8 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr"/>
@@ -4122,14 +4122,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr"/>
@@ -4155,142 +4155,141 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr"/>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr"/>
+    </row>
+    <row r="133" ht="44" customHeight="1">
+      <c r="A133" s="6" t="inlineStr"/>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr"/>
+      <c r="G133" s="6" t="inlineStr"/>
+      <c r="H133" s="6" t="inlineStr"/>
+    </row>
+    <row r="134" ht="44" customHeight="1">
+      <c r="A134" s="6" t="inlineStr"/>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D134" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr"/>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr"/>
+    </row>
+    <row r="135" ht="44" customHeight="1">
+      <c r="A135" s="6" t="inlineStr"/>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr"/>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr"/>
+    </row>
+    <row r="136" ht="44" customHeight="1">
+      <c r="A136" s="6" t="inlineStr"/>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があり、当広域連合が対象となる場合は単価を上げる向きに働きます。いずれの</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr"/>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr"/>
+    </row>
+    <row r="137" ht="44" customHeight="1">
+      <c r="A137" s="6" t="inlineStr"/>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr"/>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr"/>
-    </row>
-    <row r="133" ht="44" customHeight="1">
-      <c r="A133" s="6" t="inlineStr"/>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D133" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
-        </is>
-      </c>
-      <c r="F133" s="6" t="inlineStr"/>
-      <c r="G133" s="6" t="inlineStr"/>
-      <c r="H133" s="6" t="inlineStr"/>
-    </row>
-    <row r="134" ht="44" customHeight="1">
-      <c r="A134" s="6" t="inlineStr"/>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
-        </is>
-      </c>
-      <c r="F134" s="6" t="inlineStr"/>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr"/>
-    </row>
-    <row r="135" ht="44" customHeight="1">
-      <c r="A135" s="6" t="inlineStr"/>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
-      <c r="F135" s="6" t="inlineStr"/>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr"/>
-    </row>
-    <row r="136" ht="44" customHeight="1">
-      <c r="A136" s="6" t="inlineStr"/>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
-      <c r="F136" s="6" t="inlineStr"/>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr"/>
-    </row>
-    <row r="137" ht="44" customHeight="1">
-      <c r="A137" s="6" t="inlineStr"/>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
-        <is>
-          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
-注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
-        </is>
-      </c>
       <c r="F137" s="6" t="inlineStr"/>
       <c r="G137" s="6" t="inlineStr"/>
       <c r="H137" s="6" t="inlineStr"/>
@@ -4304,17 +4303,17 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr"/>
@@ -4330,7 +4329,7 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D139" s="6" t="inlineStr">
@@ -4340,188 +4339,319 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr"/>
       <c r="G139" s="6" t="inlineStr"/>
       <c r="H139" s="6" t="inlineStr"/>
     </row>
-    <row r="141" ht="28" customHeight="1">
-      <c r="A141" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は30種の表に135箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+    <row r="140" ht="44" customHeight="1">
+      <c r="A140" s="6" t="inlineStr"/>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr"/>
+      <c r="G140" s="6" t="inlineStr"/>
+      <c r="H140" s="6" t="inlineStr"/>
+    </row>
+    <row r="141" ht="44" customHeight="1">
+      <c r="A141" s="6" t="inlineStr"/>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr"/>
+      <c r="G141" s="6" t="inlineStr"/>
+      <c r="H141" s="6" t="inlineStr"/>
+    </row>
+    <row r="142" ht="44" customHeight="1">
+      <c r="A142" s="6" t="inlineStr"/>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr"/>
+      <c r="G142" s="6" t="inlineStr"/>
+      <c r="H142" s="6" t="inlineStr"/>
+    </row>
+    <row r="143" ht="44" customHeight="1">
+      <c r="A143" s="6" t="inlineStr"/>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr"/>
+      <c r="G143" s="6" t="inlineStr"/>
+      <c r="H143" s="6" t="inlineStr"/>
+    </row>
+    <row r="144" ht="44" customHeight="1">
+      <c r="A144" s="6" t="inlineStr"/>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr"/>
+      <c r="G144" s="6" t="inlineStr"/>
+      <c r="H144" s="6" t="inlineStr"/>
+    </row>
+    <row r="146" ht="28" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は31種の表に141箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="143" ht="20" customHeight="1">
-      <c r="A143" s="3" t="inlineStr">
+    <row r="148" ht="20" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="30" customHeight="1">
-      <c r="A144" s="4" t="inlineStr"/>
-      <c r="B144" s="4" t="inlineStr">
+    <row r="149" ht="30" customHeight="1">
+      <c r="A149" s="4" t="inlineStr"/>
+      <c r="B149" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C144" s="4" t="inlineStr">
+      <c r="C149" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D144" s="4" t="inlineStr">
+      <c r="D149" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
+      <c r="E149" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F144" s="4" t="inlineStr">
+      <c r="F149" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G144" s="4" t="inlineStr">
+      <c r="G149" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H144" s="4" t="inlineStr">
+      <c r="H149" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
         </is>
       </c>
     </row>
-    <row r="145" ht="44" customHeight="1">
-      <c r="A145" s="6" t="inlineStr"/>
-      <c r="B145" s="6" t="inlineStr">
+    <row r="150" ht="44" customHeight="1">
+      <c r="A150" s="6" t="inlineStr"/>
+      <c r="B150" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C145" s="6" t="inlineStr">
+      <c r="C150" s="6" t="inlineStr">
         <is>
           <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
-      <c r="D145" s="5" t="n">
+      <c r="D150" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E145" s="5" t="n">
+      <c r="E150" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F145" s="5" t="n">
+      <c r="F150" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G145" s="5" t="n">
+      <c r="G150" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H145" s="6" t="inlineStr">
+      <c r="H150" s="6" t="inlineStr">
         <is>
           <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="146" ht="44" customHeight="1">
-      <c r="A146" s="6" t="inlineStr"/>
-      <c r="B146" s="6" t="inlineStr">
+    <row r="151" ht="44" customHeight="1">
+      <c r="A151" s="6" t="inlineStr"/>
+      <c r="B151" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C146" s="6" t="inlineStr">
+      <c r="C151" s="6" t="inlineStr">
         <is>
           <t>第4節　計画期間</t>
         </is>
       </c>
-      <c r="D146" s="5" t="n">
+      <c r="D151" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E146" s="5" t="n">
+      <c r="E151" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F146" s="5" t="n">
+      <c r="F151" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G146" s="5" t="n">
+      <c r="G151" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H146" s="6" t="inlineStr">
+      <c r="H151" s="6" t="inlineStr">
         <is>
           <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="147" ht="44" customHeight="1">
-      <c r="A147" s="6" t="inlineStr"/>
-      <c r="B147" s="6" t="inlineStr">
+    <row r="152" ht="44" customHeight="1">
+      <c r="A152" s="6" t="inlineStr"/>
+      <c r="B152" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C147" s="6" t="inlineStr">
+      <c r="C152" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D147" s="5" t="n">
+      <c r="D152" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E147" s="5" t="n">
+      <c r="E152" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F147" s="5" t="n">
+      <c r="F152" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G147" s="5" t="n">
+      <c r="G152" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H147" s="6" t="inlineStr">
+      <c r="H152" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="148" ht="44" customHeight="1">
-      <c r="A148" s="6" t="inlineStr"/>
-      <c r="B148" s="6" t="inlineStr">
+    <row r="153" ht="44" customHeight="1">
+      <c r="A153" s="6" t="inlineStr"/>
+      <c r="B153" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr">
+      <c r="C153" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D148" s="5" t="n">
+      <c r="D153" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E148" s="5" t="n">
+      <c r="E153" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F148" s="5" t="n">
+      <c r="F153" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G148" s="5" t="n">
+      <c r="G153" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H148" s="6" t="inlineStr">
+      <c r="H153" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="42" customHeight="1">
-      <c r="A150" s="7" t="inlineStr">
+    <row r="155" ht="42" customHeight="1">
+      <c r="A155" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は4節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -4532,12 +4662,12 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A143:H143"/>
+    <mergeCell ref="A146:H146"/>
+    <mergeCell ref="A155:H155"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A148:H148"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A150:H150"/>
-    <mergeCell ref="A141:H141"/>
     <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4550,7 +4680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4631,7 +4761,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
@@ -4773,62 +4903,54 @@
       <c r="F16" s="6" t="inlineStr"/>
       <c r="G16" s="6" t="inlineStr"/>
     </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="6" t="inlineStr"/>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>一部提供（R8.10.14）</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>2　期限別（未回答のみ）</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="B19" s="4" t="inlineStr">
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="4" t="inlineStr"/>
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>うち計画素案を止めている</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>うち第1次概算を止めている</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr"/>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="6" t="inlineStr"/>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>期限が過ぎているもの</t>
         </is>
       </c>
     </row>
@@ -4836,14 +4958,14 @@
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
@@ -4859,14 +4981,14 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>0</v>
@@ -4882,14 +5004,14 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D23" s="5" t="n">
         <v>5</v>
-      </c>
-      <c r="D23" s="5" t="n">
-        <v>0</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
@@ -4905,33 +5027,37 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>79</v>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="6" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>期限が過ぎているもの</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="6" t="inlineStr"/>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>R8.9.2</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>0</v>
@@ -4943,14 +5069,14 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.9.2</t>
         </is>
       </c>
       <c r="C26" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" s="5" t="n">
         <v>0</v>
@@ -4962,14 +5088,14 @@
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>0</v>
@@ -4981,14 +5107,14 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R9.4</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>0</v>
@@ -4996,58 +5122,62 @@
       <c r="F28" s="6" t="inlineStr"/>
       <c r="G28" s="6" t="inlineStr"/>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="6" t="inlineStr"/>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr"/>
+      <c r="G29" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>3　確認先別（未回答のみ）</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="4" t="inlineStr"/>
-      <c r="B31" s="4" t="inlineStr">
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr"/>
-      <c r="G31" s="4" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr"/>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="18" customHeight="1">
-      <c r="A32" s="6" t="inlineStr"/>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
@@ -5058,11 +5188,11 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="6" t="inlineStr"/>
@@ -5073,11 +5203,11 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="6" t="inlineStr"/>
@@ -5088,11 +5218,11 @@
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="6" t="inlineStr"/>
@@ -5103,11 +5233,11 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
       <c r="E37" s="6" t="inlineStr"/>
@@ -5118,7 +5248,7 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>発注者・東神楽町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -5133,11 +5263,11 @@
       <c r="A39" s="6" t="inlineStr"/>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者・東神楽町</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D39" s="6" t="inlineStr"/>
       <c r="E39" s="6" t="inlineStr"/>
@@ -5148,7 +5278,7 @@
       <c r="A40" s="6" t="inlineStr"/>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
@@ -5163,7 +5293,7 @@
       <c r="A41" s="6" t="inlineStr"/>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>北海道上川総合振興局</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
@@ -5178,7 +5308,7 @@
       <c r="A42" s="6" t="inlineStr"/>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
@@ -5193,7 +5323,7 @@
       <c r="A43" s="6" t="inlineStr"/>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町・事業者</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="C43" s="5" t="n">
@@ -5204,8 +5334,23 @@
       <c r="F43" s="6" t="inlineStr"/>
       <c r="G43" s="6" t="inlineStr"/>
     </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="6" t="inlineStr"/>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町・事業者</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="6" t="inlineStr"/>
+      <c r="G44" s="6" t="inlineStr"/>
+    </row>
+    <row r="46" ht="42" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>注1）期限が令和8年8月以前のもの（90件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（27件）は、3町への照会の様式と時期の決定を先に要します。
@@ -5216,11 +5361,11 @@
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A46:G46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6191,7 +6336,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議136・要確認95・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議138・要確認104・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -6303,7 +6448,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1027段落153表36図／233箇所</t>
+          <t>1031段落153表36図／244箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -6329,7 +6474,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>233＝233</t>
+          <t>244＝244</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -6355,7 +6500,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>233＝233</t>
+          <t>244＝244</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -6537,7 +6682,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み／61／233箇所（26％）</t>
+          <t>第4節 介護保険サービス等における施設の見込み／62／244箇所（25％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -6776,7 +6921,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は233箇所ある（要協議136・要確認95・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は244箇所ある（要協議138・要確認104・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>244箇所</t>
+          <t>253箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議138・要確認104・要内訳2。本文103箇所・表31種141箇所（01シート）</t>
+          <t>要協議142・要確認109・要内訳2。本文109箇所・表31種144箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1031段落153表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1038段落153表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>244箇所のうち62箇所（25％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>253箇所のうち62箇所（25％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H155"/>
+  <dimension ref="A1:H162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1031段落153表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計244箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1038段落153表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計253箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>73</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -900,10 +900,10 @@
       </c>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="8" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>13</v>
@@ -926,13 +926,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="8" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -948,13 +948,13 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>4</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
@@ -1048,13 +1048,13 @@
       </c>
       <c r="C13" s="9" t="inlineStr"/>
       <c r="D13" s="10" t="n">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>2</v>
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>7</v>
@@ -1286,29 +1286,29 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1316,29 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
         <v>9</v>
       </c>
       <c r="E24" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="F24" s="5" t="n">
-        <v>6</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
+          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
         </is>
       </c>
     </row>
@@ -1376,29 +1376,29 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
         <v>7</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>No.75（代表KPIの再整理案）</t>
+          <t>No.8（3調査の点検事項）</t>
         </is>
       </c>
     </row>
@@ -1406,29 +1406,29 @@
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>No.8（3調査の点検事項）</t>
+          <t>No.75（代表KPIの再整理案）</t>
         </is>
       </c>
     </row>
@@ -1720,86 +1720,86 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>資料7 図表番号一覧</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>（節の前）</t>
+          <t>第7節 低所得者支援</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="6" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>資料7 図表番号一覧</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>（節の前）</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="G39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="6" t="inlineStr"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>3　本文の未確定箇所（103件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="4" t="inlineStr"/>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>3　本文の未確定箇所（109件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>本文（抜粋）</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr"/>
-    </row>
-    <row r="42" ht="44" customHeight="1">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>注）各法律の条文の受領前であるため、条番号のみを記載し項番号は記載していません［要確認］。構成3町の高齢者福祉計画が老人福祉法第20条の8による市町村老人福祉計画に当たることの確認、成年後見制度の利用の促進に関する施策についての基本的な計画の構成3町における策定の状況、及び一体のものとして作成する方法は構成3町と協議して定めます［要協議］。</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="6" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="6" t="inlineStr"/>
@@ -1813,9 +1813,9 @@
           <t>第2節　計画の位置付け</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
+          <t>注）各法律の条文の受領前であるため、条番号のみを記載し項番号は記載していません［要確認］。構成3町の高齢者福祉計画が老人福祉法第20条の8による市町村老人福祉計画に当たることの確認、成年後見制度の利用の促進に関する施策についての基本的な計画の構成3町における策定の状況、及び一体のものとして作成する方法は構成3町と協議して定めます［要協議］。</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1862,17 +1862,17 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第6節　計画の進行管理・推進体制</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>注）北海道の高齢者保健福祉計画が定める評価指標のうち「取り組んでいる市町村数」を単位とするものは、1保険者である当広域連合にそのまま適用することができません。読替えの方法は第8節に掲げます。北海道から広域連合に対する読替えの考え方は示されていないため、本計画は当広域連合の整理によっており、考え方が示された場合はこれに合わせて改めます［要確認］。</t>
+          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
+          <t>第6節　計画の進行管理・推進体制</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1924,8 +1924,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
-注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
+          <t>注）北海道の高齢者保健福祉計画が定める評価指標のうち「取り組んでいる市町村数」を単位とするものは、1保険者である当広域連合にそのまま適用することができません。読替えの方法は第8節に掲げます。北海道から広域連合に対する読替えの考え方は示されていないため、本計画は当広域連合の整理によっており、考え方が示された場合はこれに合わせて改めます［要確認］。</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1968,7 +1967,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1978,7 +1977,8 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条は、市町村介護保険事業計画は医療計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合は、在宅医療・介護連携（第5章 基本目標1）、協力医療機関の確保（第1章第9節1）並びに施設・居住系サービスの整備（第6章第5節）において図ります。北海道の第10期高齢者保健福祉計画・介護保険事業支援計画</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
+注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
+          <t>介護保険法第117条は、市町村介護保険事業計画は医療計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合は、在宅医療・介護連携（第5章 基本目標1）、協力医療機関の確保（第1章第9節1）並びに施設・居住系サービスの整備（第6章第5節）において図ります。北海道の第10期高齢者保健福祉計画・介護保険事業支援計画</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2075,14 +2075,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
+          <t>要件を満たす協力医療機関を定めることの義務化には令和9年3月31日までの経過措置が設けられており、本計画の初日である令和9年4月1日から義務となります。国は、全国における要件を満たす体制の整備割合を介護老人福祉施設67.9％、介護老人保健施設83.3％、介護医療院84.9％としたうえで、定めの状況について集計していないと回答した自治体が一定程度存在し、地域差</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
+          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2127,9 +2127,9 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -2179,14 +2179,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2197,22 +2197,22 @@
       <c r="A58" s="6" t="inlineStr"/>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2223,12 +2223,12 @@
       <c r="A59" s="6" t="inlineStr"/>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D59" s="6" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
+          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
+          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2309,14 +2309,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2332,17 +2332,17 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
+          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D64" s="6" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2384,17 +2384,17 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D67" s="6" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr">
@@ -2472,8 +2472,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
-注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
+          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2489,7 +2488,7 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
@@ -2499,8 +2498,7 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
-注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
+          <t>本広域連合の訪問介護の1人1月あたり利用回数は全国の1.87倍であり（第2節1）、区域内の訪問介護13事業所のうち8事業所が住まいに併設しています（第6節）。上記の全国の実態と同じ構造によるものと考えられますが、同一の建物に居住する方への提供の割合は把握していないため、本計画では要因を特定していません［要確認］。</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2516,17 +2514,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 高齢者の生活実態</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2542,7 +2540,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2552,7 +2550,8 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
+          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
+注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2568,7 +2567,7 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="D72" s="6" t="inlineStr">
@@ -2578,7 +2577,8 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
+注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2589,22 +2589,22 @@
       <c r="A73" s="6" t="inlineStr"/>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
-        </is>
-      </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2615,12 +2615,12 @@
       <c r="A74" s="6" t="inlineStr"/>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2630,8 +2630,7 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
-注）分母は地域包括ケア「見え</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -2642,12 +2641,12 @@
       <c r="A75" s="6" t="inlineStr"/>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2657,7 +2656,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2673,7 +2672,7 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2683,7 +2682,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
+          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr"/>
@@ -2699,17 +2698,18 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 第9期計画の基本目標</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
+注）分母は地域包括ケア「見え</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2772,22 +2772,22 @@
       <c r="A80" s="6" t="inlineStr"/>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D80" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr"/>
@@ -2798,22 +2798,22 @@
       <c r="A81" s="6" t="inlineStr"/>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr"/>
@@ -2824,12 +2824,12 @@
       <c r="A82" s="6" t="inlineStr"/>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
@@ -2850,22 +2850,22 @@
       <c r="A83" s="6" t="inlineStr"/>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
-        </is>
-      </c>
-      <c r="D83" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr"/>
@@ -2876,12 +2876,12 @@
       <c r="A84" s="6" t="inlineStr"/>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr"/>
@@ -2902,22 +2902,22 @@
       <c r="A85" s="6" t="inlineStr"/>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr"/>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr"/>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr"/>
@@ -3014,9 +3014,9 @@
           <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
@@ -3037,17 +3037,17 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
-        </is>
-      </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr"/>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
-        </is>
-      </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr"/>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr"/>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D93" s="6" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr"/>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D94" s="6" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr"/>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D95" s="6" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr"/>
@@ -3188,12 +3188,12 @@
       <c r="A96" s="6" t="inlineStr"/>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D96" s="6" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr"/>
@@ -3214,12 +3214,12 @@
       <c r="A97" s="6" t="inlineStr"/>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D97" s="6" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr"/>
@@ -3240,12 +3240,12 @@
       <c r="A98" s="6" t="inlineStr"/>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>BCPについて、策定率、訓練の実施状況、相互応援協定の締結状況を把握します。策定は令和6年度から義務化されており、指定・指導の際に確認できます。国は、BCPの実効性を高めるには行政や他の介護施設等との平時からの連携が重要であるとしたうえで、市区町村の約6割が介護事業所等に対して業務継続を可能とする備えに関する助言等を行っていない状況にあることを示しています。</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr"/>
@@ -3266,12 +3266,12 @@
       <c r="A99" s="6" t="inlineStr"/>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>介護事故の防止について、事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行います。国は、事故防止を推進するための国・都道府県・市町村の役割として、市町村が事故が発生した事業所からの報告の受付並びに報告内容の集計及び傾向の把握を担うことを示し、介護サービス情報公表システムを活用した報告のための仕組みの構築と報告様式の見直しを検討しています（第1章第9</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr"/>
@@ -3292,22 +3292,22 @@
       <c r="A100" s="6" t="inlineStr"/>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D100" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D100" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr"/>
@@ -3323,17 +3323,17 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr"/>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr"/>
@@ -3375,18 +3375,17 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr"/>
@@ -3402,18 +3401,17 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr"/>
@@ -3432,15 +3430,14 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr"/>
@@ -3459,15 +3456,14 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D106" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr"/>
@@ -3486,15 +3482,14 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D107" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr"/>
@@ -3537,18 +3532,18 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D109" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr"/>
@@ -3564,7 +3559,7 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -3574,7 +3569,8 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr"/>
@@ -3590,17 +3586,18 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D111" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr"/>
@@ -3616,179 +3613,181 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr"/>
+      <c r="G112" s="6" t="inlineStr"/>
+      <c r="H112" s="6" t="inlineStr"/>
+    </row>
+    <row r="113" ht="44" customHeight="1">
+      <c r="A113" s="6" t="inlineStr"/>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr"/>
+      <c r="G113" s="6" t="inlineStr"/>
+      <c r="H113" s="6" t="inlineStr"/>
+    </row>
+    <row r="114" ht="44" customHeight="1">
+      <c r="A114" s="6" t="inlineStr"/>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr"/>
+      <c r="G114" s="6" t="inlineStr"/>
+      <c r="H114" s="6" t="inlineStr"/>
+    </row>
+    <row r="115" ht="44" customHeight="1">
+      <c r="A115" s="6" t="inlineStr"/>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D112" s="11" t="inlineStr">
+      <c r="D115" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr"/>
+      <c r="G115" s="6" t="inlineStr"/>
+      <c r="H115" s="6" t="inlineStr"/>
+    </row>
+    <row r="116" ht="44" customHeight="1">
+      <c r="A116" s="6" t="inlineStr"/>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr"/>
+      <c r="G116" s="6" t="inlineStr"/>
+      <c r="H116" s="6" t="inlineStr"/>
+    </row>
+    <row r="117" ht="44" customHeight="1">
+      <c r="A117" s="6" t="inlineStr"/>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr"/>
+      <c r="G117" s="6" t="inlineStr"/>
+      <c r="H117" s="6" t="inlineStr"/>
+    </row>
+    <row r="118" ht="44" customHeight="1">
+      <c r="A118" s="6" t="inlineStr"/>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
         <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F112" s="6" t="inlineStr"/>
-      <c r="G112" s="6" t="inlineStr"/>
-      <c r="H112" s="6" t="inlineStr"/>
-    </row>
-    <row r="113" ht="44" customHeight="1">
-      <c r="A113" s="6" t="inlineStr"/>
-      <c r="B113" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C113" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D113" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F113" s="6" t="inlineStr"/>
-      <c r="G113" s="6" t="inlineStr"/>
-      <c r="H113" s="6" t="inlineStr"/>
-    </row>
-    <row r="114" ht="44" customHeight="1">
-      <c r="A114" s="6" t="inlineStr"/>
-      <c r="B114" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C114" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D114" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
-        </is>
-      </c>
-      <c r="F114" s="6" t="inlineStr"/>
-      <c r="G114" s="6" t="inlineStr"/>
-      <c r="H114" s="6" t="inlineStr"/>
-    </row>
-    <row r="115" ht="44" customHeight="1">
-      <c r="A115" s="6" t="inlineStr"/>
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D115" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
-        </is>
-      </c>
-      <c r="F115" s="6" t="inlineStr"/>
-      <c r="G115" s="6" t="inlineStr"/>
-      <c r="H115" s="6" t="inlineStr"/>
-    </row>
-    <row r="116" ht="44" customHeight="1">
-      <c r="A116" s="6" t="inlineStr"/>
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
-        </is>
-      </c>
-      <c r="F116" s="6" t="inlineStr"/>
-      <c r="G116" s="6" t="inlineStr"/>
-      <c r="H116" s="6" t="inlineStr"/>
-    </row>
-    <row r="117" ht="44" customHeight="1">
-      <c r="A117" s="6" t="inlineStr"/>
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D117" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F117" s="6" t="inlineStr"/>
-      <c r="G117" s="6" t="inlineStr"/>
-      <c r="H117" s="6" t="inlineStr"/>
-    </row>
-    <row r="118" ht="44" customHeight="1">
-      <c r="A118" s="6" t="inlineStr"/>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D118" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
       <c r="F118" s="6" t="inlineStr"/>
       <c r="G118" s="6" t="inlineStr"/>
       <c r="H118" s="6" t="inlineStr"/>
@@ -3802,18 +3801,17 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr"/>
@@ -3832,15 +3830,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr"/>
@@ -3856,7 +3853,7 @@
       </c>
       <c r="C121" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
@@ -3866,7 +3863,7 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr"/>
@@ -3882,7 +3879,7 @@
       </c>
       <c r="C122" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
@@ -3892,7 +3889,7 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr"/>
@@ -3908,17 +3905,18 @@
       </c>
       <c r="C123" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr"/>
@@ -3934,17 +3932,18 @@
       </c>
       <c r="C124" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr"/>
@@ -3960,7 +3959,7 @@
       </c>
       <c r="C125" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D125" s="6" t="inlineStr">
@@ -3970,8 +3969,8 @@
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
-注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr"/>
@@ -3987,7 +3986,7 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D126" s="6" t="inlineStr">
@@ -3997,7 +3996,8 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr"/>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr"/>
@@ -4039,17 +4039,17 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D128" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr"/>
@@ -4065,7 +4065,7 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -4075,8 +4075,7 @@
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr"/>
@@ -4102,8 +4101,7 @@
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr"/>
@@ -4129,7 +4127,8 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
+注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr"/>
@@ -4155,7 +4154,7 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr"/>
@@ -4181,7 +4180,7 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr"/>
@@ -4200,14 +4199,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D134" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr"/>
@@ -4226,14 +4225,15 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D135" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr"/>
@@ -4259,7 +4259,8 @@
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があり、当広域連合が対象となる場合は単価を上げる向きに働きます。いずれの</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr"/>
@@ -4285,168 +4286,167 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr"/>
+      <c r="G137" s="6" t="inlineStr"/>
+      <c r="H137" s="6" t="inlineStr"/>
+    </row>
+    <row r="138" ht="44" customHeight="1">
+      <c r="A138" s="6" t="inlineStr"/>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr"/>
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="6" t="inlineStr"/>
+    </row>
+    <row r="139" ht="44" customHeight="1">
+      <c r="A139" s="6" t="inlineStr"/>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr"/>
+      <c r="G139" s="6" t="inlineStr"/>
+      <c r="H139" s="6" t="inlineStr"/>
+    </row>
+    <row r="140" ht="44" customHeight="1">
+      <c r="A140" s="6" t="inlineStr"/>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F140" s="6" t="inlineStr"/>
+      <c r="G140" s="6" t="inlineStr"/>
+      <c r="H140" s="6" t="inlineStr"/>
+    </row>
+    <row r="141" ht="44" customHeight="1">
+      <c r="A141" s="6" t="inlineStr"/>
+      <c r="B141" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C141" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E141" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F141" s="6" t="inlineStr"/>
+      <c r="G141" s="6" t="inlineStr"/>
+      <c r="H141" s="6" t="inlineStr"/>
+    </row>
+    <row r="142" ht="44" customHeight="1">
+      <c r="A142" s="6" t="inlineStr"/>
+      <c r="B142" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C142" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D142" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E142" s="6" t="inlineStr">
+        <is>
+          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があり、当広域連合が対象となる場合は単価を上げる向きに働きます。いずれの</t>
+        </is>
+      </c>
+      <c r="F142" s="6" t="inlineStr"/>
+      <c r="G142" s="6" t="inlineStr"/>
+      <c r="H142" s="6" t="inlineStr"/>
+    </row>
+    <row r="143" ht="44" customHeight="1">
+      <c r="A143" s="6" t="inlineStr"/>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E143" s="6" t="inlineStr">
+        <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F137" s="6" t="inlineStr"/>
-      <c r="G137" s="6" t="inlineStr"/>
-      <c r="H137" s="6" t="inlineStr"/>
-    </row>
-    <row r="138" ht="44" customHeight="1">
-      <c r="A138" s="6" t="inlineStr"/>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D138" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
-        </is>
-      </c>
-      <c r="F138" s="6" t="inlineStr"/>
-      <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="6" t="inlineStr"/>
-    </row>
-    <row r="139" ht="44" customHeight="1">
-      <c r="A139" s="6" t="inlineStr"/>
-      <c r="B139" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
-        </is>
-      </c>
-      <c r="F139" s="6" t="inlineStr"/>
-      <c r="G139" s="6" t="inlineStr"/>
-      <c r="H139" s="6" t="inlineStr"/>
-    </row>
-    <row r="140" ht="44" customHeight="1">
-      <c r="A140" s="6" t="inlineStr"/>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
-      <c r="F140" s="6" t="inlineStr"/>
-      <c r="G140" s="6" t="inlineStr"/>
-      <c r="H140" s="6" t="inlineStr"/>
-    </row>
-    <row r="141" ht="44" customHeight="1">
-      <c r="A141" s="6" t="inlineStr"/>
-      <c r="B141" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C141" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E141" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
-      <c r="F141" s="6" t="inlineStr"/>
-      <c r="G141" s="6" t="inlineStr"/>
-      <c r="H141" s="6" t="inlineStr"/>
-    </row>
-    <row r="142" ht="44" customHeight="1">
-      <c r="A142" s="6" t="inlineStr"/>
-      <c r="B142" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C142" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
-注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
-        </is>
-      </c>
-      <c r="F142" s="6" t="inlineStr"/>
-      <c r="G142" s="6" t="inlineStr"/>
-      <c r="H142" s="6" t="inlineStr"/>
-    </row>
-    <row r="143" ht="44" customHeight="1">
-      <c r="A143" s="6" t="inlineStr"/>
-      <c r="B143" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C143" s="6" t="inlineStr">
-        <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
-        </is>
-      </c>
       <c r="F143" s="6" t="inlineStr"/>
       <c r="G143" s="6" t="inlineStr"/>
       <c r="H143" s="6" t="inlineStr"/>
@@ -4460,198 +4460,381 @@
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr"/>
       <c r="G144" s="6" t="inlineStr"/>
       <c r="H144" s="6" t="inlineStr"/>
     </row>
-    <row r="146" ht="28" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は31種の表に141箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
-注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="20" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="30" customHeight="1">
-      <c r="A149" s="4" t="inlineStr"/>
-      <c r="B149" s="4" t="inlineStr">
-        <is>
-          <t>章</t>
-        </is>
-      </c>
-      <c r="C149" s="4" t="inlineStr">
-        <is>
-          <t>節</t>
-        </is>
-      </c>
-      <c r="D149" s="4" t="inlineStr">
-        <is>
-          <t>段落</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>うち注・出典</t>
-        </is>
-      </c>
-      <c r="F149" s="4" t="inlineStr">
-        <is>
-          <t>表</t>
-        </is>
-      </c>
-      <c r="G149" s="4" t="inlineStr">
-        <is>
-          <t>未確定</t>
-        </is>
-      </c>
-      <c r="H149" s="4" t="inlineStr">
-        <is>
-          <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
+    <row r="145" ht="44" customHeight="1">
+      <c r="A145" s="6" t="inlineStr"/>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr"/>
+      <c r="G145" s="6" t="inlineStr"/>
+      <c r="H145" s="6" t="inlineStr"/>
+    </row>
+    <row r="146" ht="44" customHeight="1">
+      <c r="A146" s="6" t="inlineStr"/>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr"/>
+      <c r="G146" s="6" t="inlineStr"/>
+      <c r="H146" s="6" t="inlineStr"/>
+    </row>
+    <row r="147" ht="44" customHeight="1">
+      <c r="A147" s="6" t="inlineStr"/>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr"/>
+      <c r="G147" s="6" t="inlineStr"/>
+      <c r="H147" s="6" t="inlineStr"/>
+    </row>
+    <row r="148" ht="44" customHeight="1">
+      <c r="A148" s="6" t="inlineStr"/>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr"/>
+      <c r="G148" s="6" t="inlineStr"/>
+      <c r="H148" s="6" t="inlineStr"/>
+    </row>
+    <row r="149" ht="44" customHeight="1">
+      <c r="A149" s="6" t="inlineStr"/>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr"/>
+      <c r="G149" s="6" t="inlineStr"/>
+      <c r="H149" s="6" t="inlineStr"/>
     </row>
     <row r="150" ht="44" customHeight="1">
       <c r="A150" s="6" t="inlineStr"/>
       <c r="B150" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D150" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E150" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F150" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G150" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H150" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr"/>
+      <c r="G150" s="6" t="inlineStr"/>
+      <c r="H150" s="6" t="inlineStr"/>
     </row>
     <row r="151" ht="44" customHeight="1">
       <c r="A151" s="6" t="inlineStr"/>
       <c r="B151" s="6" t="inlineStr">
         <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr"/>
+      <c r="G151" s="6" t="inlineStr"/>
+      <c r="H151" s="6" t="inlineStr"/>
+    </row>
+    <row r="153" ht="28" customHeight="1">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は31種の表に144箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="30" customHeight="1">
+      <c r="A156" s="4" t="inlineStr"/>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>章</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>節</t>
+        </is>
+      </c>
+      <c r="D156" s="4" t="inlineStr">
+        <is>
+          <t>段落</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>うち注・出典</t>
+        </is>
+      </c>
+      <c r="F156" s="4" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>本来入るべき内容と所在</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="44" customHeight="1">
+      <c r="A157" s="6" t="inlineStr"/>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C151" s="6" t="inlineStr">
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>第1節　計画策定の趣旨</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E157" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" s="6" t="inlineStr">
+        <is>
+          <t>趣旨の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="44" customHeight="1">
+      <c r="A158" s="6" t="inlineStr"/>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
         <is>
           <t>第4節　計画期間</t>
         </is>
       </c>
-      <c r="D151" s="5" t="n">
+      <c r="D158" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E151" s="5" t="n">
+      <c r="E158" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F151" s="5" t="n">
+      <c r="F158" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G151" s="5" t="n">
+      <c r="G158" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H151" s="6" t="inlineStr">
+      <c r="H158" s="6" t="inlineStr">
         <is>
           <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="44" customHeight="1">
-      <c r="A152" s="6" t="inlineStr"/>
-      <c r="B152" s="6" t="inlineStr">
+    <row r="159" ht="44" customHeight="1">
+      <c r="A159" s="6" t="inlineStr"/>
+      <c r="B159" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C152" s="6" t="inlineStr">
+      <c r="C159" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D152" s="5" t="n">
+      <c r="D159" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E152" s="5" t="n">
+      <c r="E159" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F152" s="5" t="n">
+      <c r="F159" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G152" s="5" t="n">
+      <c r="G159" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="H152" s="6" t="inlineStr">
+      <c r="H159" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="44" customHeight="1">
-      <c r="A153" s="6" t="inlineStr"/>
-      <c r="B153" s="6" t="inlineStr">
+    <row r="160" ht="44" customHeight="1">
+      <c r="A160" s="6" t="inlineStr"/>
+      <c r="B160" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C153" s="6" t="inlineStr">
+      <c r="C160" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D153" s="5" t="n">
+      <c r="D160" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E153" s="5" t="n">
+      <c r="E160" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F153" s="5" t="n">
+      <c r="F160" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G153" s="5" t="n">
+      <c r="G160" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H153" s="6" t="inlineStr">
+      <c r="H160" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="42" customHeight="1">
-      <c r="A155" s="7" t="inlineStr">
+    <row r="162" ht="42" customHeight="1">
+      <c r="A162" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は4節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -4662,13 +4845,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A146:H146"/>
+    <mergeCell ref="A153:H153"/>
     <mergeCell ref="A155:H155"/>
+    <mergeCell ref="A162:H162"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A148:H148"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5873,7 +6056,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第5節・第6節（未確定11箇所）</t>
+          <t>第2章第3節・第5節・第6節（未確定12箇所）</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -6336,7 +6519,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議138・要確認104・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議142・要確認109・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -6448,7 +6631,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1031段落153表36図／244箇所</t>
+          <t>1038段落153表36図／253箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -6474,7 +6657,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>244＝244</t>
+          <t>253＝253</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -6500,7 +6683,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>244＝244</t>
+          <t>253＝253</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -6682,7 +6865,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み／62／244箇所（25％）</t>
+          <t>第4節 介護保険サービス等における施設の見込み／62／253箇所（25％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -6921,7 +7104,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は244箇所ある（要協議138・要確認104・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は253箇所ある（要協議142・要確認109・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>253箇所</t>
+          <t>273箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議142・要確認109・要内訳2。本文109箇所・表31種144箇所（01シート）</t>
+          <t>要協議158・要確認113・要内訳2。本文123箇所・表32種150箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>184件</t>
+          <t>186件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>173件</t>
+          <t>175件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが103件（02シート）</t>
+          <t>このうち計画素案を止めているものが105件（02シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1038段落153表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1060段落156表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>253箇所のうち62箇所（25％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>273箇所のうち62箇所（23％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H162"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1038段落153表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計253箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1060段落156表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計273箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -900,13 +900,13 @@
       </c>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0</v>
@@ -926,13 +926,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="8" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -948,13 +948,13 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
@@ -1048,13 +1048,13 @@
       </c>
       <c r="C13" s="9" t="inlineStr"/>
       <c r="D13" s="10" t="n">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>2</v>
@@ -1148,14 +1148,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n">
-        <v>29</v>
+      <c r="D18" s="8" t="n">
+        <v>41</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
@@ -1205,13 +1205,13 @@
         </is>
       </c>
       <c r="D20" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>11</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0</v>
@@ -1256,29 +1256,29 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>No.4（代表KPIの代理指標）</t>
+          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
         </is>
       </c>
     </row>
@@ -1286,29 +1286,29 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>10</v>
       </c>
       <c r="E23" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F23" s="5" t="n">
         <v>3</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>7</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>No.100・No.101（基準年度と数値の差し替え）・No.131（表に何を掲げるか）</t>
+          <t>No.4（代表KPIの代理指標）</t>
         </is>
       </c>
     </row>
@@ -1321,24 +1321,24 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E24" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="F24" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+          <t>確認事項B No.19（医療側の連携の実施状況）</t>
         </is>
       </c>
     </row>
@@ -1351,24 +1351,24 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>確認事項B No.19（医療側の連携の実施状況）</t>
+          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
         </is>
       </c>
     </row>
@@ -1385,13 +1385,13 @@
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0</v>
@@ -1406,29 +1406,29 @@
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>No.75（代表KPIの再整理案）</t>
+          <t>No.112（地域支援事業の量）</t>
         </is>
       </c>
     </row>
@@ -1436,29 +1436,29 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>5</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
         <is>
-          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
+          <t>No.75（代表KPIの再整理案）</t>
         </is>
       </c>
     </row>
@@ -1466,29 +1466,29 @@
       <c r="A29" s="6" t="inlineStr"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>6</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>No.112（地域支援事業の量）</t>
+          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
         </is>
       </c>
     </row>
@@ -1526,42 +1526,38 @@
       <c r="A31" s="6" t="inlineStr"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>No.114（中長期推計の範囲）</t>
-        </is>
-      </c>
+      <c r="H31" s="6" t="inlineStr"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
@@ -1582,12 +1578,12 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
@@ -1602,93 +1598,93 @@
       <c r="G33" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="6" t="inlineStr">
-        <is>
-          <t>No.1（認定率のシナリオ）</t>
-        </is>
-      </c>
+      <c r="H33" s="6" t="inlineStr"/>
     </row>
     <row r="34" ht="32" customHeight="1">
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第2節　計画の位置付け</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="6" t="inlineStr"/>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t>No.1（認定率のシナリオ）</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>No.8（同）</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="6" t="inlineStr">
-        <is>
-          <t>No.8（同）</t>
-        </is>
-      </c>
+      <c r="H36" s="6" t="inlineStr"/>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="6" t="inlineStr"/>
@@ -1699,17 +1695,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第7節 低所得者支援</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>0</v>
@@ -1720,86 +1716,86 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>資料7 図表番号一覧</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>（節の前）</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" s="6" t="inlineStr"/>
     </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="6" t="inlineStr"/>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>資料7 図表番号一覧</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>（節の前）</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H39" s="6" t="inlineStr"/>
-    </row>
-    <row r="41" ht="20" customHeight="1">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>3　本文の未確定箇所（109件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="4" t="inlineStr"/>
-      <c r="B42" s="4" t="inlineStr">
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>3　本文の未確定箇所（123件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
+      <c r="C41" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D41" s="4" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
+      <c r="E41" s="4" t="inlineStr">
         <is>
           <t>本文（抜粋）</t>
         </is>
       </c>
-      <c r="F42" s="4" t="inlineStr"/>
-      <c r="G42" s="4" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42" ht="44" customHeight="1">
+      <c r="A42" s="6" t="inlineStr"/>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、市町村老人福祉計画の記載事項として老人福祉事業その他の老人の生活に直接影響を及ぼす事業を営む者と支援関係機関との連携に関する事項を定めるよう努めるものとされ、市町村地域福祉計画の記載事項として保健医療、労働、教育、住まい、地域再生及び防災に関する施策その他の関連施策との連携に関する事項を定めるも</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr"/>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr"/>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="6" t="inlineStr"/>
@@ -2238,7 +2234,8 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
+          <t>資料：社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）
+注）期限の目安は、公布の日（令和8年6月25日）から要綱が定める期間を加えたものです。実際の施行の日は政令により定まります［要確認］。</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2249,22 +2246,23 @@
       <c r="A60" s="6" t="inlineStr"/>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>資料：社会福祉法等の一部を改正する法律案要綱（令和8年10月14日に確認）
+注）要綱は改正事項の要旨を示すものであり、改正後の条文及び附則の経過措置の内容を確認できていないため、項番号及び号番号は要綱の記載によっています［要確認］。</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2275,12 +2273,12 @@
       <c r="A61" s="6" t="inlineStr"/>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
       <c r="D61" s="6" t="inlineStr">
@@ -2290,7 +2288,7 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
+          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2316,7 +2314,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2342,7 +2340,7 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
+          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2361,14 +2359,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2384,17 +2382,17 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
+          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2410,7 +2408,7 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D66" s="6" t="inlineStr">
@@ -2420,7 +2418,7 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2436,17 +2434,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2472,7 +2470,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2498,7 +2496,7 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>本広域連合の訪問介護の1人1月あたり利用回数は全国の1.87倍であり（第2節1）、区域内の訪問介護13事業所のうち8事業所が住まいに併設しています（第6節）。上記の全国の実態と同じ構造によるものと考えられますが、同一の建物に居住する方への提供の割合は把握していないため、本計画では要因を特定していません［要確認］。</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2514,7 +2512,7 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D70" s="6" t="inlineStr">
@@ -2524,7 +2522,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2540,7 +2538,7 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
@@ -2550,8 +2548,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
-注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
+          <t>本広域連合の訪問介護の1人1月あたり利用回数は全国の1.87倍であり（第2節1）、区域内の訪問介護13事業所のうち8事業所が住まいに併設しています（第6節）。上記の全国の実態と同じ構造によるものと考えられますが、同一の建物に居住する方への提供の割合は把握していないため、本計画では要因を特定していません［要確認］。</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2567,18 +2564,18 @@
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D72" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 サービス提供体制の状況</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
-注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
+          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
+注2）登録有料老人ホームの制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施行されるため、本計画の策定の時点では登録を受けた有料老人ホームはありません（第1章第9節2）</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2594,17 +2591,18 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 サービス提供体制の状況</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
+注2）登録有料老人ホームの制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施行されるため、本計画の策定の時点では登録を受けた有料老人ホームはありません（第1章第9節2）</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2620,7 +2618,7 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2630,7 +2628,7 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -2646,7 +2644,7 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2656,7 +2654,8 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
+注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2667,12 +2666,12 @@
       <c r="A76" s="6" t="inlineStr"/>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2682,7 +2681,8 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
+          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
+注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr"/>
@@ -2693,23 +2693,22 @@
       <c r="A77" s="6" t="inlineStr"/>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
-        </is>
-      </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
-注）分母は地域包括ケア「見え</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2720,12 +2719,12 @@
       <c r="A78" s="6" t="inlineStr"/>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2735,7 +2734,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2746,12 +2745,12 @@
       <c r="A79" s="6" t="inlineStr"/>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2761,7 +2760,7 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2772,12 +2771,12 @@
       <c r="A80" s="6" t="inlineStr"/>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
@@ -2787,7 +2786,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>地域支援事業の量の中長期的な推計は、令和6年度の実績を据え置き、サービス事業は認定者数、一般介護予防事業は第1号被保険者数の伸びにより延ばしています（第6章第3節2）。認定者数が令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。事業費の中長期的な推計は、令和7年度の事業ごと</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr"/>
@@ -2803,7 +2802,7 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -2813,7 +2812,7 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr"/>
@@ -2829,7 +2828,7 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2839,7 +2838,8 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
+注）分母は地域包括ケア「見え</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
@@ -2850,12 +2850,12 @@
       <c r="A83" s="6" t="inlineStr"/>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
+          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr"/>
@@ -2876,22 +2876,22 @@
       <c r="A84" s="6" t="inlineStr"/>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 地域支援事業の実績</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr"/>
@@ -2902,22 +2902,22 @@
       <c r="A85" s="6" t="inlineStr"/>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D85" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr"/>
@@ -2928,22 +2928,22 @@
       <c r="A86" s="6" t="inlineStr"/>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr"/>
@@ -2954,22 +2954,22 @@
       <c r="A87" s="6" t="inlineStr"/>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr"/>
@@ -2980,22 +2980,22 @@
       <c r="A88" s="6" t="inlineStr"/>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
-        </is>
-      </c>
-      <c r="D88" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr"/>
@@ -3006,12 +3006,12 @@
       <c r="A89" s="6" t="inlineStr"/>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr"/>
@@ -3032,22 +3032,22 @@
       <c r="A90" s="6" t="inlineStr"/>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
-        </is>
-      </c>
-      <c r="D90" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr"/>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>地域ケア会議の個別事例の検討から地域課題の抽出、資源開発、施策化への接続を制度化します。社会福祉法等の一部を改正する法律（令和8年法律第51号）により、地域ケア会議は、社会福祉法の支援会議、障害者総合支援法の支援協議会、住宅確保要配慮者に対する賃貸住宅の供給の促進に関する法律の支援協議会、生活困窮者自立支援法の支援会議その他の会議が組織され、又は置かれている</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr"/>
@@ -3089,17 +3089,17 @@
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
-        </is>
-      </c>
-      <c r="D92" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>虐待の初動、成年後見制度の利用、意思決定支援、消費者被害防止を一体で管理します。同法により、市町村は、高齢者及び障害者による成年後見制度又は権利擁護事業（包括的支援事業）等の適切な利用の支援のため、権利利益の擁護に係る支援に従事する者に対する相談・助言及び関係機関等との連絡調整等の事務の実施に努めるものとされ、中核的な役割を担う機関として地域権利擁護相談支援</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr"/>
@@ -3115,17 +3115,17 @@
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
-        </is>
-      </c>
-      <c r="D93" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr"/>
@@ -3141,17 +3141,17 @@
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
-        </is>
-      </c>
-      <c r="D94" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr"/>
@@ -3167,17 +3167,17 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
-        </is>
-      </c>
-      <c r="D95" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr"/>
@@ -3193,17 +3193,17 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D96" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr"/>
@@ -3219,17 +3219,17 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D97" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>BCPについて、策定率、訓練の実施状況、相互応援協定の締結状況を把握します。策定は令和6年度から義務化されており、指定・指導の際に確認できます。国は、BCPの実効性を高めるには行政や他の介護施設等との平時からの連携が重要であるとしたうえで、市区町村の約6割が介護事業所等に対して業務継続を可能とする備えに関する助言等を行っていない状況にあることを示しています。</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr"/>
@@ -3271,17 +3271,17 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D99" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D99" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>介護事故の防止について、事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行います。国は、事故防止を推進するための国・都道府県・市町村の役割として、市町村が事故が発生した事業所からの報告の受付並びに報告内容の集計及び傾向の把握を担うことを示し、介護サービス情報公表システムを活用した報告のための仕組みの構築と報告様式の見直しを検討しています（第1章第9</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr"/>
@@ -3318,22 +3318,22 @@
       <c r="A101" s="6" t="inlineStr"/>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
+          <t>同法により、都道府県は、質の高い介護サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組を促進するための協議会を置くものとされ、市町村は構成員として参画するものとされました（第1章第9節2）。北海道における協議会の設置の状況を確認し、本広域連合と構成3町のいずれが参画するかを含めて協議します［要協議］。</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr"/>
@@ -3344,12 +3344,12 @@
       <c r="A102" s="6" t="inlineStr"/>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D102" s="6" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr"/>
@@ -3370,22 +3370,22 @@
       <c r="A103" s="6" t="inlineStr"/>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D103" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr"/>
@@ -3396,22 +3396,22 @@
       <c r="A104" s="6" t="inlineStr"/>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D104" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr"/>
@@ -3422,22 +3422,22 @@
       <c r="A105" s="6" t="inlineStr"/>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D105" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr"/>
@@ -3448,12 +3448,12 @@
       <c r="A106" s="6" t="inlineStr"/>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>BCPについて、策定率、訓練の実施状況、相互応援協定の締結状況を把握します。策定は令和6年度から義務化されており、指定・指導の際に確認できます。国は、BCPの実効性を高めるには行政や他の介護施設等との平時からの連携が重要であるとしたうえで、市区町村の約6割が介護事業所等に対して業務継続を可能とする備えに関する助言等を行っていない状況にあることを示しています。</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr"/>
@@ -3474,22 +3474,22 @@
       <c r="A107" s="6" t="inlineStr"/>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>介護事故の防止について、事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行います。国は、事故防止を推進するための国・都道府県・市町村の役割として、市町村が事故が発生した事業所からの報告の受付並びに報告内容の集計及び傾向の把握を担うことを示し、介護サービス情報公表システムを活用した報告のための仕組みの構築と報告様式の見直しを検討しています（第1章第9</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr"/>
@@ -3500,12 +3500,12 @@
       <c r="A108" s="6" t="inlineStr"/>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D108" s="6" t="inlineStr">
@@ -3515,8 +3515,7 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr"/>
@@ -3527,12 +3526,12 @@
       <c r="A109" s="6" t="inlineStr"/>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -3542,8 +3541,7 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>同法により、災害が発生した区域に派遣されて災害時における福祉サービスの提供を行う災害時福祉業務従事者の登録の制度が設けられました（第1章第9節2）。介護福祉士、介護支援専門員、社会福祉士等であって厚生労働大臣が実施する研修の課程を修了した者等が対象となり、都道府県知事は、災害が発生した場合に従事することを要請することができるものとされています。区域内の事業所</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr"/>
@@ -3559,7 +3557,7 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -3569,8 +3567,7 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr"/>
@@ -3586,7 +3583,7 @@
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -3596,8 +3593,7 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr"/>
@@ -3613,7 +3609,7 @@
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
@@ -3623,8 +3619,7 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr"/>
@@ -3640,18 +3635,17 @@
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr"/>
@@ -3670,15 +3664,14 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr"/>
@@ -3694,7 +3687,7 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
@@ -3704,8 +3697,7 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr"/>
@@ -3721,7 +3713,7 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D116" s="6" t="inlineStr">
@@ -3731,7 +3723,7 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr"/>
@@ -3747,17 +3739,18 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D117" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr"/>
@@ -3773,364 +3766,372 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F118" s="6" t="inlineStr"/>
+      <c r="G118" s="6" t="inlineStr"/>
+      <c r="H118" s="6" t="inlineStr"/>
+    </row>
+    <row r="119" ht="44" customHeight="1">
+      <c r="A119" s="6" t="inlineStr"/>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr"/>
+      <c r="G119" s="6" t="inlineStr"/>
+      <c r="H119" s="6" t="inlineStr"/>
+    </row>
+    <row r="120" ht="44" customHeight="1">
+      <c r="A120" s="6" t="inlineStr"/>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D120" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F120" s="6" t="inlineStr"/>
+      <c r="G120" s="6" t="inlineStr"/>
+      <c r="H120" s="6" t="inlineStr"/>
+    </row>
+    <row r="121" ht="44" customHeight="1">
+      <c r="A121" s="6" t="inlineStr"/>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D121" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E121" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F121" s="6" t="inlineStr"/>
+      <c r="G121" s="6" t="inlineStr"/>
+      <c r="H121" s="6" t="inlineStr"/>
+    </row>
+    <row r="122" ht="44" customHeight="1">
+      <c r="A122" s="6" t="inlineStr"/>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr"/>
+      <c r="G122" s="6" t="inlineStr"/>
+      <c r="H122" s="6" t="inlineStr"/>
+    </row>
+    <row r="123" ht="44" customHeight="1">
+      <c r="A123" s="6" t="inlineStr"/>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr"/>
+      <c r="G123" s="6" t="inlineStr"/>
+      <c r="H123" s="6" t="inlineStr"/>
+    </row>
+    <row r="124" ht="44" customHeight="1">
+      <c r="A124" s="6" t="inlineStr"/>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr"/>
+      <c r="G124" s="6" t="inlineStr"/>
+      <c r="H124" s="6" t="inlineStr"/>
+    </row>
+    <row r="125" ht="44" customHeight="1">
+      <c r="A125" s="6" t="inlineStr"/>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr"/>
+      <c r="G125" s="6" t="inlineStr"/>
+      <c r="H125" s="6" t="inlineStr"/>
+    </row>
+    <row r="126" ht="44" customHeight="1">
+      <c r="A126" s="6" t="inlineStr"/>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D118" s="11" t="inlineStr">
+      <c r="D126" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr"/>
+      <c r="G126" s="6" t="inlineStr"/>
+      <c r="H126" s="6" t="inlineStr"/>
+    </row>
+    <row r="127" ht="44" customHeight="1">
+      <c r="A127" s="6" t="inlineStr"/>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
+注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
+注3）通いの場の箇所数は3町の事業</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr"/>
+      <c r="G127" s="6" t="inlineStr"/>
+      <c r="H127" s="6" t="inlineStr"/>
+    </row>
+    <row r="128" ht="44" customHeight="1">
+      <c r="A128" s="6" t="inlineStr"/>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
+          <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
+注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
+注3）通いの場の箇所数は3町の事業</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr"/>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr"/>
+    </row>
+    <row r="129" ht="44" customHeight="1">
+      <c r="A129" s="6" t="inlineStr"/>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D129" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr"/>
+      <c r="G129" s="6" t="inlineStr"/>
+      <c r="H129" s="6" t="inlineStr"/>
+    </row>
+    <row r="130" ht="44" customHeight="1">
+      <c r="A130" s="6" t="inlineStr"/>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr"/>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="6" t="inlineStr"/>
+    </row>
+    <row r="131" ht="44" customHeight="1">
+      <c r="A131" s="6" t="inlineStr"/>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
         <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F118" s="6" t="inlineStr"/>
-      <c r="G118" s="6" t="inlineStr"/>
-      <c r="H118" s="6" t="inlineStr"/>
-    </row>
-    <row r="119" ht="44" customHeight="1">
-      <c r="A119" s="6" t="inlineStr"/>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D119" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F119" s="6" t="inlineStr"/>
-      <c r="G119" s="6" t="inlineStr"/>
-      <c r="H119" s="6" t="inlineStr"/>
-    </row>
-    <row r="120" ht="44" customHeight="1">
-      <c r="A120" s="6" t="inlineStr"/>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D120" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
-        </is>
-      </c>
-      <c r="F120" s="6" t="inlineStr"/>
-      <c r="G120" s="6" t="inlineStr"/>
-      <c r="H120" s="6" t="inlineStr"/>
-    </row>
-    <row r="121" ht="44" customHeight="1">
-      <c r="A121" s="6" t="inlineStr"/>
-      <c r="B121" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C121" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
-        </is>
-      </c>
-      <c r="F121" s="6" t="inlineStr"/>
-      <c r="G121" s="6" t="inlineStr"/>
-      <c r="H121" s="6" t="inlineStr"/>
-    </row>
-    <row r="122" ht="44" customHeight="1">
-      <c r="A122" s="6" t="inlineStr"/>
-      <c r="B122" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C122" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
-        </is>
-      </c>
-      <c r="F122" s="6" t="inlineStr"/>
-      <c r="G122" s="6" t="inlineStr"/>
-      <c r="H122" s="6" t="inlineStr"/>
-    </row>
-    <row r="123" ht="44" customHeight="1">
-      <c r="A123" s="6" t="inlineStr"/>
-      <c r="B123" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C123" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F123" s="6" t="inlineStr"/>
-      <c r="G123" s="6" t="inlineStr"/>
-      <c r="H123" s="6" t="inlineStr"/>
-    </row>
-    <row r="124" ht="44" customHeight="1">
-      <c r="A124" s="6" t="inlineStr"/>
-      <c r="B124" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C124" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D124" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F124" s="6" t="inlineStr"/>
-      <c r="G124" s="6" t="inlineStr"/>
-      <c r="H124" s="6" t="inlineStr"/>
-    </row>
-    <row r="125" ht="44" customHeight="1">
-      <c r="A125" s="6" t="inlineStr"/>
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
-        </is>
-      </c>
-      <c r="F125" s="6" t="inlineStr"/>
-      <c r="G125" s="6" t="inlineStr"/>
-      <c r="H125" s="6" t="inlineStr"/>
-    </row>
-    <row r="126" ht="44" customHeight="1">
-      <c r="A126" s="6" t="inlineStr"/>
-      <c r="B126" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C126" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
-        <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
-        </is>
-      </c>
-      <c r="F126" s="6" t="inlineStr"/>
-      <c r="G126" s="6" t="inlineStr"/>
-      <c r="H126" s="6" t="inlineStr"/>
-    </row>
-    <row r="127" ht="44" customHeight="1">
-      <c r="A127" s="6" t="inlineStr"/>
-      <c r="B127" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C127" s="6" t="inlineStr">
-        <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D127" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
-        <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
-        </is>
-      </c>
-      <c r="F127" s="6" t="inlineStr"/>
-      <c r="G127" s="6" t="inlineStr"/>
-      <c r="H127" s="6" t="inlineStr"/>
-    </row>
-    <row r="128" ht="44" customHeight="1">
-      <c r="A128" s="6" t="inlineStr"/>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
-        </is>
-      </c>
-      <c r="F128" s="6" t="inlineStr"/>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="6" t="inlineStr"/>
-    </row>
-    <row r="129" ht="44" customHeight="1">
-      <c r="A129" s="6" t="inlineStr"/>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
-        </is>
-      </c>
-      <c r="F129" s="6" t="inlineStr"/>
-      <c r="G129" s="6" t="inlineStr"/>
-      <c r="H129" s="6" t="inlineStr"/>
-    </row>
-    <row r="130" ht="44" customHeight="1">
-      <c r="A130" s="6" t="inlineStr"/>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
-        </is>
-      </c>
-      <c r="F130" s="6" t="inlineStr"/>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="6" t="inlineStr"/>
-    </row>
-    <row r="131" ht="44" customHeight="1">
-      <c r="A131" s="6" t="inlineStr"/>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
-注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
-        </is>
-      </c>
       <c r="F131" s="6" t="inlineStr"/>
       <c r="G131" s="6" t="inlineStr"/>
       <c r="H131" s="6" t="inlineStr"/>
@@ -4144,17 +4145,17 @@
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D132" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr"/>
@@ -4170,7 +4171,7 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
@@ -4180,7 +4181,7 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr"/>
@@ -4196,7 +4197,7 @@
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
@@ -4206,7 +4207,7 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr"/>
@@ -4222,7 +4223,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -4232,8 +4233,7 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr"/>
@@ -4249,18 +4249,18 @@
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr"/>
@@ -4276,17 +4276,18 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D137" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr"/>
@@ -4302,7 +4303,7 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D138" s="6" t="inlineStr">
@@ -4312,7 +4313,8 @@
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr"/>
@@ -4328,17 +4330,18 @@
       </c>
       <c r="C139" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D139" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr"/>
@@ -4354,17 +4357,17 @@
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr"/>
@@ -4380,17 +4383,17 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D141" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr"/>
@@ -4406,7 +4409,7 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -4416,7 +4419,7 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があり、当広域連合が対象となる場合は単価を上げる向きに働きます。いずれの</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr"/>
@@ -4442,399 +4445,740 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+        </is>
+      </c>
+      <c r="F143" s="6" t="inlineStr"/>
+      <c r="G143" s="6" t="inlineStr"/>
+      <c r="H143" s="6" t="inlineStr"/>
+    </row>
+    <row r="144" ht="44" customHeight="1">
+      <c r="A144" s="6" t="inlineStr"/>
+      <c r="B144" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C144" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D144" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
+注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
+        </is>
+      </c>
+      <c r="F144" s="6" t="inlineStr"/>
+      <c r="G144" s="6" t="inlineStr"/>
+      <c r="H144" s="6" t="inlineStr"/>
+    </row>
+    <row r="145" ht="44" customHeight="1">
+      <c r="A145" s="6" t="inlineStr"/>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
+        </is>
+      </c>
+      <c r="F145" s="6" t="inlineStr"/>
+      <c r="G145" s="6" t="inlineStr"/>
+      <c r="H145" s="6" t="inlineStr"/>
+    </row>
+    <row r="146" ht="44" customHeight="1">
+      <c r="A146" s="6" t="inlineStr"/>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+        </is>
+      </c>
+      <c r="F146" s="6" t="inlineStr"/>
+      <c r="G146" s="6" t="inlineStr"/>
+      <c r="H146" s="6" t="inlineStr"/>
+    </row>
+    <row r="147" ht="44" customHeight="1">
+      <c r="A147" s="6" t="inlineStr"/>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+        </is>
+      </c>
+      <c r="F147" s="6" t="inlineStr"/>
+      <c r="G147" s="6" t="inlineStr"/>
+      <c r="H147" s="6" t="inlineStr"/>
+    </row>
+    <row r="148" ht="44" customHeight="1">
+      <c r="A148" s="6" t="inlineStr"/>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+        </is>
+      </c>
+      <c r="F148" s="6" t="inlineStr"/>
+      <c r="G148" s="6" t="inlineStr"/>
+      <c r="H148" s="6" t="inlineStr"/>
+    </row>
+    <row r="149" ht="44" customHeight="1">
+      <c r="A149" s="6" t="inlineStr"/>
+      <c r="B149" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C149" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E149" s="6" t="inlineStr">
+        <is>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+        </is>
+      </c>
+      <c r="F149" s="6" t="inlineStr"/>
+      <c r="G149" s="6" t="inlineStr"/>
+      <c r="H149" s="6" t="inlineStr"/>
+    </row>
+    <row r="150" ht="44" customHeight="1">
+      <c r="A150" s="6" t="inlineStr"/>
+      <c r="B150" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C150" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E150" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F150" s="6" t="inlineStr"/>
+      <c r="G150" s="6" t="inlineStr"/>
+      <c r="H150" s="6" t="inlineStr"/>
+    </row>
+    <row r="151" ht="44" customHeight="1">
+      <c r="A151" s="6" t="inlineStr"/>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E151" s="6" t="inlineStr">
+        <is>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+        </is>
+      </c>
+      <c r="F151" s="6" t="inlineStr"/>
+      <c r="G151" s="6" t="inlineStr"/>
+      <c r="H151" s="6" t="inlineStr"/>
+    </row>
+    <row r="152" ht="44" customHeight="1">
+      <c r="A152" s="6" t="inlineStr"/>
+      <c r="B152" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C152" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D152" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F152" s="6" t="inlineStr"/>
+      <c r="G152" s="6" t="inlineStr"/>
+      <c r="H152" s="6" t="inlineStr"/>
+    </row>
+    <row r="153" ht="44" customHeight="1">
+      <c r="A153" s="6" t="inlineStr"/>
+      <c r="B153" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C153" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E153" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F153" s="6" t="inlineStr"/>
+      <c r="G153" s="6" t="inlineStr"/>
+      <c r="H153" s="6" t="inlineStr"/>
+    </row>
+    <row r="154" ht="44" customHeight="1">
+      <c r="A154" s="6" t="inlineStr"/>
+      <c r="B154" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C154" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E154" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F154" s="6" t="inlineStr"/>
+      <c r="G154" s="6" t="inlineStr"/>
+      <c r="H154" s="6" t="inlineStr"/>
+    </row>
+    <row r="155" ht="44" customHeight="1">
+      <c r="A155" s="6" t="inlineStr"/>
+      <c r="B155" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C155" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E155" s="6" t="inlineStr">
+        <is>
+          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があり、当広域連合が対象となる場合は単価を上げる向きに働きます。いずれの</t>
+        </is>
+      </c>
+      <c r="F155" s="6" t="inlineStr"/>
+      <c r="G155" s="6" t="inlineStr"/>
+      <c r="H155" s="6" t="inlineStr"/>
+    </row>
+    <row r="156" ht="44" customHeight="1">
+      <c r="A156" s="6" t="inlineStr"/>
+      <c r="B156" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C156" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D156" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E156" s="6" t="inlineStr">
+        <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F143" s="6" t="inlineStr"/>
-      <c r="G143" s="6" t="inlineStr"/>
-      <c r="H143" s="6" t="inlineStr"/>
-    </row>
-    <row r="144" ht="44" customHeight="1">
-      <c r="A144" s="6" t="inlineStr"/>
-      <c r="B144" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C144" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D144" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
-        </is>
-      </c>
-      <c r="F144" s="6" t="inlineStr"/>
-      <c r="G144" s="6" t="inlineStr"/>
-      <c r="H144" s="6" t="inlineStr"/>
-    </row>
-    <row r="145" ht="44" customHeight="1">
-      <c r="A145" s="6" t="inlineStr"/>
-      <c r="B145" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C145" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D145" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
-        </is>
-      </c>
-      <c r="F145" s="6" t="inlineStr"/>
-      <c r="G145" s="6" t="inlineStr"/>
-      <c r="H145" s="6" t="inlineStr"/>
-    </row>
-    <row r="146" ht="44" customHeight="1">
-      <c r="A146" s="6" t="inlineStr"/>
-      <c r="B146" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C146" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
-      <c r="F146" s="6" t="inlineStr"/>
-      <c r="G146" s="6" t="inlineStr"/>
-      <c r="H146" s="6" t="inlineStr"/>
-    </row>
-    <row r="147" ht="44" customHeight="1">
-      <c r="A147" s="6" t="inlineStr"/>
-      <c r="B147" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C147" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
-      <c r="F147" s="6" t="inlineStr"/>
-      <c r="G147" s="6" t="inlineStr"/>
-      <c r="H147" s="6" t="inlineStr"/>
-    </row>
-    <row r="148" ht="44" customHeight="1">
-      <c r="A148" s="6" t="inlineStr"/>
-      <c r="B148" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C148" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E148" s="6" t="inlineStr">
-        <is>
-          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
-注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
-        </is>
-      </c>
-      <c r="F148" s="6" t="inlineStr"/>
-      <c r="G148" s="6" t="inlineStr"/>
-      <c r="H148" s="6" t="inlineStr"/>
-    </row>
-    <row r="149" ht="44" customHeight="1">
-      <c r="A149" s="6" t="inlineStr"/>
-      <c r="B149" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C149" s="6" t="inlineStr">
-        <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D149" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
-        </is>
-      </c>
-      <c r="F149" s="6" t="inlineStr"/>
-      <c r="G149" s="6" t="inlineStr"/>
-      <c r="H149" s="6" t="inlineStr"/>
-    </row>
-    <row r="150" ht="44" customHeight="1">
-      <c r="A150" s="6" t="inlineStr"/>
-      <c r="B150" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C150" s="6" t="inlineStr">
-        <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E150" s="6" t="inlineStr">
-        <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
-        </is>
-      </c>
-      <c r="F150" s="6" t="inlineStr"/>
-      <c r="G150" s="6" t="inlineStr"/>
-      <c r="H150" s="6" t="inlineStr"/>
-    </row>
-    <row r="151" ht="44" customHeight="1">
-      <c r="A151" s="6" t="inlineStr"/>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E151" s="6" t="inlineStr">
-        <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
-        </is>
-      </c>
-      <c r="F151" s="6" t="inlineStr"/>
-      <c r="G151" s="6" t="inlineStr"/>
-      <c r="H151" s="6" t="inlineStr"/>
-    </row>
-    <row r="153" ht="28" customHeight="1">
-      <c r="A153" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は31種の表に144箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
-注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="20" customHeight="1">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="30" customHeight="1">
-      <c r="A156" s="4" t="inlineStr"/>
-      <c r="B156" s="4" t="inlineStr">
-        <is>
-          <t>章</t>
-        </is>
-      </c>
-      <c r="C156" s="4" t="inlineStr">
-        <is>
-          <t>節</t>
-        </is>
-      </c>
-      <c r="D156" s="4" t="inlineStr">
-        <is>
-          <t>段落</t>
-        </is>
-      </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>うち注・出典</t>
-        </is>
-      </c>
-      <c r="F156" s="4" t="inlineStr">
-        <is>
-          <t>表</t>
-        </is>
-      </c>
-      <c r="G156" s="4" t="inlineStr">
-        <is>
-          <t>未確定</t>
-        </is>
-      </c>
-      <c r="H156" s="4" t="inlineStr">
-        <is>
-          <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
+      <c r="F156" s="6" t="inlineStr"/>
+      <c r="G156" s="6" t="inlineStr"/>
+      <c r="H156" s="6" t="inlineStr"/>
     </row>
     <row r="157" ht="44" customHeight="1">
       <c r="A157" s="6" t="inlineStr"/>
       <c r="B157" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C157" s="6" t="inlineStr">
         <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D157" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E157" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F157" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G157" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H157" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr"/>
+      <c r="G157" s="6" t="inlineStr"/>
+      <c r="H157" s="6" t="inlineStr"/>
     </row>
     <row r="158" ht="44" customHeight="1">
       <c r="A158" s="6" t="inlineStr"/>
       <c r="B158" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C158" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
-        </is>
-      </c>
-      <c r="D158" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E158" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F158" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G158" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H158" s="6" t="inlineStr">
-        <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
-        </is>
-      </c>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr"/>
+      <c r="G158" s="6" t="inlineStr"/>
+      <c r="H158" s="6" t="inlineStr"/>
     </row>
     <row r="159" ht="44" customHeight="1">
       <c r="A159" s="6" t="inlineStr"/>
       <c r="B159" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C159" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
-        </is>
-      </c>
-      <c r="D159" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="E159" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F159" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G159" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H159" s="6" t="inlineStr">
-        <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
-        </is>
-      </c>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr"/>
+      <c r="G159" s="6" t="inlineStr"/>
+      <c r="H159" s="6" t="inlineStr"/>
     </row>
     <row r="160" ht="44" customHeight="1">
       <c r="A160" s="6" t="inlineStr"/>
       <c r="B160" s="6" t="inlineStr">
         <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr"/>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="6" t="inlineStr"/>
+    </row>
+    <row r="161" ht="44" customHeight="1">
+      <c r="A161" s="6" t="inlineStr"/>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr"/>
+      <c r="G161" s="6" t="inlineStr"/>
+      <c r="H161" s="6" t="inlineStr"/>
+    </row>
+    <row r="162" ht="44" customHeight="1">
+      <c r="A162" s="6" t="inlineStr"/>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr"/>
+      <c r="G162" s="6" t="inlineStr"/>
+      <c r="H162" s="6" t="inlineStr"/>
+    </row>
+    <row r="163" ht="44" customHeight="1">
+      <c r="A163" s="6" t="inlineStr"/>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr"/>
+      <c r="G163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr"/>
+    </row>
+    <row r="164" ht="44" customHeight="1">
+      <c r="A164" s="6" t="inlineStr"/>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr"/>
+      <c r="G164" s="6" t="inlineStr"/>
+      <c r="H164" s="6" t="inlineStr"/>
+    </row>
+    <row r="166" ht="28" customHeight="1">
+      <c r="A166" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は32種の表に150箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="30" customHeight="1">
+      <c r="A169" s="4" t="inlineStr"/>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>章</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>節</t>
+        </is>
+      </c>
+      <c r="D169" s="4" t="inlineStr">
+        <is>
+          <t>段落</t>
+        </is>
+      </c>
+      <c r="E169" s="4" t="inlineStr">
+        <is>
+          <t>うち注・出典</t>
+        </is>
+      </c>
+      <c r="F169" s="4" t="inlineStr">
+        <is>
+          <t>表</t>
+        </is>
+      </c>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>未確定</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>本来入るべき内容と所在</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="44" customHeight="1">
+      <c r="A170" s="6" t="inlineStr"/>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>第1節　計画策定の趣旨</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" s="6" t="inlineStr">
+        <is>
+          <t>趣旨の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="44" customHeight="1">
+      <c r="A171" s="6" t="inlineStr"/>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>第4節　計画期間</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E171" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" s="6" t="inlineStr">
+        <is>
+          <t>計画期間の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="44" customHeight="1">
+      <c r="A172" s="6" t="inlineStr"/>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>第5節　計画の策定体制</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E172" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H172" s="6" t="inlineStr">
+        <is>
+          <t>策定体制の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="44" customHeight="1">
+      <c r="A173" s="6" t="inlineStr"/>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C160" s="6" t="inlineStr">
+      <c r="C173" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D160" s="5" t="n">
+      <c r="D173" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E160" s="5" t="n">
+      <c r="E173" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F160" s="5" t="n">
+      <c r="F173" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G160" s="5" t="n">
+      <c r="G173" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H160" s="6" t="inlineStr">
+      <c r="H173" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="162" ht="42" customHeight="1">
-      <c r="A162" s="7" t="inlineStr">
+    <row r="175" ht="42" customHeight="1">
+      <c r="A175" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は4節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -4845,13 +5189,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A153:H153"/>
-    <mergeCell ref="A155:H155"/>
-    <mergeCell ref="A162:H162"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A166:H166"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A175:H175"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A168:H168"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4878,7 +5222,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（184件）</t>
+          <t>確認事項の棚卸し（186件）</t>
         </is>
       </c>
     </row>
@@ -4932,7 +5276,7 @@
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は173件</t>
+          <t>完了・了承済を除く未回答は175件</t>
         </is>
       </c>
     </row>
@@ -4944,7 +5288,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
@@ -5191,10 +5535,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
@@ -5375,7 +5719,7 @@
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="6" t="inlineStr"/>
@@ -5390,7 +5734,7 @@
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="6" t="inlineStr"/>
@@ -5535,8 +5879,8 @@
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（90件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
-注2）確認先が「発注者・3町」のもの（27件）は、3町への照会の様式と時期の決定を先に要します。
+          <t>注1）期限が令和8年8月以前のもの（92件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+注2）確認先が「発注者・3町」のもの（28件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
       </c>
@@ -6056,7 +6400,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第5節・第6節（未確定12箇所）</t>
+          <t>第2章第3節・第5節・第6節（未確定14箇所）</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -6519,7 +6863,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議142・要確認109・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議158・要確認113・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -6631,7 +6975,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1038段落153表36図／253箇所</t>
+          <t>1060段落156表36図／273箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -6657,7 +7001,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>253＝253</t>
+          <t>273＝273</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -6683,7 +7027,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>253＝253</t>
+          <t>273＝273</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -6709,7 +7053,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>184件（未回答173件）</t>
+          <t>186件（未回答175件）</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -6735,7 +7079,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>184件／一意184件</t>
+          <t>186件／一意186件</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -6865,7 +7209,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み／62／253箇所（25％）</t>
+          <t>第4節 介護保険サービス等における施設の見込み／62／273箇所（23％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -7104,7 +7448,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は253箇所ある（要協議142・要確認109・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は273箇所ある（要協議158・要確認113・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -7127,7 +7471,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている173件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている175件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1060段落156表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1059段落156表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1060段落156表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計273箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1059段落156表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計273箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -1149,13 +1149,13 @@
         </is>
       </c>
       <c r="D18" s="8" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>13</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>0</v>
@@ -1634,12 +1634,12 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -1654,37 +1654,37 @@
       <c r="G35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>No.8（同）</t>
-        </is>
-      </c>
+      <c r="H35" s="6" t="inlineStr"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="6" t="inlineStr"/>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t>No.8（同）</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="32" customHeight="1">
       <c r="A37" s="6" t="inlineStr"/>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>0</v>
@@ -1716,86 +1716,86 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>資料7 図表番号一覧</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>（節の前）</t>
+          <t>第7節 低所得者支援</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="6" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>資料7 図表番号一覧</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>（節の前）</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="G39" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="H38" s="6" t="inlineStr"/>
-    </row>
-    <row r="40" ht="20" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="H39" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>3　本文の未確定箇所（123件）</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="4" t="inlineStr"/>
-      <c r="B41" s="4" t="inlineStr">
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>本文（抜粋）</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr"/>
-    </row>
-    <row r="42" ht="44" customHeight="1">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>第2節　計画の位置付け</t>
-        </is>
-      </c>
-      <c r="D42" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、市町村老人福祉計画の記載事項として老人福祉事業その他の老人の生活に直接影響を及ぼす事業を営む者と支援関係機関との連携に関する事項を定めるよう努めるものとされ、市町村地域福祉計画の記載事項として保健医療、労働、教育、住まい、地域再生及び防災に関する施策その他の関連施策との連携に関する事項を定めるも</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="6" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr"/>
+      <c r="H42" s="4" t="inlineStr"/>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="6" t="inlineStr"/>
@@ -1809,14 +1809,14 @@
           <t>第2節　計画の位置付け</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>注）各法律の条文の受領前であるため、条番号のみを記載し項番号は記載していません［要確認］。構成3町の高齢者福祉計画が老人福祉法第20条の8による市町村老人福祉計画に当たることの確認、成年後見制度の利用の促進に関する施策についての基本的な計画の構成3町における策定の状況、及び一体のものとして作成する方法は構成3町と協議して定めます［要協議］。</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、市町村老人福祉計画の記載事項として老人福祉事業その他の老人の生活に直接影響を及ぼす事業を営む者と支援関係機関との連携に関する事項を定めるよう努めるものとされ、市町村地域福祉計画の記載事項として保健医療、労働、教育、住まい、地域再生及び防災に関する施策その他の関連施策との連携に関する事項を定めるも</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1835,9 +1835,9 @@
           <t>第2節　計画の位置付け</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
+          <t>注）各法律の条文の受領前であるため、条番号のみを記載し項番号は記載していません［要確認］。構成3町の高齢者福祉計画が老人福祉法第20条の8による市町村老人福祉計画に当たることの確認、成年後見制度の利用の促進に関する施策についての基本的な計画の構成3町における策定の状況、及び一体のものとして作成する方法は構成3町と協議して定めます［要協議］。</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1884,17 +1884,17 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第6節　計画の進行管理・推進体制</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>注）北海道の高齢者保健福祉計画が定める評価指標のうち「取り組んでいる市町村数」を単位とするものは、1保険者である当広域連合にそのまま適用することができません。読替えの方法は第8節に掲げます。北海道から広域連合に対する読替えの考え方は示されていないため、本計画は当広域連合の整理によっており、考え方が示された場合はこれに合わせて改めます［要確認］。</t>
+          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
+          <t>第6節　計画の進行管理・推進体制</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
@@ -1946,8 +1946,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
-注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
+          <t>注）北海道の高齢者保健福祉計画が定める評価指標のうち「取り組んでいる市町村数」を単位とするものは、1保険者である当広域連合にそのまま適用することができません。読替えの方法は第8節に掲げます。北海道から広域連合に対する読替えの考え方は示されていないため、本計画は当広域連合の整理によっており、考え方が示された場合はこれに合わせて改めます［要確認］。</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr"/>
@@ -1990,7 +1989,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -2000,7 +1999,8 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条は、市町村介護保険事業計画は医療計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合は、在宅医療・介護連携（第5章 基本目標1）、協力医療機関の確保（第1章第9節1）並びに施設・居住系サービスの整備（第6章第5節）において図ります。北海道の第10期高齢者保健福祉計画・介護保険事業支援計画</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
+注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
+          <t>介護保険法第117条は、市町村介護保険事業計画は医療計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合は、在宅医療・介護連携（第5章 基本目標1）、協力医療機関の確保（第1章第9節1）並びに施設・居住系サービスの整備（第6章第5節）において図ります。北海道の第10期高齢者保健福祉計画・介護保険事業支援計画</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
+          <t>介護保険法第117条は、市町村介護保険事業計画は医療計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合は、在宅医療・介護連携（第5章 基本目標1）、協力医療機関の確保（第1章第9節1）並びに施設・居住系サービスの整備（第6章第5節）において図ります。北海道の第10期高齢者保健福祉計画・介護保険事業支援計画</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
-        </is>
-      </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第8節　関係計画等との関係</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>要件を満たす協力医療機関を定めることの義務化には令和9年3月31日までの経過措置が設けられており、本計画の初日である令和9年4月1日から義務となります。国は、全国における要件を満たす体制の整備割合を介護老人福祉施設67.9％、介護老人保健施設83.3％、介護医療院84.9％としたうえで、定めの状況について集計していないと回答した自治体が一定程度存在し、地域差</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2123,14 +2123,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
+          <t>要件を満たす協力医療機関を定めることの義務化には令和9年3月31日までの経過措置が設けられており、本計画の初日である令和9年4月1日から義務となります。国は、全国における要件を満たす体制の整備割合を介護老人福祉施設67.9％、介護老人保健施設83.3％、介護医療院84.9％としたうえで、定めの状況について集計していないと回答した自治体が一定程度存在し、地域差</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
+          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2175,14 +2175,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。指定に係る構成</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2201,14 +2201,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。基準①の根拠と</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。指定に係る構成</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2234,8 +2234,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>資料：社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）
-注）期限の目安は、公布の日（令和8年6月25日）から要綱が定める期間を加えたものです。実際の施行の日は政令により定まります［要確認］。</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。指定に係る構成</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2261,8 +2260,8 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>資料：社会福祉法等の一部を改正する法律案要綱（令和8年10月14日に確認）
-注）要綱は改正事項の要旨を示すものであり、改正後の条文及び附則の経過措置の内容を確認できていないため、項番号及び号番号は要綱の記載によっています［要確認］。</t>
+          <t>資料：社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）
+注）期限の目安は、公布の日（令和8年6月25日）から要綱が定める期間を加えたものです。実際の施行の日は政令により定まります［要確認］。</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2288,7 +2287,8 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
+          <t>資料：社会福祉法等の一部を改正する法律案要綱（令和8年10月14日に確認）
+注）要綱は改正事項の要旨を示すものであり、改正後の条文及び附則の経過措置の内容を確認できていないため、項番号及び号番号は要綱の記載によっています［要確認］。</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2299,22 +2299,22 @@
       <c r="A62" s="6" t="inlineStr"/>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2333,14 +2333,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2359,14 +2359,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2385,14 +2385,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2434,17 +2434,17 @@
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2460,17 +2460,17 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>本広域連合の訪問介護の1人1月あたり利用回数は全国の1.87倍であり（第2節1）、区域内の訪問介護13事業所のうち8事業所が住まいに併設しています（第6節）。上記の全国の実態と同じ構造によるものと考えられますが、同一の建物に居住する方への提供の割合は把握していないため、本計画では要因を特定していません［要確認］。</t>
+          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2567,15 +2567,14 @@
           <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D72" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
-注2）登録有料老人ホームの制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施行されるため、本計画の策定の時点では登録を受けた有料老人ホームはありません（第1章第9節2）</t>
+          <t>本広域連合の訪問介護の1人1月あたり利用回数は全国の1.87倍であり（第2節1）、区域内の訪問介護13事業所のうち8事業所が住まいに併設しています（第6節）。上記の全国の実態と同じ構造によるものと考えられますが、同一の建物に居住する方への提供の割合は把握していないため、本計画では要因を特定していません［要確認］。</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2594,15 +2593,15 @@
           <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
-      <c r="D73" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
           <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
-注2）登録有料老人ホームの制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施行されるため、本計画の策定の時点では登録を受けた有料老人ホームはありません（第1章第9節2）</t>
+注2）登録有料老人ホームの入居定員総数が記載及び勘案の対象に加わるのは、登録制度の施行に合わせた改正によるものです。同制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2618,7 +2617,7 @@
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D74" s="6" t="inlineStr">
@@ -2628,7 +2627,8 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
+注2）登録有料老人ホームの入居定員総数が記載及び勘案の対象に加わるのは、登録制度の施行に合わせた改正によるものです。同制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -2654,8 +2654,7 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
-注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2671,7 +2670,7 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D76" s="6" t="inlineStr">
@@ -2681,8 +2680,8 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
-注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
+          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
+注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr"/>
@@ -2701,14 +2700,15 @@
           <t>第5節 在宅介護の実態</t>
         </is>
       </c>
-      <c r="D77" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
+注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D78" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
-        </is>
-      </c>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の中長期的な推計は、令和6年度の実績を据え置き、サービス事業は認定者数、一般介護予防事業は第1号被保険者数の伸びにより延ばしています（第6章第3節2）。認定者数が令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。事業費の中長期的な推計は、令和7年度の事業ごと</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr"/>
@@ -2797,22 +2797,22 @@
       <c r="A81" s="6" t="inlineStr"/>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
+          <t>地域支援事業の量の中長期的な推計は、令和6年度の実績を据え置き、サービス事業は認定者数、一般介護予防事業は第1号被保険者数の伸びにより延ばしています（第6章第3節2）。認定者数が令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。事業費の中長期的な推計は、令和7年度の事業ごと</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr"/>
@@ -2838,8 +2838,7 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
-注）分母は地域包括ケア「見え</t>
+          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
@@ -2855,7 +2854,7 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2865,7 +2864,8 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
+          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
+注）分母は地域包括ケア「見え</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr"/>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
+          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr"/>
@@ -2907,17 +2907,17 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D85" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 地域支援事業の実績</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr"/>
@@ -2936,14 +2936,14 @@
           <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr"/>
@@ -2980,12 +2980,12 @@
       <c r="A88" s="6" t="inlineStr"/>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr"/>
@@ -3014,14 +3014,14 @@
           <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr"/>
@@ -3040,14 +3040,14 @@
           <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
-      <c r="D90" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr"/>
@@ -3058,22 +3058,22 @@
       <c r="A91" s="6" t="inlineStr"/>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
-        </is>
-      </c>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の個別事例の検討から地域課題の抽出、資源開発、施策化への接続を制度化します。社会福祉法等の一部を改正する法律（令和8年法律第51号）により、地域ケア会議は、社会福祉法の支援会議、障害者総合支援法の支援協議会、住宅確保要配慮者に対する賃貸住宅の供給の促進に関する法律の支援協議会、生活困窮者自立支援法の支援会議その他の会議が組織され、又は置かれている</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr"/>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>虐待の初動、成年後見制度の利用、意思決定支援、消費者被害防止を一体で管理します。同法により、市町村は、高齢者及び障害者による成年後見制度又は権利擁護事業（包括的支援事業）等の適切な利用の支援のため、権利利益の擁護に係る支援に従事する者に対する相談・助言及び関係機関等との連絡調整等の事務の実施に努めるものとされ、中核的な役割を担う機関として地域権利擁護相談支援</t>
+          <t>地域ケア会議の個別事例の検討から地域課題の抽出、資源開発、施策化への接続を制度化します。社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護保険法第115条の48の会議は改正後「支援会議」と称し、構成員として地域包括支援センターが明示されます。地域ケア会議は、社会福祉法の支援会議、障害者総合支援法の支援協議会、住宅確保要配慮者に対する賃貸住宅</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr"/>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>虐待の初動、成年後見制度の利用、意思決定支援、消費者被害防止を一体で管理します。同法により、市町村は、高齢者及び障害者による成年後見制度又は権利擁護事業（包括的支援事業）等の適切な利用の支援のため、権利利益の擁護に係る支援に従事する者に対する相談・助言及び関係機関等との連絡調整等の事務の実施に努めるものとされ、中核的な役割を担う機関として地域権利擁護相談支援</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr"/>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr"/>
@@ -3274,9 +3274,9 @@
           <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
-      <c r="D99" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E99" s="6" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D100" s="6" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr"/>
@@ -3323,17 +3323,17 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
-        </is>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
+        </is>
+      </c>
+      <c r="D101" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>同法により、都道府県は、質の高い介護サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組を促進するための協議会を置くものとされ、市町村は構成員として参画するものとされました（第1章第9節2）。北海道における協議会の設置の状況を確認し、本広域連合と構成3町のいずれが参画するかを含めて協議します［要協議］。</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr"/>
@@ -3352,14 +3352,14 @@
           <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>同法により、都道府県は、質の高い介護サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組を促進するための協議会を置くものとされ、市町村は構成員として参画するものとされました（第1章第9節2）。北海道における協議会の設置の状況を確認し、本広域連合と構成3町のいずれが参画するかを含めて協議します［要協議］。</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr"/>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr"/>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr"/>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr"/>
@@ -3456,14 +3456,14 @@
           <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
-      <c r="D106" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>BCPについて、策定率、訓練の実施状況、相互応援協定の締結状況を把握します。策定は令和6年度から義務化されており、指定・指導の際に確認できます。国は、BCPの実効性を高めるには行政や他の介護施設等との平時からの連携が重要であるとしたうえで、市区町村の約6割が介護事業所等に対して業務継続を可能とする備えに関する助言等を行っていない状況にあることを示しています。</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr"/>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>介護事故の防止について、事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行います。国は、事故防止を推進するための国・都道府県・市町村の役割として、市町村が事故が発生した事業所からの報告の受付並びに報告内容の集計及び傾向の把握を担うことを示し、介護サービス情報公表システムを活用した報告のための仕組みの構築と報告様式の見直しを検討しています（第1章第9</t>
+          <t>BCPについて、策定率、訓練の実施状況、相互応援協定の締結状況を把握します。策定は令和6年度から義務化されており、指定・指導の際に確認できます。国は、BCPの実効性を高めるには行政や他の介護施設等との平時からの連携が重要であるとしたうえで、市区町村の約6割が介護事業所等に対して業務継続を可能とする備えに関する助言等を行っていない状況にあることを示しています。</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr"/>
@@ -3508,14 +3508,14 @@
           <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
+          <t>介護事故の防止について、事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行います。国は、事故防止を推進するための国・都道府県・市町村の役割として、市町村が事故が発生した事業所からの報告の受付並びに報告内容の集計及び傾向の把握を担うことを示し、介護サービス情報公表システムを活用した報告のための仕組みの構築と報告様式の見直しを検討しています（第1章第9</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr"/>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>同法により、災害が発生した区域に派遣されて災害時における福祉サービスの提供を行う災害時福祉業務従事者の登録の制度が設けられました（第1章第9節2）。介護福祉士、介護支援専門員、社会福祉士等であって厚生労働大臣が実施する研修の課程を修了した者等が対象となり、都道府県知事は、災害が発生した場合に従事することを要請することができるものとされています。区域内の事業所</t>
+          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr"/>
@@ -3552,12 +3552,12 @@
       <c r="A110" s="6" t="inlineStr"/>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D110" s="6" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
+          <t>同法により、災害が発生した区域に派遣されて災害時における福祉サービスの提供を行う災害時福祉業務従事者の登録の制度が設けられました（第1章第9節2）。介護福祉士、介護支援専門員、社会福祉士等であって厚生労働大臣が実施する研修の課程を修了した者等が対象となり、都道府県知事は、災害が発生した場合に従事することを要請することができるものとされています。区域内の事業所</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr"/>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
+          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr"/>
@@ -3612,14 +3612,14 @@
           <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
-      <c r="D112" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D112" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr"/>
@@ -3645,7 +3645,7 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr"/>
@@ -3661,7 +3661,7 @@
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr"/>
@@ -3716,9 +3716,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D116" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -3749,8 +3749,7 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr"/>
@@ -3877,9 +3876,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D122" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D122" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
@@ -3904,9 +3903,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D123" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3958,9 +3957,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -3982,7 +3981,7 @@
       </c>
       <c r="C126" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
@@ -3992,8 +3991,8 @@
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr"/>
@@ -4019,65 +4018,66 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr"/>
+      <c r="G127" s="6" t="inlineStr"/>
+      <c r="H127" s="6" t="inlineStr"/>
+    </row>
+    <row r="128" ht="44" customHeight="1">
+      <c r="A128" s="6" t="inlineStr"/>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E128" s="6" t="inlineStr">
+        <is>
           <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
 注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
 注3）通いの場の箇所数は3町の事業</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr"/>
-      <c r="G127" s="6" t="inlineStr"/>
-      <c r="H127" s="6" t="inlineStr"/>
-    </row>
-    <row r="128" ht="44" customHeight="1">
-      <c r="A128" s="6" t="inlineStr"/>
-      <c r="B128" s="6" t="inlineStr">
+      <c r="F128" s="6" t="inlineStr"/>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr"/>
+    </row>
+    <row r="129" ht="44" customHeight="1">
+      <c r="A129" s="6" t="inlineStr"/>
+      <c r="B129" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C128" s="6" t="inlineStr">
+      <c r="C129" s="6" t="inlineStr">
         <is>
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D128" s="11" t="inlineStr">
+      <c r="D129" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E129" s="6" t="inlineStr">
         <is>
           <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
 注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
 注3）通いの場の箇所数は3町の事業</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr"/>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="6" t="inlineStr"/>
-    </row>
-    <row r="129" ht="44" customHeight="1">
-      <c r="A129" s="6" t="inlineStr"/>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
-        </is>
-      </c>
       <c r="F129" s="6" t="inlineStr"/>
       <c r="G129" s="6" t="inlineStr"/>
       <c r="H129" s="6" t="inlineStr"/>
@@ -4094,9 +4094,9 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D130" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -4127,37 +4127,37 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F131" s="6" t="inlineStr"/>
+      <c r="G131" s="6" t="inlineStr"/>
+      <c r="H131" s="6" t="inlineStr"/>
+    </row>
+    <row r="132" ht="44" customHeight="1">
+      <c r="A132" s="6" t="inlineStr"/>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F131" s="6" t="inlineStr"/>
-      <c r="G131" s="6" t="inlineStr"/>
-      <c r="H131" s="6" t="inlineStr"/>
-    </row>
-    <row r="132" ht="44" customHeight="1">
-      <c r="A132" s="6" t="inlineStr"/>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D132" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
       <c r="F132" s="6" t="inlineStr"/>
       <c r="G132" s="6" t="inlineStr"/>
       <c r="H132" s="6" t="inlineStr"/>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="C133" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
@@ -4181,7 +4181,7 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr"/>
@@ -4207,7 +4207,7 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr"/>
@@ -4226,14 +4226,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
+          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr"/>
@@ -4252,15 +4252,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D136" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr"/>
@@ -4306,9 +4305,9 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -4340,8 +4339,8 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr"/>
@@ -4357,17 +4356,18 @@
       </c>
       <c r="C140" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D140" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D140" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr"/>
@@ -4386,9 +4386,9 @@
           <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr"/>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D143" s="6" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr"/>
@@ -4471,8 +4471,7 @@
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
-注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr"/>
@@ -4498,7 +4497,8 @@
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
+          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
+注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr"/>
@@ -4517,14 +4517,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D146" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr"/>
@@ -4569,15 +4569,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D148" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D148" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr"/>
@@ -4630,7 +4629,8 @@
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr"/>
@@ -4675,14 +4675,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D152" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D152" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr"/>
@@ -4701,9 +4701,9 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D153" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
@@ -4727,14 +4727,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D154" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr"/>
@@ -4753,14 +4753,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D155" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D155" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があり、当広域連合が対象となる場合は単価を上げる向きに働きます。いずれの</t>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr"/>
@@ -4786,37 +4786,37 @@
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
+          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があります。構成3町は特別地域加算の対象地域に掲げられていない一方、後の</t>
+        </is>
+      </c>
+      <c r="F156" s="6" t="inlineStr"/>
+      <c r="G156" s="6" t="inlineStr"/>
+      <c r="H156" s="6" t="inlineStr"/>
+    </row>
+    <row r="157" ht="44" customHeight="1">
+      <c r="A157" s="6" t="inlineStr"/>
+      <c r="B157" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C157" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E157" s="6" t="inlineStr">
+        <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F156" s="6" t="inlineStr"/>
-      <c r="G156" s="6" t="inlineStr"/>
-      <c r="H156" s="6" t="inlineStr"/>
-    </row>
-    <row r="157" ht="44" customHeight="1">
-      <c r="A157" s="6" t="inlineStr"/>
-      <c r="B157" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C157" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D157" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E157" s="6" t="inlineStr">
-        <is>
-          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
-        </is>
-      </c>
       <c r="F157" s="6" t="inlineStr"/>
       <c r="G157" s="6" t="inlineStr"/>
       <c r="H157" s="6" t="inlineStr"/>
@@ -4833,14 +4833,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
+          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr"/>
@@ -4866,7 +4866,7 @@
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
         </is>
       </c>
       <c r="F159" s="6" t="inlineStr"/>
@@ -4918,8 +4918,7 @@
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
-注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr"/>
@@ -4935,7 +4934,7 @@
       </c>
       <c r="C162" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D162" s="6" t="inlineStr">
@@ -4945,7 +4944,8 @@
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr"/>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr"/>
@@ -5004,86 +5004,82 @@
       <c r="G164" s="6" t="inlineStr"/>
       <c r="H164" s="6" t="inlineStr"/>
     </row>
-    <row r="166" ht="28" customHeight="1">
-      <c r="A166" s="7" t="inlineStr">
+    <row r="165" ht="44" customHeight="1">
+      <c r="A165" s="6" t="inlineStr"/>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D165" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr"/>
+      <c r="G165" s="6" t="inlineStr"/>
+      <c r="H165" s="6" t="inlineStr"/>
+    </row>
+    <row r="167" ht="28" customHeight="1">
+      <c r="A167" s="7" t="inlineStr">
         <is>
           <t>注1）表の中の未確定箇所は32種の表に150箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="20" customHeight="1">
-      <c r="A168" s="3" t="inlineStr">
+    <row r="169" ht="20" customHeight="1">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="30" customHeight="1">
-      <c r="A169" s="4" t="inlineStr"/>
-      <c r="B169" s="4" t="inlineStr">
+    <row r="170" ht="30" customHeight="1">
+      <c r="A170" s="4" t="inlineStr"/>
+      <c r="B170" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C169" s="4" t="inlineStr">
+      <c r="C170" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D169" s="4" t="inlineStr">
+      <c r="D170" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E169" s="4" t="inlineStr">
+      <c r="E170" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F169" s="4" t="inlineStr">
+      <c r="F170" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G169" s="4" t="inlineStr">
+      <c r="G170" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H169" s="4" t="inlineStr">
+      <c r="H170" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="44" customHeight="1">
-      <c r="A170" s="6" t="inlineStr"/>
-      <c r="B170" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C170" s="6" t="inlineStr">
-        <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D170" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E170" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F170" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G170" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H170" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -5096,11 +5092,11 @@
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>第4節　計画期間</t>
+          <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
       <c r="D171" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E171" s="5" t="n">
         <v>0</v>
@@ -5113,7 +5109,7 @@
       </c>
       <c r="H171" s="6" t="inlineStr">
         <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
+          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -5126,24 +5122,24 @@
       </c>
       <c r="C172" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第4節　計画期間</t>
         </is>
       </c>
       <c r="D172" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E172" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H172" s="6" t="inlineStr">
         <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
+          <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -5151,34 +5147,64 @@
       <c r="A173" s="6" t="inlineStr"/>
       <c r="B173" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>第1節 計画の基本理念</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F173" s="5" t="n">
         <v>1</v>
       </c>
       <c r="G173" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H173" s="6" t="inlineStr">
+        <is>
+          <t>策定体制の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="44" customHeight="1">
+      <c r="A174" s="6" t="inlineStr"/>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>第4章　計画の基本理念及び基本目標</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>第1節 計画の基本理念</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E174" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H173" s="6" t="inlineStr">
+      <c r="F174" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="42" customHeight="1">
-      <c r="A175" s="7" t="inlineStr">
+    <row r="176" ht="42" customHeight="1">
+      <c r="A176" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は4節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -5189,13 +5215,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A176:H176"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A166:H166"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A175:H175"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A169:H169"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A168:H168"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A167:H167"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5269,7 +5295,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
@@ -5329,7 +5355,7 @@
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>解決</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
@@ -5344,11 +5370,11 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>解決</t>
+          <t>対応中</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="6" t="inlineStr"/>
@@ -6975,7 +7001,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1060段落156表36図／273箇所</t>
+          <t>1059段落156表36図／273箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>273箇所</t>
+          <t>275箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議158・要確認113・要内訳2。本文123箇所・表32種150箇所（01シート）</t>
+          <t>要協議158・要確認115・要内訳2。本文125箇所・表32種150箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>186件</t>
+          <t>189件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>175件</t>
+          <t>178件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが105件（02シート）</t>
+          <t>このうち計画素案を止めているものが108件（02シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1059段落156表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1062段落156表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>273箇所のうち62箇所（23％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>275箇所のうち62箇所（23％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H176"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1059段落156表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計273箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1062段落156表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計275箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>76</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -926,13 +926,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="8" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>18</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -1048,13 +1048,13 @@
       </c>
       <c r="C13" s="9" t="inlineStr"/>
       <c r="D13" s="10" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E13" s="10" t="n">
         <v>158</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>2</v>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>1</v>
@@ -1578,22 +1578,22 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0</v>
@@ -1604,12 +1604,12 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -1624,37 +1624,37 @@
       <c r="G34" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="6" t="inlineStr">
-        <is>
-          <t>No.1（認定率のシナリオ）</t>
-        </is>
-      </c>
+      <c r="H34" s="6" t="inlineStr"/>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="6" t="inlineStr"/>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t>No.1（認定率のシナリオ）</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="6" t="inlineStr"/>
@@ -1767,7 +1767,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（123件）</t>
+          <t>3　本文の未確定箇所（125件）</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条は、市町村介護保険事業計画は医療計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合は、在宅医療・介護連携（第5章 基本目標1）、協力医療機関の確保（第1章第9節1）並びに施設・居住系サービスの整備（第6章第5節）において図ります。北海道の第10期高齢者保健福祉計画・介護保険事業支援計画</t>
+          <t>介護保険法第117条第10項は、市町村介護保険事業計画は、地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項に規定する市町村計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合性の確保は、同法第118条第10項により都道府県介護保険事業支援計画について定められているものです。本計画において</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条は、市町村介護保険事業計画は医療計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合は、在宅医療・介護連携（第5章 基本目標1）、協力医療機関の確保（第1章第9節1）並びに施設・居住系サービスの整備（第6章第5節）において図ります。北海道の第10期高齢者保健福祉計画・介護保険事業支援計画</t>
+          <t>介護保険法第117条第10項は、市町村介護保険事業計画は、地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項に規定する市町村計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合性の確保は、同法第118条第10項により都道府県介護保険事業支援計画について定められているものです。本計画において</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2078,7 +2078,7 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
+          <t>介護保険法第117条第10項は、市町村介護保険事業計画は、地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項に規定する市町村計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合性の確保は、同法第118条第10項により都道府県介護保険事業支援計画について定められているものです。本計画において</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr"/>
@@ -2094,7 +2094,7 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D54" s="6" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2123,14 +2123,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>要件を満たす協力医療機関を定めることの義務化には令和9年3月31日までの経過措置が設けられており、本計画の初日である令和9年4月1日から義務となります。国は、全国における要件を満たす体制の整備割合を介護老人福祉施設67.9％、介護老人保健施設83.3％、介護医療院84.9％としたうえで、定めの状況について集計していないと回答した自治体が一定程度存在し、地域差</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2149,14 +2149,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
+          <t>要件を満たす協力医療機関を定めることの義務化には令和9年3月31日までの経過措置が設けられており、本計画の初日である令和9年4月1日から義務となります。国は、全国における要件を満たす体制の整備割合を介護老人福祉施設67.9％、介護老人保健施設83.3％、介護医療院84.9％としたうえで、定めの状況について集計していないと回答した自治体が一定程度存在し、地域差</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。指定に係る構成</t>
+          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2201,9 +2201,9 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -2227,9 +2227,9 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2260,8 +2260,7 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>資料：社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）
-注）期限の目安は、公布の日（令和8年6月25日）から要綱が定める期間を加えたものです。実際の施行の日は政令により定まります［要確認］。</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。指定に係る構成</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr"/>
@@ -2287,8 +2286,8 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>資料：社会福祉法等の一部を改正する法律案要綱（令和8年10月14日に確認）
-注）要綱は改正事項の要旨を示すものであり、改正後の条文及び附則の経過措置の内容を確認できていないため、項番号及び号番号は要綱の記載によっています［要確認］。</t>
+          <t>資料：社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）
+注）期限の目安は、公布の日（令和8年6月25日）から要綱が定める期間を加えたものです。実際の施行の日は政令により定まります［要確認］。</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2314,7 +2313,8 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
+          <t>資料：社会福祉法等の一部を改正する法律案要綱（令和8年10月14日に確認）
+注）要綱は改正事項の要旨を示すものであり、改正後の条文及び附則の経過措置の内容を確認できていないため、項番号及び号番号は要綱の記載によっています［要確認］。</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2325,22 +2325,22 @@
       <c r="A63" s="6" t="inlineStr"/>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2359,14 +2359,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2385,14 +2385,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2411,14 +2411,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2460,17 +2460,17 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
-        </is>
-      </c>
-      <c r="D68" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D69" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>本広域連合の訪問介護の1人1月あたり利用回数は全国の1.87倍であり（第2節1）、区域内の訪問介護13事業所のうち8事業所が住まいに併設しています（第6節）。上記の全国の実態と同じ構造によるものと考えられますが、同一の建物に居住する方への提供の割合は把握していないため、本計画では要因を特定していません［要確認］。</t>
+          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2593,15 +2593,14 @@
           <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
-注2）登録有料老人ホームの入居定員総数が記載及び勘案の対象に加わるのは、登録制度の施行に合わせた改正によるものです。同制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施</t>
+          <t>本広域連合の訪問介護の1人1月あたり利用回数は全国の1.87倍であり（第2節1）、区域内の訪問介護13事業所のうち8事業所が住まいに併設しています（第6節）。上記の全国の実態と同じ構造によるものと考えられますが、同一の建物に居住する方への提供の割合は把握していないため、本計画では要因を特定していません［要確認］。</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2620,9 +2619,9 @@
           <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
-      <c r="D74" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -2644,7 +2643,7 @@
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D75" s="6" t="inlineStr">
@@ -2654,7 +2653,8 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
+注2）登録有料老人ホームの入居定員総数が記載及び勘案の対象に加わるのは、登録制度の施行に合わせた改正によるものです。同制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2680,8 +2680,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
-注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr"/>
@@ -2697,7 +2696,7 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2707,8 +2706,8 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
-注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
+          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
+注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2727,14 +2726,15 @@
           <t>第5節 在宅介護の実態</t>
         </is>
       </c>
-      <c r="D78" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D78" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
+注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2750,17 +2750,17 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr"/>
@@ -2802,17 +2802,17 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の中長期的な推計は、令和6年度の実績を据え置き、サービス事業は認定者数、一般介護予防事業は第1号被保険者数の伸びにより延ばしています（第6章第3節2）。認定者数が令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。事業費の中長期的な推計は、令和7年度の事業ごと</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr"/>
@@ -2823,22 +2823,22 @@
       <c r="A82" s="6" t="inlineStr"/>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
-        </is>
-      </c>
-      <c r="D82" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
+          <t>地域支援事業の量の中長期的な推計は、令和6年度の実績を据え置き、サービス事業は認定者数、一般介護予防事業は第1号被保険者数の伸びにより延ばしています（第6章第3節2）。認定者数が令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。事業費の中長期的な推計は、令和7年度の事業ごと</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
@@ -2864,8 +2864,7 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
-注）分母は地域包括ケア「見え</t>
+          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr"/>
@@ -2881,7 +2880,7 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D84" s="6" t="inlineStr">
@@ -2891,7 +2890,8 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
+          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
+注）分母は地域包括ケア「見え</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr"/>
@@ -2917,7 +2917,7 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
+          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr"/>
@@ -2933,17 +2933,17 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D86" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 地域支援事業の実績</t>
+        </is>
+      </c>
+      <c r="D86" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr"/>
@@ -2962,14 +2962,14 @@
           <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr"/>
@@ -3006,12 +3006,12 @@
       <c r="A89" s="6" t="inlineStr"/>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D89" s="6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr"/>
@@ -3040,14 +3040,14 @@
           <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
-      <c r="D90" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D90" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr"/>
@@ -3066,14 +3066,14 @@
           <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr"/>
@@ -3084,22 +3084,22 @@
       <c r="A92" s="6" t="inlineStr"/>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
-        </is>
-      </c>
-      <c r="D92" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D92" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の個別事例の検討から地域課題の抽出、資源開発、施策化への接続を制度化します。社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護保険法第115条の48の会議は改正後「支援会議」と称し、構成員として地域包括支援センターが明示されます。地域ケア会議は、社会福祉法の支援会議、障害者総合支援法の支援協議会、住宅確保要配慮者に対する賃貸住宅</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr"/>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>虐待の初動、成年後見制度の利用、意思決定支援、消費者被害防止を一体で管理します。同法により、市町村は、高齢者及び障害者による成年後見制度又は権利擁護事業（包括的支援事業）等の適切な利用の支援のため、権利利益の擁護に係る支援に従事する者に対する相談・助言及び関係機関等との連絡調整等の事務の実施に努めるものとされ、中核的な役割を担う機関として地域権利擁護相談支援</t>
+          <t>地域ケア会議の個別事例の検討から地域課題の抽出、資源開発、施策化への接続を制度化します。社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護保険法第115条の48の会議は改正後「支援会議」と称し、構成員として地域包括支援センターが明示されます。地域ケア会議は、社会福祉法の支援会議、障害者総合支援法の支援協議会、住宅確保要配慮者に対する賃貸住宅</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>虐待の初動、成年後見制度の利用、意思決定支援、消費者被害防止を一体で管理します。同法により、市町村は、高齢者及び障害者による成年後見制度又は権利擁護事業（包括的支援事業）等の適切な利用の支援のため、権利利益の擁護に係る支援に従事する者に対する相談・助言及び関係機関等との連絡調整等の事務の実施に努めるものとされ、中核的な役割を担う機関として地域権利擁護相談支援</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr"/>
@@ -3193,7 +3193,7 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr"/>
@@ -3300,9 +3300,9 @@
           <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
-      <c r="D100" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E100" s="6" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D101" s="6" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr"/>
@@ -3349,17 +3349,17 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
+        </is>
+      </c>
+      <c r="D102" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>同法により、都道府県は、質の高い介護サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組を促進するための協議会を置くものとされ、市町村は構成員として参画するものとされました（第1章第9節2）。北海道における協議会の設置の状況を確認し、本広域連合と構成3町のいずれが参画するかを含めて協議します［要協議］。</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr"/>
@@ -3378,14 +3378,14 @@
           <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>同法により、都道府県は、質の高い介護サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組を促進するための協議会を置くものとされ、市町村は構成員として参画するものとされました（第1章第9節2）。北海道における協議会の設置の状況を確認し、本広域連合と構成3町のいずれが参画するかを含めて協議します［要協議］。</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr"/>
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr"/>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D105" s="6" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr"/>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr"/>
@@ -3482,14 +3482,14 @@
           <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
-      <c r="D107" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>BCPについて、策定率、訓練の実施状況、相互応援協定の締結状況を把握します。策定は令和6年度から義務化されており、指定・指導の際に確認できます。国は、BCPの実効性を高めるには行政や他の介護施設等との平時からの連携が重要であるとしたうえで、市区町村の約6割が介護事業所等に対して業務継続を可能とする備えに関する助言等を行っていない状況にあることを示しています。</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr"/>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>介護事故の防止について、事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行います。国は、事故防止を推進するための国・都道府県・市町村の役割として、市町村が事故が発生した事業所からの報告の受付並びに報告内容の集計及び傾向の把握を担うことを示し、介護サービス情報公表システムを活用した報告のための仕組みの構築と報告様式の見直しを検討しています（第1章第9</t>
+          <t>BCPについて、策定率、訓練の実施状況、相互応援協定の締結状況を把握します。策定は令和6年度から義務化されており、指定・指導の際に確認できます。国は、BCPの実効性を高めるには行政や他の介護施設等との平時からの連携が重要であるとしたうえで、市区町村の約6割が介護事業所等に対して業務継続を可能とする備えに関する助言等を行っていない状況にあることを示しています。</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr"/>
@@ -3534,14 +3534,14 @@
           <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
-      <c r="D109" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
+          <t>介護事故の防止について、事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行います。国は、事故防止を推進するための国・都道府県・市町村の役割として、市町村が事故が発生した事業所からの報告の受付並びに報告内容の集計及び傾向の把握を担うことを示し、介護サービス情報公表システムを活用した報告のための仕組みの構築と報告様式の見直しを検討しています（第1章第9</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr"/>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>同法により、災害が発生した区域に派遣されて災害時における福祉サービスの提供を行う災害時福祉業務従事者の登録の制度が設けられました（第1章第9節2）。介護福祉士、介護支援専門員、社会福祉士等であって厚生労働大臣が実施する研修の課程を修了した者等が対象となり、都道府県知事は、災害が発生した場合に従事することを要請することができるものとされています。区域内の事業所</t>
+          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr"/>
@@ -3578,12 +3578,12 @@
       <c r="A111" s="6" t="inlineStr"/>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D111" s="6" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
+          <t>同法により、災害が発生した区域に派遣されて災害時における福祉サービスの提供を行う災害時福祉業務従事者の登録の制度が設けられました（第1章第9節2）。介護福祉士、介護支援専門員、社会福祉士等であって厚生労働大臣が実施する研修の課程を修了した者等が対象となり、都道府県知事は、災害が発生した場合に従事することを要請することができるものとされています。区域内の事業所</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr"/>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
+          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr"/>
@@ -3638,14 +3638,14 @@
           <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
-      <c r="D113" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D113" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr"/>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr"/>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr"/>
@@ -3742,9 +3742,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D117" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D117" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -3775,8 +3775,7 @@
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr"/>
@@ -3903,9 +3902,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D123" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D123" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E123" s="6" t="inlineStr">
@@ -3930,9 +3929,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3984,9 +3983,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D126" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -4008,7 +4007,7 @@
       </c>
       <c r="C127" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
@@ -4018,8 +4017,8 @@
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr"/>
@@ -4045,65 +4044,66 @@
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F128" s="6" t="inlineStr"/>
+      <c r="G128" s="6" t="inlineStr"/>
+      <c r="H128" s="6" t="inlineStr"/>
+    </row>
+    <row r="129" ht="44" customHeight="1">
+      <c r="A129" s="6" t="inlineStr"/>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
           <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
 注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
 注3）通いの場の箇所数は3町の事業</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr"/>
-      <c r="G128" s="6" t="inlineStr"/>
-      <c r="H128" s="6" t="inlineStr"/>
-    </row>
-    <row r="129" ht="44" customHeight="1">
-      <c r="A129" s="6" t="inlineStr"/>
-      <c r="B129" s="6" t="inlineStr">
+      <c r="F129" s="6" t="inlineStr"/>
+      <c r="G129" s="6" t="inlineStr"/>
+      <c r="H129" s="6" t="inlineStr"/>
+    </row>
+    <row r="130" ht="44" customHeight="1">
+      <c r="A130" s="6" t="inlineStr"/>
+      <c r="B130" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C129" s="6" t="inlineStr">
+      <c r="C130" s="6" t="inlineStr">
         <is>
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr">
+      <c r="D130" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E130" s="6" t="inlineStr">
         <is>
           <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
 注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
 注3）通いの場の箇所数は3町の事業</t>
         </is>
       </c>
-      <c r="F129" s="6" t="inlineStr"/>
-      <c r="G129" s="6" t="inlineStr"/>
-      <c r="H129" s="6" t="inlineStr"/>
-    </row>
-    <row r="130" ht="44" customHeight="1">
-      <c r="A130" s="6" t="inlineStr"/>
-      <c r="B130" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C130" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D130" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
-        <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
-        </is>
-      </c>
       <c r="F130" s="6" t="inlineStr"/>
       <c r="G130" s="6" t="inlineStr"/>
       <c r="H130" s="6" t="inlineStr"/>
@@ -4120,9 +4120,9 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -4153,63 +4153,63 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F132" s="6" t="inlineStr"/>
+      <c r="G132" s="6" t="inlineStr"/>
+      <c r="H132" s="6" t="inlineStr"/>
+    </row>
+    <row r="133" ht="44" customHeight="1">
+      <c r="A133" s="6" t="inlineStr"/>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D133" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F133" s="6" t="inlineStr"/>
+      <c r="G133" s="6" t="inlineStr"/>
+      <c r="H133" s="6" t="inlineStr"/>
+    </row>
+    <row r="134" ht="44" customHeight="1">
+      <c r="A134" s="6" t="inlineStr"/>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C134" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr"/>
-      <c r="G132" s="6" t="inlineStr"/>
-      <c r="H132" s="6" t="inlineStr"/>
-    </row>
-    <row r="133" ht="44" customHeight="1">
-      <c r="A133" s="6" t="inlineStr"/>
-      <c r="B133" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C133" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D133" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F133" s="6" t="inlineStr"/>
-      <c r="G133" s="6" t="inlineStr"/>
-      <c r="H133" s="6" t="inlineStr"/>
-    </row>
-    <row r="134" ht="44" customHeight="1">
-      <c r="A134" s="6" t="inlineStr"/>
-      <c r="B134" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C134" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D134" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
-        <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
-        </is>
-      </c>
       <c r="F134" s="6" t="inlineStr"/>
       <c r="G134" s="6" t="inlineStr"/>
       <c r="H134" s="6" t="inlineStr"/>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr"/>
@@ -4252,14 +4252,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr"/>
@@ -4285,8 +4285,7 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr"/>
@@ -4305,15 +4304,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D138" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr"/>
@@ -4332,9 +4330,9 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D139" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D139" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -4359,15 +4357,15 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D140" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支援2を含みます。定員に対する受給者数の割合が低いことは、区域内に空きがあることを意味しません（第4節2の注）。</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr"/>
@@ -4383,17 +4381,18 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D141" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D141" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr"/>
@@ -4409,7 +4408,7 @@
       </c>
       <c r="C142" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D142" s="6" t="inlineStr">
@@ -4419,7 +4418,8 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。同法第8条第21項により、介護専用型特定施設はその入居者が要介護者、その配偶者その他厚生労働省令で定める者に限られるものであり、類型は入居の要件により定まります。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr"/>
@@ -4438,14 +4438,14 @@
           <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
-      <c r="D143" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D143" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr"/>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr"/>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
@@ -4497,8 +4497,7 @@
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
-注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr"/>
@@ -4524,7 +4523,7 @@
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr"/>
@@ -4543,14 +4542,15 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
+注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr"/>
@@ -4569,14 +4569,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D148" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr"/>
@@ -4595,15 +4595,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D149" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D149" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr"/>
@@ -4622,15 +4621,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr"/>
@@ -4656,7 +4654,8 @@
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr"/>
@@ -4682,7 +4681,8 @@
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr"/>
@@ -4701,14 +4701,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr"/>
@@ -4734,7 +4734,7 @@
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr"/>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr"/>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があります。構成3町は特別地域加算の対象地域に掲げられていない一方、後の</t>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr"/>
@@ -4805,70 +4805,70 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D157" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F157" s="6" t="inlineStr"/>
+      <c r="G157" s="6" t="inlineStr"/>
+      <c r="H157" s="6" t="inlineStr"/>
+    </row>
+    <row r="158" ht="44" customHeight="1">
+      <c r="A158" s="6" t="inlineStr"/>
+      <c r="B158" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C158" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D158" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E158" s="6" t="inlineStr">
+        <is>
+          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があります。構成3町は特別地域加算の対象地域に掲げられていない一方、後の</t>
+        </is>
+      </c>
+      <c r="F158" s="6" t="inlineStr"/>
+      <c r="G158" s="6" t="inlineStr"/>
+      <c r="H158" s="6" t="inlineStr"/>
+    </row>
+    <row r="159" ht="44" customHeight="1">
+      <c r="A159" s="6" t="inlineStr"/>
+      <c r="B159" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C159" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E159" s="6" t="inlineStr">
         <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F157" s="6" t="inlineStr"/>
-      <c r="G157" s="6" t="inlineStr"/>
-      <c r="H157" s="6" t="inlineStr"/>
-    </row>
-    <row r="158" ht="44" customHeight="1">
-      <c r="A158" s="6" t="inlineStr"/>
-      <c r="B158" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C158" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D158" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E158" s="6" t="inlineStr">
-        <is>
-          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
-        </is>
-      </c>
-      <c r="F158" s="6" t="inlineStr"/>
-      <c r="G158" s="6" t="inlineStr"/>
-      <c r="H158" s="6" t="inlineStr"/>
-    </row>
-    <row r="159" ht="44" customHeight="1">
-      <c r="A159" s="6" t="inlineStr"/>
-      <c r="B159" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C159" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D159" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E159" s="6" t="inlineStr">
-        <is>
-          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
-        </is>
-      </c>
       <c r="F159" s="6" t="inlineStr"/>
       <c r="G159" s="6" t="inlineStr"/>
       <c r="H159" s="6" t="inlineStr"/>
@@ -4885,14 +4885,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D160" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D160" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr"/>
@@ -4944,8 +4944,7 @@
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
-注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr"/>
@@ -4961,7 +4960,7 @@
       </c>
       <c r="C163" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D163" s="6" t="inlineStr">
@@ -4971,7 +4970,7 @@
       </c>
       <c r="E163" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr"/>
@@ -4987,7 +4986,7 @@
       </c>
       <c r="C164" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D164" s="6" t="inlineStr">
@@ -4997,7 +4996,8 @@
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr"/>
@@ -5023,123 +5023,115 @@
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr"/>
       <c r="G165" s="6" t="inlineStr"/>
       <c r="H165" s="6" t="inlineStr"/>
     </row>
-    <row r="167" ht="28" customHeight="1">
-      <c r="A167" s="7" t="inlineStr">
+    <row r="166" ht="44" customHeight="1">
+      <c r="A166" s="6" t="inlineStr"/>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D166" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr"/>
+      <c r="G166" s="6" t="inlineStr"/>
+      <c r="H166" s="6" t="inlineStr"/>
+    </row>
+    <row r="167" ht="44" customHeight="1">
+      <c r="A167" s="6" t="inlineStr"/>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr"/>
+      <c r="G167" s="6" t="inlineStr"/>
+      <c r="H167" s="6" t="inlineStr"/>
+    </row>
+    <row r="169" ht="28" customHeight="1">
+      <c r="A169" s="7" t="inlineStr">
         <is>
           <t>注1）表の中の未確定箇所は32種の表に150箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="20" customHeight="1">
-      <c r="A169" s="3" t="inlineStr">
+    <row r="171" ht="20" customHeight="1">
+      <c r="A171" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="170" ht="30" customHeight="1">
-      <c r="A170" s="4" t="inlineStr"/>
-      <c r="B170" s="4" t="inlineStr">
+    <row r="172" ht="30" customHeight="1">
+      <c r="A172" s="4" t="inlineStr"/>
+      <c r="B172" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C170" s="4" t="inlineStr">
+      <c r="C172" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D170" s="4" t="inlineStr">
+      <c r="D172" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E170" s="4" t="inlineStr">
+      <c r="E172" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F170" s="4" t="inlineStr">
+      <c r="F172" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G170" s="4" t="inlineStr">
+      <c r="G172" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H170" s="4" t="inlineStr">
+      <c r="H172" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="44" customHeight="1">
-      <c r="A171" s="6" t="inlineStr"/>
-      <c r="B171" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C171" s="6" t="inlineStr">
-        <is>
-          <t>第1節　計画策定の趣旨</t>
-        </is>
-      </c>
-      <c r="D171" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E171" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F171" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G171" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H171" s="6" t="inlineStr">
-        <is>
-          <t>趣旨の記述であり、短いことは妥当</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="44" customHeight="1">
-      <c r="A172" s="6" t="inlineStr"/>
-      <c r="B172" s="6" t="inlineStr">
-        <is>
-          <t>第1章　計画策定の意義</t>
-        </is>
-      </c>
-      <c r="C172" s="6" t="inlineStr">
-        <is>
-          <t>第4節　計画期間</t>
-        </is>
-      </c>
-      <c r="D172" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G172" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H172" s="6" t="inlineStr">
-        <is>
-          <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -5152,24 +5144,24 @@
       </c>
       <c r="C173" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
       <c r="D173" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E173" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F173" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H173" s="6" t="inlineStr">
         <is>
-          <t>策定体制の記述であり、短いことは妥当</t>
+          <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
@@ -5177,12 +5169,12 @@
       <c r="A174" s="6" t="inlineStr"/>
       <c r="B174" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
         <is>
-          <t>第1節 計画の基本理念</t>
+          <t>第4節　計画期間</t>
         </is>
       </c>
       <c r="D174" s="5" t="n">
@@ -5192,19 +5184,79 @@
         <v>0</v>
       </c>
       <c r="F174" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G174" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H174" s="6" t="inlineStr">
         <is>
+          <t>計画期間の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="44" customHeight="1">
+      <c r="A175" s="6" t="inlineStr"/>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>第1章　計画策定の意義</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>第5節　計画の策定体制</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="E175" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H175" s="6" t="inlineStr">
+        <is>
+          <t>策定体制の記述であり、短いことは妥当</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="44" customHeight="1">
+      <c r="A176" s="6" t="inlineStr"/>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>第4章　計画の基本理念及び基本目標</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>第1節 計画の基本理念</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" s="6" t="inlineStr">
+        <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="42" customHeight="1">
-      <c r="A176" s="7" t="inlineStr">
+    <row r="178" ht="42" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は4節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -5215,13 +5267,13 @@
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A176:H176"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A171:H171"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A178:H178"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="A169:H169"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A167:H167"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5248,7 +5300,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（186件）</t>
+          <t>確認事項の棚卸し（189件）</t>
         </is>
       </c>
     </row>
@@ -5295,14 +5347,14 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>完了・了承済を除く未回答は175件</t>
+          <t>完了・了承済を除く未回答は178件</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5366,7 @@
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
@@ -5325,7 +5377,7 @@
       <c r="A8" s="6" t="inlineStr"/>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>了承済</t>
+          <t>解決</t>
         </is>
       </c>
       <c r="C8" s="12" t="n">
@@ -5340,7 +5392,7 @@
       <c r="A9" s="6" t="inlineStr"/>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>了承済</t>
         </is>
       </c>
       <c r="C9" s="12" t="n">
@@ -5355,11 +5407,11 @@
       <c r="A10" s="6" t="inlineStr"/>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>解決</t>
+          <t>完了</t>
         </is>
       </c>
       <c r="C10" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="6" t="inlineStr"/>
@@ -5561,10 +5613,10 @@
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
@@ -5730,7 +5782,7 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
@@ -5905,7 +5957,7 @@
     <row r="46" ht="42" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（92件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（95件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（28件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -6889,7 +6941,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議158・要確認113・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議158・要確認115・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -7001,7 +7053,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1059段落156表36図／273箇所</t>
+          <t>1062段落156表36図／275箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -7027,7 +7079,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>273＝273</t>
+          <t>275＝275</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -7053,7 +7105,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>273＝273</t>
+          <t>275＝275</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -7079,7 +7131,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>186件（未回答175件）</t>
+          <t>189件（未回答178件）</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -7105,7 +7157,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>186件／一意186件</t>
+          <t>189件／一意189件</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -7235,7 +7287,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み／62／273箇所（23％）</t>
+          <t>第4節 介護保険サービス等における施設の見込み／62／275箇所（23％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -7474,7 +7526,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は273箇所ある（要協議158・要確認113・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は275箇所ある（要協議158・要確認115・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -7497,7 +7549,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている175件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている178件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -5285,7 +5285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G46"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5343,30 +5343,26 @@
       <c r="A6" s="6" t="inlineStr"/>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>確認待ち</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>149</v>
+          <t>受託者案で確定</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="n">
+        <v>160</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>完了・了承済を除く未回答は178件</t>
-        </is>
-      </c>
+      <c r="G6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="6" t="inlineStr"/>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>受託者案で確定（告示後に再算定）</t>
         </is>
       </c>
       <c r="C7" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D7" s="6" t="inlineStr"/>
       <c r="E7" s="6" t="inlineStr"/>
@@ -5422,289 +5418,280 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>対応中</t>
+          <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="6" t="inlineStr"/>
       <c r="F11" s="6" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr"/>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="6" t="inlineStr"/>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>一部回答済</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr"/>
-      <c r="G12" s="6" t="inlineStr"/>
-    </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="6" t="inlineStr"/>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>了承済（保管せず廃棄）</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="6" t="inlineStr"/>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>実施中</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>2　期限別（未回答のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="4" t="inlineStr"/>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>期限</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>うち計画素案を止めている</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>うち第1次概算を止めている</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="6" t="inlineStr"/>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>一部確認済み</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
+          <t>R8.10</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>期限が過ぎているもの</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>一部解消</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="6" t="inlineStr"/>
+          <t>R8.11</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="6" t="inlineStr"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>期限が過ぎているもの</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="6" t="inlineStr"/>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>一部提供（R8.10.14）</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
+          <t>R8.12</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>期限が過ぎているもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="6" t="inlineStr"/>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>期限が過ぎているもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>R8.9</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>79</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>R8.9.2</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="6" t="inlineStr"/>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>2　期限別（未回答のみ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="4" t="inlineStr"/>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>期限</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>うち計画素案を止めている</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>うち第1次概算を止めている</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr"/>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>70</v>
+          <t>R8.9.24</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>期限が過ぎているもの</t>
-        </is>
-      </c>
+      <c r="G21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>R8.11</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>9</v>
+          <t>R9.4</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>期限が過ぎているもの</t>
-        </is>
-      </c>
+      <c r="G22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="18" customHeight="1">
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>R8.12</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>11</v>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>期限が過ぎているもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="6" t="inlineStr"/>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>R8.8</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="6" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr">
-        <is>
-          <t>期限が過ぎているもの</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="6" t="inlineStr"/>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="n">
-        <v>79</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <v>40</v>
-      </c>
-      <c r="E25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="6" t="inlineStr"/>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>R8.9.2</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
+      <c r="G23" s="6" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>3　確認先別（未回答のみ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>確認先</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>件数</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr"/>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1">
       <c r="A27" s="6" t="inlineStr"/>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr"/>
       <c r="G27" s="6" t="inlineStr"/>
     </row>
@@ -5712,18 +5699,14 @@
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
       <c r="F28" s="6" t="inlineStr"/>
       <c r="G28" s="6" t="inlineStr"/>
     </row>
@@ -5731,58 +5714,71 @@
       <c r="A29" s="6" t="inlineStr"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr"/>
+      <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr"/>
       <c r="G29" s="6" t="inlineStr"/>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>3　確認先別（未回答のみ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="4" t="inlineStr"/>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>確認先</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>件数</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr"/>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="6" t="inlineStr"/>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>発注者・美瑛町</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr"/>
+      <c r="E30" s="6" t="inlineStr"/>
+      <c r="F30" s="6" t="inlineStr"/>
+      <c r="G30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="6" t="inlineStr"/>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>発注者・東川町</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="6" t="inlineStr"/>
+      <c r="G31" s="6" t="inlineStr"/>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="6" t="inlineStr"/>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>北海道</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="6" t="inlineStr"/>
+      <c r="G32" s="6" t="inlineStr"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>発注者</t>
+          <t>発注者・東神楽町</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="D33" s="6" t="inlineStr"/>
       <c r="E33" s="6" t="inlineStr"/>
@@ -5793,11 +5789,11 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="6" t="inlineStr"/>
@@ -5808,11 +5804,11 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>北海道上川総合振興局</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D35" s="6" t="inlineStr"/>
       <c r="E35" s="6" t="inlineStr"/>
@@ -5823,11 +5819,11 @@
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D36" s="6" t="inlineStr"/>
       <c r="E36" s="6" t="inlineStr"/>
@@ -5838,11 +5834,11 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D37" s="6" t="inlineStr"/>
       <c r="E37" s="6" t="inlineStr"/>
@@ -5853,109 +5849,19 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・3町・事業者</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D38" s="6" t="inlineStr"/>
       <c r="E38" s="6" t="inlineStr"/>
       <c r="F38" s="6" t="inlineStr"/>
       <c r="G38" s="6" t="inlineStr"/>
     </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="6" t="inlineStr"/>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>発注者・東神楽町</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="6" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr"/>
-      <c r="G39" s="6" t="inlineStr"/>
-    </row>
-    <row r="40" ht="18" customHeight="1">
-      <c r="A40" s="6" t="inlineStr"/>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>3町</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="6" t="inlineStr"/>
-      <c r="F40" s="6" t="inlineStr"/>
-      <c r="G40" s="6" t="inlineStr"/>
-    </row>
-    <row r="41" ht="18" customHeight="1">
-      <c r="A41" s="6" t="inlineStr"/>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>北海道上川総合振興局</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D41" s="6" t="inlineStr"/>
-      <c r="E41" s="6" t="inlineStr"/>
-      <c r="F41" s="6" t="inlineStr"/>
-      <c r="G41" s="6" t="inlineStr"/>
-    </row>
-    <row r="42" ht="18" customHeight="1">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町・北海道</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D42" s="6" t="inlineStr"/>
-      <c r="E42" s="6" t="inlineStr"/>
-      <c r="F42" s="6" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr"/>
-    </row>
-    <row r="43" ht="18" customHeight="1">
-      <c r="A43" s="6" t="inlineStr"/>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>国の情報</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="6" t="inlineStr"/>
-      <c r="F43" s="6" t="inlineStr"/>
-      <c r="G43" s="6" t="inlineStr"/>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="6" t="inlineStr"/>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>発注者・3町・事業者</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="6" t="inlineStr"/>
-      <c r="F44" s="6" t="inlineStr"/>
-      <c r="G44" s="6" t="inlineStr"/>
-    </row>
-    <row r="46" ht="42" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
+    <row r="40" ht="42" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>注1）期限が令和8年8月以前のもの（95件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（28件）は、3町への照会の様式と時期の決定を先に要します。
@@ -5965,12 +5871,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>189件</t>
+          <t>190件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>178件</t>
+          <t>179件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが108件（02シート）</t>
+          <t>このうち計画素案を止めているものが109件（02シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1062段落156表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1063段落156表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1062段落156表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計275箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1063段落156表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計275箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -5285,7 +5285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G40"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5300,7 +5300,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（189件）</t>
+          <t>確認事項の棚卸し（190件）</t>
         </is>
       </c>
     </row>
@@ -5429,62 +5429,54 @@
       <c r="F11" s="6" t="inlineStr"/>
       <c r="G11" s="6" t="inlineStr"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>未回答</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>2　期限別（未回答のみ）</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="4" t="inlineStr"/>
-      <c r="B14" s="4" t="inlineStr">
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>期限</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>うち計画素案を止めている</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>うち第1次概算を止めている</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
-      <c r="G14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>内容</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="6" t="inlineStr"/>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>R8.10</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>70</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>期限が過ぎているもの</t>
         </is>
       </c>
     </row>
@@ -5492,14 +5484,14 @@
       <c r="A16" s="6" t="inlineStr"/>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>R8.11</t>
+          <t>R8.10</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="E16" s="5" t="n">
         <v>0</v>
@@ -5515,14 +5507,14 @@
       <c r="A17" s="6" t="inlineStr"/>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>R8.12</t>
+          <t>R8.11</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
@@ -5538,14 +5530,14 @@
       <c r="A18" s="6" t="inlineStr"/>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>R8.8</t>
+          <t>R8.12</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>0</v>
@@ -5561,33 +5553,37 @@
       <c r="A19" s="6" t="inlineStr"/>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>R8.9</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n">
-        <v>79</v>
+          <t>R8.8</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>5</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E19" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>期限が過ぎているもの</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="6" t="inlineStr"/>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>R8.9.2</t>
+          <t>R8.9</t>
         </is>
       </c>
       <c r="C20" s="5" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="E20" s="5" t="n">
         <v>0</v>
@@ -5599,14 +5595,14 @@
       <c r="A21" s="6" t="inlineStr"/>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>R8.9.24</t>
+          <t>R8.9.2</t>
         </is>
       </c>
       <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>0</v>
@@ -5618,14 +5614,14 @@
       <c r="A22" s="6" t="inlineStr"/>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>R9.4</t>
+          <t>R8.9.24</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>0</v>
@@ -5637,14 +5633,14 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>告示後</t>
+          <t>R9.4</t>
         </is>
       </c>
       <c r="C23" s="5" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>0</v>
@@ -5652,58 +5648,62 @@
       <c r="F23" s="6" t="inlineStr"/>
       <c r="G23" s="6" t="inlineStr"/>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>告示後</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr"/>
+      <c r="G24" s="6" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>3　確認先別（未回答のみ）</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="4" t="inlineStr"/>
-      <c r="B26" s="4" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>確認先</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>件数</t>
         </is>
       </c>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr"/>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="6" t="inlineStr"/>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>発注者</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
     </row>
     <row r="28" ht="18" customHeight="1">
       <c r="A28" s="6" t="inlineStr"/>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町</t>
+          <t>発注者</t>
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -5714,11 +5714,11 @@
       <c r="A29" s="6" t="inlineStr"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>発注者・北海道</t>
+          <t>発注者・3町</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
       <c r="E29" s="6" t="inlineStr"/>
@@ -5729,11 +5729,11 @@
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>発注者・美瑛町</t>
+          <t>発注者・北海道</t>
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D30" s="6" t="inlineStr"/>
       <c r="E30" s="6" t="inlineStr"/>
@@ -5744,11 +5744,11 @@
       <c r="A31" s="6" t="inlineStr"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>発注者・東川町</t>
+          <t>発注者・美瑛町</t>
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D31" s="6" t="inlineStr"/>
       <c r="E31" s="6" t="inlineStr"/>
@@ -5759,11 +5759,11 @@
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>北海道</t>
+          <t>発注者・東川町</t>
         </is>
       </c>
       <c r="C32" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D32" s="6" t="inlineStr"/>
       <c r="E32" s="6" t="inlineStr"/>
@@ -5774,7 +5774,7 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>発注者・東神楽町</t>
+          <t>北海道</t>
         </is>
       </c>
       <c r="C33" s="5" t="n">
@@ -5789,11 +5789,11 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>3町</t>
+          <t>発注者・東神楽町</t>
         </is>
       </c>
       <c r="C34" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" s="6" t="inlineStr"/>
       <c r="E34" s="6" t="inlineStr"/>
@@ -5804,7 +5804,7 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>北海道上川総合振興局</t>
+          <t>3町</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
@@ -5819,7 +5819,7 @@
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町・北海道</t>
+          <t>北海道上川総合振興局</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
@@ -5834,7 +5834,7 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>国の情報</t>
+          <t>発注者・3町・北海道</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
@@ -5849,7 +5849,7 @@
       <c r="A38" s="6" t="inlineStr"/>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>発注者・3町・事業者</t>
+          <t>国の情報</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
@@ -5860,10 +5860,25 @@
       <c r="F38" s="6" t="inlineStr"/>
       <c r="G38" s="6" t="inlineStr"/>
     </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>注1）期限が令和8年8月以前のもの（95件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="6" t="inlineStr"/>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>発注者・3町・事業者</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="6" t="inlineStr"/>
+      <c r="G39" s="6" t="inlineStr"/>
+    </row>
+    <row r="41" ht="42" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>注1）期限が令和8年8月以前のもの（96件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（28件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -5871,12 +5886,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A14:G14"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A40:G40"/>
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A26:G26"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A41:G41"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6959,7 +6974,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1062段落156表36図／275箇所</t>
+          <t>1063段落156表36図／275箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -7037,7 +7052,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>189件（未回答178件）</t>
+          <t>190件（未回答179件）</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -7063,7 +7078,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>189件／一意189件</t>
+          <t>190件／一意190件</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -7455,7 +7470,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている178件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている179件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>275箇所</t>
+          <t>282箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議158・要確認115・要内訳2。本文125箇所・表32種150箇所（01シート）</t>
+          <t>要協議162・要確認118・要内訳2。本文129箇所・表33種153箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1063段落156表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1074段落158表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>275箇所のうち62箇所（23％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>282箇所のうち63箇所（22％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H178"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1063段落156表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計275箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1074段落158表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計282箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -926,13 +926,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="8" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>18</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -948,10 +948,10 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>17</v>
@@ -1048,13 +1048,13 @@
       </c>
       <c r="C13" s="9" t="inlineStr"/>
       <c r="D13" s="10" t="n">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>2</v>
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="D17" s="8" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F17" s="5" t="n">
         <v>6</v>
@@ -1286,29 +1286,29 @@
       <c r="A23" s="6" t="inlineStr"/>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>10</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>No.4（代表KPIの代理指標）</t>
+          <t>No.8（3調査の点検事項）</t>
         </is>
       </c>
     </row>
@@ -1316,29 +1316,29 @@
       <c r="A24" s="6" t="inlineStr"/>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
         <v>10</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>確認事項B No.19（医療側の連携の実施状況）</t>
+          <t>No.4（代表KPIの代理指標）</t>
         </is>
       </c>
     </row>
@@ -1351,24 +1351,24 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>10</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G25" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
+          <t>確認事項B No.19（医療側の連携の実施状況）</t>
         </is>
       </c>
     </row>
@@ -1376,29 +1376,29 @@
       <c r="A26" s="6" t="inlineStr"/>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G26" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>No.8（3調査の点検事項）</t>
+          <t>No.10（採用者数・退職者数）・No.116（人材の制約）</t>
         </is>
       </c>
     </row>
@@ -1466,59 +1466,55 @@
       <c r="A29" s="6" t="inlineStr"/>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="6" t="inlineStr">
-        <is>
-          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
-        </is>
-      </c>
+      <c r="H29" s="6" t="inlineStr"/>
     </row>
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E30" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E30" s="5" t="n">
-        <v>2</v>
-      </c>
       <c r="F30" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>No.3（町別人口）</t>
+          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
         </is>
       </c>
     </row>
@@ -1531,17 +1527,17 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第2節　計画の位置付け</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
@@ -1552,27 +1548,31 @@
       <c r="A32" s="6" t="inlineStr"/>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第1節 高齢者の状況</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E32" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="6" t="inlineStr"/>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t>No.3（町別人口）</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="6" t="inlineStr"/>
@@ -1583,17 +1583,17 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0</v>
@@ -1604,12 +1604,12 @@
       <c r="A34" s="6" t="inlineStr"/>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
@@ -1630,12 +1630,12 @@
       <c r="A35" s="6" t="inlineStr"/>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
@@ -1650,39 +1650,35 @@
       <c r="G35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H35" s="6" t="inlineStr">
-        <is>
-          <t>No.1（認定率のシナリオ）</t>
-        </is>
-      </c>
+      <c r="H35" s="6" t="inlineStr"/>
     </row>
     <row r="36" ht="32" customHeight="1">
       <c r="A36" s="6" t="inlineStr"/>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>No.8（同）</t>
+          <t>No.1（認定率のシナリオ）</t>
         </is>
       </c>
     </row>
@@ -1690,27 +1686,31 @@
       <c r="A37" s="6" t="inlineStr"/>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="6" t="inlineStr"/>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t>No.8（同）</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="6" t="inlineStr"/>
@@ -1767,7 +1767,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（125件）</t>
+          <t>3　本文の未確定箇所（129件）</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。認知症施策推進基本計画及び都道府県認知症施策推進計画の内容及び策定の状況は［要確認］です。</t>
+          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。都道府県認知症施策推進計画については、北海道の第10期高齢者保健福祉計画・介護保険事業支援計画の骨子（案）において、第5章第5節「認知症施策の推進」として北海道認知症施策推進計画を一体のものとして策定することとされています。認知症施</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
+          <t>資料：令和8年度第3回北海道高齢者保健福祉施策検討協議会（令和8年8月27日）資料5 第10期北海道高齢者保健福祉計画・介護保険事業支援計画骨子（案）。北海道の評価指標（第10期）は骨子（案）に示されておらず、各目標の達成目標は計画の第5章でまとめて整理することとされています。このため、評価指標による対応は次の第9期の表によります［要確認］。</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2149,14 +2149,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>要件を満たす協力医療機関を定めることの義務化には令和9年3月31日までの経過措置が設けられており、本計画の初日である令和9年4月1日から義務となります。国は、全国における要件を満たす体制の整備割合を介護老人福祉施設67.9％、介護老人保健施設83.3％、介護医療院84.9％としたうえで、定めの状況について集計していないと回答した自治体が一定程度存在し、地域差</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2175,14 +2175,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
+          <t>要件を満たす協力医療機関を定めることの義務化には令和9年3月31日までの経過措置が設けられており、本計画の初日である令和9年4月1日から義務となります。国は、全国における要件を満たす体制の整備割合を介護老人福祉施設67.9％、介護老人保健施設83.3％、介護医療院84.9％としたうえで、定めの状況について集計していないと回答した自治体が一定程度存在し、地域差</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。指定に係る構成</t>
+          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2227,9 +2227,9 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -2253,9 +2253,9 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2286,8 +2286,7 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>資料：社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）
-注）期限の目安は、公布の日（令和8年6月25日）から要綱が定める期間を加えたものです。実際の施行の日は政令により定まります［要確認］。</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。指定に係る構成</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr"/>
@@ -2313,8 +2312,8 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>資料：社会福祉法等の一部を改正する法律案要綱（令和8年10月14日に確認）
-注）要綱は改正事項の要旨を示すものであり、改正後の条文及び附則の経過措置の内容を確認できていないため、項番号及び号番号は要綱の記載によっています［要確認］。</t>
+          <t>資料：社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）
+注）期限の目安は、公布の日（令和8年6月25日）から要綱が定める期間を加えたものです。実際の施行の日は政令により定まります［要確認］。</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2340,7 +2339,8 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
+          <t>資料：社会福祉法等の一部を改正する法律案要綱（令和8年10月14日に確認）
+注）要綱は改正事項の要旨を示すものであり、改正後の条文及び附則の経過措置の内容を確認できていないため、項番号及び号番号は要綱の記載によっています［要確認］。</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2351,22 +2351,22 @@
       <c r="A64" s="6" t="inlineStr"/>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D64" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2385,14 +2385,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2411,14 +2411,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2437,14 +2437,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D67" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
-        </is>
-      </c>
-      <c r="D69" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2512,17 +2512,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>本広域連合の訪問介護の1人1月あたり利用回数は全国の1.87倍であり（第2節1）、区域内の訪問介護13事業所のうち8事業所が住まいに併設しています（第6節）。上記の全国の実態と同じ構造によるものと考えられますが、同一の建物に居住する方への提供の割合は把握していないため、本計画では要因を特定していません［要確認］。</t>
+          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2619,15 +2619,14 @@
           <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
-注2）登録有料老人ホームの入居定員総数が記載及び勘案の対象に加わるのは、登録制度の施行に合わせた改正によるものです。同制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施</t>
+          <t>本広域連合の訪問介護の1人1月あたり利用回数は全国の1.87倍であり（第2節1）、区域内の訪問介護13事業所のうち8事業所が住まいに併設しています（第6節）。上記の全国の実態と同じ構造によるものと考えられますが、同一の建物に居住する方への提供の割合は把握していないため、本計画では要因を特定していません［要確認］。</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -2646,15 +2645,14 @@
           <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
-注2）登録有料老人ホームの入居定員総数が記載及び勘案の対象に加わるのは、登録制度の施行に合わせた改正によるものです。同制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施</t>
+          <t>北海道の第10期計画の策定に係る道作成指針（案）は、一部の住宅型有料老人ホームにおける入居者の保護やいわゆる「囲い込み」の問題等に対する実効性のある対応として、住宅担当部局との連携により入居実態等を把握するとともに、必要に応じて、指導監督を行う北海道に対し速やかに情報提供を行うこととし、また、入居定員総数、入居者のうち要介護者である者の割合、在宅サービスの利</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2670,17 +2668,18 @@
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
-        </is>
-      </c>
-      <c r="D76" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 サービス提供体制の状況</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
+注2）登録有料老人ホームの入居定員総数が記載及び勘案の対象に加わるのは、登録制度の施行に合わせた改正によるものです。同制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr"/>
@@ -2696,7 +2695,7 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
@@ -2706,8 +2705,8 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
-注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
+          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
+注2）登録有料老人ホームの入居定員総数が記載及び勘案の対象に加わるのは、登録制度の施行に合わせた改正によるものです。同制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr"/>
@@ -2723,7 +2722,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2733,8 +2732,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
-注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2750,17 +2748,18 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 高齢者の生活実態</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
+注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2776,7 +2775,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2786,7 +2785,8 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
+          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
+注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr"/>
@@ -2802,17 +2802,17 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D81" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr"/>
@@ -2828,17 +2828,17 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
-        </is>
-      </c>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D82" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の中長期的な推計は、令和6年度の実績を据え置き、サービス事業は認定者数、一般介護予防事業は第1号被保険者数の伸びにより延ばしています（第6章第3節2）。認定者数が令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。事業費の中長期的な推計は、令和7年度の事業ごと</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
@@ -2849,12 +2849,12 @@
       <c r="A83" s="6" t="inlineStr"/>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D83" s="6" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr"/>
@@ -2875,23 +2875,22 @@
       <c r="A84" s="6" t="inlineStr"/>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
-        </is>
-      </c>
-      <c r="D84" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
-注）分母は地域包括ケア「見え</t>
+          <t>地域支援事業の量の中長期的な推計は、令和6年度の実績を据え置き、サービス事業は認定者数、一般介護予防事業は第1号被保険者数の伸びにより延ばしています（第6章第3節2）。認定者数が令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。事業費の中長期的な推計は、令和7年度の事業ごと</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr"/>
@@ -2907,7 +2906,7 @@
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2917,7 +2916,7 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
+          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr"/>
@@ -2933,7 +2932,7 @@
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D86" s="6" t="inlineStr">
@@ -2943,7 +2942,8 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
+          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
+注）分母は地域包括ケア「見え</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr"/>
@@ -2959,17 +2959,17 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D87" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 地域支援事業の実績</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr"/>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr"/>
@@ -3014,14 +3014,14 @@
           <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
-      <c r="D89" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr"/>
@@ -3032,12 +3032,12 @@
       <c r="A90" s="6" t="inlineStr"/>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr"/>
@@ -3058,22 +3058,22 @@
       <c r="A91" s="6" t="inlineStr"/>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr"/>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr"/>
@@ -3110,12 +3110,12 @@
       <c r="A93" s="6" t="inlineStr"/>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の個別事例の検討から地域課題の抽出、資源開発、施策化への接続を制度化します。社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護保険法第115条の48の会議は改正後「支援会議」と称し、構成員として地域包括支援センターが明示されます。地域ケア会議は、社会福祉法の支援会議、障害者総合支援法の支援協議会、住宅確保要配慮者に対する賃貸住宅</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr"/>
@@ -3136,22 +3136,22 @@
       <c r="A94" s="6" t="inlineStr"/>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
-        </is>
-      </c>
-      <c r="D94" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>虐待の初動、成年後見制度の利用、意思決定支援、消費者被害防止を一体で管理します。同法により、市町村は、高齢者及び障害者による成年後見制度又は権利擁護事業（包括的支援事業）等の適切な利用の支援のため、権利利益の擁護に係る支援に従事する者に対する相談・助言及び関係機関等との連絡調整等の事務の実施に努めるものとされ、中核的な役割を担う機関として地域権利擁護相談支援</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr"/>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>地域ケア会議の個別事例の検討から地域課題の抽出、資源開発、施策化への接続を制度化します。社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護保険法第115条の48の会議は改正後「支援会議」と称し、構成員として地域包括支援センターが明示されます。地域ケア会議は、社会福祉法の支援会議、障害者総合支援法の支援協議会、住宅確保要配慮者に対する賃貸住宅</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr"/>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>虐待の初動、成年後見制度の利用、意思決定支援、消費者被害防止を一体で管理します。同法により、市町村は、高齢者及び障害者による成年後見制度又は権利擁護事業（包括的支援事業）等の適切な利用の支援のため、権利利益の擁護に係る支援に従事する者に対する相談・助言及び関係機関等との連絡調整等の事務の実施に努めるものとされ、中核的な役割を担う機関として地域権利擁護相談支援</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr"/>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
@@ -3255,7 +3255,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr"/>
@@ -3326,9 +3326,9 @@
           <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
-      <c r="D101" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E101" s="6" t="inlineStr">
@@ -3349,17 +3349,17 @@
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
-        </is>
-      </c>
-      <c r="D102" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr"/>
@@ -3375,17 +3375,17 @@
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
-        </is>
-      </c>
-      <c r="D103" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>同法により、都道府県は、質の高い介護サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組を促進するための協議会を置くものとされ、市町村は構成員として参画するものとされました（第1章第9節2）。北海道における協議会の設置の状況を確認し、本広域連合と構成3町のいずれが参画するかを含めて協議します［要協議］。</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr"/>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D104" s="6" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr"/>
@@ -3430,14 +3430,14 @@
           <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
-      <c r="D105" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>同法により、都道府県は、質の高い介護サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組を促進するための協議会を置くものとされ、市町村は構成員として参画するものとされました（第1章第9節2）。北海道における協議会の設置の状況を確認し、本広域連合と構成3町のいずれが参画するかを含めて協議します［要協議］。</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr"/>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr"/>
@@ -3508,14 +3508,14 @@
           <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
-      <c r="D108" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D108" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>BCPについて、策定率、訓練の実施状況、相互応援協定の締結状況を把握します。策定は令和6年度から義務化されており、指定・指導の際に確認できます。国は、BCPの実効性を高めるには行政や他の介護施設等との平時からの連携が重要であるとしたうえで、市区町村の約6割が介護事業所等に対して業務継続を可能とする備えに関する助言等を行っていない状況にあることを示しています。</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr"/>
@@ -3534,14 +3534,14 @@
           <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
-      <c r="D109" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D109" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>介護事故の防止について、事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行います。国は、事故防止を推進するための国・都道府県・市町村の役割として、市町村が事故が発生した事業所からの報告の受付並びに報告内容の集計及び傾向の把握を担うことを示し、介護サービス情報公表システムを活用した報告のための仕組みの構築と報告様式の見直しを検討しています（第1章第9</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr"/>
@@ -3560,14 +3560,14 @@
           <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
-      <c r="D110" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
+          <t>BCPについて、策定率、訓練の実施状況、相互応援協定の締結状況を把握します。策定は令和6年度から義務化されており、指定・指導の際に確認できます。国は、BCPの実効性を高めるには行政や他の介護施設等との平時からの連携が重要であるとしたうえで、市区町村の約6割が介護事業所等に対して業務継続を可能とする備えに関する助言等を行っていない状況にあることを示しています。</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr"/>
@@ -3586,14 +3586,14 @@
           <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
-      <c r="D111" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>同法により、災害が発生した区域に派遣されて災害時における福祉サービスの提供を行う災害時福祉業務従事者の登録の制度が設けられました（第1章第9節2）。介護福祉士、介護支援専門員、社会福祉士等であって厚生労働大臣が実施する研修の課程を修了した者等が対象となり、都道府県知事は、災害が発生した場合に従事することを要請することができるものとされています。区域内の事業所</t>
+          <t>介護事故の防止について、事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行います。国は、事故防止を推進するための国・都道府県・市町村の役割として、市町村が事故が発生した事業所からの報告の受付並びに報告内容の集計及び傾向の把握を担うことを示し、介護サービス情報公表システムを活用した報告のための仕組みの構築と報告様式の見直しを検討しています（第1章第9</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr"/>
@@ -3604,12 +3604,12 @@
       <c r="A112" s="6" t="inlineStr"/>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D112" s="6" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
+          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr"/>
@@ -3630,12 +3630,12 @@
       <c r="A113" s="6" t="inlineStr"/>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D113" s="6" t="inlineStr">
@@ -3645,7 +3645,7 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
+          <t>同法により、災害が発生した区域に派遣されて災害時における福祉サービスの提供を行う災害時福祉業務従事者の登録の制度が設けられました（第1章第9節2）。介護福祉士、介護支援専門員、社会福祉士等であって厚生労働大臣が実施する研修の課程を修了した者等が対象となり、都道府県知事は、災害が発生した場合に従事することを要請することができるものとされています。区域内の事業所</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr"/>
@@ -3664,14 +3664,14 @@
           <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
-      <c r="D114" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr"/>
@@ -3690,14 +3690,14 @@
           <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
-      <c r="D115" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr"/>
@@ -3713,7 +3713,7 @@
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr"/>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
@@ -3749,7 +3749,7 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr"/>
@@ -3768,9 +3768,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D118" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -3794,15 +3794,14 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D119" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr"/>
@@ -3828,8 +3827,7 @@
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr"/>
@@ -3929,9 +3927,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D124" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -3983,9 +3981,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D126" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -4010,9 +4008,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D127" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D127" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -4034,18 +4032,18 @@
       </c>
       <c r="C128" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D128" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D128" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr"/>
@@ -4061,101 +4059,103 @@
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
+        </is>
+      </c>
+      <c r="F129" s="6" t="inlineStr"/>
+      <c r="G129" s="6" t="inlineStr"/>
+      <c r="H129" s="6" t="inlineStr"/>
+    </row>
+    <row r="130" ht="44" customHeight="1">
+      <c r="A130" s="6" t="inlineStr"/>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr">
+      <c r="D130" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+        </is>
+      </c>
+      <c r="F130" s="6" t="inlineStr"/>
+      <c r="G130" s="6" t="inlineStr"/>
+      <c r="H130" s="6" t="inlineStr"/>
+    </row>
+    <row r="131" ht="44" customHeight="1">
+      <c r="A131" s="6" t="inlineStr"/>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
         <is>
           <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
 注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
 注3）通いの場の箇所数は3町の事業</t>
         </is>
       </c>
-      <c r="F129" s="6" t="inlineStr"/>
-      <c r="G129" s="6" t="inlineStr"/>
-      <c r="H129" s="6" t="inlineStr"/>
-    </row>
-    <row r="130" ht="44" customHeight="1">
-      <c r="A130" s="6" t="inlineStr"/>
-      <c r="B130" s="6" t="inlineStr">
+      <c r="F131" s="6" t="inlineStr"/>
+      <c r="G131" s="6" t="inlineStr"/>
+      <c r="H131" s="6" t="inlineStr"/>
+    </row>
+    <row r="132" ht="44" customHeight="1">
+      <c r="A132" s="6" t="inlineStr"/>
+      <c r="B132" s="6" t="inlineStr">
         <is>
           <t>第6章　介護保険事業等の見込み</t>
         </is>
       </c>
-      <c r="C130" s="6" t="inlineStr">
+      <c r="C132" s="6" t="inlineStr">
         <is>
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D130" s="11" t="inlineStr">
+      <c r="D132" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E130" s="6" t="inlineStr">
+      <c r="E132" s="6" t="inlineStr">
         <is>
           <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
 注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
 注3）通いの場の箇所数は3町の事業</t>
         </is>
       </c>
-      <c r="F130" s="6" t="inlineStr"/>
-      <c r="G130" s="6" t="inlineStr"/>
-      <c r="H130" s="6" t="inlineStr"/>
-    </row>
-    <row r="131" ht="44" customHeight="1">
-      <c r="A131" s="6" t="inlineStr"/>
-      <c r="B131" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C131" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D131" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E131" s="6" t="inlineStr">
-        <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
-        </is>
-      </c>
-      <c r="F131" s="6" t="inlineStr"/>
-      <c r="G131" s="6" t="inlineStr"/>
-      <c r="H131" s="6" t="inlineStr"/>
-    </row>
-    <row r="132" ht="44" customHeight="1">
-      <c r="A132" s="6" t="inlineStr"/>
-      <c r="B132" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C132" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D132" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E132" s="6" t="inlineStr">
-        <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
-        </is>
-      </c>
       <c r="F132" s="6" t="inlineStr"/>
       <c r="G132" s="6" t="inlineStr"/>
       <c r="H132" s="6" t="inlineStr"/>
@@ -4205,63 +4205,63 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F134" s="6" t="inlineStr"/>
+      <c r="G134" s="6" t="inlineStr"/>
+      <c r="H134" s="6" t="inlineStr"/>
+    </row>
+    <row r="135" ht="44" customHeight="1">
+      <c r="A135" s="6" t="inlineStr"/>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F135" s="6" t="inlineStr"/>
+      <c r="G135" s="6" t="inlineStr"/>
+      <c r="H135" s="6" t="inlineStr"/>
+    </row>
+    <row r="136" ht="44" customHeight="1">
+      <c r="A136" s="6" t="inlineStr"/>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr"/>
-      <c r="G134" s="6" t="inlineStr"/>
-      <c r="H134" s="6" t="inlineStr"/>
-    </row>
-    <row r="135" ht="44" customHeight="1">
-      <c r="A135" s="6" t="inlineStr"/>
-      <c r="B135" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C135" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D135" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F135" s="6" t="inlineStr"/>
-      <c r="G135" s="6" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr"/>
-    </row>
-    <row r="136" ht="44" customHeight="1">
-      <c r="A136" s="6" t="inlineStr"/>
-      <c r="B136" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C136" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D136" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E136" s="6" t="inlineStr">
-        <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
-        </is>
-      </c>
       <c r="F136" s="6" t="inlineStr"/>
       <c r="G136" s="6" t="inlineStr"/>
       <c r="H136" s="6" t="inlineStr"/>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="C137" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr"/>
@@ -4304,14 +4304,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D138" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
+          <t>北海道の第10期計画の策定に係る道作成指針（案）は、中山間・人口減少地域において利用者への介護サービスが適切に提供されるよう、次の順序により議論することとしています。ア　指定サービスの実施を基本とし、人材確保や生産性向上に係る支援を行う。イ　指定サービスの確保に係る施策を行っても、指定サービスのみによるサービス提供体制の維持・確保になお課題を抱える場合は、特</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr"/>
@@ -4337,8 +4337,7 @@
       </c>
       <c r="E139" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr"/>
@@ -4364,8 +4363,7 @@
       </c>
       <c r="E140" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr"/>
@@ -4391,8 +4389,7 @@
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr"/>
@@ -4411,15 +4408,15 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D142" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D142" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。同法第8条第21項により、介護専用型特定施設はその入居者が要介護者、その配偶者その他厚生労働省令で定める者に限られるものであり、類型は入居の要件により定まります。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr"/>
@@ -4435,7 +4432,7 @@
       </c>
       <c r="C143" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
@@ -4445,7 +4442,8 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr"/>
@@ -4461,7 +4459,7 @@
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
@@ -4471,7 +4469,8 @@
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr"/>
@@ -4487,7 +4486,7 @@
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
@@ -4497,7 +4496,8 @@
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。同法第8条第21項により、介護専用型特定施設はその入居者が要介護者、その配偶者その他厚生労働省令で定める者に限られるものであり、類型は入居の要件により定まります。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr"/>
@@ -4513,17 +4513,17 @@
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D146" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D146" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr"/>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
@@ -4549,8 +4549,7 @@
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
-注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr"/>
@@ -4566,7 +4565,7 @@
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
@@ -4576,7 +4575,7 @@
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr"/>
@@ -4592,17 +4591,17 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D149" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D149" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>出典：令和8年度第3回北海道高齢者保健福祉施策検討協議会（令和8年8月27日）資料4 第10期介護保険事業（支援）計画の策定に係る道作成指針（案）。同指針は案の段階であり、確定した指針により改めて確かめます［要確認］。</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr"/>
@@ -4621,14 +4620,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D150" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D150" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr"/>
@@ -4654,8 +4653,8 @@
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
+注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr"/>
@@ -4681,8 +4680,7 @@
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr"/>
@@ -4701,14 +4699,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D153" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D153" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr"/>
@@ -4727,14 +4725,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D154" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D154" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr"/>
@@ -4753,14 +4751,15 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D155" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D155" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr"/>
@@ -4786,7 +4785,8 @@
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr"/>
@@ -4805,14 +4805,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D157" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D157" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があります。構成3町は特別地域加算の対象地域に掲げられていない一方、後の</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr"/>
@@ -4857,122 +4857,122 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D159" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D159" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F159" s="6" t="inlineStr"/>
+      <c r="G159" s="6" t="inlineStr"/>
+      <c r="H159" s="6" t="inlineStr"/>
+    </row>
+    <row r="160" ht="44" customHeight="1">
+      <c r="A160" s="6" t="inlineStr"/>
+      <c r="B160" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C160" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D160" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E160" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F160" s="6" t="inlineStr"/>
+      <c r="G160" s="6" t="inlineStr"/>
+      <c r="H160" s="6" t="inlineStr"/>
+    </row>
+    <row r="161" ht="44" customHeight="1">
+      <c r="A161" s="6" t="inlineStr"/>
+      <c r="B161" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C161" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D161" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E161" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F161" s="6" t="inlineStr"/>
+      <c r="G161" s="6" t="inlineStr"/>
+      <c r="H161" s="6" t="inlineStr"/>
+    </row>
+    <row r="162" ht="44" customHeight="1">
+      <c r="A162" s="6" t="inlineStr"/>
+      <c r="B162" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C162" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D162" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E162" s="6" t="inlineStr">
+        <is>
+          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があります。構成3町は特別地域加算の対象地域に掲げられていない一方、後の</t>
+        </is>
+      </c>
+      <c r="F162" s="6" t="inlineStr"/>
+      <c r="G162" s="6" t="inlineStr"/>
+      <c r="H162" s="6" t="inlineStr"/>
+    </row>
+    <row r="163" ht="44" customHeight="1">
+      <c r="A163" s="6" t="inlineStr"/>
+      <c r="B163" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C163" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D163" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E163" s="6" t="inlineStr">
         <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F159" s="6" t="inlineStr"/>
-      <c r="G159" s="6" t="inlineStr"/>
-      <c r="H159" s="6" t="inlineStr"/>
-    </row>
-    <row r="160" ht="44" customHeight="1">
-      <c r="A160" s="6" t="inlineStr"/>
-      <c r="B160" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C160" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D160" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E160" s="6" t="inlineStr">
-        <is>
-          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
-        </is>
-      </c>
-      <c r="F160" s="6" t="inlineStr"/>
-      <c r="G160" s="6" t="inlineStr"/>
-      <c r="H160" s="6" t="inlineStr"/>
-    </row>
-    <row r="161" ht="44" customHeight="1">
-      <c r="A161" s="6" t="inlineStr"/>
-      <c r="B161" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C161" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D161" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E161" s="6" t="inlineStr">
-        <is>
-          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
-        </is>
-      </c>
-      <c r="F161" s="6" t="inlineStr"/>
-      <c r="G161" s="6" t="inlineStr"/>
-      <c r="H161" s="6" t="inlineStr"/>
-    </row>
-    <row r="162" ht="44" customHeight="1">
-      <c r="A162" s="6" t="inlineStr"/>
-      <c r="B162" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C162" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D162" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
-      <c r="F162" s="6" t="inlineStr"/>
-      <c r="G162" s="6" t="inlineStr"/>
-      <c r="H162" s="6" t="inlineStr"/>
-    </row>
-    <row r="163" ht="44" customHeight="1">
-      <c r="A163" s="6" t="inlineStr"/>
-      <c r="B163" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C163" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E163" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
       <c r="F163" s="6" t="inlineStr"/>
       <c r="G163" s="6" t="inlineStr"/>
       <c r="H163" s="6" t="inlineStr"/>
@@ -4989,15 +4989,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D164" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D164" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E164" s="6" t="inlineStr">
         <is>
-          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
-注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr"/>
@@ -5013,7 +5012,7 @@
       </c>
       <c r="C165" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D165" s="6" t="inlineStr">
@@ -5023,7 +5022,7 @@
       </c>
       <c r="E165" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr"/>
@@ -5039,7 +5038,7 @@
       </c>
       <c r="C166" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D166" s="6" t="inlineStr">
@@ -5049,7 +5048,7 @@
       </c>
       <c r="E166" s="6" t="inlineStr">
         <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr"/>
@@ -5065,7 +5064,7 @@
       </c>
       <c r="C167" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D167" s="6" t="inlineStr">
@@ -5075,188 +5074,293 @@
       </c>
       <c r="E167" s="6" t="inlineStr">
         <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr"/>
       <c r="G167" s="6" t="inlineStr"/>
       <c r="H167" s="6" t="inlineStr"/>
     </row>
-    <row r="169" ht="28" customHeight="1">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t>注1）表の中の未確定箇所は32種の表に150箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
+    <row r="168" ht="44" customHeight="1">
+      <c r="A168" s="6" t="inlineStr"/>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
+        <is>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+        </is>
+      </c>
+      <c r="F168" s="6" t="inlineStr"/>
+      <c r="G168" s="6" t="inlineStr"/>
+      <c r="H168" s="6" t="inlineStr"/>
+    </row>
+    <row r="169" ht="44" customHeight="1">
+      <c r="A169" s="6" t="inlineStr"/>
+      <c r="B169" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C169" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D169" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E169" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F169" s="6" t="inlineStr"/>
+      <c r="G169" s="6" t="inlineStr"/>
+      <c r="H169" s="6" t="inlineStr"/>
+    </row>
+    <row r="170" ht="44" customHeight="1">
+      <c r="A170" s="6" t="inlineStr"/>
+      <c r="B170" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C170" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D170" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E170" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F170" s="6" t="inlineStr"/>
+      <c r="G170" s="6" t="inlineStr"/>
+      <c r="H170" s="6" t="inlineStr"/>
+    </row>
+    <row r="171" ht="44" customHeight="1">
+      <c r="A171" s="6" t="inlineStr"/>
+      <c r="B171" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C171" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D171" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E171" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F171" s="6" t="inlineStr"/>
+      <c r="G171" s="6" t="inlineStr"/>
+      <c r="H171" s="6" t="inlineStr"/>
+    </row>
+    <row r="173" ht="28" customHeight="1">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>注1）表の中の未確定箇所は33種の表に153箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="171" ht="20" customHeight="1">
-      <c r="A171" s="3" t="inlineStr">
+    <row r="175" ht="20" customHeight="1">
+      <c r="A175" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="172" ht="30" customHeight="1">
-      <c r="A172" s="4" t="inlineStr"/>
-      <c r="B172" s="4" t="inlineStr">
+    <row r="176" ht="30" customHeight="1">
+      <c r="A176" s="4" t="inlineStr"/>
+      <c r="B176" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C172" s="4" t="inlineStr">
+      <c r="C176" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D172" s="4" t="inlineStr">
+      <c r="D176" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E172" s="4" t="inlineStr">
+      <c r="E176" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F172" s="4" t="inlineStr">
+      <c r="F176" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G172" s="4" t="inlineStr">
+      <c r="G176" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H172" s="4" t="inlineStr">
+      <c r="H176" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
         </is>
       </c>
     </row>
-    <row r="173" ht="44" customHeight="1">
-      <c r="A173" s="6" t="inlineStr"/>
-      <c r="B173" s="6" t="inlineStr">
+    <row r="177" ht="44" customHeight="1">
+      <c r="A177" s="6" t="inlineStr"/>
+      <c r="B177" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C173" s="6" t="inlineStr">
+      <c r="C177" s="6" t="inlineStr">
         <is>
           <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
-      <c r="D173" s="5" t="n">
+      <c r="D177" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E173" s="5" t="n">
+      <c r="E177" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F173" s="5" t="n">
+      <c r="F177" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G173" s="5" t="n">
+      <c r="G177" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H173" s="6" t="inlineStr">
+      <c r="H177" s="6" t="inlineStr">
         <is>
           <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="174" ht="44" customHeight="1">
-      <c r="A174" s="6" t="inlineStr"/>
-      <c r="B174" s="6" t="inlineStr">
+    <row r="178" ht="44" customHeight="1">
+      <c r="A178" s="6" t="inlineStr"/>
+      <c r="B178" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C174" s="6" t="inlineStr">
+      <c r="C178" s="6" t="inlineStr">
         <is>
           <t>第4節　計画期間</t>
         </is>
       </c>
-      <c r="D174" s="5" t="n">
+      <c r="D178" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E174" s="5" t="n">
+      <c r="E178" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F174" s="5" t="n">
+      <c r="F178" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G174" s="5" t="n">
+      <c r="G178" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H174" s="6" t="inlineStr">
+      <c r="H178" s="6" t="inlineStr">
         <is>
           <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="44" customHeight="1">
-      <c r="A175" s="6" t="inlineStr"/>
-      <c r="B175" s="6" t="inlineStr">
+    <row r="179" ht="44" customHeight="1">
+      <c r="A179" s="6" t="inlineStr"/>
+      <c r="B179" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C175" s="6" t="inlineStr">
+      <c r="C179" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D175" s="5" t="n">
+      <c r="D179" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E175" s="5" t="n">
+      <c r="E179" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F175" s="5" t="n">
+      <c r="F179" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G175" s="5" t="n">
+      <c r="G179" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H175" s="6" t="inlineStr">
+      <c r="H179" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="44" customHeight="1">
-      <c r="A176" s="6" t="inlineStr"/>
-      <c r="B176" s="6" t="inlineStr">
+    <row r="180" ht="44" customHeight="1">
+      <c r="A180" s="6" t="inlineStr"/>
+      <c r="B180" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C176" s="6" t="inlineStr">
+      <c r="C180" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D176" s="5" t="n">
+      <c r="D180" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E176" s="5" t="n">
+      <c r="E180" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F176" s="5" t="n">
+      <c r="F180" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G176" s="5" t="n">
+      <c r="G180" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H176" s="6" t="inlineStr">
+      <c r="H180" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="42" customHeight="1">
-      <c r="A178" s="7" t="inlineStr">
+    <row r="182" ht="42" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は4節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -5268,12 +5372,12 @@
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A171:H171"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A178:H178"/>
+    <mergeCell ref="A182:H182"/>
+    <mergeCell ref="A175:H175"/>
     <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A169:H169"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A173:H173"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6399,7 +6503,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第5節・第6節（未確定14箇所）</t>
+          <t>第2章第3節・第5節・第6節（未確定15箇所）</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -6862,7 +6966,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議158・要確認115・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議162・要確認118・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -6974,7 +7078,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1063段落156表36図／275箇所</t>
+          <t>1074段落158表36図／282箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -7000,7 +7104,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>275＝275</t>
+          <t>282＝282</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -7026,7 +7130,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>275＝275</t>
+          <t>282＝282</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -7208,7 +7312,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み／62／275箇所（23％）</t>
+          <t>第4節 介護保険サービス等における施設の見込み／63／282箇所（22％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -7447,7 +7551,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は275箇所ある（要協議158・要確認115・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は282箇所ある（要協議162・要確認118・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>190件</t>
+          <t>192件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>179件</t>
+          <t>181件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが109件（02シート）</t>
+          <t>このうち計画素案を止めているものが111件（02シート）</t>
         </is>
       </c>
     </row>
@@ -5404,7 +5404,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（190件）</t>
+          <t>確認事項の棚卸し（192件）</t>
         </is>
       </c>
     </row>
@@ -5522,11 +5522,11 @@
       <c r="A11" s="6" t="inlineStr"/>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>了承済（保管せず廃棄）</t>
+          <t>未回答</t>
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="6" t="inlineStr"/>
@@ -5537,7 +5537,7 @@
       <c r="A12" s="6" t="inlineStr"/>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>未回答</t>
+          <t>了承済（保管せず廃棄）</t>
         </is>
       </c>
       <c r="C12" s="12" t="n">
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="C17" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>10</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>8</v>
       </c>
       <c r="E17" s="5" t="n">
         <v>0</v>
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -5982,7 +5982,7 @@
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（96件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（98件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（28件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>190件（未回答179件）</t>
+          <t>192件（未回答181件）</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>190件／一意190件</t>
+          <t>192件／一意192件</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -7574,7 +7574,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている179件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている181件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>

--- a/output/第10期計画_計画素案の課題整理.xlsx
+++ b/output/第10期計画_計画素案の課題整理.xlsx
@@ -596,12 +596,12 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>282箇所</t>
+          <t>287箇所</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>要協議162・要確認118・要内訳2。本文129箇所・表33種153箇所（01シート）</t>
+          <t>要協議166・要確認119・要内訳2。本文134箇所・表33種153箇所（01シート）</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>192件</t>
+          <t>193件</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -636,12 +636,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>181件</t>
+          <t>182件</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>このうち計画素案を止めているものが111件（02シート）</t>
+          <t>このうち計画素案を止めているものが112件（02シート）</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>注1）未確定箇所は計画素案の実物（1074段落158表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
+          <t>注1）未確定箇所は計画素案の実物（1090段落161表36図）から数えています。確認事項は `build_process_control.py` のソースから読み取っています。いずれも固定値を書いていないため、素案又は確認事項を更新すれば本表も追随します。
 注2）本表は素案の本文には反映しません。計画素案の本文に確認事項の注記を書かないという指示によります。本文に残すのは図表を読むために必要な注記（出典・単位・欠測・数値の性質・記号の意味）に限っています。
 注3）［要協議］［要確認］［要内訳］は本文に残します。確定しない値を推測して埋めることはしません。</t>
         </is>
@@ -715,7 +715,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>282箇所のうち63箇所（22％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
+          <t>287箇所のうち63箇所（22％）が第6章第4節（施設の見込み）にあります。日常生活圏域ごとの必要利用定員総数（確認事項No.88）が決まらないためです</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -820,7 +820,7 @@
     <row r="2" ht="82" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>計画素案（1074段落158表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計282箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
+          <t>計画素案（1090段落161表36図）の［要協議］［要確認］［要内訳］を章節別・表別に数えたもの。合計287箇所。あわせて節ごとの記述量を測り、記述が薄い節を示す。</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       </c>
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="8" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1</v>
@@ -900,10 +900,10 @@
       </c>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F7" s="5" t="n">
         <v>14</v>
@@ -926,13 +926,13 @@
       </c>
       <c r="C8" s="6" t="inlineStr"/>
       <c r="D8" s="8" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" s="5" t="n">
         <v>0</v>
@@ -948,13 +948,13 @@
       </c>
       <c r="C9" s="6" t="inlineStr"/>
       <c r="D9" s="5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>7</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>0</v>
@@ -1048,13 +1048,13 @@
       </c>
       <c r="C13" s="9" t="inlineStr"/>
       <c r="D13" s="10" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G13" s="10" t="n">
         <v>2</v>
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="D19" s="5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>14</v>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="D21" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="E21" s="5" t="n">
         <v>12</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>11</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>1</v>
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="D23" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E23" s="5" t="n">
         <v>2</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>0</v>
@@ -1415,13 +1415,13 @@
         </is>
       </c>
       <c r="D27" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E27" s="5" t="n">
         <v>6</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>1</v>
@@ -1492,12 +1492,12 @@
       <c r="A30" s="6" t="inlineStr"/>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
+          <t>第2節　計画の位置付け</t>
         </is>
       </c>
       <c r="D30" s="5" t="n">
@@ -1512,37 +1512,37 @@
       <c r="G30" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
-        </is>
-      </c>
+      <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="6" t="inlineStr"/>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>第1章　計画策定の意義</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D31" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F31" s="5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>No.98（省令上の類型）・確認事項A No.15（24時間対応の確保方策）</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="6" t="inlineStr"/>
@@ -1583,17 +1583,17 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>第2節　計画の位置付け</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>0</v>
@@ -1609,17 +1609,17 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
         <v>4</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>0</v>
@@ -1767,7 +1767,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3　本文の未確定箇所（129件）</t>
+          <t>3　本文の未確定箇所（134件）</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、市町村老人福祉計画の記載事項として老人福祉事業その他の老人の生活に直接影響を及ぼす事業を営む者と支援関係機関との連携に関する事項を定めるよう努めるものとされ、市町村地域福祉計画の記載事項として保健医療、労働、教育、住まい、地域再生及び防災に関する施策その他の関連施策との連携に関する事項を定めるも</t>
+          <t>国の認知症施策推進基本計画は、市町村計画に定める内容が介護保険事業計画等の既存の行政計画に定める内容と重複する場合に、これらを一体のものとして策定することは差し支えないものとするなど、必要に応じて柔軟に運用できることとしています。また、市町村が市町村計画を介護保険事業計画等と一体のものとして策定する際に、複数の市町村による広域の計画が策定される可能性があるこ</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr"/>
@@ -1835,14 +1835,14 @@
           <t>第2節　計画の位置付け</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>注）各法律の条文の受領前であるため、条番号のみを記載し項番号は記載していません［要確認］。構成3町の高齢者福祉計画が老人福祉法第20条の8による市町村老人福祉計画に当たることの確認、成年後見制度の利用の促進に関する施策についての基本的な計画の構成3町における策定の状況、及び一体のものとして作成する方法は構成3町と協議して定めます［要協議］。</t>
+          <t>認知症基本法第13条第2項により、市町村認知症施策推進計画は、市町村地域福祉計画（社会福祉法第107条第1項）、市町村老人福祉計画（老人福祉法第20条の8第1項）、市町村介護保険事業計画（介護保険法第117条第1項）その他の法令の規定による計画であって認知症施策に関連する事項を定めるものと調和が保たれたものでなければならないこととされています。また、同条第3</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>注）各法律の条文の受領前であるため、条番号のみを記載し項番号は記載していません［要確認］。構成3町の高齢者福祉計画が老人福祉法第20条の8による市町村老人福祉計画に当たることの確認、成年後見制度の利用の促進に関する施策についての基本的な計画の構成3町における策定の状況、及び一体のものとして作成する方法は構成3町と協議して定めます［要協議］。</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、市町村老人福祉計画の記載事項として老人福祉事業その他の老人の生活に直接影響を及ぼす事業を営む者と支援関係機関との連携に関する事項を定めるよう努めるものとされ、市町村地域福祉計画の記載事項として保健医療、労働、教育、住まい、地域再生及び防災に関する施策その他の関連施策との連携に関する事項を定めるも</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr"/>
@@ -1887,14 +1887,14 @@
           <t>第2節　計画の位置付け</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
+          <t>注）認知症基本法、老人福祉法、成年後見制度の利用の促進に関する法律及び高齢者虐待の防止、高齢者の養護者に対する支援等に関する法律の各条項は、法令の本文により確認したものです。社会福祉法等の一部を改正する法律（令和8年法律第51号）による改正後の条項は、新旧対照条文により確認した範囲で項番号を記載し、確認できていないものは条番号のみを記載しています［要確認］。</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr"/>
@@ -1910,17 +1910,17 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>第5節　計画の策定体制</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
+          <t>注）認知症基本法、老人福祉法、成年後見制度の利用の促進に関する法律及び高齢者虐待の防止、高齢者の養護者に対する支援等に関する法律の各条項は、法令の本文により確認したものです。社会福祉法等の一部を改正する法律（令和8年法律第51号）による改正後の条項は、新旧対照条文により確認した範囲で項番号を記載し、確認できていないものは条番号のみを記載しています［要確認］。</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr"/>
@@ -1936,17 +1936,17 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>第6節　計画の進行管理・推進体制</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節　計画の位置付け</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>注）北海道の高齢者保健福祉計画が定める評価指標のうち「取り組んでいる市町村数」を単位とするものは、1保険者である当広域連合にそのまま適用することができません。読替えの方法は第8節に掲げます。北海道から広域連合に対する読替えの考え方は示されていないため、本計画は当広域連合の整理によっており、考え方が示された場合はこれに合わせて改めます［要確認］。</t>
+          <t>認知症の人及びその家族等からの意見の聴取は、計画の策定の過程において行います。聴取の主体、方法及び時期は構成3町と調整のうえ定めます［要協議］。</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr"/>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
+          <t>第5節　計画の策定体制</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
@@ -1972,8 +1972,7 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
-注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
+          <t>注）介護保険法の条文の受領前であるため、項番号は記載していません［要確認］。認知症の人及びその家族等からの意見の聴取は、認知症基本法第13条が市町村認知症施策推進計画について定めるものであり、同計画は構成3町が策定します（第1章第2節）。本計画の認知症施策に関する事項についても同様に意見を聴きます。</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr"/>
@@ -1989,7 +1988,7 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>第7節　日常生活圏域の設定</t>
+          <t>第6節　計画の進行管理・推進体制</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
@@ -1999,8 +1998,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
-注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
+          <t>注）北海道の高齢者保健福祉計画が定める評価指標のうち「取り組んでいる市町村数」を単位とするものは、1保険者である当広域連合にそのまま適用することができません。読替えの方法は第8節に掲げます。北海道から広域連合に対する読替えの考え方は示されていないため、本計画は当広域連合の整理によっており、考え方が示された場合はこれに合わせて改めます［要確認］。</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr"/>
@@ -2016,7 +2014,7 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
@@ -2026,7 +2024,8 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第10項は、市町村介護保険事業計画は、地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項に規定する市町村計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合性の確保は、同法第118条第10項により都道府県介護保険事業支援計画について定められているものです。本計画において</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
+注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
         </is>
       </c>
       <c r="F51" s="6" t="inlineStr"/>
@@ -2042,7 +2041,7 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>第8節　関係計画等との関係</t>
+          <t>第7節　日常生活圏域の設定</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
@@ -2052,7 +2051,8 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>介護保険法第117条第10項は、市町村介護保険事業計画は、地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項に規定する市町村計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合性の確保は、同法第118条第10項により都道府県介護保険事業支援計画について定められているものです。本計画において</t>
+          <t>3事業所は実施地域欄が空欄であるため、上表の事業所数には含めていません。訪問・通所困難地域の確定は、圏域（地区）単位の実施地域の記載と突き合わせて行います。地区単位の記載がない事業所については3町への照会を要します［要確認］。
+注）圏域別の面積、人口、高齢者人口、認定者数等は第9期計画による令和5年10月1日現在の値です。これより新しい時点の圏域別の値は提供</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr"/>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>市町村認知症施策推進計画は構成3町がそれぞれ策定します（第2節）。本計画との調和は資料2の役割分担及び共通KPIにより保ちます。都道府県認知症施策推進計画については、北海道の第10期高齢者保健福祉計画・介護保険事業支援計画の骨子（案）において、第5章第5節「認知症施策の推進」として北海道認知症施策推進計画を一体のものとして策定することとされています。認知症施</t>
+          <t>介護保険法第117条第10項は、市町村介護保険事業計画は、地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項に規定する市町村計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合性の確保は、同法第118条第10項により都道府県介護保険事業支援計画について定められているものです。本計画において</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr"/>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>資料：令和8年度第3回北海道高齢者保健福祉施策検討協議会（令和8年8月27日）資料5 第10期北海道高齢者保健福祉計画・介護保険事業支援計画骨子（案）。北海道の評価指標（第10期）は骨子（案）に示されておらず、各目標の達成目標は計画の第5章でまとめて整理することとされています。このため、評価指標による対応は次の第9期の表によります［要確認］。</t>
+          <t>介護保険法第117条第10項は、市町村介護保険事業計画は、地域における医療及び介護の総合的な確保の促進に関する法律第5条第1項に規定する市町村計画との整合性の確保が図られたものでなければならないことを定めています。医療計画及び地域医療構想との整合性の確保は、同法第118条第10項により都道府県介護保険事業支援計画について定められているものです。本計画において</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr"/>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>第9節　介護保険制度改正の主な内容</t>
+          <t>第8節　関係計画等との関係</t>
         </is>
       </c>
       <c r="D56" s="6" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
+          <t>資料：令和8年度第3回北海道高齢者保健福祉施策検討協議会（令和8年8月27日）資料5 第10期北海道高齢者保健福祉計画・介護保険事業支援計画骨子（案）。北海道の評価指標（第10期）は骨子（案）に示されておらず、各目標の達成目標は計画の第5章でまとめて整理することとされています。このため、評価指標による対応は次の第9期の表によります［要確認］。</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr"/>
@@ -2175,14 +2175,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>要件を満たす協力医療機関を定めることの義務化には令和9年3月31日までの経過措置が設けられており、本計画の初日である令和9年4月1日から義務となります。国は、全国における要件を満たす体制の整備割合を介護老人福祉施設67.9％、介護老人保健施設83.3％、介護医療院84.9％としたうえで、定めの状況について集計していないと回答した自治体が一定程度存在し、地域差</t>
+          <t>協力医療機関については、3要件（①入所者の病状が急変した場合等の相談体制、②診療の求めがあった場合の診療体制、③入院を要すると認められた入所者の入院受入体制）を満たす協力医療機関を定めていない高齢者施設等のリストと、協力医療機関として想定される医療機関のリストを早急に作成することが求められています。当広域連合において対象となるのは、認知症対応型共同生活介護7</t>
         </is>
       </c>
       <c r="F57" s="6" t="inlineStr"/>
@@ -2201,14 +2201,14 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
+          <t>要件を満たす協力医療機関を定めることの義務化には令和9年3月31日までの経過措置が設けられており、本計画の初日である令和9年4月1日から義務となります。国は、全国における要件を満たす体制の整備割合を介護老人福祉施設67.9％、介護老人保健施設83.3％、介護医療院84.9％としたうえで、定めの状況について集計していないと回答した自治体が一定程度存在し、地域差</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr"/>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。指定に係る構成</t>
+          <t>あわせて、生産性向上の取組に係る委員会の設置についても、経過措置の終了により令和9年4月1日から義務となります。当広域連合において対象となるのは、小規模多機能型居宅介護5事業所、認知症対応型共同生活介護7事業所、地域密着型介護老人福祉施設入所者生活介護3事業所の計15事業所です。いずれも指定地域密着型サービスであり、広域連合の条例において対応する規定を整えて</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr"/>
@@ -2253,9 +2253,9 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -2279,9 +2279,9 @@
           <t>第9節　介護保険制度改正の主な内容</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -2312,8 +2312,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>資料：社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）
-注）期限の目安は、公布の日（令和8年6月25日）から要綱が定める期間を加えたものです。実際の施行の日は政令により定まります［要確認］。</t>
+          <t>注）本表の75歳以上人口は按分による推計値であり、密度及び判定はいずれも試算です。また、基準は令和8年6月29日の社会保障審議会介護保険部会に素案として示されたものであり、省令等により確定したものではありません。最終的な対象地域は、確定した基準及び構成町の意向を踏まえて北海道が定めるものであり、本計画はその指定の結果により確認します［要確認］。指定に係る構成</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr"/>
@@ -2339,8 +2338,8 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>資料：社会福祉法等の一部を改正する法律案要綱（令和8年10月14日に確認）
-注）要綱は改正事項の要旨を示すものであり、改正後の条文及び附則の経過措置の内容を確認できていないため、項番号及び号番号は要綱の記載によっています［要確認］。</t>
+          <t>資料：社会福祉法等の一部を改正する法律案要綱 第10の1（附則第1条関係）
+注）期限の目安は、公布の日（令和8年6月25日）から要綱が定める期間を加えたものです。実際の施行の日は政令により定まります［要確認］。</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr"/>
@@ -2366,7 +2365,8 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
+          <t>資料：社会福祉法等の一部を改正する法律案要綱（令和8年10月14日に確認）
+注）要綱は改正事項の要旨を示すものであり、改正後の条文及び附則の経過措置の内容を確認できていないため、項番号及び号番号は要綱の記載によっています［要確認］。</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr"/>
@@ -2377,22 +2377,22 @@
       <c r="A65" s="6" t="inlineStr"/>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>第2章　高齢者及び介護保険の状況</t>
+          <t>第1章　計画策定の意義</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>第1節 高齢者の状況</t>
-        </is>
-      </c>
-      <c r="D65" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第9節　介護保険制度改正の主な内容</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
+          <t>注2）夜間対応型訪問介護の経過措置について、第269回介護給付費分科会 資料1は、現状と課題において「令和8年度末（現在の第9期計画期間）をもって廃止し、経過措置（令和11年度末まで（第10期計画期間中）は経過措置として、従前どおりの実施が可能）を設けることとされている」とする一方、論点において「令和11年3月までの猶予期間」としています。本計画の期間（令和</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr"/>
@@ -2411,14 +2411,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
+          <t>美瑛町の第3期総合戦略には人口の目標値が示されていません。また東神楽町は実績が目標を下回る見込みです。このため総人口の目標値を3町一律には用いられません。町別の総人口の置き方については、住民基本台帳の実績趨勢によることとする案を示しています［要協議］。</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr"/>
@@ -2437,14 +2437,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
+          <t>注）上記の町別・年齢4区分別の人口は、住民基本台帳の各年10月1日現在の値であり、令和5年までの提供を受けているものです。令和6年以降の同じ時点の町別の値は提供を受けていないため、年齢階級別の趨勢及び将来推計の基礎には、公表されている各年1月1日現在の値を用いています。両者は時点が9か月異なるため、同じ系列としてつなげていません［要確認］。</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr"/>
@@ -2463,14 +2463,14 @@
           <t>第1節 高齢者の状況</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
+          <t>一方、一般世帯そのものが減少しているのは美瑛町のみです（4,289世帯→4,205世帯）。このため、一般世帯に占める高齢者単身世帯の割合の上昇は美瑛町が最も速く、分母と分子の双方が影響しています。施策の対象を「独居の実数」で捉えるか「独居の割合」で捉えるかによって、重点を置く町が変わります［要協議］。</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr"/>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
+          <t>注）認定者数は各年10月末現在であり、第2号被保険者を含みます。年度末現在の第1号被保険者の認定者数（第1節2）とは時点及び対象が異なります。自立度Ⅱ以上はⅡa・Ⅱb・Ⅲa・Ⅲb・Ⅳ・Mの合計です。本表は要介護認定を受けた方の認定調査の結果によるものであり、認定を受けていない方を含みません。国は、認知症又は軽度認知障害の高齢者が65歳以上の高齢者の約3割を占</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr"/>
@@ -2512,17 +2512,17 @@
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
-        </is>
-      </c>
-      <c r="D70" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 高齢者の状況</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
+          <t>注）令和8年度分は令和8年4月1日から8月7日までの集計であり通年ではないため掲げていません。主治医意見書の入手日は3年度とも未入力であるため、申請から主治医意見書の入手までの日数は算定できません［要確認］。</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr"/>
@@ -2538,17 +2538,17 @@
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>第3節 サービス提供体制の状況</t>
-        </is>
-      </c>
-      <c r="D71" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第2節 保険給付や地域支援事業の実態把握と分析</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
+          <t>注）類似保険者との比較は、全国、北海道及び上川管内21保険者との比較によっています。地域包括ケア「見える化」システムの地域比較は当広域連合のデータの登録がないため出力できず、住民の心身の状態及び社会参加については健康とくらしの調査の同規模保険者40団体（人口5万人未満）との比較によります（第4節）。給付及び供給の面で比較する類似保険者の選定条件（人口規模、高</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr"/>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
+          <t>区域外の事業所が旭川市に所在するのか他の市町村なのかは、自給率からは分かりません。国民健康保険団体連合会の給付実績情報と指定事業所台帳の突合により確認します（第5章 基本目標3）。［要確認］</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr"/>
@@ -2600,7 +2600,7 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
+          <t>注1）令和2年度は「介護サービス施設・事業所調査」が実施されなかったため、全国・北海道を含め欠測です。注2）訪問介護（H29 59人）、通所介護（同13人）、居宅介護支援（同32人）は平成29年度のみの収録のため掲載していません。注3）介護老人福祉施設は平成29年度に認定者1万対616.37（全国520.67の1.18倍）でしたが、令和6年度は535.17（</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr"/>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>本広域連合の訪問介護の1人1月あたり利用回数は全国の1.87倍であり（第2節1）、区域内の訪問介護13事業所のうち8事業所が住まいに併設しています（第6節）。上記の全国の実態と同じ構造によるものと考えられますが、同一の建物に居住する方への提供の割合は把握していないため、本計画では要因を特定していません［要確認］。</t>
+          <t>注）上表は定員（戸数）によるものです。家賃、共益費、食費等の費用の水準は、北海道において情報の収集が行われていることを確認できていないため把握していません。このため、費用の面から住まいを選ぶことができるかどうかは本計画では扱っていません［要確認］。国の第10期基本指針（案）の別表が求める高齢者向け住まいの状況は、施設数・定員・入居者数の範囲で整理しています（</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr"/>
@@ -2645,14 +2645,14 @@
           <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
-      <c r="D75" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>北海道の第10期計画の策定に係る道作成指針（案）は、一部の住宅型有料老人ホームにおける入居者の保護やいわゆる「囲い込み」の問題等に対する実効性のある対応として、住宅担当部局との連携により入居実態等を把握するとともに、必要に応じて、指導監督を行う北海道に対し速やかに情報提供を行うこととし、また、入居定員総数、入居者のうち要介護者である者の割合、在宅サービスの利</t>
+          <t>本広域連合の訪問介護の1人1月あたり利用回数は全国の1.87倍であり（第2節1）、区域内の訪問介護13事業所のうち8事業所が住まいに併設しています（第6節）。上記の全国の実態と同じ構造によるものと考えられますが、同一の建物に居住する方への提供の割合は把握していないため、本計画では要因を特定していません［要確認］。</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr"/>
@@ -2678,8 +2678,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
-注2）登録有料老人ホームの入居定員総数が記載及び勘案の対象に加わるのは、登録制度の施行に合わせた改正によるものです。同制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施</t>
+          <t>北海道の第10期計画の策定に係る道作成指針（案）は、一部の住宅型有料老人ホームにおける入居者の保護やいわゆる「囲い込み」の問題等に対する実効性のある対応として、住宅担当部局との連携により入居実態等を把握するとともに、必要に応じて、指導監督を行う北海道に対し速やかに情報提供を行うこととし、また、入居定員総数、入居者のうち要介護者である者の割合、在宅サービスの利</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr"/>
@@ -2698,9 +2697,9 @@
           <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -2722,7 +2721,7 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr">
@@ -2732,7 +2731,8 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
+          <t>注1）本広域連合が定める区域（日常生活圏域）は3町（3圏域）とする案によっています（第6章第4節4）［要協議］。圏域が確定した時点で圏域ごとの入居定員総数を掲げます。
+注2）登録有料老人ホームの入居定員総数が記載及び勘案の対象に加わるのは、登録制度の施行に合わせた改正によるものです。同制度は公布の日から起算して2年を超えない範囲内において政令で定める日から施</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr"/>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>第4節 高齢者の生活実態</t>
+          <t>第3節 サービス提供体制の状況</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -2758,8 +2758,7 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
-注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
+          <t>定員及び従事者数は介護サービス情報公表システム（各年9月時点）、利用者数は介護保険総合データベース（各年9月サービス分）によります。対象は最新年度の9月サービス分の算定実績のある事業所に限られ、介護予防給付のみの事業所は対象外であるため、区域内のすべての事業所を覆うものではありません。認知症対応型共同生活介護は5事業所・定員81人が掲げられており、第3節6に</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr"/>
@@ -2775,7 +2774,7 @@
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
+          <t>第4節 高齢者の生活実態</t>
         </is>
       </c>
       <c r="D80" s="6" t="inlineStr">
@@ -2785,8 +2784,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
-注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
+          <t>本調査は小学校区別の集計ができます。東神楽町3・東川町4・美瑛町5の計12小学校区のうち、回答者数が100票に満たない地区が4地区あり、値の変動が大きくなります。日常生活圏域（第1章第7節）の設定において、統計の単位として小学校区を用いるかは［要確認］とします。</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr"/>
@@ -2802,17 +2800,18 @@
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>第5節 在宅介護の実態</t>
-        </is>
-      </c>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 高齢者の生活実態</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
+          <t>前回と今回で回収票数・回収率が異なるため、割合で比較し、実数では比較していません。また各指標の分母は設問により異なり（今回は4,128票から4,729票）、前回の指標別の分母は第9期計画の本文からは確認できません。設問文と判定の方法が前回と同一であることを確かめた指標のみ掲げています。
+注）令和4年度調査の指標別の有効回答数を確認できないため、統計的な差の検</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr"/>
@@ -2828,7 +2827,7 @@
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
+          <t>第5節 在宅介護の実態</t>
         </is>
       </c>
       <c r="D82" s="6" t="inlineStr">
@@ -2838,7 +2837,8 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
+          <t>複数回答。出典：在宅生活改善調査（第10期分・利用者票99票）。本調査は事業所が課題があると判断した利用者を抽出して回答する設計であり、区域内の在宅利用者全体の割合ではありません。
+注）回答者の要介護度の分布は、年報による在宅の認定者の分布と比べて要介護3以上が多く要支援1が少ない側に偏っており、この偏りは回答者が98人であることによる偶然だけでは説明しにく</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr"/>
@@ -2854,17 +2854,17 @@
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>第6節 介護事業所の現状</t>
-        </is>
-      </c>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 在宅介護の実態</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
+          <t>［要協議］「より適切と思われるサービス」の集計値の掲載方法は、回答した事業所が自らの提供するサービスを挙げる構造があるため、件数の掲載の可否を含めて協議します。</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr"/>
@@ -2880,17 +2880,17 @@
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>第8節 中長期推計からみた需要と財政</t>
-        </is>
-      </c>
-      <c r="D84" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第6節 介護事業所の現状</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業の量の中長期的な推計は、令和6年度の実績を据え置き、サービス事業は認定者数、一般介護予防事業は第1号被保険者数の伸びにより延ばしています（第6章第3節2）。認定者数が令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。事業費の中長期的な推計は、令和7年度の事業ごと</t>
+          <t>［要確認］同一法人が施設・通所系と訪問系の両方に同一の職員13人を記入しているため、単純合計では二重に計上されます。総数の取扱いを協議のうえ確定します。重複の判別は、職員個票（氏名等を含むもの）の突合によらず、当該事業所への照会により行います。個人情報は保管しない方針によるものです。</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr"/>
@@ -2901,12 +2901,12 @@
       <c r="A85" s="6" t="inlineStr"/>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
+          <t>第6節 介護事業所の現状</t>
         </is>
       </c>
       <c r="D85" s="6" t="inlineStr">
@@ -2916,7 +2916,7 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
+          <t>［要確認］介護老人保健施設3施設の介護職員77人は、見える化システムの従事者数（令和6年度59人）と一致しません。通所リハビリテーションも同様です。「介護職員」の範囲の解釈を確認したうえで数値を確定します。</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr"/>
@@ -2927,23 +2927,22 @@
       <c r="A86" s="6" t="inlineStr"/>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>第3章　第9期計画の実施状況と評価</t>
+          <t>第2章　高齢者及び介護保険の状況</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>第1節 第9期計画の基本目標</t>
-        </is>
-      </c>
-      <c r="D86" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第8節 中長期推計からみた需要と財政</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
-注）分母は地域包括ケア「見え</t>
+          <t>地域支援事業の量の中長期的な推計は、令和6年度の実績を据え置き、サービス事業は認定者数、一般介護予防事業は第1号被保険者数の伸びにより延ばしています（第6章第3節2）。認定者数が令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。事業費の中長期的な推計は、量の見込みと同じ伸び</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr"/>
@@ -2959,7 +2958,7 @@
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D87" s="6" t="inlineStr">
@@ -2969,7 +2968,7 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
+          <t>注）②重度要介護認定率の実績6.3％は、地域包括ケア「見える化」システムの系列（B4-a）による値です。年報（令和7年度）から算定すると6.38％となり、0.08ポイントの差があります。本計画は全国・北海道との比較に用いる系列とそろえるため見える化システムの値を用いています。いずれによっても第9期目標6.4％を下回り、判定は変わりません［要確認］。</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr"/>
@@ -2985,7 +2984,7 @@
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>第2節 地域支援事業の実績</t>
+          <t>第1節 第9期計画の基本目標</t>
         </is>
       </c>
       <c r="D88" s="6" t="inlineStr">
@@ -2995,7 +2994,8 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
+          <t>令和6年度は「介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査」の令和6年度実績によります（令和8年8月受領）。参加率の分母は令和6年（2024年）の65歳以上人口9,346人です。見える化システムのF系列の収録は令和2年度までであり、令和3年度から令和5年度は本調査の当該年度分を受領していないため空白です。
+注）分母は地域包括ケア「見え</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr"/>
@@ -3011,17 +3011,17 @@
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
-        </is>
-      </c>
-      <c r="D89" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 地域支援事業の実績</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
+          <t>注）区分の名称及び科目は、令和6年度大雪地区広域連合介護保険特別会計歳入歳出決算書の表記によっています。決算書及び年報の様式4には「一般介護予防事業費」の項がなく、介護予防把握事業、介護予防普及啓発事業等の経費がいずれの科目で執行されているかは確認できていません［要確認］。いずれの場合も地域支援事業費の総額は変わりません。</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr"/>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>第4節 第9期計画の評価と第10期への課題</t>
+          <t>第2節 地域支援事業の実績</t>
         </is>
       </c>
       <c r="D90" s="6" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>注）第9期の施策及び事業の実績（事業量、対象実人数、予算及び決算）の提供を受けられない間は、本章の評価は公表されている資料（保険者機能強化推進交付金等の評価結果、介護予防・日常生活支援総合事業（地域支援事業）の実施状況に関する調査及び介護保険事業状況報告年報）によっています。事業量及び対象実人数による評価は行っていません［要確認］。</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr"/>
@@ -3066,14 +3066,14 @@
           <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
-      <c r="D91" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
+          <t>3町の高齢者保健福祉計画、地方創生総合戦略、地域福祉計画等で対応している可能性があります。広域連合の計画で扱うか3町の計画で扱うかは、役割分担の確認を経て決定します［要協議］。</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr"/>
@@ -3084,12 +3084,12 @@
       <c r="A92" s="6" t="inlineStr"/>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
         </is>
       </c>
       <c r="D92" s="6" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr"/>
@@ -3110,22 +3110,22 @@
       <c r="A93" s="6" t="inlineStr"/>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>第4章　計画の基本理念及び基本目標</t>
+          <t>第3章　第9期計画の実施状況と評価</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>第3節 施策の体系と成果指標</t>
-        </is>
-      </c>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第4節 第9期計画の評価と第10期への課題</t>
+        </is>
+      </c>
+      <c r="D93" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
+          <t>注）保険者機能強化推進交付金等の評価について、本章では公表されている評価指標及び全国集計の値によっています。得点が0である項目について、取組がないのか、取組はあるが要件を満たさないのか、又は該当状況調査において報告していないのかは、公表されている資料からは判別できません。第10期の施策に位置づけるかどうかは取組の必要性から判断するものであり、得点のみを理由と</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr"/>
@@ -3151,7 +3151,7 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
+          <t>H03（75歳以上新規認定率）は、認定台帳を管理する情報システムから新規認定者数を抽出して算定するものです。年齢階級別の抽出及び過年度（令和4年度まで）に遡る抽出が可能であることを確認できていないため、基準値及び第9期中の推移を算定していません［要確認］。抽出が可能となった時点で算定し、要因分析に用います。</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr"/>
@@ -3162,12 +3162,12 @@
       <c r="A95" s="6" t="inlineStr"/>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
+          <t>第3節 施策の体系と成果指標</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>地域ケア会議の個別事例の検討から地域課題の抽出、資源開発、施策化への接続を制度化します。社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護保険法第115条の48の会議は改正後「支援会議」と称し、構成員として地域包括支援センターが明示されます。地域ケア会議は、社会福祉法の支援会議、障害者総合支援法の支援協議会、住宅確保要配慮者に対する賃貸住宅</t>
+          <t>［要協議］4項目とも指標名の改称を伴います。改称により、第9期の定義による系列とは接続しません。また目標値は、H07を「水準の維持」、H16を「100％」とする案ですが、H08・H12は目標の方向（低下を目指すか、水準の維持か）の決定を要します。H12の町別の値は、利用者の居住地ではなく調査票を提出した事業所の所在地による区分となるため掲げていません。</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr"/>
@@ -3188,22 +3188,22 @@
       <c r="A96" s="6" t="inlineStr"/>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>第5章　施策の展開</t>
+          <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
-        </is>
-      </c>
-      <c r="D96" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第3節 施策の体系と成果指標</t>
+        </is>
+      </c>
+      <c r="D96" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>虐待の初動、成年後見制度の利用、意思決定支援、消費者被害防止を一体で管理します。同法により、市町村は、高齢者及び障害者による成年後見制度又は権利擁護事業（包括的支援事業）等の適切な利用の支援のため、権利利益の擁護に係る支援に従事する者に対する相談・助言及び関係機関等との連絡調整等の事務の実施に努めるものとされ、中核的な役割を担う機関として地域権利擁護相談支援</t>
+          <t>一方、サービス別・職種別の従事者数（認定者1万対）は平成29年度から令和6年度まで得られます。このため、H13を「職種別従事者数（認定者1万対）の推移」に改めます。またH14は、北海道の第9期評価指標⑥と同じ「採用率と離職率の差」（採用（離職）者数÷各年9月30日の在籍者数×100）に改めます。算定には採用者数、離職者数及び各年9月30日現在の在籍者数が必要</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr"/>
@@ -3229,7 +3229,7 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>地域ケア会議の個別事例の検討から地域課題の抽出、資源開発、施策化への接続を制度化します。社会福祉法等の一部を改正する法律（令和8年法律第51号）により、介護保険法第115条の48の会議は改正後「支援会議」と称し、構成員として地域包括支援センターが明示されます。地域ケア会議は、社会福祉法の支援会議、障害者総合支援法の支援協議会、住宅確保要配慮者に対する賃貸住宅</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr"/>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
+          <t>虐待の初動、成年後見制度の利用、意思決定支援、消費者被害防止を一体で管理します。同法により、市町村は、高齢者及び障害者による成年後見制度又は権利擁護事業（包括的支援事業）等の適切な利用の支援のため、権利利益の擁護に係る支援に従事する者に対する相談・助言及び関係機関等との連絡調整等の事務の実施に努めるものとされ、中核的な役割を担う機関として地域権利擁護相談支援</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr"/>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr"/>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+          <t>基本目標1　地域包括ケア・相談・医療介護連携</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>注）第9期の施策2-5「地域ケア会議の推進」は、指標が会議の開催回数のみであり、成果を測る指標がありませんでした（第3章第4節）。第10期は、提起された地域課題のうち翌年度の事業又は予算に反映されたものの割合（施策化への転換率）を施策の指標とします。基準値がないため、令和9年度は記録様式を整えて基準値を把握する年度とし、令和10年度及び令和11年度に目標値を</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr"/>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
+          <t>国の認知症施策推進基本計画（令和6年12月3日 閣議決定）が掲げる重点目標4件との対応を確かめ、同計画が示す指標の3つの観点（プロセス指標・アウトプット指標・アウトカム指標）に沿って本計画の指標を整理します。同計画は、認知症施策推進計画には介護保険の給付及び地域支援事業に位置づけられた事業以外にも広範な施策が位置づけられる必要があるとしており、本計画が扱う範</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr"/>
@@ -3378,9 +3378,9 @@
           <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
-      <c r="D103" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E103" s="6" t="inlineStr">
@@ -3401,17 +3401,17 @@
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>基本目標3　持続可能なサービス提供・住まい</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr"/>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>同法により、都道府県は、質の高い介護サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組を促進するための協議会を置くものとされ、市町村は構成員として参画するものとされました（第1章第9節2）。北海道における協議会の設置の状況を確認し、本広域連合と構成3町のいずれが参画するかを含めて協議します［要協議］。</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr"/>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標2　介護予防・生活支援・認知症・家族支援</t>
         </is>
       </c>
       <c r="D106" s="6" t="inlineStr">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
+          <t>注）上表の事業のうち、現に実施されているのが1町のみであるものがあります。チームオレンジは東川町が令和7年3月に結成会を開催し令和8年度の事業として立てているもの、地域リハビリテーション活動支援事業及び介護予防のポイント事業は美瑛町が実施しているものです。本計画はこれらを当該の町の取組として掲げるものであり、他の町への展開は、担い手及び派遣元の確保の見通しを</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+          <t>基本目標3　持続可能なサービス提供・住まい</t>
         </is>
       </c>
       <c r="D107" s="6" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
+          <t>サービスの提供体制の維持について、国は、一定期間の事業継続や事業者間の連携・協働を推進する法人・事業所が都道府県と協定を締結する仕組みを示しています（第1章第9節5）。区域内に事業所がないサービス種別が11あり、既存の事業所も小規模なものが多いことから、北海道及び事業者とともにこの仕組みの活用を検討します。検討の対象とするのは、一定期間の事業継続、人材の相互</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr"/>
@@ -3505,17 +3505,17 @@
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D108" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
+          <t>同法により、都道府県は、質の高い介護サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組を促進するための協議会を置くものとされ、市町村は構成員として参画するものとされました（第1章第9節2）。北海道における協議会の設置の状況を確認し、本広域連合と構成3町のいずれが参画するかを含めて協議します［要協議］。</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr"/>
@@ -3531,7 +3531,7 @@
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
         </is>
       </c>
       <c r="D109" s="6" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
+          <t>サービスの供給の継続に関する状況の把握に、介護サービス事業者経営情報データベースの公表結果を用います（第1章第9節5）。事業者の経営情報の報告が義務づけられ、国において属性等に応じて区分した分析結果が公表されます。小規模な事業所が多い当区域の状況に照らして用いられる区分を確かめ、事業の継続が難しくなる兆しを早期に把握する材料とします。市町村の区域を単位とする</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr"/>
@@ -3557,17 +3557,17 @@
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
-        </is>
-      </c>
-      <c r="D110" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標4　介護人材・生産性・質・経営支援</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>BCPについて、策定率、訓練の実施状況、相互応援協定の締結状況を把握します。策定は令和6年度から義務化されており、指定・指導の際に確認できます。国は、BCPの実効性を高めるには行政や他の介護施設等との平時からの連携が重要であるとしたうえで、市区町村の約6割が介護事業所等に対して業務継続を可能とする備えに関する助言等を行っていない状況にあることを示しています。</t>
+          <t>事業者間の連携・協働化について、北海道と協定を締結した法人・事業所への支援の仕組みの活用を検討します（第1章第9節5）。令和9年度概算要求において、協定に基づく連携の取組に要する経費への支援及び連携に参画する事業所に対する介護テクノロジー導入支援の補助率の上乗せが盛り込まれています。区域内の事業所は小規模なものが多く、人材の相互応援、共同採用・共同研修、事務</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr"/>
@@ -3586,14 +3586,14 @@
           <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
-      <c r="D111" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D111" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>介護事故の防止について、事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行います。国は、事故防止を推進するための国・都道府県・市町村の役割として、市町村が事故が発生した事業所からの報告の受付並びに報告内容の集計及び傾向の把握を担うことを示し、介護サービス情報公表システムを活用した報告のための仕組みの構築と報告様式の見直しを検討しています（第1章第9</t>
+          <t>当広域連合はケアプラン等の点検を実施していないため、この減額の対象となります。減額は年齢区分の精緻化により交付額が増加する場合の増加額を限度とするものであり、減額の額は当広域連合に係る交付割合が示された時点で確認します。本計画の保険料の算定（第6章第6節）は、調整交付金の見込交付割合を第9期計画と同水準として置いており、この減額を織り込んでいません［要確認］</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr"/>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
+          <t>指針が「積極的な実施が望まれる取組」とする給付実績の活用による確認等及び介護給付費通知について、実施の状況を確認し、第10期における実施の方針を定めます［要確認］。給付実績の活用は、国保連の介護給付適正化システムに強調表示等の工夫が取り入れられており、小規模保険者でも実施しやすいとされています。</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr"/>
@@ -3638,14 +3638,14 @@
           <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
-      <c r="D113" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>同法により、災害が発生した区域に派遣されて災害時における福祉サービスの提供を行う災害時福祉業務従事者の登録の制度が設けられました（第1章第9節2）。介護福祉士、介護支援専門員、社会福祉士等であって厚生労働大臣が実施する研修の課程を修了した者等が対象となり、都道府県知事は、災害が発生した場合に従事することを要請することができるものとされています。区域内の事業所</t>
+          <t>BCPについて、策定率、訓練の実施状況、相互応援協定の締結状況を把握します。策定は令和6年度から義務化されており、指定・指導の際に確認できます。国は、BCPの実効性を高めるには行政や他の介護施設等との平時からの連携が重要であるとしたうえで、市区町村の約6割が介護事業所等に対して業務継続を可能とする備えに関する助言等を行っていない状況にあることを示しています。</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr"/>
@@ -3656,22 +3656,22 @@
       <c r="A114" s="6" t="inlineStr"/>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D114" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
+          <t>介護事故の防止について、事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行います。国は、事故防止を推進するための国・都道府県・市町村の役割として、市町村が事故が発生した事業所からの報告の受付並びに報告内容の集計及び傾向の把握を担うことを示し、介護サービス情報公表システムを活用した報告のための仕組みの構築と報告様式の見直しを検討しています（第1章第9</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr"/>
@@ -3682,12 +3682,12 @@
       <c r="A115" s="6" t="inlineStr"/>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
         </is>
       </c>
       <c r="D115" s="6" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
+          <t>要配慮者利用施設の避難確保計画について、作成及び避難訓練の実施の状況を把握します。水防法及び土砂災害警戒区域等における土砂災害防止対策の推進に関する法律は、市町村地域防災計画に定められた要配慮者利用施設の所有者又は管理者に対し、避難確保計画の作成及び避難訓練の実施を求めています。北海道の評価指標⑦は避難確保計画を作成した施設数を指標としており、本計画はこれを</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr"/>
@@ -3708,22 +3708,22 @@
       <c r="A116" s="6" t="inlineStr"/>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>第6章　介護保険事業等の見込み</t>
+          <t>第5章　施策の展開</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>第1節 要介護認定者数の見込み</t>
-        </is>
-      </c>
-      <c r="D116" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>基本目標5　保険運営・レジリエンス・PDCA</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。［要協議］</t>
+          <t>同法により、災害が発生した区域に派遣されて災害時における福祉サービスの提供を行う災害時福祉業務従事者の登録の制度が設けられました（第1章第9節2）。介護福祉士、介護支援専門員、社会福祉士等であって厚生労働大臣が実施する研修の課程を修了した者等が対象となり、都道府県知事は、災害が発生した場合に従事することを要請することができるものとされています。区域内の事業所</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr"/>
@@ -3742,14 +3742,14 @@
           <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
-      <c r="D117" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D117" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
+          <t>注）認定率は、年報（各年度末現在）の第1号被保険者の認定者数を第1号被保険者数で除したものです。地域包括ケア「見える化」システムの総括表の要介護認定率は各年9月末現在の値であり、将来推計の参考シートが表示する認定率はさらにこれと異なります。いずれも分母・分子の定義によるものではなく時点等の違いによるものであり、本計画は年度末現在の値で統一しています［要確認］</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr"/>
@@ -3765,17 +3765,17 @@
       </c>
       <c r="C118" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D118" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>注）要介護度の構成は、施設に入所している方と在宅の方を分けずに置いています。施設入所者と在宅者を分けた要介護度の変化を把握できないためです。施設及び居住系サービスの定員が縮小する一方で重度者の在宅・居住系割合が上昇しており（第2章第5節）、入所の状況によって重度化の見え方は変わりますが、本計画はその経路を分けて算定していません［要確認］。</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr"/>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="C119" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
+          <t>第1節 要介護認定者数の見込み</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>階級別認定率の置き方について、次の3つを算定しました。上表は②によっています。置き方により保険料基準額が分かれるため、ご協議をお願いします。［要協議］</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr"/>
@@ -3817,17 +3817,17 @@
       </c>
       <c r="C120" s="6" t="inlineStr">
         <is>
-          <t>第2節 介護給付等サービスの見込量</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第1節 要介護認定者数の見込み</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
+          <t>総人口の目標値は3町一律には用いられません。美瑛町の第3期総合戦略に人口の目標値がないこと、東神楽町の実績が目標（9,500人の維持）を下回る見込みであること、東川町の実績が目標（8,635人）を既に上回っていることによります。このため、総人口は3町計を総合戦略の目標の水準により置き、年齢階級別の内訳及び町別の総人口は住民基本台帳の実績趨勢によることとしてい</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr"/>
@@ -3846,15 +3846,14 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D121" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr"/>
@@ -3873,15 +3872,14 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D122" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr"/>
@@ -3907,8 +3905,7 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
-注1-1）基準年度は令和7年度（12か月）で</t>
+          <t>注1）定期巡回・随時対応型訪問介護看護は、区域内に事業所が存在しませんが区域外の事業所により給付が行われています。上表は現在の利用の水準を延ばしたものであり、整備による上乗せは含んでいません［要協議］（第4節1）。看護小規模多機能型居宅介護も同様です［要協議］。第4節1の確保方策により整備又は事業の実施を行う場合は、開始する年度から利用者数及び給付費を加えま</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr"/>
@@ -3981,9 +3978,9 @@
           <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
-      <c r="D126" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D126" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -4086,18 +4083,18 @@
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D130" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D130" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
-注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr"/>
@@ -4113,19 +4110,18 @@
       </c>
       <c r="C131" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D131" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第2節 介護給付等サービスの見込量</t>
+        </is>
+      </c>
+      <c r="D131" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
-注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
-注3）通いの場の箇所数は3町の事業</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr"/>
@@ -4141,7 +4137,7 @@
       </c>
       <c r="C132" s="6" t="inlineStr">
         <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
+          <t>第2節 介護給付等サービスの見込量</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
@@ -4151,9 +4147,8 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
-注2）事業費の中長期的な推計は、令和7年度の事業ごとの実績及び特定地域居宅サービス等事業その他の令和9年度に創設される事業の費用の額が定まった時点で算定します［要協議］。
-注3）通いの場の箇所数は3町の事業</t>
+          <t>注1）R7実績は、厚生労働省「介護保険事業状況報告」年報（令和7年度）の要介護度別の利用者数を12で除した1月当たりの値です。R9以降は、要介護度別の認定者数の伸びを乗じた見込量です。利用率、1人1月当たりの利用回（日）数及び単価は令和7年度で固定しています。報酬改定、供給の制約及び施策の効果は反映していません。
+注1-1）基準年度は令和7年度（12か月）で</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr"/>
@@ -4172,14 +4167,15 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D133" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）通いの場の箇所数は3町の事業計画により定まるものであり、人口や認定者数により延ばすものではありません。令和6年度の実績を据え置いています。目標値は3町と協議のうえ定めます［要協議］。
+注2）令和7年度の事業ごとの実施状況は、構成3町の地域包括支援センター事業実施報告書により確認しています。同報告書の量は延べ人数によるものであり、本表の利用者実人数とは数</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr"/>
@@ -4205,7 +4201,8 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
+注2）事業費の中長期的な推計は、量の見込みと同じ伸び（介護予防・日常生活支援総合事業費は認定者数、そのほかは第1号被保険者数）により算定しています。第10期（令和9年度から令和11年度まで）は令和6年度決算</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr"/>
@@ -4224,14 +4221,15 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+          <t>注1）認定者数は令和22年度にかけて増えるためサービス事業の量も増え、第1号被保険者数はおおむね横ばいであるため一般介護予防事業の量は横ばいとなります。
+注2）事業費の中長期的な推計は、量の見込みと同じ伸び（介護予防・日常生活支援総合事業費は認定者数、そのほかは第1号被保険者数）により算定しています。第10期（令和9年度から令和11年度まで）は令和6年度決算</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr"/>
@@ -4250,122 +4248,122 @@
           <t>第3節 介護保険サービス事業費の見込み</t>
         </is>
       </c>
-      <c r="D136" s="11" t="inlineStr">
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F136" s="6" t="inlineStr"/>
+      <c r="G136" s="6" t="inlineStr"/>
+      <c r="H136" s="6" t="inlineStr"/>
+    </row>
+    <row r="137" ht="44" customHeight="1">
+      <c r="A137" s="6" t="inlineStr"/>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
         <is>
           <t>要協議</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F137" s="6" t="inlineStr"/>
+      <c r="G137" s="6" t="inlineStr"/>
+      <c r="H137" s="6" t="inlineStr"/>
+    </row>
+    <row r="138" ht="44" customHeight="1">
+      <c r="A138" s="6" t="inlineStr"/>
+      <c r="B138" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C138" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D138" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F138" s="6" t="inlineStr"/>
+      <c r="G138" s="6" t="inlineStr"/>
+      <c r="H138" s="6" t="inlineStr"/>
+    </row>
+    <row r="139" ht="44" customHeight="1">
+      <c r="A139" s="6" t="inlineStr"/>
+      <c r="B139" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C139" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D139" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>注）令和6年度は決算額です。決算の科目は上記の4区分であり、包括的支援事業の6事業別及び任意事業別の内訳、並びに社会保障充実分の別は決算書からは分かりません。事業別の実績の受領後に内訳を加えます。総合事業費は、決算科目の「介護予防・生活支援サービス事業費」101,274,621円とは基礎が異なり、5,854,697円の差があります［要確認］（第6節）。第10</t>
+        </is>
+      </c>
+      <c r="F139" s="6" t="inlineStr"/>
+      <c r="G139" s="6" t="inlineStr"/>
+      <c r="H139" s="6" t="inlineStr"/>
+    </row>
+    <row r="140" ht="44" customHeight="1">
+      <c r="A140" s="6" t="inlineStr"/>
+      <c r="B140" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C140" s="6" t="inlineStr">
+        <is>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D140" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
         <is>
           <t>注1）量の欄は報告書の記載のとおりです。回数・件数・人数・対象者数が混在しており、町の間で単位がそろわないため合計できません。東神楽町の「対象2,910人」は第1号被保険者数であり、取組の回数ではありません。
 注2）美瑛町の認知症初期集中支援推進事業は、医師を確保できないため令和7年度の対応件数が0件で休止しています（第5章 基本目標2）。
 注3）事業ごとの</t>
         </is>
       </c>
-      <c r="F136" s="6" t="inlineStr"/>
-      <c r="G136" s="6" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr"/>
-    </row>
-    <row r="137" ht="44" customHeight="1">
-      <c r="A137" s="6" t="inlineStr"/>
-      <c r="B137" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C137" s="6" t="inlineStr">
-        <is>
-          <t>第3節 介護保険サービス事業費の見込み</t>
-        </is>
-      </c>
-      <c r="D137" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E137" s="6" t="inlineStr">
-        <is>
-          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
-        </is>
-      </c>
-      <c r="F137" s="6" t="inlineStr"/>
-      <c r="G137" s="6" t="inlineStr"/>
-      <c r="H137" s="6" t="inlineStr"/>
-    </row>
-    <row r="138" ht="44" customHeight="1">
-      <c r="A138" s="6" t="inlineStr"/>
-      <c r="B138" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C138" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D138" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E138" s="6" t="inlineStr">
-        <is>
-          <t>北海道の第10期計画の策定に係る道作成指針（案）は、中山間・人口減少地域において利用者への介護サービスが適切に提供されるよう、次の順序により議論することとしています。ア　指定サービスの実施を基本とし、人材確保や生産性向上に係る支援を行う。イ　指定サービスの確保に係る施策を行っても、指定サービスのみによるサービス提供体制の維持・確保になお課題を抱える場合は、特</t>
-        </is>
-      </c>
-      <c r="F138" s="6" t="inlineStr"/>
-      <c r="G138" s="6" t="inlineStr"/>
-      <c r="H138" s="6" t="inlineStr"/>
-    </row>
-    <row r="139" ht="44" customHeight="1">
-      <c r="A139" s="6" t="inlineStr"/>
-      <c r="B139" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C139" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D139" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
-        <is>
-          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
-        </is>
-      </c>
-      <c r="F139" s="6" t="inlineStr"/>
-      <c r="G139" s="6" t="inlineStr"/>
-      <c r="H139" s="6" t="inlineStr"/>
-    </row>
-    <row r="140" ht="44" customHeight="1">
-      <c r="A140" s="6" t="inlineStr"/>
-      <c r="B140" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C140" s="6" t="inlineStr">
-        <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D140" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E140" s="6" t="inlineStr">
-        <is>
-          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
-        </is>
-      </c>
       <c r="F140" s="6" t="inlineStr"/>
       <c r="G140" s="6" t="inlineStr"/>
       <c r="H140" s="6" t="inlineStr"/>
@@ -4379,17 +4377,17 @@
       </c>
       <c r="C141" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み</t>
-        </is>
-      </c>
-      <c r="D141" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第3節 介護保険サービス事業費の見込み</t>
+        </is>
+      </c>
+      <c r="D141" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
         <is>
-          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
+          <t>注）標準給付費見込額（A）は、総給付費に高額介護サービス費・高額医療合算介護サービス費・特定入所者介護サービス費・審査支払手数料を加えるための割増率1.0591を乗じたものです。割増率は令和6年度の決算（給付費2,817,194,455円に対し保険給付費2,983,668,988円）により算定しました。サービス種別ごとに積み上げる方法に置き直すことを予定して</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr"/>
@@ -4415,8 +4413,7 @@
       </c>
       <c r="E142" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>北海道の第10期計画の策定に係る道作成指針（案）は、中山間・人口減少地域において利用者への介護サービスが適切に提供されるよう、次の順序により議論することとしています。ア　指定サービスの実施を基本とし、人材確保や生産性向上に係る支援を行う。イ　指定サービスの確保に係る施策を行っても、指定サービスのみによるサービス提供体制の維持・確保になお課題を抱える場合は、特</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr"/>
@@ -4442,8 +4439,7 @@
       </c>
       <c r="E143" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>いずれの案によるかが定まるまでの間、第2節の見込量は現在の利用の水準を延ばした自然体の値としており、整備又は事業の実施による上乗せは含んでいません［要協議］。案A、案B又は案Dによる場合は、開始する年度から利用者数及び給付費を加えて見込量を置き直します。本計画の保険料の算定（第6節）は、整備による上乗せを含まない見込量によっています。</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr"/>
@@ -4462,15 +4458,14 @@
           <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
-      <c r="D144" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D144" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E144" s="6" t="inlineStr">
         <is>
-          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
-注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
+          <t>なお、定期巡回・随時対応型訪問介護看護については、新規に開設する際に利用者の確保が困難である場合の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがってサービスを提供する事業所の評価の在り方が検討されています（第1章第9節6）。いずれも整備を検討する際の条件に関わるものであるため、案を定めるに当たり、確定した内容により確かめます［要協</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr"/>
@@ -4496,8 +4491,7 @@
       </c>
       <c r="E145" s="6" t="inlineStr">
         <is>
-          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。同法第8条第21項により、介護専用型特定施設はその入居者が要介護者、その配偶者その他厚生労働省令で定める者に限られるものであり、類型は入居の要件により定まります。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
-注2）受給者数には要支援1・要支</t>
+          <t>したがって、定員に対する当広域連合の被保険者の受給者数の割合が低いことは、区域内に空きがあることを意味しません。整備の判断は、当広域連合の被保険者の受給者数と、区域内の施設の入居状況の両方を見て行います。認知症対応型共同生活介護についても、区域内の入居状況を3町に照会したうえで判断します［要確認］。</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr"/>
@@ -4513,7 +4507,7 @@
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D146" s="11" t="inlineStr">
@@ -4523,7 +4517,8 @@
       </c>
       <c r="E146" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr"/>
@@ -4539,17 +4534,18 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
-        </is>
-      </c>
-      <c r="D147" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
+        </is>
+      </c>
+      <c r="D147" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E147" s="6" t="inlineStr">
         <is>
-          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr"/>
@@ -4565,7 +4561,7 @@
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D148" s="6" t="inlineStr">
@@ -4575,7 +4571,8 @@
       </c>
       <c r="E148" s="6" t="inlineStr">
         <is>
-          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
+          <t>注1）東神楽町は令和8年10月に慈光園の視察、令和8年11月に指定管理に係る市場調査を予定しており、特別養護老人ホーム及び通所介護の整備方針を検討中です。地域密着型特定施設入居者生活介護についても同町の検討の対象となり得るため［要協議］としています。
+注2）認知症対応型共同生活介護の区域全体の定員は、平成28年から令和2年の115人が令和4年以降99人に減少</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr"/>
@@ -4591,7 +4588,7 @@
       </c>
       <c r="C149" s="6" t="inlineStr">
         <is>
-          <t>第5節 介護施設整備に係る基本方針</t>
+          <t>第4節 介護保険サービス等における施設の見込み</t>
         </is>
       </c>
       <c r="D149" s="6" t="inlineStr">
@@ -4601,7 +4598,8 @@
       </c>
       <c r="E149" s="6" t="inlineStr">
         <is>
-          <t>出典：令和8年度第3回北海道高齢者保健福祉施策検討協議会（令和8年8月27日）資料4 第10期介護保険事業（支援）計画の策定に係る道作成指針（案）。同指針は案の段階であり、確定した指針により改めて確かめます［要確認］。</t>
+          <t>注1）区域内の特定施設入居者生活介護の事業所の類型（混合型・介護専用型）は［要確認］です。同法第8条第21項により、介護専用型特定施設はその入居者が要介護者、その配偶者その他厚生労働省令で定める者に限られるものであり、類型は入居の要件により定まります。混合型特定施設に該当する事業所がある場合の整備の考え方は第5節によります。
+注2）受給者数には要支援1・要支</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr"/>
@@ -4617,17 +4615,17 @@
       </c>
       <c r="C150" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D150" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D150" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E150" s="6" t="inlineStr">
         <is>
-          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr"/>
@@ -4643,7 +4641,7 @@
       </c>
       <c r="C151" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D151" s="6" t="inlineStr">
@@ -4653,8 +4651,7 @@
       </c>
       <c r="E151" s="6" t="inlineStr">
         <is>
-          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
-注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
+          <t>社会福祉法等の一部を改正する法律（令和8年法律第51号）により、中長期的なサービスの見通しとともに、その見通しを踏まえた介護給付等対象サービスの提供体制の確保及び地域支援事業の実施のための施策に関する事項を定めることとされています。見通しそのものは第1節から第3節に掲げており、本節及び第4節1がこれを踏まえた確保の方策に当たります。令和22年度の水準（第3節</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr"/>
@@ -4670,7 +4667,7 @@
       </c>
       <c r="C152" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
         </is>
       </c>
       <c r="D152" s="6" t="inlineStr">
@@ -4680,7 +4677,7 @@
       </c>
       <c r="E152" s="6" t="inlineStr">
         <is>
-          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
+          <t>回答した18施設の分であり、区域内の施設・住まい31施設のうち13施設は回答していません（施設数ベースの把握率58.1％）。入所・退去の経路は施設の種別により異なるため、種別ごとの整備量の判断に用いる際は種別別の内訳を確認します［要確認］。なお、通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されてい</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr"/>
@@ -4696,17 +4693,17 @@
       </c>
       <c r="C153" s="6" t="inlineStr">
         <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+          <t>第5節 介護施設整備に係る基本方針</t>
+        </is>
+      </c>
+      <c r="D153" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E153" s="6" t="inlineStr">
         <is>
-          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
+          <t>出典：令和8年度第3回北海道高齢者保健福祉施策検討協議会（令和8年8月27日）資料4 第10期介護保険事業（支援）計画の策定に係る道作成指針（案）。同指針は案の段階であり、確定した指針により改めて確かめます［要確認］。</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr"/>
@@ -4725,14 +4722,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D154" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D154" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E154" s="6" t="inlineStr">
         <is>
-          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
+          <t>所得段階の数、保険料の基準額に対する割合（乗率）、公費による軽減後の割合及び第1号被保険者負担割合は、いずれも政令により定められ、これを踏まえて条例で定めます。第10期の政令改正の内容が示されるまでの間、本計画の算定は、第9期の条例による16段階と公費による軽減前の割合を据え置き、第1号被保険者負担割合23％、調整交付金相当額5％及び予定収納率99.0％によ</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr"/>
@@ -4758,8 +4755,8 @@
       </c>
       <c r="E155" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>注）国の標準は13段階です。当広域連合は第9期の条例において第13段階を多段階化し16段階としており、標準の段階と割合が異なる段階があります。保険料の基準額に対する割合は公費による軽減前の割合によっています（第7節）。
+注）標準の13段階の範囲で割合を比べると、条例の割合が標準を下回る段階が3、上回る段階が6あります。下回るのは第2段階0.639（標準0.6</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr"/>
@@ -4785,8 +4782,7 @@
       </c>
       <c r="E156" s="6" t="inlineStr">
         <is>
-          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
-注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
+          <t>所得段階別の第1号被保険者数は、令和6年度の実績の構成比を固定し、将来の第1号被保険者数（第1節）に乗じて求めています。予定保険料収納率は、所得段階別の収納率の実績を確認できていないため、全段階に一律に99.0％を用いています。段階別の収納率に差がある場合は、低い割合の段階の人数が多いほど必要額の確保に不足が生じる側に働くため、段階別の収納実績を確認して第1</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr"/>
@@ -4805,14 +4801,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D157" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D157" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E157" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>符号は施設・居住系の扱いで反転します。施設・居住系の実績の減少には定員の縮小が含まれており（第4節2）、趨勢をそのまま延長すると「さらに定員が縮小する」ことを前提にしてしまいます。本計画の見込量は補正を行っていません［要協議］。</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr"/>
@@ -4831,14 +4827,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D158" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D158" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E158" s="6" t="inlineStr">
         <is>
-          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
+          <t>特に認知症対応型共同生活介護は、区域全体の定員が平成28年から令和2年の115人から令和4年以降99人に減っており、令和4年度の落ち込みは1事業所の定員縮小によるものです（令和6年度から令和7年度は増に転じています）。介護老人福祉施設も平成29年度の234人から令和2年度以降160人へ縮小しています。この2つのサービスは、実績の減少が定員の縮小によるものであ</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr"/>
@@ -4857,14 +4853,15 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D159" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D159" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E159" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F159" s="6" t="inlineStr"/>
@@ -4890,7 +4887,8 @@
       </c>
       <c r="E160" s="6" t="inlineStr">
         <is>
-          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+          <t>注）上表の基礎は②一律の伸びであり、本計画が採用している①要介護度別とは基礎が異なります。総給付費の予測誤差は、過去の実績による検証で一律1.68％に対し補正1.13％です。
+注）補正を行っても計画値と実績値の開きが残るサービスが6種別あります（居宅療養管理指導、地域密着型通所介護、短期入所生活介護、短期入所療養介護、訪問看護、訪問リハビリテーション）。いず</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr"/>
@@ -4909,14 +4907,14 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D161" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
+      <c r="D161" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
         </is>
       </c>
       <c r="E161" s="6" t="inlineStr">
         <is>
-          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr"/>
@@ -4942,7 +4940,7 @@
       </c>
       <c r="E162" s="6" t="inlineStr">
         <is>
-          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があります。構成3町は特別地域加算の対象地域に掲げられていない一方、後の</t>
+          <t>地域支援事業費（B）からは、保険者機能強化推進事業費及び保険者努力支援事業費を除いています。いずれも交付金を財源とする事業であり、第1号被保険者負担分の算定基礎には含まれないためです。国の様式には保険料収納必要額から交付金の交付見込額を控除する欄がありますが、本計画はBから当該2事業を除く方法によっているため、収納必要額からの控除は行っていません。両方を行う</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr"/>
@@ -4961,149 +4959,148 @@
           <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
-      <c r="D163" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+      <c r="D163" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E163" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F163" s="6" t="inlineStr"/>
+      <c r="G163" s="6" t="inlineStr"/>
+      <c r="H163" s="6" t="inlineStr"/>
+    </row>
+    <row r="164" ht="44" customHeight="1">
+      <c r="A164" s="6" t="inlineStr"/>
+      <c r="B164" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C164" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D164" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E164" s="6" t="inlineStr">
+        <is>
+          <t>効きの大きいものは、財政調整基金の取崩しと第1号被保険者負担割合です。いずれも第10期の算定に当たって決定を要する事項であり、負担割合は国の政令、取崩額は広域連合の方針によります［要協議］。本計画の算定は、基金を取り崩さないものとしています（不足する側に誤らない置き方です）。取り崩す場合は、1億円当たり月額▲308円に相当します。介護報酬改定率は1％当たり月</t>
+        </is>
+      </c>
+      <c r="F164" s="6" t="inlineStr"/>
+      <c r="G164" s="6" t="inlineStr"/>
+      <c r="H164" s="6" t="inlineStr"/>
+    </row>
+    <row r="165" ht="44" customHeight="1">
+      <c r="A165" s="6" t="inlineStr"/>
+      <c r="B165" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C165" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D165" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E165" s="6" t="inlineStr">
+        <is>
+          <t>認定率の置き方は、第1節のとおり3つを算定しており、本計画は②トレンド継続によっています。①現状固定とした場合は月額＋85円、③令和元年水準とした場合は月額＋234円であり、保険料基準額は①6,500円・②6,400円・③6,700円に分かれます。②は3つのうち最も低く出る置き方です［要協議］。</t>
+        </is>
+      </c>
+      <c r="F165" s="6" t="inlineStr"/>
+      <c r="G165" s="6" t="inlineStr"/>
+      <c r="H165" s="6" t="inlineStr"/>
+    </row>
+    <row r="166" ht="44" customHeight="1">
+      <c r="A166" s="6" t="inlineStr"/>
+      <c r="B166" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C166" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D166" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
+        </is>
+      </c>
+      <c r="E166" s="6" t="inlineStr">
+        <is>
+          <t>当区域の単価は、構成を固定した指数でみると過去7年間で年率1.32％から1.75％の幅で伸びており、改定のあった年となかった年で差が見られません。本計画は単価を令和7年度で固定しているため、この趨勢を織り込んでいません［要協議］。改定率を乗じることと趨勢を延ばすことを重ねると二重になるため、いずれか一方によります。</t>
+        </is>
+      </c>
+      <c r="F166" s="6" t="inlineStr"/>
+      <c r="G166" s="6" t="inlineStr"/>
+      <c r="H166" s="6" t="inlineStr"/>
+    </row>
+    <row r="167" ht="44" customHeight="1">
+      <c r="A167" s="6" t="inlineStr"/>
+      <c r="B167" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C167" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D167" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E167" s="6" t="inlineStr">
+        <is>
+          <t>なお、令和9年度介護報酬改定に向けた基本的な視点には、中山間地域の加算のあり方の見直しが掲げられています（第1章第9節6）。交通の便が悪い地域における経営の安定等を目的とする加算には特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類があります。構成3町は特別地域加算の対象地域に掲げられていない一方、後の</t>
+        </is>
+      </c>
+      <c r="F167" s="6" t="inlineStr"/>
+      <c r="G167" s="6" t="inlineStr"/>
+      <c r="H167" s="6" t="inlineStr"/>
+    </row>
+    <row r="168" ht="44" customHeight="1">
+      <c r="A168" s="6" t="inlineStr"/>
+      <c r="B168" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C168" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D168" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E168" s="6" t="inlineStr">
         <is>
           <t>注1）各欄は、基本ケースから当該の前提のみを動かした場合の値です。複数を同時に動かした場合の値ではありません。
 注2）介護報酬改定率と単価の実績の趨勢は、いずれも単価を動かすものであり重ねて適用しません。
 注3）「調整交付金の一定の取組による減額」は、調整交付金見込額が5％減少した場合の値です。実際の減額は年齢区分の精緻化による増加額の5％であり、増加額が示</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr"/>
-      <c r="G163" s="6" t="inlineStr"/>
-      <c r="H163" s="6" t="inlineStr"/>
-    </row>
-    <row r="164" ht="44" customHeight="1">
-      <c r="A164" s="6" t="inlineStr"/>
-      <c r="B164" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C164" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D164" s="11" t="inlineStr">
-        <is>
-          <t>要協議</t>
-        </is>
-      </c>
-      <c r="E164" s="6" t="inlineStr">
-        <is>
-          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
-        </is>
-      </c>
-      <c r="F164" s="6" t="inlineStr"/>
-      <c r="G164" s="6" t="inlineStr"/>
-      <c r="H164" s="6" t="inlineStr"/>
-    </row>
-    <row r="165" ht="44" customHeight="1">
-      <c r="A165" s="6" t="inlineStr"/>
-      <c r="B165" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C165" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D165" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E165" s="6" t="inlineStr">
-        <is>
-          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
-        </is>
-      </c>
-      <c r="F165" s="6" t="inlineStr"/>
-      <c r="G165" s="6" t="inlineStr"/>
-      <c r="H165" s="6" t="inlineStr"/>
-    </row>
-    <row r="166" ht="44" customHeight="1">
-      <c r="A166" s="6" t="inlineStr"/>
-      <c r="B166" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C166" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D166" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E166" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
-      <c r="F166" s="6" t="inlineStr"/>
-      <c r="G166" s="6" t="inlineStr"/>
-      <c r="H166" s="6" t="inlineStr"/>
-    </row>
-    <row r="167" ht="44" customHeight="1">
-      <c r="A167" s="6" t="inlineStr"/>
-      <c r="B167" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C167" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D167" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E167" s="6" t="inlineStr">
-        <is>
-          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
-        </is>
-      </c>
-      <c r="F167" s="6" t="inlineStr"/>
-      <c r="G167" s="6" t="inlineStr"/>
-      <c r="H167" s="6" t="inlineStr"/>
-    </row>
-    <row r="168" ht="44" customHeight="1">
-      <c r="A168" s="6" t="inlineStr"/>
-      <c r="B168" s="6" t="inlineStr">
-        <is>
-          <t>第6章　介護保険事業等の見込み</t>
-        </is>
-      </c>
-      <c r="C168" s="6" t="inlineStr">
-        <is>
-          <t>第6節 第1号被保険者の介護保険料試算</t>
-        </is>
-      </c>
-      <c r="D168" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
-        </is>
-      </c>
-      <c r="E168" s="6" t="inlineStr">
-        <is>
-          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
-注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
-        </is>
-      </c>
       <c r="F168" s="6" t="inlineStr"/>
       <c r="G168" s="6" t="inlineStr"/>
       <c r="H168" s="6" t="inlineStr"/>
@@ -5117,17 +5114,17 @@
       </c>
       <c r="C169" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
-        </is>
-      </c>
-      <c r="D169" s="6" t="inlineStr">
-        <is>
-          <t>要確認</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D169" s="11" t="inlineStr">
+        <is>
+          <t>要協議</t>
         </is>
       </c>
       <c r="E169" s="6" t="inlineStr">
         <is>
-          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+          <t>本計画の暫定算定は、単価を令和7年度で固定し、施策による効果を見込まず、給付の適正化による抑制を織り込まず、財政調整基金を取り崩さない置き方によっています。いずれも保険料が不足する側に誤らないための置き方であり、上表の前提を動かすと月額は上がる側に動くものが多くなります。このため、算定上の月額基準額は、現在置いている前提の下では低い側の水準にあります。条例で</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr"/>
@@ -5143,7 +5140,7 @@
       </c>
       <c r="C170" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D170" s="6" t="inlineStr">
@@ -5153,7 +5150,7 @@
       </c>
       <c r="E170" s="6" t="inlineStr">
         <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+          <t>利用者負担の一定以上所得の判断基準は、第10期計画期間の開始前までに結論を得ることとされており、見直しの内容及び施行の時期は定まっていません（第1章第9節4）。基準が示された時点で、対象となる方の数を確認し、第3節の給付費に加えて本節の保険料収納必要額まで再算定します。負担を理由とする利用の控えは、給付費を一時的に下げる一方で重度化を通じて将来の給付費を上げ</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr"/>
@@ -5169,7 +5166,7 @@
       </c>
       <c r="C171" s="6" t="inlineStr">
         <is>
-          <t>第7節 低所得者支援</t>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
         </is>
       </c>
       <c r="D171" s="6" t="inlineStr">
@@ -5179,188 +5176,319 @@
       </c>
       <c r="E171" s="6" t="inlineStr">
         <is>
-          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr"/>
       <c r="G171" s="6" t="inlineStr"/>
       <c r="H171" s="6" t="inlineStr"/>
     </row>
-    <row r="173" ht="28" customHeight="1">
-      <c r="A173" s="7" t="inlineStr">
+    <row r="172" ht="44" customHeight="1">
+      <c r="A172" s="6" t="inlineStr"/>
+      <c r="B172" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C172" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D172" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E172" s="6" t="inlineStr">
+        <is>
+          <t>注）算定上の月額基準額は、基金取崩0円、予定収納率99.0％、令和7年度の単価による暫定の値です。条例で採用する基準額ではありません。年度別の月額は、当該年度の額を3年間続けた場合の水準を示すものであり、保険料は3か年を通じて同一の額とします。①はA＋B、②はA＋介護予防・日常生活支援総合事業費であり、②に包括的支援事業費及び任意事業費は含みません。この扱い</t>
+        </is>
+      </c>
+      <c r="F172" s="6" t="inlineStr"/>
+      <c r="G172" s="6" t="inlineStr"/>
+      <c r="H172" s="6" t="inlineStr"/>
+    </row>
+    <row r="173" ht="44" customHeight="1">
+      <c r="A173" s="6" t="inlineStr"/>
+      <c r="B173" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C173" s="6" t="inlineStr">
+        <is>
+          <t>第6節 第1号被保険者の介護保険料試算</t>
+        </is>
+      </c>
+      <c r="D173" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E173" s="6" t="inlineStr">
+        <is>
+          <t>注1）いずれの案も公費による軽減前の割合によっています。保険料収納必要額、予定収納率99.0％及び段階別の第1号被保険者数は3案で同じものを用い、割合のみを置き換えています。補正後被保険者数及び月額は、第4項の値に段階別の人数に割合を乗じた和の比を乗じて求めたものです。
+注2）「割合が変わる被保険者数」は、現行の条例の割合と異なる割合となる段階に属する方の数</t>
+        </is>
+      </c>
+      <c r="F173" s="6" t="inlineStr"/>
+      <c r="G173" s="6" t="inlineStr"/>
+      <c r="H173" s="6" t="inlineStr"/>
+    </row>
+    <row r="174" ht="44" customHeight="1">
+      <c r="A174" s="6" t="inlineStr"/>
+      <c r="B174" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C174" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D174" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E174" s="6" t="inlineStr">
+        <is>
+          <t>補足給付の所得区分の細分化は、令和9年度から行われます。対象となる方に必要な負担軽減が確実に届くよう、認定証の更新の時期に合わせた個別の案内を行うとともに、未申請の把握と申請の勧奨を構成3町と連携して行います。負担限度額、対象者数及び影響額は［要確認］として残し、省令・告示等が示された時点で補います。</t>
+        </is>
+      </c>
+      <c r="F174" s="6" t="inlineStr"/>
+      <c r="G174" s="6" t="inlineStr"/>
+      <c r="H174" s="6" t="inlineStr"/>
+    </row>
+    <row r="175" ht="44" customHeight="1">
+      <c r="A175" s="6" t="inlineStr"/>
+      <c r="B175" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C175" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D175" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E175" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F175" s="6" t="inlineStr"/>
+      <c r="G175" s="6" t="inlineStr"/>
+      <c r="H175" s="6" t="inlineStr"/>
+    </row>
+    <row r="176" ht="44" customHeight="1">
+      <c r="A176" s="6" t="inlineStr"/>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>第6章　介護保険事業等の見込み</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>第7節 低所得者支援</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="E176" s="6" t="inlineStr">
+        <is>
+          <t>一定以上所得基準の見直しについては、第10期計画期間の開始前までに結論を得ることとされているにとどまり、見直しの内容及び施行の時期は示されていません。本計画は現行の基準により給付費及び保険料を算定しており、見直しを織り込んでいません。基準及び施行の時期が示された時点で、対象となる方の数を確認したうえで第3節の給付費及び第6節の保険料収納必要額を再算定します［</t>
+        </is>
+      </c>
+      <c r="F176" s="6" t="inlineStr"/>
+      <c r="G176" s="6" t="inlineStr"/>
+      <c r="H176" s="6" t="inlineStr"/>
+    </row>
+    <row r="178" ht="28" customHeight="1">
+      <c r="A178" s="7" t="inlineStr">
         <is>
           <t>注1）表の中の未確定箇所は33種の表に153箇所あります。多くは施策の目標値の欄と必要利用定員総数の欄です。
 注2）本シートは実物から数えています。素案を更新して本表を作り直せば数は自動で変わります。固定値で書くと実物とずれるため、数える形にしています。</t>
         </is>
       </c>
     </row>
-    <row r="175" ht="20" customHeight="1">
-      <c r="A175" s="3" t="inlineStr">
+    <row r="180" ht="20" customHeight="1">
+      <c r="A180" s="3" t="inlineStr">
         <is>
           <t>4　記述が薄い節（未確定箇所とは別の課題）</t>
         </is>
       </c>
     </row>
-    <row r="176" ht="30" customHeight="1">
-      <c r="A176" s="4" t="inlineStr"/>
-      <c r="B176" s="4" t="inlineStr">
+    <row r="181" ht="30" customHeight="1">
+      <c r="A181" s="4" t="inlineStr"/>
+      <c r="B181" s="4" t="inlineStr">
         <is>
           <t>章</t>
         </is>
       </c>
-      <c r="C176" s="4" t="inlineStr">
+      <c r="C181" s="4" t="inlineStr">
         <is>
           <t>節</t>
         </is>
       </c>
-      <c r="D176" s="4" t="inlineStr">
+      <c r="D181" s="4" t="inlineStr">
         <is>
           <t>段落</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
+      <c r="E181" s="4" t="inlineStr">
         <is>
           <t>うち注・出典</t>
         </is>
       </c>
-      <c r="F176" s="4" t="inlineStr">
+      <c r="F181" s="4" t="inlineStr">
         <is>
           <t>表</t>
         </is>
       </c>
-      <c r="G176" s="4" t="inlineStr">
+      <c r="G181" s="4" t="inlineStr">
         <is>
           <t>未確定</t>
         </is>
       </c>
-      <c r="H176" s="4" t="inlineStr">
+      <c r="H181" s="4" t="inlineStr">
         <is>
           <t>本来入るべき内容と所在</t>
         </is>
       </c>
     </row>
-    <row r="177" ht="44" customHeight="1">
-      <c r="A177" s="6" t="inlineStr"/>
-      <c r="B177" s="6" t="inlineStr">
+    <row r="182" ht="44" customHeight="1">
+      <c r="A182" s="6" t="inlineStr"/>
+      <c r="B182" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C177" s="6" t="inlineStr">
+      <c r="C182" s="6" t="inlineStr">
         <is>
           <t>第1節　計画策定の趣旨</t>
         </is>
       </c>
-      <c r="D177" s="5" t="n">
+      <c r="D182" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="E177" s="5" t="n">
+      <c r="E182" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F177" s="5" t="n">
+      <c r="F182" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G177" s="5" t="n">
+      <c r="G182" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H177" s="6" t="inlineStr">
+      <c r="H182" s="6" t="inlineStr">
         <is>
           <t>趣旨の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="44" customHeight="1">
-      <c r="A178" s="6" t="inlineStr"/>
-      <c r="B178" s="6" t="inlineStr">
+    <row r="183" ht="44" customHeight="1">
+      <c r="A183" s="6" t="inlineStr"/>
+      <c r="B183" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C178" s="6" t="inlineStr">
+      <c r="C183" s="6" t="inlineStr">
         <is>
           <t>第4節　計画期間</t>
         </is>
       </c>
-      <c r="D178" s="5" t="n">
+      <c r="D183" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E178" s="5" t="n">
+      <c r="E183" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F178" s="5" t="n">
+      <c r="F183" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G178" s="5" t="n">
+      <c r="G183" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H178" s="6" t="inlineStr">
+      <c r="H183" s="6" t="inlineStr">
         <is>
           <t>計画期間の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="44" customHeight="1">
-      <c r="A179" s="6" t="inlineStr"/>
-      <c r="B179" s="6" t="inlineStr">
+    <row r="184" ht="44" customHeight="1">
+      <c r="A184" s="6" t="inlineStr"/>
+      <c r="B184" s="6" t="inlineStr">
         <is>
           <t>第1章　計画策定の意義</t>
         </is>
       </c>
-      <c r="C179" s="6" t="inlineStr">
+      <c r="C184" s="6" t="inlineStr">
         <is>
           <t>第5節　計画の策定体制</t>
         </is>
       </c>
-      <c r="D179" s="5" t="n">
+      <c r="D184" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E179" s="5" t="n">
+      <c r="E184" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F179" s="5" t="n">
+      <c r="F184" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G179" s="5" t="n">
+      <c r="G184" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="H179" s="6" t="inlineStr">
+      <c r="H184" s="6" t="inlineStr">
         <is>
           <t>策定体制の記述であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="44" customHeight="1">
-      <c r="A180" s="6" t="inlineStr"/>
-      <c r="B180" s="6" t="inlineStr">
+    <row r="185" ht="44" customHeight="1">
+      <c r="A185" s="6" t="inlineStr"/>
+      <c r="B185" s="6" t="inlineStr">
         <is>
           <t>第4章　計画の基本理念及び基本目標</t>
         </is>
       </c>
-      <c r="C180" s="6" t="inlineStr">
+      <c r="C185" s="6" t="inlineStr">
         <is>
           <t>第1節 計画の基本理念</t>
         </is>
       </c>
-      <c r="D180" s="5" t="n">
+      <c r="D185" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="E180" s="5" t="n">
+      <c r="E185" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F180" s="5" t="n">
+      <c r="F185" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="G180" s="5" t="n">
+      <c r="G185" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="H180" s="6" t="inlineStr">
+      <c r="H185" s="6" t="inlineStr">
         <is>
           <t>基本理念であり、短いことは妥当</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="42" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
+    <row r="187" ht="42" customHeight="1">
+      <c r="A187" s="7" t="inlineStr">
         <is>
           <t>注3）未確定箇所（［要協議］等）は「書く内容は決まっているが値が決まらない」箇所です。本節は「書くべき内容がまだ入っていない」節を示すもので、性質が異なります。記号が置かれていないため未確定箇所の集計には現れません。
 注4）記述が薄い節は4節あり、うち短いことが妥当なもの（計画期間・基本理念など）を除くと0節です。
@@ -5372,12 +5500,12 @@
   <mergeCells count="8">
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A180:H180"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A182:H182"/>
-    <mergeCell ref="A175:H175"/>
+    <mergeCell ref="A178:H178"/>
+    <mergeCell ref="A187:H187"/>
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A173:H173"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5404,7 +5532,7 @@
     <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>確認事項の棚卸し（192件）</t>
+          <t>確認事項の棚卸し（193件）</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5579,7 @@
         </is>
       </c>
       <c r="C6" s="12" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D6" s="6" t="inlineStr"/>
       <c r="E6" s="6" t="inlineStr"/>
@@ -5481,7 +5609,7 @@
         </is>
       </c>
       <c r="C8" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="6" t="inlineStr"/>
@@ -5526,7 +5654,7 @@
         </is>
       </c>
       <c r="C11" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="6" t="inlineStr"/>
@@ -5638,10 +5766,10 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" s="5" t="n">
         <v>11</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>10</v>
       </c>
       <c r="E18" s="5" t="n">
         <v>0</v>
@@ -5807,7 +5935,7 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D28" s="6" t="inlineStr"/>
       <c r="E28" s="6" t="inlineStr"/>
@@ -5982,7 +6110,7 @@
     <row r="41" ht="42" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>注1）期限が令和8年8月以前のもの（98件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
+          <t>注1）期限が令和8年8月以前のもの（99件）は期限を過ぎています。いずれも当方から催促する性質のものではなく、決定又は資料のご提供をお待ちしている状態です。
 注2）確認先が「発注者・3町」のもの（28件）は、3町への照会の様式と時期の決定を先に要します。
 注3）本シートは件数の把握のためのものです。個々の内容は業務工程管理表 03_確認事項一覧をご覧ください。</t>
         </is>
@@ -6503,7 +6631,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>第2章第3節・第5節・第6節（未確定15箇所）</t>
+          <t>第2章第3節・第5節・第6節（未確定16箇所）</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
@@ -6966,7 +7094,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議162・要確認118・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
+          <t>［要協議］［要確認］［要内訳］の使い分けを揃える。現在は要協議166・要確認119・要内訳2で、同じ性質のものに異なる記号を用いている箇所がある</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -7078,7 +7206,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>1074段落158表36図／282箇所</t>
+          <t>1090段落161表36図／287箇所</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -7104,7 +7232,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>282＝282</t>
+          <t>287＝287</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -7130,7 +7258,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>282＝282</t>
+          <t>287＝287</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -7156,7 +7284,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>192件（未回答181件）</t>
+          <t>193件（未回答182件）</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -7182,7 +7310,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>192件／一意192件</t>
+          <t>193件／一意193件</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -7312,7 +7440,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>第4節 介護保険サービス等における施設の見込み／63／282箇所（22％）</t>
+          <t>第4節 介護保険サービス等における施設の見込み／63／287箇所（22％）</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -7551,7 +7679,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>計画素案の未確定箇所は282箇所ある（要協議162・要確認118・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
+          <t>計画素案の未確定箇所は287箇所ある（要協議166・要確認119・要内訳2）。①［要協議］は決定を要するもの、［要確認］は事実の確認を要するもの、［要内訳］は内訳の提供を要するものという使い分けでよいか。②現在は同じ性質のものに異なる記号を用いている箇所がある。使い分けを揃える作業は受託者の作業だけで進む。③策定委員会にお諮りする版では、未確定箇所をそのまま残すか、一覧表に移して本文からは外すかをご判断いただきたい。</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -7574,7 +7702,7 @@
       <c r="A8" s="7" t="inlineStr">
         <is>
           <t>注1）本表により新たに起票した確認事項は2件（No.142・No.143）です。
-注2）本表は確認事項を新たに増やすことよりも、既にお願いしている181件の優先順位を示すことを目的としています。</t>
+注2）本表は確認事項を新たに増やすことよりも、既にお願いしている182件の優先順位を示すことを目的としています。</t>
         </is>
       </c>
     </row>
